--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G34">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G37">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G44">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G101">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G106">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P114">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G129">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G136">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G183">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G240">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G241">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G284">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G285">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G291">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G293">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G294">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G32">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G94">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G129">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G136">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G157">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G159">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G190">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G195">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G201">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,14 +44808,14 @@
         </is>
       </c>
       <c r="N273">
+        <v>2.25</v>
+      </c>
+      <c r="O273">
+        <v>3.25</v>
+      </c>
+      <c r="P273">
         <v>3.1</v>
       </c>
-      <c r="O273">
-        <v>3.4</v>
-      </c>
-      <c r="P273">
-        <v>2.2</v>
-      </c>
       <c r="Q273">
         <v>0</v>
       </c>
@@ -44847,10 +44847,10 @@
         <v>0</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC273">
         <v>0</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="O274">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P274">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB274">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G284">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G285">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G287">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G290">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G20">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G29">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G36">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G101">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G105">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="O116">
-        <v>4.45</v>
+        <v>3.98</v>
       </c>
       <c r="P116">
-        <v>5.18</v>
+        <v>4.67</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Khor fakkan</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G139">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Khor fakkan</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G140">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N140">
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G184">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G185">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G186">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G188">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G203">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G207">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G289">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G51">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12416,10 +12416,10 @@
         <v>0</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12579,10 +12579,10 @@
         <v>0</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12742,10 +12742,10 @@
         <v>0</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G96">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G101">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O174">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P174">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G183">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G195">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G198">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G202">
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G206">
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O220">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P220">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G287">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G288">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G289">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G290">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G291">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G32">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G111">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G195">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G202">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P10">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="O11">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O276">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P276">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q276">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34578,10 +34578,10 @@
         <v>0</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC210">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -41055,7 +41055,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N250">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O254">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P254">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O256">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P256">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O258">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P258">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42402,10 +42402,10 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB258">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC258">
         <v>0</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O277">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P277">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q277">
         <v>0</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q300">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU303"/>
+  <dimension ref="A1:AU307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,22 +14774,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G89">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="O91">
-        <v>3.48</v>
+        <v>3.65</v>
       </c>
       <c r="P91">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="O94">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P94">
-        <v>1.98</v>
+        <v>2.64</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G97">
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-18 09:15:00</t>
+          <t>2026-10-18 09:00:00</t>
         </is>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="G99">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G100">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-18 09:30:00</t>
+          <t>2026-10-18 09:15:00</t>
         </is>
       </c>
     </row>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17056,22 +17056,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>3.14</v>
+        <v>1.79</v>
       </c>
       <c r="O103">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>2.14</v>
+        <v>3.71</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17219,22 +17219,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17795,10 +17795,10 @@
         <v>0</v>
       </c>
       <c r="AC107">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="O108">
-        <v>3.62</v>
+        <v>5.95</v>
       </c>
       <c r="P108">
-        <v>2.73</v>
+        <v>9.75</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE108">
         <v>0</v>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>7.65</v>
+        <v>2.34</v>
       </c>
       <c r="O109">
-        <v>5.45</v>
+        <v>3.62</v>
       </c>
       <c r="P109">
-        <v>1.37</v>
+        <v>2.73</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18121,10 +18121,10 @@
         <v>0</v>
       </c>
       <c r="AC109">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD109">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE109">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18284,10 +18284,10 @@
         <v>0</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G111">
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-18 09:45:00</t>
+          <t>2026-10-18 09:30:00</t>
         </is>
       </c>
     </row>
@@ -18681,12 +18681,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="O113">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P113">
-        <v>3.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18767,10 +18767,10 @@
         <v>0</v>
       </c>
       <c r="AA113">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB113">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 09:45:00</t>
         </is>
       </c>
     </row>
@@ -18849,7 +18849,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="O114">
-        <v>4.45</v>
+        <v>3.36</v>
       </c>
       <c r="P114">
-        <v>5.18</v>
+        <v>3.33</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O115">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="P115">
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spaeri</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G120">
@@ -19865,17 +19865,17 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G121">
@@ -20028,17 +20028,17 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N121">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G124">
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="N124">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O124">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P124">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q124">
         <v>0</v>
@@ -20642,22 +20642,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>2.41</v>
+        <v>3.62</v>
       </c>
       <c r="O125">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="P125">
-        <v>3.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20805,22 +20805,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G136">
@@ -22598,22 +22598,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G137">
@@ -22636,68 +22636,68 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N137">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O137">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P137">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q137">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R137">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S137">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T137">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U137">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V137">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W137">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X137">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y137">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z137">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA137">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB137">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC137">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD137">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE137">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF137">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG137">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK137">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22761,22 +22761,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G138">
@@ -22799,68 +22799,68 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N138">
-        <v>3.46</v>
+        <v>1.33</v>
       </c>
       <c r="O138">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="P138">
-        <v>2.14</v>
+        <v>8</v>
       </c>
       <c r="Q138">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R138">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S138">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T138">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U138">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V138">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W138">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X138">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y138">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z138">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA138">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD138">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE138">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF138">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG138">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK138">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22919,12 +22919,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23070,7 +23070,7 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>2026-10-18 10:05:00</t>
+          <t>2026-10-18 10:00:00</t>
         </is>
       </c>
     </row>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Khor fakkan</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G140">
@@ -23125,7 +23125,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N140">
@@ -23245,12 +23245,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Khor fakkan</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G141">
@@ -23288,17 +23288,17 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N141">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O141">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="P141">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q141">
         <v>0</v>
@@ -23396,7 +23396,7 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>2026-10-18 10:15:00</t>
+          <t>2026-10-18 10:05:00</t>
         </is>
       </c>
     </row>
@@ -23413,7 +23413,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O142">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P142">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q142">
         <v>0</v>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-10-18 10:30:00</t>
+          <t>2026-10-18 10:15:00</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G144">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G145">
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G146">
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G148">
@@ -24433,13 +24433,13 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O148">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="P148">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Q148">
         <v>0</v>
@@ -24478,10 +24478,10 @@
         <v>0</v>
       </c>
       <c r="AC148">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD148">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE148">
         <v>0</v>
@@ -24549,12 +24549,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G149">
@@ -24596,13 +24596,13 @@
         </is>
       </c>
       <c r="N149">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O149">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="P149">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q149">
         <v>0</v>
@@ -24641,10 +24641,10 @@
         <v>0</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE149">
         <v>0</v>
@@ -24700,7 +24700,7 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>2026-10-18 11:00:00</t>
+          <t>2026-10-18 10:30:00</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G151">
@@ -25043,22 +25043,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G152">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -25287,10 +25287,10 @@
         <v>0</v>
       </c>
       <c r="AA153">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB153">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="N155">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="O155">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P155">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q155">
         <v>0</v>
@@ -25613,10 +25613,10 @@
         <v>0</v>
       </c>
       <c r="AA155">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB155">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC155">
         <v>0</v>
@@ -25695,22 +25695,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O156">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P156">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25858,22 +25858,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G157">
@@ -26021,22 +26021,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G160">
@@ -26510,22 +26510,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G161">
@@ -26673,22 +26673,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G162">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O163">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P163">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -26999,22 +26999,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G164">
@@ -27037,68 +27037,68 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N164">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O164">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P164">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="Q164">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="R164">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S164">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T164">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U164">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V164">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W164">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X164">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y164">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z164">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA164">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB164">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AC164">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD164">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE164">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF164">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG164">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH164" t="inlineStr">
         <is>
@@ -27111,10 +27111,10 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK164">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL164">
         <v>0</v>
@@ -27157,12 +27157,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O165">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P165">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27308,7 +27308,7 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>2026-10-18 11:05:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -27320,27 +27320,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G166">
@@ -27363,68 +27363,68 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N166">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="O166">
-        <v>3.63</v>
+        <v>3.92</v>
       </c>
       <c r="P166">
-        <v>4.46</v>
+        <v>8.1</v>
       </c>
       <c r="Q166">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="R166">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S166">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T166">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U166">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V166">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W166">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X166">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y166">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z166">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA166">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB166">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC166">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD166">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE166">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF166">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG166">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
@@ -27437,10 +27437,10 @@
         </is>
       </c>
       <c r="AJ166">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK166">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL166">
         <v>0</v>
@@ -27471,7 +27471,7 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>2026-10-18 11:15:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -27483,12 +27483,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G167">
@@ -27634,7 +27634,7 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>2026-10-18 11:15:00</t>
+          <t>2026-10-18 11:05:00</t>
         </is>
       </c>
     </row>
@@ -27646,12 +27646,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27797,7 +27797,7 @@
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>2026-10-18 11:30:00</t>
+          <t>2026-10-18 11:15:00</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27809,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G169">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>2026-10-18 11:30:00</t>
+          <t>2026-10-18 11:15:00</t>
         </is>
       </c>
     </row>
@@ -27977,7 +27977,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G170">
@@ -28140,7 +28140,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O171">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="P171">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28303,22 +28303,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="O172">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="P172">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28466,22 +28466,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>2.27</v>
+        <v>1.26</v>
       </c>
       <c r="O173">
-        <v>3.7</v>
+        <v>5.35</v>
       </c>
       <c r="P173">
-        <v>2.76</v>
+        <v>11.1</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>4.32</v>
+        <v>11.8</v>
       </c>
       <c r="O174">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="P174">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28792,22 +28792,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28950,27 +28950,27 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29101,7 +29101,7 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>2026-10-18 11:45:00</t>
+          <t>2026-10-18 11:30:00</t>
         </is>
       </c>
     </row>
@@ -29113,12 +29113,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="O177">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P177">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29205,10 +29205,10 @@
         <v>0</v>
       </c>
       <c r="AC177">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD177">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE177">
         <v>0</v>
@@ -29264,7 +29264,7 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>2026-10-18 11:45:00</t>
+          <t>2026-10-18 11:30:00</t>
         </is>
       </c>
     </row>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G178">
@@ -29439,12 +29439,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29531,10 +29531,10 @@
         <v>0</v>
       </c>
       <c r="AC179">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD179">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE179">
         <v>0</v>
@@ -29590,7 +29590,7 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 11:45:00</t>
         </is>
       </c>
     </row>
@@ -29602,27 +29602,27 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G180">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>2026-10-18 12:00:00</t>
+          <t>2026-10-18 11:45:00</t>
         </is>
       </c>
     </row>
@@ -29770,7 +29770,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G181">
@@ -29933,22 +29933,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G182">
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,22 +30259,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30422,22 +30422,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.4</v>
+        <v>2.47</v>
       </c>
       <c r="O186">
-        <v>5.4</v>
+        <v>3.71</v>
       </c>
       <c r="P186">
-        <v>6.86</v>
+        <v>2.68</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30748,22 +30748,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30911,22 +30911,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G189">
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G190">
@@ -31400,7 +31400,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O191">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P191">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G192">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G195">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G196">
@@ -32378,7 +32378,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G197">
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G198">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G199">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G203">
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G208">
@@ -34334,22 +34334,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G209">
@@ -34492,27 +34492,27 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O210">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P210">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34578,10 +34578,10 @@
         <v>0</v>
       </c>
       <c r="AA210">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB210">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC210">
         <v>0</v>
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>2026-10-18 12:15:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -34655,12 +34655,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O211">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P211">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34741,10 +34741,10 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB211">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC211">
         <v>0</v>
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>2026-10-18 12:15:00</t>
+          <t>2026-10-18 12:00:00</t>
         </is>
       </c>
     </row>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="O212">
-        <v>3.9</v>
+        <v>3.13</v>
       </c>
       <c r="P212">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34904,10 +34904,10 @@
         <v>0</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>4.01</v>
+        <v>2.45</v>
       </c>
       <c r="O213">
-        <v>3.91</v>
+        <v>3.55</v>
       </c>
       <c r="P213">
-        <v>1.96</v>
+        <v>3.08</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35067,10 +35067,10 @@
         <v>0</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC213">
         <v>0</v>
@@ -35149,7 +35149,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="O214">
-        <v>3.24</v>
+        <v>3.9</v>
       </c>
       <c r="P214">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35307,27 +35307,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>2026-10-18 12:30:00</t>
+          <t>2026-10-18 12:15:00</t>
         </is>
       </c>
     </row>
@@ -35470,27 +35470,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35621,7 +35621,7 @@
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>2026-10-18 12:30:00</t>
+          <t>2026-10-18 12:15:00</t>
         </is>
       </c>
     </row>
@@ -35638,22 +35638,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G217">
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="O218">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="P218">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35882,10 +35882,10 @@
         <v>0</v>
       </c>
       <c r="AA218">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB218">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC218">
         <v>0</v>
@@ -35964,7 +35964,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G219">
@@ -36127,7 +36127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G220">
@@ -36169,13 +36169,13 @@
         </is>
       </c>
       <c r="N220">
-        <v>1.5</v>
+        <v>5.69</v>
       </c>
       <c r="O220">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="P220">
-        <v>5.5</v>
+        <v>1.65</v>
       </c>
       <c r="Q220">
         <v>0</v>
@@ -36208,10 +36208,10 @@
         <v>0</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC220">
         <v>0</v>
@@ -36290,7 +36290,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G221">
@@ -36453,7 +36453,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G222">
@@ -36495,13 +36495,13 @@
         </is>
       </c>
       <c r="N222">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O222">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P222">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q222">
         <v>0</v>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -36626,12 +36626,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G223">
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O223">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="P223">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="Q223">
         <v>0</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G226">
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O227">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="P227">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37355,10 +37355,10 @@
         <v>0</v>
       </c>
       <c r="AC227">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD227">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE227">
         <v>0</v>
@@ -37426,12 +37426,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G228">
@@ -37577,7 +37577,7 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>2026-10-18 12:45:00</t>
+          <t>2026-10-18 12:30:00</t>
         </is>
       </c>
     </row>
@@ -37589,12 +37589,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37681,10 +37681,10 @@
         <v>0</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE229">
         <v>0</v>
@@ -37740,7 +37740,7 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>2026-10-18 12:45:00</t>
+          <t>2026-10-18 12:30:00</t>
         </is>
       </c>
     </row>
@@ -37752,12 +37752,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="G230">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O231">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P231">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-10-18 13:00:00</t>
+          <t>2026-10-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="G232">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>5.68</v>
+        <v>2.36</v>
       </c>
       <c r="O233">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="P233">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38409,22 +38409,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38735,22 +38735,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G238">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G239">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G240">
@@ -39550,7 +39550,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,7 +39713,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G242">
@@ -39755,13 +39755,13 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O242">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P242">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q242">
         <v>0</v>
@@ -39794,10 +39794,10 @@
         <v>0</v>
       </c>
       <c r="AA242">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB242">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC242">
         <v>0</v>
@@ -39871,12 +39871,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G243">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>2026-10-18 13:15:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -40034,27 +40034,27 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G244">
@@ -40185,7 +40185,7 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>2026-10-18 13:15:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -40197,12 +40197,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="O245">
-        <v>3.53</v>
+        <v>3.95</v>
       </c>
       <c r="P245">
-        <v>3.74</v>
+        <v>4.43</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>2026-10-18 13:30:00</t>
+          <t>2026-10-18 13:00:00</t>
         </is>
       </c>
     </row>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O246">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P246">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40511,7 +40511,7 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>2026-10-18 13:30:00</t>
+          <t>2026-10-18 13:15:00</t>
         </is>
       </c>
     </row>
@@ -40523,12 +40523,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -40538,12 +40538,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O247">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P247">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40674,7 +40674,7 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>2026-10-18 13:30:00</t>
+          <t>2026-10-18 13:15:00</t>
         </is>
       </c>
     </row>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G248">
@@ -40849,12 +40849,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41000,7 +41000,7 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>2026-10-18 13:45:00</t>
+          <t>2026-10-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41012,12 +41012,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O250">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P250">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -41163,7 +41163,7 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>2026-10-18 13:45:00</t>
+          <t>2026-10-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41175,27 +41175,27 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41326,7 +41326,7 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>2026-10-18 13:45:00</t>
+          <t>2026-10-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41338,12 +41338,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G252">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>2026-10-18 13:45:00</t>
+          <t>2026-10-18 13:30:00</t>
         </is>
       </c>
     </row>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O253">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P253">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41664,27 +41664,27 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G254">
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="O254">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P254">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41827,12 +41827,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G255">
@@ -41978,7 +41978,7 @@
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>2026-10-18 14:00:00</t>
+          <t>2026-10-18 13:45:00</t>
         </is>
       </c>
     </row>
@@ -41990,27 +41990,27 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G256">
@@ -42037,13 +42037,13 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O256">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P256">
-        <v>5.99</v>
+        <v>0</v>
       </c>
       <c r="Q256">
         <v>0</v>
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>2026-10-18 14:15:00</t>
+          <t>2026-10-18 13:45:00</t>
         </is>
       </c>
     </row>
@@ -42153,12 +42153,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G257">
@@ -42200,13 +42200,13 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q257">
         <v>0</v>
@@ -42304,7 +42304,7 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>2026-10-18 14:15:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42316,27 +42316,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G258">
@@ -42363,13 +42363,13 @@
         </is>
       </c>
       <c r="N258">
-        <v>1.8</v>
+        <v>2.81</v>
       </c>
       <c r="O258">
-        <v>3.64</v>
+        <v>3.44</v>
       </c>
       <c r="P258">
-        <v>4.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q258">
         <v>0</v>
@@ -42402,10 +42402,10 @@
         <v>0</v>
       </c>
       <c r="AA258">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB258">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC258">
         <v>0</v>
@@ -42467,7 +42467,7 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>2026-10-18 14:30:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42479,12 +42479,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="G259">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>2026-10-18 14:30:00</t>
+          <t>2026-10-18 14:00:00</t>
         </is>
       </c>
     </row>
@@ -42642,27 +42642,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G260">
@@ -42689,13 +42689,13 @@
         </is>
       </c>
       <c r="N260">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="O260">
-        <v>3.53</v>
+        <v>4.34</v>
       </c>
       <c r="P260">
-        <v>3.54</v>
+        <v>5.99</v>
       </c>
       <c r="Q260">
         <v>0</v>
@@ -42793,7 +42793,7 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>2026-10-18 14:45:00</t>
+          <t>2026-10-18 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42805,27 +42805,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G261">
@@ -42956,7 +42956,7 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 14:15:00</t>
         </is>
       </c>
     </row>
@@ -42968,12 +42968,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43054,10 +43054,10 @@
         <v>0</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC262">
         <v>0</v>
@@ -43119,7 +43119,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43131,27 +43131,27 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G263">
@@ -43282,7 +43282,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 14:30:00</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43294,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>2026-10-18 15:00:00</t>
+          <t>2026-10-18 14:45:00</t>
         </is>
       </c>
     </row>
@@ -43462,22 +43462,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O266">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P266">
-        <v>6.03</v>
+        <v>0</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43788,22 +43788,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O267">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="P267">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43875,10 +43875,10 @@
         <v>0</v>
       </c>
       <c r="AC267">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD267">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE267">
         <v>0</v>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="O268">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="P268">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44038,10 +44038,10 @@
         <v>0</v>
       </c>
       <c r="AC268">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD268">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE268">
         <v>0</v>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G269">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-10-18 15:30:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-10-18 15:30:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="O271">
-        <v>4.31</v>
+        <v>5.32</v>
       </c>
       <c r="P271">
-        <v>5.49</v>
+        <v>7.26</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44527,10 +44527,10 @@
         <v>0</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE271">
         <v>0</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-10-18 15:45:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44598,12 +44598,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,13 +44645,13 @@
         </is>
       </c>
       <c r="N272">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="O272">
-        <v>4.06</v>
+        <v>6.15</v>
       </c>
       <c r="P272">
-        <v>5.25</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44684,16 +44684,16 @@
         <v>0</v>
       </c>
       <c r="AA272">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB272">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC272">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD272">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE272">
         <v>0</v>
@@ -44749,7 +44749,7 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>2026-10-18 15:45:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -44761,27 +44761,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O273">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P273">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44847,10 +44847,10 @@
         <v>0</v>
       </c>
       <c r="AA273">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB273">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC273">
         <v>0</v>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -44924,27 +44924,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45075,7 +45075,7 @@
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 15:30:00</t>
         </is>
       </c>
     </row>
@@ -45087,27 +45087,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45238,7 +45238,7 @@
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -45250,12 +45250,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G276">
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.57</v>
+        <v>1.73</v>
       </c>
       <c r="O276">
-        <v>3.06</v>
+        <v>4.06</v>
       </c>
       <c r="P276">
-        <v>3.06</v>
+        <v>5.25</v>
       </c>
       <c r="Q276">
         <v>0</v>
@@ -45336,10 +45336,10 @@
         <v>0</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC276">
         <v>0</v>
@@ -45401,7 +45401,7 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>2026-10-18 16:00:00</t>
+          <t>2026-10-18 15:45:00</t>
         </is>
       </c>
     </row>
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,10 +45460,10 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O277">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P277">
         <v>3.1</v>
@@ -45499,10 +45499,10 @@
         <v>0</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC277">
         <v>0</v>
@@ -45581,22 +45581,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,22 +45907,22 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O281">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P281">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46228,27 +46228,27 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G282">
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-10-18 16:15:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G283">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46554,12 +46554,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G284">
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46717,12 +46717,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G285">
@@ -46868,7 +46868,7 @@
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 16:00:00</t>
         </is>
       </c>
     </row>
@@ -46880,27 +46880,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G286">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>2026-10-18 17:00:00</t>
+          <t>2026-10-18 16:15:00</t>
         </is>
       </c>
     </row>
@@ -47043,27 +47043,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G287">
@@ -47194,7 +47194,7 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47206,27 +47206,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G288">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47369,27 +47369,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G289">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47532,12 +47532,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="G290">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G291">
@@ -47858,27 +47858,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G292">
@@ -48009,7 +48009,7 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48021,27 +48021,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G293">
@@ -48172,7 +48172,7 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48184,27 +48184,27 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G294">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48347,27 +48347,27 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O295">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P295">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48498,7 +48498,7 @@
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>2026-10-18 18:00:00</t>
+          <t>2026-10-18 17:30:00</t>
         </is>
       </c>
     </row>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G296">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G297">
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-18 18:15:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="O299">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="P299">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-18 18:30:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="O300">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P300">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49254,10 +49254,10 @@
         <v>0</v>
       </c>
       <c r="AC300">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD300">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-10-18 18:30:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
     </row>
@@ -49325,12 +49325,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O301">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P301">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49411,10 +49411,10 @@
         <v>0</v>
       </c>
       <c r="AA301">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB301">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC301">
         <v>0</v>
@@ -49476,7 +49476,7 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>2026-10-18 19:30:00</t>
+          <t>2026-10-18 18:00:00</t>
         </is>
       </c>
     </row>
@@ -49488,12 +49488,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G302">
@@ -49639,7 +49639,7 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>2026-10-18 20:00:00</t>
+          <t>2026-10-18 18:15:00</t>
         </is>
       </c>
     </row>
@@ -49651,156 +49651,808 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>0</v>
+      </c>
+      <c r="J303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>0</v>
+      </c>
+      <c r="L303">
+        <v>0</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N303">
+        <v>2.82</v>
+      </c>
+      <c r="O303">
+        <v>3.65</v>
+      </c>
+      <c r="P303">
+        <v>2.42</v>
+      </c>
+      <c r="Q303">
+        <v>0</v>
+      </c>
+      <c r="R303">
+        <v>0</v>
+      </c>
+      <c r="S303">
+        <v>0</v>
+      </c>
+      <c r="T303">
+        <v>0</v>
+      </c>
+      <c r="U303">
+        <v>0</v>
+      </c>
+      <c r="V303">
+        <v>0</v>
+      </c>
+      <c r="W303">
+        <v>0</v>
+      </c>
+      <c r="X303">
+        <v>0</v>
+      </c>
+      <c r="Y303">
+        <v>0</v>
+      </c>
+      <c r="Z303">
+        <v>0</v>
+      </c>
+      <c r="AA303">
+        <v>0</v>
+      </c>
+      <c r="AB303">
+        <v>0</v>
+      </c>
+      <c r="AC303">
+        <v>0</v>
+      </c>
+      <c r="AD303">
+        <v>0</v>
+      </c>
+      <c r="AE303">
+        <v>0</v>
+      </c>
+      <c r="AF303">
+        <v>0</v>
+      </c>
+      <c r="AG303">
+        <v>0</v>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ303">
+        <v>0</v>
+      </c>
+      <c r="AK303">
+        <v>0</v>
+      </c>
+      <c r="AL303">
+        <v>0</v>
+      </c>
+      <c r="AM303">
+        <v>-1</v>
+      </c>
+      <c r="AN303">
+        <v>-1</v>
+      </c>
+      <c r="AO303">
+        <v>-1</v>
+      </c>
+      <c r="AP303">
+        <v>-1</v>
+      </c>
+      <c r="AQ303">
+        <v>0</v>
+      </c>
+      <c r="AR303">
+        <v>0</v>
+      </c>
+      <c r="AS303">
+        <v>0</v>
+      </c>
+      <c r="AT303">
+        <v>0</v>
+      </c>
+      <c r="AU303" t="inlineStr">
+        <is>
+          <t>2026-10-18 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>CD Universidad Católica</t>
+        </is>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>0</v>
+      </c>
+      <c r="L304">
+        <v>0</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N304">
+        <v>2.2</v>
+      </c>
+      <c r="O304">
+        <v>3.3</v>
+      </c>
+      <c r="P304">
+        <v>2.8</v>
+      </c>
+      <c r="Q304">
+        <v>0</v>
+      </c>
+      <c r="R304">
+        <v>0</v>
+      </c>
+      <c r="S304">
+        <v>0</v>
+      </c>
+      <c r="T304">
+        <v>0</v>
+      </c>
+      <c r="U304">
+        <v>0</v>
+      </c>
+      <c r="V304">
+        <v>0</v>
+      </c>
+      <c r="W304">
+        <v>0</v>
+      </c>
+      <c r="X304">
+        <v>0</v>
+      </c>
+      <c r="Y304">
+        <v>0</v>
+      </c>
+      <c r="Z304">
+        <v>0</v>
+      </c>
+      <c r="AA304">
+        <v>0</v>
+      </c>
+      <c r="AB304">
+        <v>0</v>
+      </c>
+      <c r="AC304">
+        <v>0</v>
+      </c>
+      <c r="AD304">
+        <v>0</v>
+      </c>
+      <c r="AE304">
+        <v>0</v>
+      </c>
+      <c r="AF304">
+        <v>0</v>
+      </c>
+      <c r="AG304">
+        <v>0</v>
+      </c>
+      <c r="AH304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI304" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ304">
+        <v>0</v>
+      </c>
+      <c r="AK304">
+        <v>0</v>
+      </c>
+      <c r="AL304">
+        <v>0</v>
+      </c>
+      <c r="AM304">
+        <v>-1</v>
+      </c>
+      <c r="AN304">
+        <v>-1</v>
+      </c>
+      <c r="AO304">
+        <v>-1</v>
+      </c>
+      <c r="AP304">
+        <v>-1</v>
+      </c>
+      <c r="AQ304">
+        <v>0</v>
+      </c>
+      <c r="AR304">
+        <v>0</v>
+      </c>
+      <c r="AS304">
+        <v>0</v>
+      </c>
+      <c r="AT304">
+        <v>0</v>
+      </c>
+      <c r="AU304" t="inlineStr">
+        <is>
+          <t>2026-10-18 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="G305">
+        <v>0</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>0</v>
+      </c>
+      <c r="L305">
+        <v>0</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N305">
+        <v>2.9</v>
+      </c>
+      <c r="O305">
+        <v>3.4</v>
+      </c>
+      <c r="P305">
+        <v>2.35</v>
+      </c>
+      <c r="Q305">
+        <v>0</v>
+      </c>
+      <c r="R305">
+        <v>0</v>
+      </c>
+      <c r="S305">
+        <v>0</v>
+      </c>
+      <c r="T305">
+        <v>0</v>
+      </c>
+      <c r="U305">
+        <v>0</v>
+      </c>
+      <c r="V305">
+        <v>0</v>
+      </c>
+      <c r="W305">
+        <v>0</v>
+      </c>
+      <c r="X305">
+        <v>0</v>
+      </c>
+      <c r="Y305">
+        <v>0</v>
+      </c>
+      <c r="Z305">
+        <v>0</v>
+      </c>
+      <c r="AA305">
+        <v>1.88</v>
+      </c>
+      <c r="AB305">
+        <v>1.98</v>
+      </c>
+      <c r="AC305">
+        <v>0</v>
+      </c>
+      <c r="AD305">
+        <v>0</v>
+      </c>
+      <c r="AE305">
+        <v>0</v>
+      </c>
+      <c r="AF305">
+        <v>0</v>
+      </c>
+      <c r="AG305">
+        <v>0</v>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ305">
+        <v>0</v>
+      </c>
+      <c r="AK305">
+        <v>0</v>
+      </c>
+      <c r="AL305">
+        <v>0</v>
+      </c>
+      <c r="AM305">
+        <v>-1</v>
+      </c>
+      <c r="AN305">
+        <v>-1</v>
+      </c>
+      <c r="AO305">
+        <v>-1</v>
+      </c>
+      <c r="AP305">
+        <v>-1</v>
+      </c>
+      <c r="AQ305">
+        <v>0</v>
+      </c>
+      <c r="AR305">
+        <v>0</v>
+      </c>
+      <c r="AS305">
+        <v>0</v>
+      </c>
+      <c r="AT305">
+        <v>0</v>
+      </c>
+      <c r="AU305" t="inlineStr">
+        <is>
+          <t>2026-10-18 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="G306">
+        <v>0</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>0</v>
+      </c>
+      <c r="L306">
+        <v>0</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N306">
+        <v>0</v>
+      </c>
+      <c r="O306">
+        <v>0</v>
+      </c>
+      <c r="P306">
+        <v>0</v>
+      </c>
+      <c r="Q306">
+        <v>0</v>
+      </c>
+      <c r="R306">
+        <v>0</v>
+      </c>
+      <c r="S306">
+        <v>0</v>
+      </c>
+      <c r="T306">
+        <v>0</v>
+      </c>
+      <c r="U306">
+        <v>0</v>
+      </c>
+      <c r="V306">
+        <v>0</v>
+      </c>
+      <c r="W306">
+        <v>0</v>
+      </c>
+      <c r="X306">
+        <v>0</v>
+      </c>
+      <c r="Y306">
+        <v>0</v>
+      </c>
+      <c r="Z306">
+        <v>0</v>
+      </c>
+      <c r="AA306">
+        <v>0</v>
+      </c>
+      <c r="AB306">
+        <v>0</v>
+      </c>
+      <c r="AC306">
+        <v>0</v>
+      </c>
+      <c r="AD306">
+        <v>0</v>
+      </c>
+      <c r="AE306">
+        <v>0</v>
+      </c>
+      <c r="AF306">
+        <v>0</v>
+      </c>
+      <c r="AG306">
+        <v>0</v>
+      </c>
+      <c r="AH306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI306" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ306">
+        <v>0</v>
+      </c>
+      <c r="AK306">
+        <v>0</v>
+      </c>
+      <c r="AL306">
+        <v>0</v>
+      </c>
+      <c r="AM306">
+        <v>-1</v>
+      </c>
+      <c r="AN306">
+        <v>-1</v>
+      </c>
+      <c r="AO306">
+        <v>-1</v>
+      </c>
+      <c r="AP306">
+        <v>-1</v>
+      </c>
+      <c r="AQ306">
+        <v>0</v>
+      </c>
+      <c r="AR306">
+        <v>0</v>
+      </c>
+      <c r="AS306">
+        <v>0</v>
+      </c>
+      <c r="AT306">
+        <v>0</v>
+      </c>
+      <c r="AU306" t="inlineStr">
+        <is>
+          <t>2026-10-18 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C307" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="D307" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
+      <c r="E307" t="inlineStr">
         <is>
           <t>Guabirá</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr">
+      <c r="F307" t="inlineStr">
         <is>
           <t>Oriente Petrolero</t>
         </is>
       </c>
-      <c r="G303">
-        <v>0</v>
-      </c>
-      <c r="H303">
-        <v>0</v>
-      </c>
-      <c r="I303">
-        <v>0</v>
-      </c>
-      <c r="J303">
-        <v>0</v>
-      </c>
-      <c r="K303">
-        <v>0</v>
-      </c>
-      <c r="L303">
-        <v>0</v>
-      </c>
-      <c r="M303" t="inlineStr">
+      <c r="G307">
+        <v>0</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>0</v>
+      </c>
+      <c r="L307">
+        <v>0</v>
+      </c>
+      <c r="M307" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N303">
-        <v>0</v>
-      </c>
-      <c r="O303">
-        <v>0</v>
-      </c>
-      <c r="P303">
-        <v>0</v>
-      </c>
-      <c r="Q303">
-        <v>0</v>
-      </c>
-      <c r="R303">
-        <v>0</v>
-      </c>
-      <c r="S303">
-        <v>0</v>
-      </c>
-      <c r="T303">
-        <v>0</v>
-      </c>
-      <c r="U303">
-        <v>0</v>
-      </c>
-      <c r="V303">
-        <v>0</v>
-      </c>
-      <c r="W303">
-        <v>0</v>
-      </c>
-      <c r="X303">
-        <v>0</v>
-      </c>
-      <c r="Y303">
-        <v>0</v>
-      </c>
-      <c r="Z303">
-        <v>0</v>
-      </c>
-      <c r="AA303">
-        <v>0</v>
-      </c>
-      <c r="AB303">
-        <v>0</v>
-      </c>
-      <c r="AC303">
-        <v>0</v>
-      </c>
-      <c r="AD303">
-        <v>0</v>
-      </c>
-      <c r="AE303">
-        <v>0</v>
-      </c>
-      <c r="AF303">
-        <v>0</v>
-      </c>
-      <c r="AG303">
-        <v>0</v>
-      </c>
-      <c r="AH303" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI303" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ303">
-        <v>0</v>
-      </c>
-      <c r="AK303">
-        <v>0</v>
-      </c>
-      <c r="AL303">
-        <v>0</v>
-      </c>
-      <c r="AM303">
-        <v>-1</v>
-      </c>
-      <c r="AN303">
-        <v>-1</v>
-      </c>
-      <c r="AO303">
-        <v>-1</v>
-      </c>
-      <c r="AP303">
-        <v>-1</v>
-      </c>
-      <c r="AQ303">
-        <v>0</v>
-      </c>
-      <c r="AR303">
-        <v>0</v>
-      </c>
-      <c r="AS303">
-        <v>0</v>
-      </c>
-      <c r="AT303">
-        <v>0</v>
-      </c>
-      <c r="AU303" t="inlineStr">
+      <c r="N307">
+        <v>0</v>
+      </c>
+      <c r="O307">
+        <v>0</v>
+      </c>
+      <c r="P307">
+        <v>0</v>
+      </c>
+      <c r="Q307">
+        <v>0</v>
+      </c>
+      <c r="R307">
+        <v>0</v>
+      </c>
+      <c r="S307">
+        <v>0</v>
+      </c>
+      <c r="T307">
+        <v>0</v>
+      </c>
+      <c r="U307">
+        <v>0</v>
+      </c>
+      <c r="V307">
+        <v>0</v>
+      </c>
+      <c r="W307">
+        <v>0</v>
+      </c>
+      <c r="X307">
+        <v>0</v>
+      </c>
+      <c r="Y307">
+        <v>0</v>
+      </c>
+      <c r="Z307">
+        <v>0</v>
+      </c>
+      <c r="AA307">
+        <v>0</v>
+      </c>
+      <c r="AB307">
+        <v>0</v>
+      </c>
+      <c r="AC307">
+        <v>0</v>
+      </c>
+      <c r="AD307">
+        <v>0</v>
+      </c>
+      <c r="AE307">
+        <v>0</v>
+      </c>
+      <c r="AF307">
+        <v>0</v>
+      </c>
+      <c r="AG307">
+        <v>0</v>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ307">
+        <v>0</v>
+      </c>
+      <c r="AK307">
+        <v>0</v>
+      </c>
+      <c r="AL307">
+        <v>0</v>
+      </c>
+      <c r="AM307">
+        <v>-1</v>
+      </c>
+      <c r="AN307">
+        <v>-1</v>
+      </c>
+      <c r="AO307">
+        <v>-1</v>
+      </c>
+      <c r="AP307">
+        <v>-1</v>
+      </c>
+      <c r="AQ307">
+        <v>0</v>
+      </c>
+      <c r="AR307">
+        <v>0</v>
+      </c>
+      <c r="AS307">
+        <v>0</v>
+      </c>
+      <c r="AT307">
+        <v>0</v>
+      </c>
+      <c r="AU307" t="inlineStr">
         <is>
           <t>2026-10-18 20:30:00</t>
         </is>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G70">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Sisaket United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sisaket United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G60">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="O75">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="P75">
-        <v>2.67</v>
+        <v>4.64</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12579,10 +12579,10 @@
         <v>0</v>
       </c>
       <c r="AC75">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD75">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="O76">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="P76">
-        <v>4.64</v>
+        <v>2.67</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12742,10 +12742,10 @@
         <v>0</v>
       </c>
       <c r="AC76">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AE76">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O153">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P153">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q153">
         <v>0</v>
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G202">
@@ -33366,12 +33366,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G203">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O297">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P297">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O298">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P298">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q298">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="O10">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>3.54</v>
+        <v>3.39</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P11">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G217">
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G218">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G228">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="O249">
-        <v>3.53</v>
+        <v>4.05</v>
       </c>
       <c r="P249">
-        <v>3.74</v>
+        <v>4.67</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G250">
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="O250">
-        <v>4.05</v>
+        <v>3.53</v>
       </c>
       <c r="P250">
-        <v>4.67</v>
+        <v>3.74</v>
       </c>
       <c r="Q250">
         <v>0</v>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46477,10 +46477,10 @@
         <v>0</v>
       </c>
       <c r="AA283">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB283">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC283">
         <v>0</v>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46640,10 +46640,10 @@
         <v>0</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC284">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46803,10 +46803,10 @@
         <v>0</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC285">
         <v>0</v>
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q301">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q157">
         <v>0</v>
@@ -25939,10 +25939,10 @@
         <v>0</v>
       </c>
       <c r="AA157">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB157">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC157">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O302">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P302">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q302">
         <v>0</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q307">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q244">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL98">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -807,34 +807,34 @@
         <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA3">
         <v>1.91</v>
@@ -843,19 +843,19 @@
         <v>1.88</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>5.02</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>3.49</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4556,34 +4556,34 @@
         <v>3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA26">
         <v>1.93</v>
@@ -4592,19 +4592,19 @@
         <v>1.83</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>2.34</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>4.17</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA55">
         <v>1.98</v>
@@ -9319,19 +9319,19 @@
         <v>1.88</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>9.4</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>2.12</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>11</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,34 +11565,34 @@
         <v>2.09</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA69">
         <v>1.95</v>
@@ -11601,19 +11601,19 @@
         <v>1.85</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>2.25</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,40 +12380,40 @@
         <v>2.72</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC74">
         <v>2</v>
@@ -12422,13 +12422,13 @@
         <v>1.7</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="O75">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="P75">
-        <v>4.64</v>
+        <v>2.67</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC75">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD75">
+        <v>1.63</v>
+      </c>
+      <c r="AE75">
+        <v>1.22</v>
+      </c>
+      <c r="AF75">
+        <v>1.4</v>
+      </c>
+      <c r="AG75">
+        <v>2.7</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>1.44</v>
+      </c>
+      <c r="AK75">
         <v>1.57</v>
-      </c>
-      <c r="AE75">
-        <v>0</v>
-      </c>
-      <c r="AF75">
-        <v>0</v>
-      </c>
-      <c r="AG75">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>0</v>
-      </c>
-      <c r="AK75">
-        <v>0</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="O76">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="P76">
-        <v>2.67</v>
+        <v>4.64</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC76">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD76">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G80">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>3.5</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,34 +15314,34 @@
         <v>2.84</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA92">
         <v>1.85</v>
@@ -15350,19 +15350,19 @@
         <v>1.92</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>2.64</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>1.98</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>3.71</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>2.14</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.25</v>
+        <v>2.34</v>
       </c>
       <c r="O108">
-        <v>5.95</v>
+        <v>3.62</v>
       </c>
       <c r="P108">
-        <v>9.75</v>
+        <v>2.73</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC108">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AD108">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="O109">
-        <v>3.62</v>
+        <v>5.95</v>
       </c>
       <c r="P109">
-        <v>2.73</v>
+        <v>9.75</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,40 +18248,40 @@
         <v>1.37</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC110">
         <v>1.95</v>
@@ -18290,13 +18290,13 @@
         <v>1.85</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18900,34 +18900,34 @@
         <v>3.33</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA114">
         <v>1.98</v>
@@ -18936,19 +18936,19 @@
         <v>1.73</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20856,55 +20856,55 @@
         <v>3.04</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21345,55 +21345,55 @@
         <v>2.93</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X130">
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q132">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R132">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S132">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T132">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U132">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V132">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W132">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X132">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z132">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC132">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD132">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE132">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF132">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG132">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O133">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P133">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q133">
         <v>0</v>
@@ -22027,10 +22027,10 @@
         <v>0</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.32</v>
+        <v>3.87</v>
       </c>
       <c r="O134">
-        <v>4.65</v>
+        <v>3.62</v>
       </c>
       <c r="P134">
-        <v>7.55</v>
+        <v>1.75</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22975,55 +22975,55 @@
         <v>2.14</v>
       </c>
       <c r="Q139">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R139">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S139">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T139">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U139">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V139">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W139">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X139">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z139">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA139">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB139">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC139">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE139">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF139">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG139">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK139">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23138,55 +23138,55 @@
         <v>0</v>
       </c>
       <c r="Q140">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R140">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S140">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U140">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V140">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W140">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X140">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z140">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA140">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB140">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC140">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD140">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE140">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF140">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG140">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK140">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23464,55 +23464,55 @@
         <v>2.78</v>
       </c>
       <c r="Q142">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R142">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S142">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T142">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U142">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V142">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W142">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X142">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y142">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z142">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA142">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB142">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC142">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD142">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE142">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF142">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG142">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK142">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -24116,55 +24116,55 @@
         <v>0</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24442,55 +24442,55 @@
         <v>0</v>
       </c>
       <c r="Q148">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R148">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S148">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T148">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U148">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V148">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W148">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y148">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z148">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA148">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB148">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC148">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD148">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE148">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF148">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG148">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK148">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24605,40 +24605,40 @@
         <v>4.78</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AC149">
         <v>2.05</v>
@@ -24647,13 +24647,13 @@
         <v>1.7</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -25257,55 +25257,55 @@
         <v>3.2</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AA153">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB153">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q154">
         <v>0</v>
@@ -25583,34 +25583,34 @@
         <v>1.37</v>
       </c>
       <c r="Q155">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R155">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S155">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T155">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U155">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V155">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W155">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y155">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z155">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA155">
         <v>1.88</v>
@@ -25619,19 +25619,19 @@
         <v>1.93</v>
       </c>
       <c r="AC155">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD155">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE155">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF155">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG155">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK155">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -26072,55 +26072,55 @@
         <v>6.16</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -27213,55 +27213,55 @@
         <v>2.27</v>
       </c>
       <c r="Q165">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R165">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S165">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T165">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U165">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V165">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W165">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X165">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z165">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA165">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB165">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC165">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD165">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE165">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF165">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG165">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK165">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27702,55 +27702,55 @@
         <v>4.46</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q172">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R172">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S172">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T172">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U172">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V172">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W172">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X172">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y172">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z172">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA172">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB172">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC172">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD172">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE172">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF172">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG172">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK172">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28680,55 +28680,55 @@
         <v>1.21</v>
       </c>
       <c r="Q174">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R174">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S174">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T174">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U174">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V174">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W174">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X174">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y174">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z174">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC174">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD174">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE174">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF174">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG174">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH174" t="inlineStr">
         <is>
@@ -28741,10 +28741,10 @@
         </is>
       </c>
       <c r="AJ174">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK174">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL174">
         <v>0</v>
@@ -28843,55 +28843,55 @@
         <v>2.76</v>
       </c>
       <c r="Q175">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R175">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S175">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T175">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U175">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V175">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W175">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X175">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y175">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z175">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC175">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD175">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE175">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF175">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG175">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH175" t="inlineStr">
         <is>
@@ -28904,10 +28904,10 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK175">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL175">
         <v>0</v>
@@ -29006,55 +29006,55 @@
         <v>1.7</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29495,40 +29495,40 @@
         <v>1.75</v>
       </c>
       <c r="Q179">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R179">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S179">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T179">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U179">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V179">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W179">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X179">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y179">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z179">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC179">
         <v>1.98</v>
@@ -29537,13 +29537,13 @@
         <v>1.83</v>
       </c>
       <c r="AE179">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF179">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG179">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK179">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29649,64 +29649,64 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q180">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R180">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S180">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T180">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U180">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V180">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W180">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X180">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z180">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA180">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB180">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC180">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD180">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE180">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF180">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG180">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK180">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -30636,55 +30636,55 @@
         <v>2.68</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30799,55 +30799,55 @@
         <v>2.58</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S187">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T187">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U187">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V187">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W187">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X187">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y187">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z187">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC187">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD187">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE187">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF187">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG187">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK187">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30962,55 +30962,55 @@
         <v>6.86</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X188">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>7.28</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE188">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31777,55 +31777,55 @@
         <v>4.61</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G208">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q286">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4.29</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB6">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AC6">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="P7">
-        <v>7.02</v>
+        <v>4.29</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
+        <v>2.26</v>
+      </c>
+      <c r="S7">
+        <v>1.29</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
         <v>2.5</v>
       </c>
-      <c r="S7">
-        <v>1.25</v>
-      </c>
-      <c r="T7">
-        <v>3.3</v>
-      </c>
-      <c r="U7">
-        <v>2.25</v>
-      </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>1.7</v>
+      </c>
+      <c r="AB7">
+        <v>2.12</v>
+      </c>
+      <c r="AC7">
+        <v>2.79</v>
+      </c>
+      <c r="AD7">
+        <v>1.42</v>
+      </c>
+      <c r="AE7">
         <v>1.15</v>
       </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.56</v>
-      </c>
-      <c r="AB7">
-        <v>2.22</v>
-      </c>
-      <c r="AC7">
-        <v>2.35</v>
-      </c>
-      <c r="AD7">
-        <v>1.47</v>
-      </c>
-      <c r="AE7">
-        <v>1.16</v>
-      </c>
       <c r="AF7">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="O74">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="P74">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="Q74">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S74">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T74">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U74">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V74">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W74">
         <v>1.17</v>
@@ -12404,25 +12404,25 @@
         <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z74">
-        <v>5.75</v>
+        <v>5.28</v>
       </c>
       <c r="AA74">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AB74">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AC74">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD74">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AE74">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF74">
         <v>1.4</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK74">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="O75">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="P75">
-        <v>2.67</v>
+        <v>4.64</v>
       </c>
       <c r="Q75">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="R75">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="S75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T75">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U75">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V75">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W75">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z75">
-        <v>5.28</v>
+        <v>4.75</v>
       </c>
       <c r="AA75">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AB75">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="AC75">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD75">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE75">
         <v>1.22</v>
       </c>
       <c r="AF75">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG75">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="O76">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="P76">
-        <v>4.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q76">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R76">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U76">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V76">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z76">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA76">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AB76">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF76">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG76">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK76">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,80 +19054,80 @@
         </is>
       </c>
       <c r="N115">
+        <v>1.82</v>
+      </c>
+      <c r="O115">
+        <v>3.98</v>
+      </c>
+      <c r="P115">
+        <v>4.67</v>
+      </c>
+      <c r="Q115">
+        <v>2.5</v>
+      </c>
+      <c r="R115">
+        <v>2.3</v>
+      </c>
+      <c r="S115">
+        <v>1.35</v>
+      </c>
+      <c r="T115">
+        <v>2.86</v>
+      </c>
+      <c r="U115">
+        <v>2.6</v>
+      </c>
+      <c r="V115">
+        <v>1.44</v>
+      </c>
+      <c r="W115">
+        <v>1.07</v>
+      </c>
+      <c r="X115">
+        <v>1.01</v>
+      </c>
+      <c r="Y115">
+        <v>1.22</v>
+      </c>
+      <c r="Z115">
+        <v>3.74</v>
+      </c>
+      <c r="AA115">
+        <v>1.83</v>
+      </c>
+      <c r="AB115">
+        <v>2.03</v>
+      </c>
+      <c r="AC115">
+        <v>2.88</v>
+      </c>
+      <c r="AD115">
+        <v>1.35</v>
+      </c>
+      <c r="AE115">
+        <v>1.08</v>
+      </c>
+      <c r="AF115">
         <v>1.67</v>
       </c>
-      <c r="O115">
-        <v>4.45</v>
-      </c>
-      <c r="P115">
-        <v>5.18</v>
-      </c>
-      <c r="Q115">
-        <v>2</v>
-      </c>
-      <c r="R115">
-        <v>2.47</v>
-      </c>
-      <c r="S115">
+      <c r="AG115">
+        <v>2.15</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ115">
         <v>1.25</v>
       </c>
-      <c r="T115">
-        <v>3.6</v>
-      </c>
-      <c r="U115">
-        <v>2.25</v>
-      </c>
-      <c r="V115">
-        <v>1.57</v>
-      </c>
-      <c r="W115">
-        <v>1.11</v>
-      </c>
-      <c r="X115">
-        <v>1.02</v>
-      </c>
-      <c r="Y115">
-        <v>1.15</v>
-      </c>
-      <c r="Z115">
-        <v>4.65</v>
-      </c>
-      <c r="AA115">
-        <v>1.55</v>
-      </c>
-      <c r="AB115">
-        <v>2.25</v>
-      </c>
-      <c r="AC115">
-        <v>2.49</v>
-      </c>
-      <c r="AD115">
-        <v>1.57</v>
-      </c>
-      <c r="AE115">
-        <v>1.18</v>
-      </c>
-      <c r="AF115">
-        <v>1.61</v>
-      </c>
-      <c r="AG115">
-        <v>2.2</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.18</v>
-      </c>
       <c r="AK115">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O116">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="P116">
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="Q116">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R116">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S116">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="U116">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V116">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
-        <v>3.74</v>
+        <v>4.65</v>
       </c>
       <c r="AA116">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB116">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC116">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD116">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE116">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG116">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK116">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA133">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB133">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>3.87</v>
+        <v>1.32</v>
       </c>
       <c r="O134">
-        <v>3.62</v>
+        <v>4.65</v>
       </c>
       <c r="P134">
-        <v>1.75</v>
+        <v>7.55</v>
       </c>
       <c r="Q134">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S134">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T134">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U134">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V134">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z134">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB134">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC134">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD134">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE134">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF134">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG134">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK134">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O135">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P135">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q135">
         <v>0</v>
@@ -22353,10 +22353,10 @@
         <v>0</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC135">
         <v>0</v>
@@ -24103,7 +24103,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N146">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N147">
@@ -24429,7 +24429,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N148">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N149">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="O217">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P217">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="Q217">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="R217">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S217">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T217">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U217">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V217">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W217">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X217">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y217">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z217">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="AA217">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AB217">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AC217">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AD217">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE217">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF217">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG217">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK217">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="O218">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P218">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="Q218">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="R218">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S218">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T218">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U218">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V218">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W218">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X218">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z218">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="AA218">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB218">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC218">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AD218">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AE218">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF218">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG218">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK218">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G233">

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="P6">
-        <v>7.02</v>
+        <v>4.29</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
+        <v>2.26</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>3.25</v>
+      </c>
+      <c r="U6">
         <v>2.5</v>
       </c>
-      <c r="S6">
-        <v>1.25</v>
-      </c>
-      <c r="T6">
-        <v>3.3</v>
-      </c>
-      <c r="U6">
-        <v>2.25</v>
-      </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
+        <v>1.17</v>
+      </c>
+      <c r="Z6">
+        <v>4</v>
+      </c>
+      <c r="AA6">
+        <v>1.7</v>
+      </c>
+      <c r="AB6">
+        <v>2.12</v>
+      </c>
+      <c r="AC6">
+        <v>2.79</v>
+      </c>
+      <c r="AD6">
+        <v>1.42</v>
+      </c>
+      <c r="AE6">
         <v>1.15</v>
       </c>
-      <c r="Z6">
-        <v>4.3</v>
-      </c>
-      <c r="AA6">
-        <v>1.56</v>
-      </c>
-      <c r="AB6">
-        <v>2.22</v>
-      </c>
-      <c r="AC6">
-        <v>2.35</v>
-      </c>
-      <c r="AD6">
-        <v>1.47</v>
-      </c>
-      <c r="AE6">
-        <v>1.16</v>
-      </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="O7">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>4.29</v>
+        <v>7.02</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB7">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AC7">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>4.59</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.82</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>2.63</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>5.58</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>7.47</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,80 +11230,80 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.18</v>
+        <v>2.94</v>
       </c>
       <c r="O67">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>11</v>
+        <v>2.12</v>
       </c>
       <c r="Q67">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="R67">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S67">
+        <v>1.29</v>
+      </c>
+      <c r="T67">
+        <v>3.3</v>
+      </c>
+      <c r="U67">
+        <v>2.55</v>
+      </c>
+      <c r="V67">
+        <v>1.45</v>
+      </c>
+      <c r="W67">
+        <v>1.08</v>
+      </c>
+      <c r="X67">
+        <v>1.03</v>
+      </c>
+      <c r="Y67">
         <v>1.17</v>
       </c>
-      <c r="T67">
-        <v>4.5</v>
-      </c>
-      <c r="U67">
-        <v>1.98</v>
-      </c>
-      <c r="V67">
-        <v>1.71</v>
-      </c>
-      <c r="W67">
-        <v>1.19</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.09</v>
-      </c>
       <c r="Z67">
-        <v>5.9</v>
+        <v>3.98</v>
       </c>
       <c r="AA67">
+        <v>1.75</v>
+      </c>
+      <c r="AB67">
+        <v>2.18</v>
+      </c>
+      <c r="AC67">
+        <v>2.62</v>
+      </c>
+      <c r="AD67">
+        <v>1.44</v>
+      </c>
+      <c r="AE67">
+        <v>1.12</v>
+      </c>
+      <c r="AF67">
+        <v>1.55</v>
+      </c>
+      <c r="AG67">
+        <v>2.23</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.29</v>
+      </c>
+      <c r="AK67">
         <v>1.36</v>
-      </c>
-      <c r="AB67">
-        <v>2.7</v>
-      </c>
-      <c r="AC67">
-        <v>1.99</v>
-      </c>
-      <c r="AD67">
-        <v>1.7</v>
-      </c>
-      <c r="AE67">
-        <v>1.26</v>
-      </c>
-      <c r="AF67">
-        <v>1.7</v>
-      </c>
-      <c r="AG67">
-        <v>1.98</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.07</v>
-      </c>
-      <c r="AK67">
-        <v>3.36</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.94</v>
+        <v>1.18</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="P68">
-        <v>2.12</v>
+        <v>11</v>
       </c>
       <c r="Q68">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.73</v>
       </c>
       <c r="S68">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T68">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="V68">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z68">
-        <v>3.98</v>
+        <v>5.9</v>
       </c>
       <c r="AA68">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AC68">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="AD68">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF68">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AK68">
-        <v>1.36</v>
+        <v>3.36</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="O75">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="P75">
-        <v>4.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q75">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R75">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V75">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z75">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA75">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AB75">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD75">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF75">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG75">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK75">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="O76">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="P76">
-        <v>2.72</v>
+        <v>4.64</v>
       </c>
       <c r="Q76">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="R76">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S76">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="V76">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W76">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z76">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AA76">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AB76">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AC76">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD76">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
+        <v>1.22</v>
+      </c>
+      <c r="AF76">
+        <v>1.5</v>
+      </c>
+      <c r="AG76">
+        <v>2.38</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.25</v>
       </c>
-      <c r="AF76">
-        <v>1.4</v>
-      </c>
-      <c r="AG76">
-        <v>2.7</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.4</v>
-      </c>
       <c r="AK76">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17433,55 +17433,55 @@
         <v>2.75</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>4.3</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,55 +17759,55 @@
         <v>2.8</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O115">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="P115">
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="Q115">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R115">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T115">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="U115">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V115">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>3.74</v>
+        <v>4.65</v>
       </c>
       <c r="AA115">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB115">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC115">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD115">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF115">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG115">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK115">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,80 +19217,80 @@
         </is>
       </c>
       <c r="N116">
+        <v>1.82</v>
+      </c>
+      <c r="O116">
+        <v>3.98</v>
+      </c>
+      <c r="P116">
+        <v>4.67</v>
+      </c>
+      <c r="Q116">
+        <v>2.5</v>
+      </c>
+      <c r="R116">
+        <v>2.3</v>
+      </c>
+      <c r="S116">
+        <v>1.35</v>
+      </c>
+      <c r="T116">
+        <v>2.86</v>
+      </c>
+      <c r="U116">
+        <v>2.6</v>
+      </c>
+      <c r="V116">
+        <v>1.44</v>
+      </c>
+      <c r="W116">
+        <v>1.07</v>
+      </c>
+      <c r="X116">
+        <v>1.01</v>
+      </c>
+      <c r="Y116">
+        <v>1.22</v>
+      </c>
+      <c r="Z116">
+        <v>3.74</v>
+      </c>
+      <c r="AA116">
+        <v>1.83</v>
+      </c>
+      <c r="AB116">
+        <v>2.03</v>
+      </c>
+      <c r="AC116">
+        <v>2.88</v>
+      </c>
+      <c r="AD116">
+        <v>1.35</v>
+      </c>
+      <c r="AE116">
+        <v>1.08</v>
+      </c>
+      <c r="AF116">
         <v>1.67</v>
       </c>
-      <c r="O116">
-        <v>4.45</v>
-      </c>
-      <c r="P116">
-        <v>5.18</v>
-      </c>
-      <c r="Q116">
-        <v>2</v>
-      </c>
-      <c r="R116">
-        <v>2.47</v>
-      </c>
-      <c r="S116">
+      <c r="AG116">
+        <v>2.15</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
         <v>1.25</v>
       </c>
-      <c r="T116">
-        <v>3.6</v>
-      </c>
-      <c r="U116">
-        <v>2.25</v>
-      </c>
-      <c r="V116">
-        <v>1.57</v>
-      </c>
-      <c r="W116">
-        <v>1.11</v>
-      </c>
-      <c r="X116">
-        <v>1.02</v>
-      </c>
-      <c r="Y116">
-        <v>1.15</v>
-      </c>
-      <c r="Z116">
-        <v>4.65</v>
-      </c>
-      <c r="AA116">
-        <v>1.55</v>
-      </c>
-      <c r="AB116">
-        <v>2.25</v>
-      </c>
-      <c r="AC116">
-        <v>2.49</v>
-      </c>
-      <c r="AD116">
-        <v>1.57</v>
-      </c>
-      <c r="AE116">
-        <v>1.18</v>
-      </c>
-      <c r="AF116">
-        <v>1.61</v>
-      </c>
-      <c r="AG116">
-        <v>2.2</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.18</v>
-      </c>
       <c r="AK116">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -21671,55 +21671,55 @@
         <v>6.4</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P140">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q140">
         <v>5.6</v>
@@ -26561,34 +26561,34 @@
         <v>2.91</v>
       </c>
       <c r="Q161">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R161">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S161">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T161">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U161">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V161">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W161">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y161">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z161">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA161">
         <v>1.89</v>
@@ -26597,19 +26597,19 @@
         <v>1.86</v>
       </c>
       <c r="AC161">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD161">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE161">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF161">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG161">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK161">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G165">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G166">
@@ -31777,55 +31777,55 @@
         <v>0</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R193">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S193">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T193">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U193">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V193">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W193">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X193">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y193">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z193">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC193">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD193">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE193">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF193">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG193">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK193">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31940,55 +31940,55 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R194">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S194">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T194">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U194">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V194">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W194">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X194">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y194">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z194">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC194">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD194">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE194">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF194">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG194">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK194">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33407,55 +33407,55 @@
         <v>0</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R203">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S203">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T203">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U203">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V203">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W203">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y203">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z203">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA203">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB203">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC203">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD203">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE203">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF203">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG203">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK203">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -35363,55 +35363,55 @@
         <v>2.48</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R215">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S215">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T215">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W215">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X215">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z215">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC215">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD215">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE215">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF215">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG215">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK215">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35526,34 +35526,34 @@
         <v>3.01</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R216">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S216">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T216">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U216">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V216">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W216">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X216">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z216">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA216">
         <v>1.87</v>
@@ -35562,19 +35562,19 @@
         <v>1.82</v>
       </c>
       <c r="AC216">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD216">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE216">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF216">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG216">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK216">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36178,55 +36178,55 @@
         <v>2.89</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R220">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S220">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T220">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U220">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V220">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W220">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X220">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y220">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z220">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AA220">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB220">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC220">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD220">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE220">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF220">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG220">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK220">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O223">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P223">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R223">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S223">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T223">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U223">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V223">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W223">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X223">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z223">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA223">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB223">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC223">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD223">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE223">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF223">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG223">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK223">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37482,55 +37482,55 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R231">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T231">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U231">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V231">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W231">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X231">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y231">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z231">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC231">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD231">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE231">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF231">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG231">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK231">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R232">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S232">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T232">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U232">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V232">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W232">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X232">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z232">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC232">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD232">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE232">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF232">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG232">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK232">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R233">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S233">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T233">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U233">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V233">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W233">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X233">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y233">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z233">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA233">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB233">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC233">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD233">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE233">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF233">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG233">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK233">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,40 +38460,40 @@
         <v>1.9</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R234">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T234">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U234">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V234">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W234">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X234">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z234">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB234">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AC234">
         <v>1.93</v>
@@ -38502,13 +38502,13 @@
         <v>1.78</v>
       </c>
       <c r="AE234">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF234">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG234">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK234">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R235">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S235">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T235">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U235">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V235">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W235">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X235">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y235">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z235">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA235">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB235">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC235">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD235">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE235">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF235">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG235">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK235">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O248">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P248">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q248">
         <v>0</v>
@@ -40905,55 +40905,55 @@
         <v>2.23</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -43341,64 +43341,64 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q264">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R264">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S264">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T264">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U264">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V264">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W264">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X264">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y264">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z264">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC264">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD264">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE264">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF264">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG264">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH264" t="inlineStr">
         <is>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK264">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43839,34 +43839,34 @@
         <v>4.18</v>
       </c>
       <c r="Q267">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R267">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T267">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U267">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V267">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W267">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X267">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y267">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z267">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA267">
         <v>1.95</v>
@@ -43875,19 +43875,19 @@
         <v>1.73</v>
       </c>
       <c r="AC267">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD267">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE267">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF267">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG267">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK267">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -45306,55 +45306,55 @@
         <v>6.03</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AA276">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB276">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL276">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4.29</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB6">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AC6">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="P7">
-        <v>7.02</v>
+        <v>4.29</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
+        <v>2.26</v>
+      </c>
+      <c r="S7">
+        <v>1.29</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
         <v>2.5</v>
       </c>
-      <c r="S7">
-        <v>1.25</v>
-      </c>
-      <c r="T7">
-        <v>3.3</v>
-      </c>
-      <c r="U7">
-        <v>2.25</v>
-      </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>4</v>
+      </c>
+      <c r="AA7">
+        <v>1.7</v>
+      </c>
+      <c r="AB7">
+        <v>2.12</v>
+      </c>
+      <c r="AC7">
+        <v>2.79</v>
+      </c>
+      <c r="AD7">
+        <v>1.42</v>
+      </c>
+      <c r="AE7">
         <v>1.15</v>
       </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.56</v>
-      </c>
-      <c r="AB7">
-        <v>2.22</v>
-      </c>
-      <c r="AC7">
-        <v>2.35</v>
-      </c>
-      <c r="AD7">
-        <v>1.47</v>
-      </c>
-      <c r="AE7">
-        <v>1.16</v>
-      </c>
       <c r="AF7">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.52</v>
+        <v>2.19</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
         <v>2.82</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,65 +3406,65 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="O19">
+        <v>3.3</v>
+      </c>
+      <c r="P19">
+        <v>2.82</v>
+      </c>
+      <c r="Q19">
+        <v>2.83</v>
+      </c>
+      <c r="R19">
+        <v>2.13</v>
+      </c>
+      <c r="S19">
+        <v>1.3</v>
+      </c>
+      <c r="T19">
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <v>2.48</v>
+      </c>
+      <c r="V19">
+        <v>1.43</v>
+      </c>
+      <c r="W19">
+        <v>1.08</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.22</v>
+      </c>
+      <c r="Z19">
         <v>3.5</v>
       </c>
-      <c r="P19">
-        <v>4.59</v>
-      </c>
-      <c r="Q19">
-        <v>2.21</v>
-      </c>
-      <c r="R19">
+      <c r="AA19">
+        <v>1.79</v>
+      </c>
+      <c r="AB19">
+        <v>1.88</v>
+      </c>
+      <c r="AC19">
+        <v>2.97</v>
+      </c>
+      <c r="AD19">
+        <v>1.3</v>
+      </c>
+      <c r="AE19">
+        <v>1.09</v>
+      </c>
+      <c r="AF19">
+        <v>1.64</v>
+      </c>
+      <c r="AG19">
         <v>2.1</v>
       </c>
-      <c r="S19">
-        <v>1.38</v>
-      </c>
-      <c r="T19">
-        <v>2.64</v>
-      </c>
-      <c r="U19">
-        <v>2.89</v>
-      </c>
-      <c r="V19">
-        <v>1.32</v>
-      </c>
-      <c r="W19">
-        <v>1.05</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.29</v>
-      </c>
-      <c r="Z19">
-        <v>3.04</v>
-      </c>
-      <c r="AA19">
-        <v>2.05</v>
-      </c>
-      <c r="AB19">
-        <v>1.75</v>
-      </c>
-      <c r="AC19">
-        <v>3.5</v>
-      </c>
-      <c r="AD19">
-        <v>1.22</v>
-      </c>
-      <c r="AE19">
-        <v>1.05</v>
-      </c>
-      <c r="AF19">
-        <v>1.95</v>
-      </c>
-      <c r="AG19">
-        <v>1.75</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>4.59</v>
       </c>
       <c r="Q20">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="R20">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>2.48</v>
+        <v>2.89</v>
       </c>
       <c r="V20">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.04</v>
+      </c>
+      <c r="AA20">
+        <v>2.05</v>
+      </c>
+      <c r="AB20">
+        <v>1.75</v>
+      </c>
+      <c r="AC20">
+        <v>3.5</v>
+      </c>
+      <c r="AD20">
         <v>1.22</v>
       </c>
-      <c r="Z20">
-        <v>3.5</v>
-      </c>
-      <c r="AA20">
-        <v>1.79</v>
-      </c>
-      <c r="AB20">
-        <v>1.88</v>
-      </c>
-      <c r="AC20">
-        <v>2.97</v>
-      </c>
-      <c r="AD20">
-        <v>1.3</v>
-      </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK20">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="O35">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>3.54</v>
+        <v>3.82</v>
       </c>
       <c r="R35">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="S35">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U35">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="V35">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB35">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC35">
-        <v>3.28</v>
+        <v>3.86</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="O36">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P36">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q36">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
       <c r="R36">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S36">
+        <v>1.35</v>
+      </c>
+      <c r="T36">
+        <v>2.77</v>
+      </c>
+      <c r="U36">
+        <v>2.65</v>
+      </c>
+      <c r="V36">
         <v>1.38</v>
       </c>
-      <c r="T36">
-        <v>2.65</v>
-      </c>
-      <c r="U36">
-        <v>2.9</v>
-      </c>
-      <c r="V36">
-        <v>1.32</v>
-      </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB36">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.86</v>
+        <v>3.28</v>
       </c>
       <c r="AD36">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="O75">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="P75">
-        <v>2.72</v>
+        <v>4.64</v>
       </c>
       <c r="Q75">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="R75">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S75">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T75">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U75">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="V75">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W75">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z75">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AA75">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AB75">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AC75">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD75">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE75">
+        <v>1.22</v>
+      </c>
+      <c r="AF75">
+        <v>1.5</v>
+      </c>
+      <c r="AG75">
+        <v>2.38</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.25</v>
       </c>
-      <c r="AF75">
-        <v>1.4</v>
-      </c>
-      <c r="AG75">
-        <v>2.7</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.4</v>
-      </c>
       <c r="AK75">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="O76">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="P76">
-        <v>4.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q76">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R76">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U76">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V76">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z76">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA76">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AB76">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="AC76">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF76">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG76">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK76">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,80 +17424,80 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.65</v>
+        <v>1.81</v>
       </c>
       <c r="O105">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P105">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q105">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="R105">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S105">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T105">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="U105">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="V105">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W105">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y105">
+        <v>1.22</v>
+      </c>
+      <c r="Z105">
+        <v>3.5</v>
+      </c>
+      <c r="AA105">
+        <v>1.81</v>
+      </c>
+      <c r="AB105">
+        <v>1.86</v>
+      </c>
+      <c r="AC105">
+        <v>2.97</v>
+      </c>
+      <c r="AD105">
         <v>1.3</v>
       </c>
-      <c r="Z105">
-        <v>2.97</v>
-      </c>
-      <c r="AA105">
-        <v>2.02</v>
-      </c>
-      <c r="AB105">
-        <v>1.68</v>
-      </c>
-      <c r="AC105">
-        <v>3.5</v>
-      </c>
-      <c r="AD105">
+      <c r="AE105">
+        <v>1.07</v>
+      </c>
+      <c r="AF105">
+        <v>1.72</v>
+      </c>
+      <c r="AG105">
+        <v>1.96</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ105">
         <v>1.22</v>
       </c>
-      <c r="AE105">
-        <v>1.04</v>
-      </c>
-      <c r="AF105">
-        <v>1.76</v>
-      </c>
-      <c r="AG105">
-        <v>1.91</v>
-      </c>
-      <c r="AH105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ105">
-        <v>1.28</v>
-      </c>
       <c r="AK105">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.81</v>
+        <v>2.65</v>
       </c>
       <c r="O106">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P106">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q106">
-        <v>2.37</v>
+        <v>3.24</v>
       </c>
       <c r="R106">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="S106">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T106">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="U106">
-        <v>2.64</v>
+        <v>2.81</v>
       </c>
       <c r="V106">
+        <v>1.34</v>
+      </c>
+      <c r="W106">
+        <v>1.05</v>
+      </c>
+      <c r="X106">
+        <v>1.02</v>
+      </c>
+      <c r="Y106">
+        <v>1.3</v>
+      </c>
+      <c r="Z106">
+        <v>2.97</v>
+      </c>
+      <c r="AA106">
+        <v>2.02</v>
+      </c>
+      <c r="AB106">
+        <v>1.68</v>
+      </c>
+      <c r="AC106">
+        <v>3.5</v>
+      </c>
+      <c r="AD106">
+        <v>1.22</v>
+      </c>
+      <c r="AE106">
+        <v>1.04</v>
+      </c>
+      <c r="AF106">
+        <v>1.76</v>
+      </c>
+      <c r="AG106">
+        <v>1.91</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
+        <v>1.28</v>
+      </c>
+      <c r="AK106">
         <v>1.38</v>
-      </c>
-      <c r="W106">
-        <v>1.04</v>
-      </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.22</v>
-      </c>
-      <c r="Z106">
-        <v>3.5</v>
-      </c>
-      <c r="AA106">
-        <v>1.81</v>
-      </c>
-      <c r="AB106">
-        <v>1.86</v>
-      </c>
-      <c r="AC106">
-        <v>2.97</v>
-      </c>
-      <c r="AD106">
-        <v>1.3</v>
-      </c>
-      <c r="AE106">
-        <v>1.07</v>
-      </c>
-      <c r="AF106">
-        <v>1.72</v>
-      </c>
-      <c r="AG106">
-        <v>1.96</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.22</v>
-      </c>
-      <c r="AK106">
-        <v>1.86</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="O115">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="P115">
-        <v>5.18</v>
+        <v>2.63</v>
       </c>
       <c r="Q115">
-        <v>2</v>
+        <v>2.81</v>
       </c>
       <c r="R115">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="S115">
         <v>1.25</v>
       </c>
       <c r="T115">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U115">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V115">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W115">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
+        <v>1.17</v>
+      </c>
+      <c r="Z115">
+        <v>4.3</v>
+      </c>
+      <c r="AA115">
+        <v>1.7</v>
+      </c>
+      <c r="AB115">
+        <v>2.3</v>
+      </c>
+      <c r="AC115">
+        <v>2.46</v>
+      </c>
+      <c r="AD115">
+        <v>1.47</v>
+      </c>
+      <c r="AE115">
         <v>1.15</v>
       </c>
-      <c r="Z115">
-        <v>4.65</v>
-      </c>
-      <c r="AA115">
-        <v>1.55</v>
-      </c>
-      <c r="AB115">
-        <v>2.25</v>
-      </c>
-      <c r="AC115">
-        <v>2.49</v>
-      </c>
-      <c r="AD115">
-        <v>1.57</v>
-      </c>
-      <c r="AE115">
-        <v>1.18</v>
-      </c>
       <c r="AF115">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG115">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK115">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="O116">
-        <v>3.98</v>
+        <v>4.45</v>
       </c>
       <c r="P116">
-        <v>4.67</v>
+        <v>5.18</v>
       </c>
       <c r="Q116">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="R116">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S116">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T116">
-        <v>2.86</v>
+        <v>3.6</v>
       </c>
       <c r="U116">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="V116">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z116">
-        <v>3.74</v>
+        <v>4.65</v>
       </c>
       <c r="AA116">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AB116">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AC116">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD116">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AE116">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG116">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK116">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.55</v>
+        <v>1.82</v>
       </c>
       <c r="O117">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="P117">
-        <v>2.63</v>
+        <v>4.67</v>
       </c>
       <c r="Q117">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="R117">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T117">
-        <v>3.28</v>
+        <v>2.86</v>
       </c>
       <c r="U117">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V117">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W117">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA117">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AB117">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AC117">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD117">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE117">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AG117">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>3.87</v>
+        <v>1.32</v>
       </c>
       <c r="O133">
-        <v>3.62</v>
+        <v>4.65</v>
       </c>
       <c r="P133">
-        <v>1.75</v>
+        <v>7.55</v>
       </c>
       <c r="Q133">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R133">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S133">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T133">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U133">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V133">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W133">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X133">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y133">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z133">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA133">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB133">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC133">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD133">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE133">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF133">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG133">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK133">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,13 +22151,13 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA135">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB135">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -23571,12 +23571,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G143">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>2026-10-18 10:15:00</t>
+          <t>2026-10-18 10:30:00</t>
         </is>
       </c>
     </row>
@@ -23739,7 +23739,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23902,7 +23902,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P145">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R145">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S145">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T145">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U145">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V145">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W145">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X145">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y145">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z145">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA145">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB145">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC145">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD145">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE145">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF145">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG145">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK145">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G146">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G147">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G149">
@@ -24605,55 +24605,55 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R149">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S149">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T149">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U149">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V149">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W149">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X149">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y149">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z149">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA149">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB149">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC149">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD149">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE149">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF149">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG149">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK149">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G150">
@@ -24768,55 +24768,55 @@
         <v>0</v>
       </c>
       <c r="Q150">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R150">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S150">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="T150">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U150">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V150">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W150">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X150">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y150">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z150">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AA150">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB150">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AC150">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD150">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE150">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF150">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG150">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
@@ -24829,10 +24829,10 @@
         </is>
       </c>
       <c r="AJ150">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK150">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AL150">
         <v>0</v>
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G151">
@@ -29169,55 +29169,55 @@
         <v>11.1</v>
       </c>
       <c r="Q177">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R177">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S177">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T177">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U177">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V177">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W177">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X177">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y177">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z177">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA177">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB177">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC177">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD177">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE177">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF177">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG177">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK177">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -30473,55 +30473,55 @@
         <v>2.88</v>
       </c>
       <c r="Q185">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S185">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T185">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U185">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V185">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W185">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X185">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y185">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z185">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC185">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD185">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE185">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF185">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG185">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK185">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL185">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G193">
@@ -31777,56 +31777,56 @@
         <v>0</v>
       </c>
       <c r="Q193">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R193">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="S193">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="T193">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="U193">
-        <v>3.18</v>
+        <v>2.48</v>
       </c>
       <c r="V193">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="W193">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X193">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y193">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="Z193">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="AA193">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AB193">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AC193">
-        <v>4.55</v>
+        <v>2.97</v>
       </c>
       <c r="AD193">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AE193">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF193">
+        <v>1.66</v>
+      </c>
+      <c r="AG193">
         <v>2.07</v>
       </c>
-      <c r="AG193">
-        <v>1.66</v>
-      </c>
       <c r="AH193" t="inlineStr">
         <is>
           <t>[]</t>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK193">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G194">
@@ -31940,56 +31940,56 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R194">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="S194">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T194">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="U194">
-        <v>2.48</v>
+        <v>3.18</v>
       </c>
       <c r="V194">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="W194">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X194">
+        <v>1.06</v>
+      </c>
+      <c r="Y194">
+        <v>1.4</v>
+      </c>
+      <c r="Z194">
+        <v>2.56</v>
+      </c>
+      <c r="AA194">
+        <v>2.37</v>
+      </c>
+      <c r="AB194">
+        <v>1.53</v>
+      </c>
+      <c r="AC194">
+        <v>4.55</v>
+      </c>
+      <c r="AD194">
+        <v>1.13</v>
+      </c>
+      <c r="AE194">
         <v>1.01</v>
       </c>
-      <c r="Y194">
-        <v>1.22</v>
-      </c>
-      <c r="Z194">
-        <v>3.5</v>
-      </c>
-      <c r="AA194">
-        <v>1.85</v>
-      </c>
-      <c r="AB194">
-        <v>1.95</v>
-      </c>
-      <c r="AC194">
-        <v>2.97</v>
-      </c>
-      <c r="AD194">
-        <v>1.3</v>
-      </c>
-      <c r="AE194">
-        <v>1.09</v>
-      </c>
       <c r="AF194">
+        <v>2.07</v>
+      </c>
+      <c r="AG194">
         <v>1.66</v>
       </c>
-      <c r="AG194">
-        <v>2.07</v>
-      </c>
       <c r="AH194" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK194">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="O217">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P217">
-        <v>2.64</v>
+        <v>3.08</v>
       </c>
       <c r="Q217">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="R217">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S217">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T217">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U217">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V217">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W217">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X217">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y217">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z217">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="AA217">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB217">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC217">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AD217">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AE217">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF217">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG217">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK217">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,19 +35843,19 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.45</v>
+        <v>4.01</v>
       </c>
       <c r="O218">
-        <v>3.55</v>
+        <v>3.91</v>
       </c>
       <c r="P218">
-        <v>3.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q218">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="R218">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S218">
         <v>1.33</v>
@@ -35864,43 +35864,43 @@
         <v>3</v>
       </c>
       <c r="U218">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="V218">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W218">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X218">
         <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z218">
-        <v>3.83</v>
+        <v>3.48</v>
       </c>
       <c r="AA218">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB218">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC218">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="AD218">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE218">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF218">
         <v>1.65</v>
       </c>
       <c r="AG218">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AK218">
-        <v>1.59</v>
+        <v>1.21</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,80 +36006,80 @@
         </is>
       </c>
       <c r="N219">
-        <v>4.01</v>
+        <v>2.63</v>
       </c>
       <c r="O219">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="P219">
-        <v>1.96</v>
+        <v>2.64</v>
       </c>
       <c r="Q219">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="R219">
+        <v>2.3</v>
+      </c>
+      <c r="S219">
+        <v>1.25</v>
+      </c>
+      <c r="T219">
+        <v>3.6</v>
+      </c>
+      <c r="U219">
+        <v>2.4</v>
+      </c>
+      <c r="V219">
+        <v>1.5</v>
+      </c>
+      <c r="W219">
+        <v>1.11</v>
+      </c>
+      <c r="X219">
+        <v>1</v>
+      </c>
+      <c r="Y219">
+        <v>1.15</v>
+      </c>
+      <c r="Z219">
+        <v>4.2</v>
+      </c>
+      <c r="AA219">
+        <v>1.7</v>
+      </c>
+      <c r="AB219">
         <v>2.2</v>
       </c>
-      <c r="S219">
-        <v>1.33</v>
-      </c>
-      <c r="T219">
-        <v>3</v>
-      </c>
-      <c r="U219">
-        <v>2.59</v>
-      </c>
-      <c r="V219">
-        <v>1.42</v>
-      </c>
-      <c r="W219">
-        <v>1.08</v>
-      </c>
-      <c r="X219">
-        <v>1.01</v>
-      </c>
-      <c r="Y219">
+      <c r="AC219">
+        <v>2.6</v>
+      </c>
+      <c r="AD219">
+        <v>1.53</v>
+      </c>
+      <c r="AE219">
+        <v>1.17</v>
+      </c>
+      <c r="AF219">
+        <v>1.51</v>
+      </c>
+      <c r="AG219">
+        <v>2.42</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ219">
         <v>1.25</v>
       </c>
-      <c r="Z219">
-        <v>3.48</v>
-      </c>
-      <c r="AA219">
-        <v>1.86</v>
-      </c>
-      <c r="AB219">
-        <v>1.85</v>
-      </c>
-      <c r="AC219">
-        <v>3.3</v>
-      </c>
-      <c r="AD219">
-        <v>1.35</v>
-      </c>
-      <c r="AE219">
-        <v>1.06</v>
-      </c>
-      <c r="AF219">
-        <v>1.65</v>
-      </c>
-      <c r="AG219">
-        <v>2.1</v>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ219">
-        <v>1.24</v>
-      </c>
       <c r="AK219">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36830,34 +36830,34 @@
         <v>1.65</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R224">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S224">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T224">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U224">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V224">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W224">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y224">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z224">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA224">
         <v>1.81</v>
@@ -36866,19 +36866,19 @@
         <v>2</v>
       </c>
       <c r="AC224">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD224">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE224">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF224">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG224">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK224">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37023,10 +37023,10 @@
         <v>0</v>
       </c>
       <c r="AA225">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB225">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC225">
         <v>0</v>
@@ -37319,55 +37319,55 @@
         <v>5.5</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R227">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S227">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T227">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U227">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V227">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W227">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X227">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z227">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA227">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB227">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC227">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD227">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE227">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF227">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG227">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK227">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37808,55 +37808,55 @@
         <v>6.26</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R230">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S230">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T230">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U230">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V230">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W230">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X230">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y230">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z230">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA230">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB230">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC230">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AD230">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE230">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF230">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG230">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK230">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R237">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S237">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T237">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V237">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W237">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X237">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y237">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z237">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA237">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB237">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC237">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD237">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE237">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF237">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG237">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK237">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39112,55 +39112,55 @@
         <v>2.52</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39266,64 +39266,64 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R239">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S239">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T239">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U239">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V239">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W239">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X239">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y239">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z239">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC239">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD239">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE239">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF239">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG239">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39336,10 +39336,10 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK239">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL239">
         <v>0</v>
@@ -39438,55 +39438,55 @@
         <v>1.44</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R240">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S240">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T240">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U240">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V240">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W240">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X240">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z240">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC240">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD240">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE240">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF240">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG240">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH240" t="inlineStr">
         <is>
@@ -39499,10 +39499,10 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK240">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -39755,64 +39755,64 @@
         </is>
       </c>
       <c r="N242">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O242">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P242">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>6.21</v>
       </c>
       <c r="R242">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S242">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T242">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U242">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V242">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W242">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X242">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y242">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z242">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA242">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB242">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC242">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD242">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE242">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF242">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG242">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH242" t="inlineStr">
         <is>
@@ -39825,10 +39825,10 @@
         </is>
       </c>
       <c r="AJ242">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK242">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R245">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S245">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T245">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U245">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V245">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W245">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X245">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y245">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z245">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC245">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD245">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE245">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF245">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG245">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK245">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -41068,34 +41068,34 @@
         <v>4.43</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R250">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S250">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T250">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U250">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V250">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W250">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X250">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y250">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z250">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA250">
         <v>1.81</v>
@@ -41104,19 +41104,19 @@
         <v>2</v>
       </c>
       <c r="AC250">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD250">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE250">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF250">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG250">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK250">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41557,55 +41557,55 @@
         <v>2.45</v>
       </c>
       <c r="Q253">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R253">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S253">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T253">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U253">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V253">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W253">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X253">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z253">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA253">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB253">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC253">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD253">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE253">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF253">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG253">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41618,10 +41618,10 @@
         </is>
       </c>
       <c r="AJ253">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK253">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>0</v>
       </c>
       <c r="AA254">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB254">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC254">
         <v>0</v>
@@ -41883,55 +41883,55 @@
         <v>3.74</v>
       </c>
       <c r="Q255">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R255">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S255">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T255">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U255">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V255">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W255">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X255">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z255">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA255">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB255">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC255">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD255">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE255">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF255">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG255">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK255">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42046,55 +42046,55 @@
         <v>5</v>
       </c>
       <c r="Q256">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="R256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S256">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T256">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U256">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V256">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W256">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X256">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y256">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z256">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA256">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB256">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC256">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD256">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE256">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF256">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG256">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42107,10 +42107,10 @@
         </is>
       </c>
       <c r="AJ256">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK256">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL256">
         <v>0</v>
@@ -42200,64 +42200,64 @@
         </is>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O257">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P257">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q257">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R257">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S257">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T257">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U257">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V257">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W257">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X257">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y257">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z257">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA257">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB257">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC257">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD257">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE257">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF257">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG257">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH257" t="inlineStr">
         <is>
@@ -42270,10 +42270,10 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK257">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL257">
         <v>0</v>
@@ -43024,55 +43024,55 @@
         <v>2.48</v>
       </c>
       <c r="Q262">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R262">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S262">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T262">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U262">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V262">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W262">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X262">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y262">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z262">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA262">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB262">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC262">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD262">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE262">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF262">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG262">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43085,10 +43085,10 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK262">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43187,55 +43187,55 @@
         <v>2.16</v>
       </c>
       <c r="Q263">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R263">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S263">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T263">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U263">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V263">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W263">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y263">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z263">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA263">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB263">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC263">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD263">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE263">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF263">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG263">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK263">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43513,55 +43513,55 @@
         <v>5.99</v>
       </c>
       <c r="Q265">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R265">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S265">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T265">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U265">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V265">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W265">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X265">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y265">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z265">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA265">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB265">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC265">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD265">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE265">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF265">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG265">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43574,10 +43574,10 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK265">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43676,55 +43676,55 @@
         <v>6.34</v>
       </c>
       <c r="Q266">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="R266">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S266">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T266">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U266">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V266">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W266">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X266">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y266">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z266">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA266">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB266">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC266">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD266">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE266">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF266">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG266">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK266">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q268">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R268">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S268">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T268">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U268">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V268">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W268">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X268">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y268">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z268">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="AA268">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB268">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AC268">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD268">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE268">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF268">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG268">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK268">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44165,55 +44165,55 @@
         <v>3.54</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44521,10 +44521,10 @@
         <v>0</v>
       </c>
       <c r="AA271">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB271">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC271">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -45469,40 +45469,40 @@
         <v>7.26</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA277">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB277">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AC277">
         <v>1.83</v>
@@ -45511,13 +45511,13 @@
         <v>1.98</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45632,40 +45632,40 @@
         <v>8.449999999999999</v>
       </c>
       <c r="Q278">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R278">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S278">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T278">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U278">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V278">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W278">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X278">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y278">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z278">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC278">
         <v>1.83</v>
@@ -45674,13 +45674,13 @@
         <v>1.98</v>
       </c>
       <c r="AE278">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF278">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG278">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK278">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45795,55 +45795,55 @@
         <v>2.72</v>
       </c>
       <c r="Q279">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R279">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S279">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T279">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U279">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V279">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W279">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X279">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y279">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z279">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA279">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB279">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC279">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD279">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE279">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF279">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG279">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK279">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -46121,55 +46121,55 @@
         <v>5.49</v>
       </c>
       <c r="Q281">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R281">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S281">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T281">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U281">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V281">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W281">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X281">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y281">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z281">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA281">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB281">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC281">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AD281">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE281">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF281">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG281">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46182,10 +46182,10 @@
         </is>
       </c>
       <c r="AJ281">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK281">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46284,34 +46284,34 @@
         <v>5.25</v>
       </c>
       <c r="Q282">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R282">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S282">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T282">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U282">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V282">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W282">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X282">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y282">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z282">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA282">
         <v>1.9</v>
@@ -46320,19 +46320,19 @@
         <v>1.9</v>
       </c>
       <c r="AC282">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AD282">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE282">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF282">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG282">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK282">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -46447,34 +46447,34 @@
         <v>3.1</v>
       </c>
       <c r="Q283">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R283">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S283">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T283">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U283">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V283">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W283">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X283">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y283">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z283">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA283">
         <v>2.05</v>
@@ -46483,19 +46483,19 @@
         <v>1.8</v>
       </c>
       <c r="AC283">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD283">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE283">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF283">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG283">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK283">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46610,55 +46610,55 @@
         <v>2.2</v>
       </c>
       <c r="Q284">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R284">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S284">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T284">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U284">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V284">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W284">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y284">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z284">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC284">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD284">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE284">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF284">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG284">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK284">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46773,55 +46773,55 @@
         <v>1.62</v>
       </c>
       <c r="Q285">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R285">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S285">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T285">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U285">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V285">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W285">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X285">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y285">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z285">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA285">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB285">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC285">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD285">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE285">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF285">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG285">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK285">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46936,55 +46936,55 @@
         <v>3.06</v>
       </c>
       <c r="Q286">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R286">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S286">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T286">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U286">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="V286">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W286">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X286">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y286">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z286">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA286">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB286">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC286">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD286">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE286">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF286">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG286">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK286">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47099,55 +47099,55 @@
         <v>3.1</v>
       </c>
       <c r="Q287">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R287">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S287">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T287">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U287">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V287">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W287">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X287">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y287">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z287">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AA287">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB287">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC287">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD287">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF287">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG287">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK287">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,64 +47253,64 @@
         </is>
       </c>
       <c r="N288">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O288">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="P288">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X288">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF288">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG288">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47425,34 +47425,34 @@
         <v>2.71</v>
       </c>
       <c r="Q289">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R289">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S289">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T289">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U289">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V289">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W289">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X289">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y289">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z289">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA289">
         <v>2.3</v>
@@ -47461,19 +47461,19 @@
         <v>1.53</v>
       </c>
       <c r="AC289">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AD289">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE289">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF289">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG289">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK289">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47588,34 +47588,34 @@
         <v>3.35</v>
       </c>
       <c r="Q290">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R290">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S290">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T290">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U290">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V290">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W290">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X290">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y290">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z290">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AA290">
         <v>2.35</v>
@@ -47624,19 +47624,19 @@
         <v>1.52</v>
       </c>
       <c r="AC290">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AD290">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE290">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF290">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG290">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK290">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47751,34 +47751,34 @@
         <v>5.31</v>
       </c>
       <c r="Q291">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R291">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S291">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T291">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U291">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V291">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W291">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X291">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y291">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z291">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA291">
         <v>1.95</v>
@@ -47787,19 +47787,19 @@
         <v>1.85</v>
       </c>
       <c r="AC291">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD291">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE291">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG291">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK291">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47914,55 +47914,55 @@
         <v>3.59</v>
       </c>
       <c r="Q292">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R292">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S292">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T292">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U292">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V292">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W292">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X292">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z292">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA292">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB292">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AC292">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD292">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE292">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF292">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG292">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK292">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="O294">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="P294">
-        <v>3.34</v>
+        <v>4.58</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="O295">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="P295">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -49544,55 +49544,55 @@
         <v>2.88</v>
       </c>
       <c r="Q302">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R302">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S302">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T302">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U302">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V302">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W302">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X302">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y302">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z302">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA302">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB302">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC302">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD302">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE302">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF302">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG302">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH302" t="inlineStr">
         <is>
@@ -49605,10 +49605,10 @@
         </is>
       </c>
       <c r="AJ302">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK302">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL302">
         <v>0</v>
@@ -50033,55 +50033,55 @@
         <v>2.38</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50359,55 +50359,55 @@
         <v>2.71</v>
       </c>
       <c r="Q307">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R307">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S307">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T307">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U307">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V307">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W307">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X307">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y307">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z307">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA307">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB307">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC307">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD307">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF307">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG307">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK307">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50522,55 +50522,55 @@
         <v>2.98</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R308">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T308">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U308">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V308">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W308">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X308">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y308">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z308">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC308">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD308">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF308">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG308">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK308">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50685,55 +50685,55 @@
         <v>2.42</v>
       </c>
       <c r="Q309">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R309">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S309">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T309">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U309">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V309">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W309">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X309">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y309">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z309">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA309">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB309">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC309">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD309">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF309">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG309">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH309" t="inlineStr">
         <is>
@@ -50746,10 +50746,10 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK309">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL309">
         <v>0</v>
@@ -50848,55 +50848,55 @@
         <v>2.8</v>
       </c>
       <c r="Q310">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R310">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S310">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T310">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U310">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V310">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W310">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X310">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y310">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z310">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA310">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB310">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC310">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD310">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF310">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG310">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK310">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51011,34 +51011,34 @@
         <v>2.35</v>
       </c>
       <c r="Q311">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R311">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S311">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T311">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U311">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V311">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W311">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X311">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y311">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z311">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA311">
         <v>1.88</v>
@@ -51047,19 +51047,19 @@
         <v>1.98</v>
       </c>
       <c r="AC311">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD311">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE311">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF311">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG311">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK311">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51174,55 +51174,55 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="R312">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S312">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T312">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U312">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V312">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W312">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y312">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z312">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA312">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB312">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC312">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD312">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE312">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF312">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG312">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51337,55 +51337,55 @@
         <v>3.2</v>
       </c>
       <c r="Q313">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R313">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S313">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T313">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U313">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V313">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W313">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X313">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y313">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z313">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA313">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB313">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC313">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD313">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE313">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF313">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG313">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK313">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL313">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="P6">
-        <v>7.02</v>
+        <v>4.29</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
+        <v>2.26</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>3.25</v>
+      </c>
+      <c r="U6">
         <v>2.5</v>
       </c>
-      <c r="S6">
-        <v>1.25</v>
-      </c>
-      <c r="T6">
-        <v>3.3</v>
-      </c>
-      <c r="U6">
-        <v>2.25</v>
-      </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
+        <v>1.17</v>
+      </c>
+      <c r="Z6">
+        <v>4</v>
+      </c>
+      <c r="AA6">
+        <v>1.7</v>
+      </c>
+      <c r="AB6">
+        <v>2.12</v>
+      </c>
+      <c r="AC6">
+        <v>2.79</v>
+      </c>
+      <c r="AD6">
+        <v>1.42</v>
+      </c>
+      <c r="AE6">
         <v>1.15</v>
       </c>
-      <c r="Z6">
-        <v>4.3</v>
-      </c>
-      <c r="AA6">
-        <v>1.56</v>
-      </c>
-      <c r="AB6">
-        <v>2.22</v>
-      </c>
-      <c r="AC6">
-        <v>2.35</v>
-      </c>
-      <c r="AD6">
-        <v>1.47</v>
-      </c>
-      <c r="AE6">
-        <v>1.16</v>
-      </c>
       <c r="AF6">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="O7">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>4.29</v>
+        <v>7.02</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AB7">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AC7">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>3.08</v>
       </c>
       <c r="AA8">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
         <v>3.48</v>
@@ -2808,10 +2808,10 @@
         <v>1.12</v>
       </c>
       <c r="AF15">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="O16">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="Q16">
         <v>2.3</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
         <v>0</v>
@@ -3276,31 +3276,31 @@
         <v>0</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,31 +3732,31 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -3765,31 +3765,31 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="O26">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="Q26">
         <v>3.02</v>
@@ -4580,19 +4580,19 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB26">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="AD26">
         <v>1.29</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -6859,7 +6859,7 @@
         <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
         <v>1.36</v>
@@ -6880,7 +6880,7 @@
         <v>1.17</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
         <v>1.91</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -7025,31 +7025,31 @@
         <v>0</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>0</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
         <v>0</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="O45">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P45">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="O48">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="P48">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="Q48">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R48">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="S48">
         <v>1.22</v>
@@ -8154,25 +8154,25 @@
         <v>3.55</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V48">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W48">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X48">
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
-        <v>5.94</v>
+        <v>5.76</v>
       </c>
       <c r="AA48">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB48">
         <v>2.7</v>
@@ -8184,13 +8184,13 @@
         <v>1.68</v>
       </c>
       <c r="AE48">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF48">
         <v>1.4</v>
       </c>
       <c r="AG48">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O49">
         <v>3.7</v>
       </c>
       <c r="P49">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="Q49">
         <v>2.34</v>
@@ -8350,10 +8350,10 @@
         <v>1.29</v>
       </c>
       <c r="AF49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG49">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="O51">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O55">
-        <v>3.76</v>
+        <v>3.52</v>
       </c>
       <c r="P55">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="Q55">
         <v>2.5</v>
@@ -9298,7 +9298,7 @@
         <v>2.97</v>
       </c>
       <c r="V55">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
         <v>1.04</v>
@@ -9307,16 +9307,16 @@
         <v>1</v>
       </c>
       <c r="Y55">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z55">
         <v>3.2</v>
       </c>
       <c r="AA55">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AB55">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AC55">
         <v>3.44</v>
@@ -9347,7 +9347,7 @@
         <v>1.23</v>
       </c>
       <c r="AK55">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>3.98</v>
       </c>
       <c r="AA67">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB67">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AC67">
         <v>2.62</v>
@@ -11565,55 +11565,55 @@
         <v>2.09</v>
       </c>
       <c r="Q69">
-        <v>3.83</v>
+        <v>3.64</v>
       </c>
       <c r="R69">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S69">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="U69">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="V69">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W69">
         <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA69">
         <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC69">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD69">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF69">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG69">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.23</v>
       </c>
       <c r="AK69">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11761,7 +11761,7 @@
         <v>2.08</v>
       </c>
       <c r="AB70">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC70">
         <v>3.7</v>
@@ -11894,31 +11894,31 @@
         <v>2.35</v>
       </c>
       <c r="R71">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U71">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V71">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z71">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA71">
         <v>1.79</v>
@@ -11933,13 +11933,13 @@
         <v>1.34</v>
       </c>
       <c r="AE71">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF71">
         <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK71">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.61</v>
+        <v>2.26</v>
       </c>
       <c r="O75">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="P75">
-        <v>4.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q75">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="R75">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="S75">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="V75">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z75">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="AA75">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AB75">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD75">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE75">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF75">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG75">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK75">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.26</v>
+        <v>1.61</v>
       </c>
       <c r="O76">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="P76">
-        <v>2.72</v>
+        <v>4.64</v>
       </c>
       <c r="Q76">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="R76">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S76">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="V76">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W76">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
         <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z76">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="AA76">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AB76">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="AC76">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD76">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
+        <v>1.22</v>
+      </c>
+      <c r="AF76">
+        <v>1.5</v>
+      </c>
+      <c r="AG76">
+        <v>2.38</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.25</v>
       </c>
-      <c r="AF76">
-        <v>1.4</v>
-      </c>
-      <c r="AG76">
-        <v>2.7</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.4</v>
-      </c>
       <c r="AK76">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
         <v>0</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="O86">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P86">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="Q86">
-        <v>3.77</v>
+        <v>3.39</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S86">
         <v>1.43</v>
@@ -14348,10 +14348,10 @@
         <v>2.71</v>
       </c>
       <c r="U86">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V86">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W86">
         <v>1.01</v>
@@ -14360,10 +14360,10 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z86">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AA86">
         <v>2.17</v>
@@ -14372,10 +14372,10 @@
         <v>1.67</v>
       </c>
       <c r="AC86">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="AD86">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE86">
         <v>1.02</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK86">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>2.49</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O106">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P106">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q106">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="R106">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S106">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="U106">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="V106">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z106">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="AA106">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB106">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AC106">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD106">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE106">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG106">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK106">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O107">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P107">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q107">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="R107">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T107">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="U107">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W107">
+        <v>1.05</v>
+      </c>
+      <c r="X107">
+        <v>1.02</v>
+      </c>
+      <c r="Y107">
+        <v>1.3</v>
+      </c>
+      <c r="Z107">
+        <v>2.97</v>
+      </c>
+      <c r="AA107">
+        <v>2.02</v>
+      </c>
+      <c r="AB107">
+        <v>1.68</v>
+      </c>
+      <c r="AC107">
+        <v>3.5</v>
+      </c>
+      <c r="AD107">
+        <v>1.22</v>
+      </c>
+      <c r="AE107">
         <v>1.04</v>
       </c>
-      <c r="X107">
-        <v>1.01</v>
-      </c>
-      <c r="Y107">
-        <v>1.24</v>
-      </c>
-      <c r="Z107">
-        <v>3.34</v>
-      </c>
-      <c r="AA107">
-        <v>1.85</v>
-      </c>
-      <c r="AB107">
-        <v>1.82</v>
-      </c>
-      <c r="AC107">
-        <v>3.08</v>
-      </c>
-      <c r="AD107">
+      <c r="AF107">
+        <v>1.76</v>
+      </c>
+      <c r="AG107">
+        <v>1.91</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.28</v>
       </c>
-      <c r="AE107">
-        <v>1.06</v>
-      </c>
-      <c r="AF107">
-        <v>1.65</v>
-      </c>
-      <c r="AG107">
-        <v>2.07</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.26</v>
-      </c>
       <c r="AK107">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA134">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB134">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O135">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P135">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q135">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R135">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S135">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T135">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U135">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V135">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W135">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y135">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z135">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA135">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB135">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AC135">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD135">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE135">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF135">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG135">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK135">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -25420,55 +25420,55 @@
         <v>0</v>
       </c>
       <c r="Q154">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S154">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T154">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y154">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z154">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA154">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB154">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF154">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG154">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK154">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S188">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T188">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U188">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V188">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W188">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X188">
         <v>0</v>
       </c>
       <c r="Y188">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z188">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA188">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB188">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC188">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD188">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE188">
         <v>0</v>
       </c>
       <c r="AF188">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG188">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK188">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R198">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T198">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U198">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V198">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W198">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X198">
         <v>0</v>
       </c>
       <c r="Y198">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z198">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC198">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD198">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE198">
         <v>0</v>
       </c>
       <c r="AF198">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG198">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK198">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R200">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S200">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T200">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U200">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V200">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W200">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X200">
         <v>0</v>
       </c>
       <c r="Y200">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z200">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA200">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB200">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC200">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD200">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE200">
         <v>0</v>
       </c>
       <c r="AF200">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG200">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK200">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O201">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R201">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T201">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U201">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W201">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X201">
         <v>0</v>
       </c>
       <c r="Y201">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z201">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA201">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB201">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC201">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD201">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE201">
         <v>0</v>
       </c>
       <c r="AF201">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG201">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK201">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33274,10 +33274,10 @@
         <v>0</v>
       </c>
       <c r="AA202">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB202">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC202">
         <v>0</v>
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="O248">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="P248">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R248">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S248">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T248">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U248">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V248">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W248">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X248">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z248">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA248">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB248">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC248">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD248">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE248">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF248">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG248">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK248">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,64 +40896,64 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O249">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="P249">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q249">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R249">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S249">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T249">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="U249">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="V249">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W249">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X249">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y249">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z249">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA249">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB249">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AC249">
-        <v>2.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD249">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE249">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF249">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG249">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK249">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41231,55 +41231,55 @@
         <v>0</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA251">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB251">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45958,55 +45958,55 @@
         <v>0</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA280">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB280">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,80 +47579,80 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.17</v>
+        <v>1.59</v>
       </c>
       <c r="O290">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="P290">
-        <v>3.35</v>
+        <v>5.31</v>
       </c>
       <c r="Q290">
-        <v>2.85</v>
+        <v>2.12</v>
       </c>
       <c r="R290">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="S290">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T290">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U290">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="V290">
+        <v>1.42</v>
+      </c>
+      <c r="W290">
+        <v>1.08</v>
+      </c>
+      <c r="X290">
+        <v>1.01</v>
+      </c>
+      <c r="Y290">
         <v>1.28</v>
       </c>
-      <c r="W290">
-        <v>1.02</v>
-      </c>
-      <c r="X290">
-        <v>1.05</v>
-      </c>
-      <c r="Y290">
-        <v>1.43</v>
-      </c>
       <c r="Z290">
-        <v>2.79</v>
+        <v>3.62</v>
       </c>
       <c r="AA290">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AB290">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC290">
-        <v>4.41</v>
+        <v>3.16</v>
       </c>
       <c r="AD290">
+        <v>1.35</v>
+      </c>
+      <c r="AE290">
+        <v>1.07</v>
+      </c>
+      <c r="AF290">
+        <v>1.85</v>
+      </c>
+      <c r="AG290">
+        <v>1.83</v>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ290">
         <v>1.2</v>
       </c>
-      <c r="AE290">
-        <v>1.02</v>
-      </c>
-      <c r="AF290">
-        <v>1.98</v>
-      </c>
-      <c r="AG290">
-        <v>1.75</v>
-      </c>
-      <c r="AH290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI290" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ290">
-        <v>1.36</v>
-      </c>
       <c r="AK290">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.59</v>
+        <v>2.17</v>
       </c>
       <c r="O291">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="P291">
-        <v>5.31</v>
+        <v>3.35</v>
       </c>
       <c r="Q291">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="R291">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="S291">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T291">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U291">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="V291">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W291">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X291">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y291">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="Z291">
-        <v>3.62</v>
+        <v>2.79</v>
       </c>
       <c r="AA291">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB291">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AC291">
-        <v>3.16</v>
+        <v>4.41</v>
       </c>
       <c r="AD291">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AE291">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF291">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG291">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK291">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q296">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -644,55 +644,55 @@
         <v>4.24</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
         <v>2.1</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA2">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AC2">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
         <v>2.06</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O3">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Q3">
         <v>3.58</v>
@@ -837,10 +837,10 @@
         <v>3.04</v>
       </c>
       <c r="AA3">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AB3">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
         <v>3.42</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O4">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>7.19</v>
+        <v>5.75</v>
       </c>
       <c r="Q4">
         <v>1.75</v>
       </c>
       <c r="R4">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="S4">
         <v>1.22</v>
@@ -997,28 +997,28 @@
         <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB4">
         <v>2.35</v>
       </c>
       <c r="AC4">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG4">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AK4">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O5">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="P5">
-        <v>3.64</v>
+        <v>3.23</v>
       </c>
       <c r="Q5">
         <v>2.5</v>
@@ -1163,10 +1163,10 @@
         <v>3.4</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC5">
         <v>3.08</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
         <v>1.79</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4.29</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>7.02</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
+        <v>2.26</v>
+      </c>
+      <c r="S7">
+        <v>1.29</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
         <v>2.5</v>
       </c>
-      <c r="S7">
-        <v>1.25</v>
-      </c>
-      <c r="T7">
-        <v>3.3</v>
-      </c>
-      <c r="U7">
-        <v>2.25</v>
-      </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>3.96</v>
+      </c>
+      <c r="AA7">
+        <v>1.7</v>
+      </c>
+      <c r="AB7">
+        <v>2.12</v>
+      </c>
+      <c r="AC7">
+        <v>2.62</v>
+      </c>
+      <c r="AD7">
+        <v>1.42</v>
+      </c>
+      <c r="AE7">
         <v>1.15</v>
       </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.56</v>
-      </c>
-      <c r="AB7">
-        <v>2.22</v>
-      </c>
-      <c r="AC7">
-        <v>2.35</v>
-      </c>
-      <c r="AD7">
-        <v>1.47</v>
-      </c>
-      <c r="AE7">
-        <v>1.16</v>
-      </c>
       <c r="AF7">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="O9">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>5.02</v>
+        <v>3.95</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -1794,7 +1794,7 @@
         <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="U9">
         <v>2.96</v>
@@ -1815,7 +1815,7 @@
         <v>3.23</v>
       </c>
       <c r="AA9">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB9">
         <v>1.69</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="R10">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="S10">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="Z10">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="AA10">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AC10">
-        <v>4.4</v>
+        <v>3.42</v>
       </c>
       <c r="AD10">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK10">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="O11">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
-        <v>3.54</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>2.07</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>2.74</v>
+        <v>3.6</v>
       </c>
       <c r="U11">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
         <v>1.02</v>
       </c>
-      <c r="X11">
-        <v>1.04</v>
-      </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="AA11">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD11">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.59</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="T12">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="U12">
+        <v>3.3</v>
+      </c>
+      <c r="V12">
+        <v>1.29</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>1.05</v>
+      </c>
+      <c r="Y12">
+        <v>1.43</v>
+      </c>
+      <c r="Z12">
+        <v>2.46</v>
+      </c>
+      <c r="AA12">
         <v>2.4</v>
       </c>
-      <c r="V12">
-        <v>1.5</v>
-      </c>
-      <c r="W12">
-        <v>1.11</v>
-      </c>
-      <c r="X12">
-        <v>1.02</v>
-      </c>
-      <c r="Y12">
-        <v>1.16</v>
-      </c>
-      <c r="Z12">
-        <v>4.15</v>
-      </c>
-      <c r="AA12">
+      <c r="AB12">
+        <v>1.53</v>
+      </c>
+      <c r="AC12">
+        <v>4.4</v>
+      </c>
+      <c r="AD12">
+        <v>1.14</v>
+      </c>
+      <c r="AE12">
+        <v>1.01</v>
+      </c>
+      <c r="AF12">
+        <v>2.02</v>
+      </c>
+      <c r="AG12">
+        <v>1.71</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.33</v>
+      </c>
+      <c r="AK12">
         <v>1.62</v>
-      </c>
-      <c r="AB12">
-        <v>2.07</v>
-      </c>
-      <c r="AC12">
-        <v>2.43</v>
-      </c>
-      <c r="AD12">
-        <v>1.44</v>
-      </c>
-      <c r="AE12">
-        <v>1.15</v>
-      </c>
-      <c r="AF12">
-        <v>1.66</v>
-      </c>
-      <c r="AG12">
-        <v>2.09</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.2</v>
-      </c>
-      <c r="AK12">
-        <v>2.29</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="O13">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.3</v>
@@ -2461,25 +2461,25 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB13">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD13">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.82</v>
+        <v>4.59</v>
       </c>
       <c r="Q19">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
+        <v>1.29</v>
+      </c>
+      <c r="Z19">
+        <v>3.04</v>
+      </c>
+      <c r="AA19">
+        <v>2.05</v>
+      </c>
+      <c r="AB19">
+        <v>1.7</v>
+      </c>
+      <c r="AC19">
+        <v>3.5</v>
+      </c>
+      <c r="AD19">
         <v>1.22</v>
       </c>
-      <c r="Z19">
-        <v>3.5</v>
-      </c>
-      <c r="AA19">
-        <v>1.79</v>
-      </c>
-      <c r="AB19">
-        <v>1.88</v>
-      </c>
-      <c r="AC19">
-        <v>2.97</v>
-      </c>
-      <c r="AD19">
-        <v>1.3</v>
-      </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="O20">
+        <v>3.3</v>
+      </c>
+      <c r="P20">
+        <v>2.82</v>
+      </c>
+      <c r="Q20">
+        <v>2.83</v>
+      </c>
+      <c r="R20">
+        <v>2.13</v>
+      </c>
+      <c r="S20">
+        <v>1.3</v>
+      </c>
+      <c r="T20">
+        <v>3.2</v>
+      </c>
+      <c r="U20">
+        <v>2.48</v>
+      </c>
+      <c r="V20">
+        <v>1.43</v>
+      </c>
+      <c r="W20">
+        <v>1.08</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.22</v>
+      </c>
+      <c r="Z20">
         <v>3.5</v>
       </c>
-      <c r="P20">
-        <v>4.59</v>
-      </c>
-      <c r="Q20">
-        <v>2.21</v>
-      </c>
-      <c r="R20">
-        <v>2.1</v>
-      </c>
-      <c r="S20">
-        <v>1.38</v>
-      </c>
-      <c r="T20">
-        <v>2.64</v>
-      </c>
-      <c r="U20">
-        <v>2.89</v>
-      </c>
-      <c r="V20">
-        <v>1.32</v>
-      </c>
-      <c r="W20">
-        <v>1.05</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.29</v>
-      </c>
-      <c r="Z20">
-        <v>3.04</v>
-      </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AC20">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK20">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,43 +4058,43 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA23">
         <v>1.8</v>
@@ -4103,19 +4103,19 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q24">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC24">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.18</v>
+        <v>2.79</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q25">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="R25">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S25">
         <v>1.18</v>
@@ -4405,10 +4405,10 @@
         <v>4.25</v>
       </c>
       <c r="U25">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V25">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="W25">
         <v>1.25</v>
@@ -4420,22 +4420,22 @@
         <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="AA25">
         <v>1.28</v>
       </c>
       <c r="AB25">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC25">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AD25">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE25">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AF25">
         <v>1.33</v>
@@ -4457,7 +4457,7 @@
         <v>1.08</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="P30">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>2.63</v>
       </c>
       <c r="Q32">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R32">
         <v>2</v>
@@ -5552,10 +5552,10 @@
         <v>1.3</v>
       </c>
       <c r="W32">
+        <v>1.05</v>
+      </c>
+      <c r="X32">
         <v>1.04</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.32</v>
@@ -5576,7 +5576,7 @@
         <v>1.2</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF32">
         <v>1.82</v>
@@ -5715,10 +5715,10 @@
         <v>1.33</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y33">
         <v>1.34</v>
@@ -5739,7 +5739,7 @@
         <v>1.2</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
         <v>2.17</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>2.27</v>
@@ -5866,19 +5866,19 @@
         <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V34">
         <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.04</v>
@@ -5890,10 +5890,10 @@
         <v>3.72</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC34">
         <v>2.88</v>
@@ -5908,7 +5908,7 @@
         <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,28 +6023,28 @@
         <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R35">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S35">
         <v>1.38</v>
       </c>
       <c r="T35">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
         <v>1.04</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.32</v>
@@ -6056,7 +6056,7 @@
         <v>2.15</v>
       </c>
       <c r="AB35">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AC35">
         <v>3.86</v>
@@ -6065,13 +6065,13 @@
         <v>1.18</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
         <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,28 +6186,28 @@
         <v>2.32</v>
       </c>
       <c r="Q36">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.28</v>
@@ -6216,7 +6216,7 @@
         <v>3.08</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB36">
         <v>1.8</v>
@@ -6228,13 +6228,13 @@
         <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
         <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6838,28 +6838,28 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V40">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W40">
         <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
         <v>1.36</v>
@@ -6880,7 +6880,7 @@
         <v>1.17</v>
       </c>
       <c r="AE40">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
         <v>1.91</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="O47">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q47">
         <v>2.18</v>
@@ -7988,13 +7988,13 @@
         <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="V47">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
         <v>1.08</v>
@@ -8794,7 +8794,7 @@
         <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="R52">
         <v>2.21</v>
@@ -8824,10 +8824,10 @@
         <v>3.4</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB52">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC52">
         <v>3.4</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,28 +8957,28 @@
         <v>3.59</v>
       </c>
       <c r="Q53">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R53">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S53">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U53">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="V53">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
         <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
         <v>1.3</v>
@@ -8987,10 +8987,10 @@
         <v>2.97</v>
       </c>
       <c r="AA53">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB53">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC53">
         <v>3.5</v>
@@ -8999,13 +8999,13 @@
         <v>1.22</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
         <v>1.83</v>
       </c>
       <c r="AG53">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>13</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sisaket United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="O59">
         <v>3.5</v>
       </c>
       <c r="P59">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R59">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S59">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U59">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V59">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y59">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="Z59">
-        <v>3.2</v>
+        <v>3.96</v>
       </c>
       <c r="AA59">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AB59">
-        <v>1.76</v>
+        <v>2.08</v>
       </c>
       <c r="AC59">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="AD59">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE59">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF59">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AG59">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Sisaket United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="O60">
         <v>3.5</v>
       </c>
       <c r="P60">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q60">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="R60">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U60">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="Z60">
-        <v>3.96</v>
+        <v>3.2</v>
       </c>
       <c r="AA60">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AB60">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="AC60">
-        <v>2.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD60">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE60">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF60">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG60">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10285,7 +10285,7 @@
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
         <v>5.4</v>
@@ -10424,13 +10424,13 @@
         <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R62">
         <v>2.1</v>
       </c>
       <c r="S62">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
         <v>3</v>
@@ -10472,7 +10472,7 @@
         <v>1.7</v>
       </c>
       <c r="AG62">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O63">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="Q63">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
         <v>1.22</v>
@@ -10620,7 +10620,7 @@
         <v>1.55</v>
       </c>
       <c r="AB63">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AC63">
         <v>2.42</v>
@@ -10934,7 +10934,7 @@
         <v>1.06</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
         <v>1.28</v>
@@ -10943,10 +10943,10 @@
         <v>3.05</v>
       </c>
       <c r="AA65">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB65">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC65">
         <v>3.28</v>
@@ -10955,13 +10955,13 @@
         <v>1.25</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF65">
         <v>2.21</v>
       </c>
       <c r="AG65">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="O66">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
       <c r="P66">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Q66">
         <v>1.82</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
         <v>1.91</v>
@@ -12211,7 +12211,7 @@
         <v>2.1</v>
       </c>
       <c r="O73">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
         <v>2.7</v>
@@ -12223,10 +12223,10 @@
         <v>2.6</v>
       </c>
       <c r="S73">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T73">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U73">
         <v>1.98</v>
@@ -12247,10 +12247,10 @@
         <v>5.95</v>
       </c>
       <c r="AA73">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB73">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AC73">
         <v>1.92</v>
@@ -12262,7 +12262,7 @@
         <v>1.29</v>
       </c>
       <c r="AF73">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG73">
         <v>2.9</v>
@@ -12374,10 +12374,10 @@
         <v>2.33</v>
       </c>
       <c r="O74">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="P74">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -12395,7 +12395,7 @@
         <v>2.28</v>
       </c>
       <c r="V74">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W74">
         <v>1.17</v>
@@ -12416,10 +12416,10 @@
         <v>2.47</v>
       </c>
       <c r="AC74">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AD74">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AE74">
         <v>1.22</v>
@@ -12558,7 +12558,7 @@
         <v>2.02</v>
       </c>
       <c r="V75">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W75">
         <v>1.17</v>
@@ -12579,10 +12579,10 @@
         <v>2.7</v>
       </c>
       <c r="AC75">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AD75">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE75">
         <v>1.25</v>
@@ -12591,7 +12591,7 @@
         <v>1.4</v>
       </c>
       <c r="AG75">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="O76">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P76">
-        <v>4.64</v>
+        <v>4.33</v>
       </c>
       <c r="Q76">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="R76">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="S76">
         <v>1.22</v>
@@ -12742,10 +12742,10 @@
         <v>2.28</v>
       </c>
       <c r="AC76">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE76">
         <v>1.22</v>
@@ -12770,7 +12770,7 @@
         <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14004,13 +14004,13 @@
         <v>1.98</v>
       </c>
       <c r="O84">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P84">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="Q84">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="R84">
         <v>2.35</v>
@@ -14022,10 +14022,10 @@
         <v>4</v>
       </c>
       <c r="U84">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V84">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14034,25 +14034,25 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z84">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="AA84">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB84">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AC84">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="AD84">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE84">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF84">
         <v>1.42</v>
@@ -14074,7 +14074,7 @@
         <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14203,7 +14203,7 @@
         <v>3.19</v>
       </c>
       <c r="AA85">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB85">
         <v>1.75</v>
@@ -14659,7 +14659,7 @@
         <v>3.1</v>
       </c>
       <c r="P88">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q88">
         <v>3.54</v>
@@ -14680,7 +14680,7 @@
         <v>1.37</v>
       </c>
       <c r="W88">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
         <v>1</v>
@@ -14988,7 +14988,7 @@
         <v>3.5</v>
       </c>
       <c r="Q90">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R90">
         <v>2.2</v>
@@ -15000,7 +15000,7 @@
         <v>3.4</v>
       </c>
       <c r="U90">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="V90">
         <v>1.51</v>
@@ -15036,7 +15036,7 @@
         <v>1.57</v>
       </c>
       <c r="AG90">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="O91">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q91">
         <v>2.68</v>
@@ -15175,22 +15175,22 @@
         <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z91">
         <v>4.15</v>
       </c>
       <c r="AA91">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB91">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AC91">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AD91">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE91">
         <v>1.15</v>
@@ -15215,7 +15215,7 @@
         <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O92">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -15338,10 +15338,10 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z92">
-        <v>4.19</v>
+        <v>3.84</v>
       </c>
       <c r="AA92">
         <v>1.7</v>
@@ -15359,10 +15359,10 @@
         <v>1.16</v>
       </c>
       <c r="AF92">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG92">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O94">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
       <c r="Q94">
         <v>3</v>
@@ -15676,7 +15676,7 @@
         <v>2.25</v>
       </c>
       <c r="AC94">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD94">
         <v>1.57</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK94">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="O95">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P95">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q95">
         <v>4</v>
@@ -15830,25 +15830,25 @@
         <v>1.13</v>
       </c>
       <c r="Z95">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="AA95">
         <v>1.47</v>
       </c>
       <c r="AB95">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AC95">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AD95">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE95">
         <v>1.22</v>
       </c>
       <c r="AF95">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG95">
         <v>2.55</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,31 +17424,31 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="O105">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P105">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q105">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="R105">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S105">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="U105">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="V105">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W105">
         <v>1.04</v>
@@ -17457,31 +17457,31 @@
         <v>1.01</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z105">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA105">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB105">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC105">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE105">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK105">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,80 +17587,80 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O106">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="P106">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q106">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="R106">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T106">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="U106">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W106">
+        <v>1.05</v>
+      </c>
+      <c r="X106">
+        <v>1.02</v>
+      </c>
+      <c r="Y106">
+        <v>1.3</v>
+      </c>
+      <c r="Z106">
+        <v>2.97</v>
+      </c>
+      <c r="AA106">
+        <v>2.02</v>
+      </c>
+      <c r="AB106">
+        <v>1.68</v>
+      </c>
+      <c r="AC106">
+        <v>3.5</v>
+      </c>
+      <c r="AD106">
+        <v>1.22</v>
+      </c>
+      <c r="AE106">
         <v>1.04</v>
       </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.24</v>
-      </c>
-      <c r="Z106">
-        <v>3.34</v>
-      </c>
-      <c r="AA106">
-        <v>1.85</v>
-      </c>
-      <c r="AB106">
-        <v>1.82</v>
-      </c>
-      <c r="AC106">
-        <v>3.08</v>
-      </c>
-      <c r="AD106">
+      <c r="AF106">
+        <v>1.76</v>
+      </c>
+      <c r="AG106">
+        <v>1.91</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ106">
         <v>1.28</v>
       </c>
-      <c r="AE106">
-        <v>1.06</v>
-      </c>
-      <c r="AF106">
-        <v>1.65</v>
-      </c>
-      <c r="AG106">
-        <v>2.07</v>
-      </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ106">
-        <v>1.26</v>
-      </c>
       <c r="AK106">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,80 +17750,80 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.65</v>
+        <v>1.81</v>
       </c>
       <c r="O107">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="P107">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="Q107">
-        <v>3.24</v>
+        <v>2.37</v>
       </c>
       <c r="R107">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="S107">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T107">
-        <v>2.61</v>
+        <v>2.76</v>
       </c>
       <c r="U107">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="V107">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W107">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X107">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
+        <v>1.22</v>
+      </c>
+      <c r="Z107">
+        <v>3.5</v>
+      </c>
+      <c r="AA107">
+        <v>1.81</v>
+      </c>
+      <c r="AB107">
+        <v>1.86</v>
+      </c>
+      <c r="AC107">
+        <v>2.97</v>
+      </c>
+      <c r="AD107">
         <v>1.3</v>
       </c>
-      <c r="Z107">
-        <v>2.97</v>
-      </c>
-      <c r="AA107">
-        <v>2.02</v>
-      </c>
-      <c r="AB107">
-        <v>1.68</v>
-      </c>
-      <c r="AC107">
-        <v>3.5</v>
-      </c>
-      <c r="AD107">
+      <c r="AE107">
+        <v>1.07</v>
+      </c>
+      <c r="AF107">
+        <v>1.72</v>
+      </c>
+      <c r="AG107">
+        <v>1.96</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ107">
         <v>1.22</v>
       </c>
-      <c r="AE107">
-        <v>1.04</v>
-      </c>
-      <c r="AF107">
-        <v>1.76</v>
-      </c>
-      <c r="AG107">
-        <v>1.91</v>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ107">
-        <v>1.28</v>
-      </c>
       <c r="AK107">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -21529,7 +21529,7 @@
         <v>1.24</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
         <v>1.07</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="O134">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P134">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q134">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R134">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S134">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T134">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U134">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V134">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W134">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y134">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z134">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB134">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AC134">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AD134">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE134">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF134">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG134">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK134">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA135">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AB135">
-        <v>2.5</v>
+        <v>2.07</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22486,55 +22486,55 @@
         <v>4.2</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22806,10 +22806,10 @@
         <v>1.33</v>
       </c>
       <c r="O138">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P138">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="Q138">
         <v>1.82</v>
@@ -22848,10 +22848,10 @@
         <v>2.25</v>
       </c>
       <c r="AC138">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AD138">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE138">
         <v>1.17</v>
@@ -25248,55 +25248,55 @@
         </is>
       </c>
       <c r="N153">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O153">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="P153">
-        <v>4.78</v>
+        <v>4.44</v>
       </c>
       <c r="Q153">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="R153">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="S153">
         <v>1.22</v>
       </c>
       <c r="T153">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="U153">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V153">
         <v>1.66</v>
       </c>
       <c r="W153">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X153">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z153">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA153">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB153">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="AC153">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD153">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE153">
         <v>1.25</v>
@@ -25305,7 +25305,7 @@
         <v>1.48</v>
       </c>
       <c r="AG153">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK153">
         <v>2.21</v>
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q154">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S154">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T154">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="U154">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V154">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W154">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X154">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y154">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z154">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA154">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB154">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC154">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AD154">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE154">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF154">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG154">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK154">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -28019,37 +28019,37 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="O170">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="P170">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="Q170">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="R170">
         <v>2.4</v>
       </c>
       <c r="S170">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T170">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U170">
         <v>2.3</v>
       </c>
       <c r="V170">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W170">
         <v>1.11</v>
       </c>
       <c r="X170">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y170">
         <v>1.2</v>
@@ -28061,7 +28061,7 @@
         <v>1.67</v>
       </c>
       <c r="AB170">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC170">
         <v>2.65</v>
@@ -28070,13 +28070,13 @@
         <v>1.41</v>
       </c>
       <c r="AE170">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF170">
         <v>1.7</v>
       </c>
       <c r="AG170">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK170">
         <v>2.18</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,64 +31279,64 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="O190">
-        <v>3.87</v>
+        <v>3.71</v>
       </c>
       <c r="P190">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="Q190">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="R190">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="S190">
         <v>1.22</v>
       </c>
       <c r="T190">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U190">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="V190">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="W190">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X190">
         <v>1.01</v>
       </c>
       <c r="Y190">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="Z190">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AA190">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AB190">
-        <v>2.74</v>
+        <v>2.37</v>
       </c>
       <c r="AC190">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AD190">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AE190">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF190">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AG190">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="O191">
-        <v>3.71</v>
+        <v>3.87</v>
       </c>
       <c r="P191">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q191">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="R191">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="S191">
         <v>1.22</v>
       </c>
       <c r="T191">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U191">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="V191">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="W191">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X191">
         <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z191">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AA191">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AB191">
-        <v>2.37</v>
+        <v>2.74</v>
       </c>
       <c r="AC191">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="AD191">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AE191">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF191">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AG191">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G193">
@@ -31777,55 +31777,55 @@
         <v>0</v>
       </c>
       <c r="Q193">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R193">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S193">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T193">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U193">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V193">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W193">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X193">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y193">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z193">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA193">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB193">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC193">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD193">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE193">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF193">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG193">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK193">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G194">
@@ -31940,55 +31940,55 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S194">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T194">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U194">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V194">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W194">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X194">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y194">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z194">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA194">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB194">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC194">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD194">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE194">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF194">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG194">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK194">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -36993,34 +36993,34 @@
         <v>1.62</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R225">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S225">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T225">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U225">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V225">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W225">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X225">
         <v>0</v>
       </c>
       <c r="Y225">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z225">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA225">
         <v>2.25</v>
@@ -37029,19 +37029,19 @@
         <v>1.61</v>
       </c>
       <c r="AC225">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD225">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE225">
         <v>0</v>
       </c>
       <c r="AF225">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG225">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK225">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37482,55 +37482,55 @@
         <v>0</v>
       </c>
       <c r="Q228">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R228">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S228">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T228">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U228">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V228">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W228">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y228">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z228">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AA228">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB228">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC228">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD228">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE228">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF228">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG228">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK228">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37645,55 +37645,55 @@
         <v>0</v>
       </c>
       <c r="Q229">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R229">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S229">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T229">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U229">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V229">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W229">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X229">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y229">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z229">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA229">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB229">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC229">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD229">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE229">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF229">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG229">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK229">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,43 +38125,43 @@
         </is>
       </c>
       <c r="N232">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="O232">
+        <v>3.08</v>
+      </c>
+      <c r="P232">
         <v>3.24</v>
       </c>
-      <c r="P232">
-        <v>3.93</v>
-      </c>
       <c r="Q232">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="R232">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="S232">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T232">
-        <v>2.57</v>
+        <v>2.69</v>
       </c>
       <c r="U232">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="V232">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W232">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X232">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y232">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z232">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA232">
         <v>1.96</v>
@@ -38170,19 +38170,19 @@
         <v>1.72</v>
       </c>
       <c r="AC232">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AD232">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE232">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF232">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG232">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK232">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,43 +38288,43 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O233">
-        <v>3.08</v>
+        <v>3.24</v>
       </c>
       <c r="P233">
-        <v>3.24</v>
+        <v>3.93</v>
       </c>
       <c r="Q233">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="R233">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="S233">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T233">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="U233">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="V233">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W233">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X233">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z233">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AA233">
         <v>1.96</v>
@@ -38333,19 +38333,19 @@
         <v>1.72</v>
       </c>
       <c r="AC233">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD233">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE233">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF233">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG233">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK233">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38451,19 +38451,19 @@
         </is>
       </c>
       <c r="N234">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="O234">
-        <v>4.42</v>
+        <v>3.9</v>
       </c>
       <c r="P234">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q234">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="R234">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S234">
         <v>1.2</v>
@@ -38487,28 +38487,28 @@
         <v>1.06</v>
       </c>
       <c r="Z234">
-        <v>6.15</v>
+        <v>7</v>
       </c>
       <c r="AA234">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AB234">
         <v>2.84</v>
       </c>
       <c r="AC234">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AD234">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE234">
         <v>1.34</v>
       </c>
       <c r="AF234">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG234">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK234">
         <v>1.38</v>
@@ -40081,64 +40081,64 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R244">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S244">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T244">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U244">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V244">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W244">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y244">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z244">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC244">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD244">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE244">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF244">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG244">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH244" t="inlineStr">
         <is>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK244">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -41222,64 +41222,64 @@
         </is>
       </c>
       <c r="N251">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O251">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P251">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q251">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R251">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S251">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T251">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U251">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V251">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W251">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y251">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z251">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA251">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB251">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC251">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD251">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE251">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF251">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG251">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK251">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -44491,34 +44491,34 @@
         <v>1.7</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X271">
         <v>0</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA271">
         <v>2</v>
@@ -44527,19 +44527,19 @@
         <v>1.8</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE271">
         <v>0</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,31 +45460,31 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="O277">
-        <v>5.32</v>
+        <v>6.15</v>
       </c>
       <c r="P277">
-        <v>7.26</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q277">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="R277">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="S277">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T277">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U277">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V277">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W277">
         <v>1.22</v>
@@ -45493,16 +45493,16 @@
         <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z277">
-        <v>6.15</v>
+        <v>6.7</v>
       </c>
       <c r="AA277">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AB277">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AC277">
         <v>1.83</v>
@@ -45511,13 +45511,13 @@
         <v>1.98</v>
       </c>
       <c r="AE277">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF277">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG277">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK277">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,31 +45623,31 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="O278">
-        <v>6.15</v>
+        <v>5.32</v>
       </c>
       <c r="P278">
-        <v>8.449999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="Q278">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="R278">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="S278">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T278">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U278">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="V278">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W278">
         <v>1.22</v>
@@ -45656,16 +45656,16 @@
         <v>1.01</v>
       </c>
       <c r="Y278">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z278">
-        <v>6.7</v>
+        <v>6.15</v>
       </c>
       <c r="AA278">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AB278">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AC278">
         <v>1.83</v>
@@ -45674,13 +45674,13 @@
         <v>1.98</v>
       </c>
       <c r="AE278">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF278">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG278">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK278">
-        <v>3.48</v>
+        <v>2.4</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45949,64 +45949,64 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q280">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R280">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S280">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T280">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U280">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V280">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W280">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X280">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y280">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z280">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA280">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB280">
         <v>1.8</v>
       </c>
       <c r="AC280">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD280">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE280">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF280">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG280">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK280">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL280">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>7.02</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
+        <v>2.26</v>
+      </c>
+      <c r="S7">
+        <v>1.29</v>
+      </c>
+      <c r="T7">
+        <v>3.25</v>
+      </c>
+      <c r="U7">
         <v>2.5</v>
       </c>
-      <c r="S7">
-        <v>1.25</v>
-      </c>
-      <c r="T7">
-        <v>3.24</v>
-      </c>
-      <c r="U7">
-        <v>2.25</v>
-      </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>3.96</v>
+      </c>
+      <c r="AA7">
+        <v>1.7</v>
+      </c>
+      <c r="AB7">
+        <v>2.12</v>
+      </c>
+      <c r="AC7">
+        <v>2.62</v>
+      </c>
+      <c r="AD7">
+        <v>1.42</v>
+      </c>
+      <c r="AE7">
         <v>1.15</v>
       </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.57</v>
-      </c>
-      <c r="AB7">
-        <v>2.25</v>
-      </c>
-      <c r="AC7">
-        <v>2.38</v>
-      </c>
-      <c r="AD7">
-        <v>1.46</v>
-      </c>
-      <c r="AE7">
-        <v>1.16</v>
-      </c>
       <c r="AF7">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="O8">
         <v>3.25</v>
@@ -2772,7 +2772,7 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U15">
         <v>2.42</v>
@@ -2920,7 +2920,7 @@
         <v>1.83</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P16">
         <v>3.25</v>
@@ -3255,7 +3255,7 @@
         <v>3.6</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S18">
         <v>1.37</v>
@@ -3273,7 +3273,7 @@
         <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
@@ -3294,7 +3294,7 @@
         <v>1.2</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,65 +3406,65 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="O19">
+        <v>3.3</v>
+      </c>
+      <c r="P19">
+        <v>2.82</v>
+      </c>
+      <c r="Q19">
+        <v>2.83</v>
+      </c>
+      <c r="R19">
+        <v>2.13</v>
+      </c>
+      <c r="S19">
+        <v>1.3</v>
+      </c>
+      <c r="T19">
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <v>2.48</v>
+      </c>
+      <c r="V19">
+        <v>1.43</v>
+      </c>
+      <c r="W19">
+        <v>1.08</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.22</v>
+      </c>
+      <c r="Z19">
         <v>3.5</v>
       </c>
-      <c r="P19">
-        <v>4.59</v>
-      </c>
-      <c r="Q19">
-        <v>2.21</v>
-      </c>
-      <c r="R19">
+      <c r="AA19">
+        <v>1.79</v>
+      </c>
+      <c r="AB19">
+        <v>1.88</v>
+      </c>
+      <c r="AC19">
+        <v>2.97</v>
+      </c>
+      <c r="AD19">
+        <v>1.3</v>
+      </c>
+      <c r="AE19">
+        <v>1.09</v>
+      </c>
+      <c r="AF19">
+        <v>1.64</v>
+      </c>
+      <c r="AG19">
         <v>2.1</v>
       </c>
-      <c r="S19">
-        <v>1.38</v>
-      </c>
-      <c r="T19">
-        <v>2.64</v>
-      </c>
-      <c r="U19">
-        <v>2.88</v>
-      </c>
-      <c r="V19">
-        <v>1.32</v>
-      </c>
-      <c r="W19">
-        <v>1.05</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.29</v>
-      </c>
-      <c r="Z19">
-        <v>3.04</v>
-      </c>
-      <c r="AA19">
-        <v>2.05</v>
-      </c>
-      <c r="AB19">
-        <v>1.7</v>
-      </c>
-      <c r="AC19">
-        <v>3.5</v>
-      </c>
-      <c r="AD19">
-        <v>1.22</v>
-      </c>
-      <c r="AE19">
-        <v>1.05</v>
-      </c>
-      <c r="AF19">
-        <v>1.95</v>
-      </c>
-      <c r="AG19">
-        <v>1.75</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>2.05</v>
+        <v>1.51</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>4.59</v>
       </c>
       <c r="Q20">
-        <v>2.83</v>
+        <v>2.21</v>
       </c>
       <c r="R20">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
+        <v>1.29</v>
+      </c>
+      <c r="Z20">
+        <v>3.04</v>
+      </c>
+      <c r="AA20">
+        <v>2.05</v>
+      </c>
+      <c r="AB20">
+        <v>1.7</v>
+      </c>
+      <c r="AC20">
+        <v>3.5</v>
+      </c>
+      <c r="AD20">
         <v>1.22</v>
       </c>
-      <c r="Z20">
-        <v>3.5</v>
-      </c>
-      <c r="AA20">
-        <v>1.79</v>
-      </c>
-      <c r="AB20">
-        <v>1.88</v>
-      </c>
-      <c r="AC20">
-        <v>2.97</v>
-      </c>
-      <c r="AD20">
-        <v>1.3</v>
-      </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AG20">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK20">
-        <v>1.51</v>
+        <v>2.05</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4263,7 +4263,7 @@
         <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC24">
         <v>2.92</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="R31">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S31">
         <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
         <v>1.04</v>
@@ -5395,19 +5395,19 @@
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z31">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA31">
         <v>2.15</v>
       </c>
       <c r="AB31">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AD31">
         <v>1.2</v>
@@ -5416,10 +5416,10 @@
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>2.28</v>
+        <v>1.82</v>
       </c>
       <c r="AG31">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,31 +5525,31 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>2.63</v>
+        <v>5.58</v>
       </c>
       <c r="Q32">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S32">
         <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
         <v>1.04</v>
@@ -5558,19 +5558,19 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z32">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB32">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC32">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AD32">
         <v>1.2</v>
@@ -5579,10 +5579,10 @@
         <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>1.82</v>
+        <v>2.17</v>
       </c>
       <c r="AG32">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.49</v>
+        <v>2.27</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R33">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S33">
         <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="U33">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
         <v>1.04</v>
@@ -5721,31 +5721,31 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AA33">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
         <v>1.63</v>
       </c>
       <c r="AC33">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AG33">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AK33">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O48">
         <v>3.77</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="Q50">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T50">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="U50">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="V50">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z50">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA50">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB50">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AC50">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD50">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE50">
         <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AG50">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="Q51">
-        <v>2.94</v>
+        <v>2.29</v>
       </c>
       <c r="R51">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
+        <v>1.38</v>
+      </c>
+      <c r="T51">
+        <v>2.64</v>
+      </c>
+      <c r="U51">
+        <v>2.88</v>
+      </c>
+      <c r="V51">
         <v>1.35</v>
       </c>
-      <c r="T51">
-        <v>2.77</v>
-      </c>
-      <c r="U51">
-        <v>2.73</v>
-      </c>
-      <c r="V51">
-        <v>1.36</v>
-      </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z51">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AB51">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AD51">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE51">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG51">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK51">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8824,7 +8824,7 @@
         <v>3.08</v>
       </c>
       <c r="AA52">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
         <v>1.86</v>
@@ -9114,7 +9114,7 @@
         <v>1.18</v>
       </c>
       <c r="O54">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P54">
         <v>11</v>
@@ -9123,49 +9123,49 @@
         <v>1.55</v>
       </c>
       <c r="R54">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="S54">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
         <v>3.42</v>
       </c>
       <c r="U54">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V54">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.12</v>
       </c>
       <c r="Z54">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AA54">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB54">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AD54">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE54">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF54">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG54">
         <v>1.62</v>
@@ -9184,7 +9184,7 @@
         <v>1.08</v>
       </c>
       <c r="AK54">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10424,10 +10424,10 @@
         <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S62">
         <v>1.35</v>
@@ -10632,7 +10632,7 @@
         <v>1.16</v>
       </c>
       <c r="AF63">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
         <v>2.63</v>
@@ -12208,31 +12208,31 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O73">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P73">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q73">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R73">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S73">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T73">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="U73">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V73">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W73">
         <v>1.16</v>
@@ -12241,25 +12241,25 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>5.95</v>
+        <v>6.23</v>
       </c>
       <c r="AA73">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AB73">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AC73">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AD73">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AE73">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF73">
         <v>1.36</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12570,13 +12570,13 @@
         <v>1.06</v>
       </c>
       <c r="Z75">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="AA75">
         <v>1.35</v>
       </c>
       <c r="AB75">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC75">
         <v>2.14</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="O91">
         <v>3.3</v>
@@ -15326,7 +15326,7 @@
         <v>3.08</v>
       </c>
       <c r="U92">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V92">
         <v>1.5</v>
@@ -16781,7 +16781,7 @@
         <v>0</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R101">
         <v>2.1</v>
@@ -16845,7 +16845,7 @@
         <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17312,13 +17312,13 @@
         <v>1.66</v>
       </c>
       <c r="AE104">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF104">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG104">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>1.64</v>
       </c>
       <c r="W109">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X109">
         <v>1.02</v>
@@ -18734,7 +18734,7 @@
         <v>3.5</v>
       </c>
       <c r="P113">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="Q113">
         <v>3.2</v>
@@ -18894,7 +18894,7 @@
         <v>2.13</v>
       </c>
       <c r="O114">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P114">
         <v>3.1</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,80 +19054,80 @@
         </is>
       </c>
       <c r="N115">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="O115">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="P115">
-        <v>2.53</v>
+        <v>5.2</v>
       </c>
       <c r="Q115">
-        <v>2.77</v>
+        <v>2</v>
       </c>
       <c r="R115">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="S115">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T115">
-        <v>3.28</v>
+        <v>3.66</v>
       </c>
       <c r="U115">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V115">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W115">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X115">
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z115">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AA115">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AB115">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AC115">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD115">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AE115">
+        <v>1.18</v>
+      </c>
+      <c r="AF115">
+        <v>1.6</v>
+      </c>
+      <c r="AG115">
+        <v>2.15</v>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ115">
         <v>1.15</v>
       </c>
-      <c r="AF115">
-        <v>1.51</v>
-      </c>
-      <c r="AG115">
-        <v>2.42</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>1.25</v>
-      </c>
       <c r="AK115">
-        <v>1.52</v>
+        <v>2.3</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19271,7 +19271,7 @@
         <v>1.08</v>
       </c>
       <c r="AF116">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG116">
         <v>2.1</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.53</v>
+        <v>2.42</v>
       </c>
       <c r="O117">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P117">
-        <v>5.2</v>
+        <v>2.53</v>
       </c>
       <c r="Q117">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="R117">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="S117">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T117">
-        <v>3.66</v>
+        <v>3.28</v>
       </c>
       <c r="U117">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W117">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
+        <v>1.17</v>
+      </c>
+      <c r="Z117">
+        <v>4.3</v>
+      </c>
+      <c r="AA117">
+        <v>1.7</v>
+      </c>
+      <c r="AB117">
+        <v>2.2</v>
+      </c>
+      <c r="AC117">
+        <v>2.46</v>
+      </c>
+      <c r="AD117">
+        <v>1.47</v>
+      </c>
+      <c r="AE117">
         <v>1.15</v>
       </c>
-      <c r="Z117">
-        <v>4.65</v>
-      </c>
-      <c r="AA117">
-        <v>1.55</v>
-      </c>
-      <c r="AB117">
-        <v>2.25</v>
-      </c>
-      <c r="AC117">
-        <v>2.5</v>
-      </c>
-      <c r="AD117">
-        <v>1.57</v>
-      </c>
-      <c r="AE117">
-        <v>1.18</v>
-      </c>
       <c r="AF117">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG117">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>2.38</v>
+        <v>1.52</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19552,7 +19552,7 @@
         <v>2.4</v>
       </c>
       <c r="Q118">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R118">
         <v>2.1</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O122">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P122">
         <v>4.3</v>
@@ -20237,7 +20237,7 @@
         <v>1.69</v>
       </c>
       <c r="AB122">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC122">
         <v>2.75</v>
@@ -20865,7 +20865,7 @@
         <v>1.43</v>
       </c>
       <c r="T126">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="U126">
         <v>2.96</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O136">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P136">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="Q136">
-        <v>2.21</v>
+        <v>2.79</v>
       </c>
       <c r="R136">
-        <v>2.21</v>
+        <v>2.08</v>
       </c>
       <c r="S136">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U136">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="V136">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W136">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z136">
-        <v>3.76</v>
+        <v>3.14</v>
       </c>
       <c r="AA136">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AB136">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC136">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="AD136">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE136">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF136">
         <v>1.72</v>
       </c>
       <c r="AG136">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK136">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O137">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q137">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="R137">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V137">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z137">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA137">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AB137">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC137">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="AD137">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE137">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF137">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG137">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK137">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N138">
@@ -22966,25 +22966,25 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O139">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P139">
         <v>2.05</v>
       </c>
       <c r="Q139">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R139">
         <v>2.26</v>
       </c>
       <c r="S139">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T139">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U139">
         <v>2.4</v>
@@ -23008,7 +23008,7 @@
         <v>1.73</v>
       </c>
       <c r="AB139">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AC139">
         <v>2.53</v>
@@ -23820,7 +23820,7 @@
         <v>4.75</v>
       </c>
       <c r="AA144">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB144">
         <v>2.31</v>
@@ -25106,10 +25106,10 @@
         <v>3.05</v>
       </c>
       <c r="U152">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V152">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W152">
         <v>1.09</v>
@@ -25269,7 +25269,7 @@
         <v>3.84</v>
       </c>
       <c r="U153">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V153">
         <v>1.66</v>
@@ -25453,7 +25453,7 @@
         <v>2.24</v>
       </c>
       <c r="AB154">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC154">
         <v>4.15</v>
@@ -25779,7 +25779,7 @@
         <v>1.31</v>
       </c>
       <c r="AB156">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AC156">
         <v>1.82</v>
@@ -26606,7 +26606,7 @@
         <v>1.1</v>
       </c>
       <c r="AF161">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG161">
         <v>2.2</v>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O170">
         <v>3.82</v>
@@ -28997,7 +28997,7 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O176">
         <v>3.6</v>
@@ -29006,25 +29006,25 @@
         <v>2.8</v>
       </c>
       <c r="Q176">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="R176">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S176">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T176">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U176">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V176">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="W176">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X176">
         <v>1.02</v>
@@ -29033,22 +29033,22 @@
         <v>1.12</v>
       </c>
       <c r="Z176">
-        <v>4.8</v>
+        <v>5.66</v>
       </c>
       <c r="AA176">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB176">
         <v>2.4</v>
       </c>
       <c r="AC176">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AD176">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AE176">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF176">
         <v>1.44</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK176">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29335,7 +29335,7 @@
         <v>8.35</v>
       </c>
       <c r="R178">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="S178">
         <v>1.16</v>
@@ -29359,7 +29359,7 @@
         <v>1.08</v>
       </c>
       <c r="Z178">
-        <v>5.99</v>
+        <v>5.71</v>
       </c>
       <c r="AA178">
         <v>1.4</v>
@@ -29371,7 +29371,7 @@
         <v>2.01</v>
       </c>
       <c r="AD178">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AE178">
         <v>1.27</v>
@@ -30476,7 +30476,7 @@
         <v>2.9</v>
       </c>
       <c r="R185">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S185">
         <v>1.37</v>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK185">
         <v>1.53</v>
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="O187">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P187">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q188">
-        <v>2.37</v>
+        <v>5.06</v>
       </c>
       <c r="R188">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S188">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T188">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U188">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="V188">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W188">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X188">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y188">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z188">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AA188">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB188">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC188">
-        <v>3.78</v>
+        <v>3.28</v>
       </c>
       <c r="AD188">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE188">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF188">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG188">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK188">
-        <v>1.88</v>
+        <v>1.14</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,64 +31116,64 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q189">
-        <v>5.06</v>
+        <v>2.37</v>
       </c>
       <c r="R189">
+        <v>2.03</v>
+      </c>
+      <c r="S189">
+        <v>1.38</v>
+      </c>
+      <c r="T189">
+        <v>2.65</v>
+      </c>
+      <c r="U189">
+        <v>2.9</v>
+      </c>
+      <c r="V189">
+        <v>1.32</v>
+      </c>
+      <c r="W189">
+        <v>1.04</v>
+      </c>
+      <c r="X189">
+        <v>1.03</v>
+      </c>
+      <c r="Y189">
+        <v>1.33</v>
+      </c>
+      <c r="Z189">
+        <v>2.83</v>
+      </c>
+      <c r="AA189">
         <v>2.1</v>
       </c>
-      <c r="S189">
-        <v>1.37</v>
-      </c>
-      <c r="T189">
-        <v>2.68</v>
-      </c>
-      <c r="U189">
-        <v>2.76</v>
-      </c>
-      <c r="V189">
-        <v>1.35</v>
-      </c>
-      <c r="W189">
-        <v>1.06</v>
-      </c>
-      <c r="X189">
-        <v>1.02</v>
-      </c>
-      <c r="Y189">
-        <v>1.28</v>
-      </c>
-      <c r="Z189">
-        <v>3.08</v>
-      </c>
-      <c r="AA189">
-        <v>1.93</v>
-      </c>
       <c r="AB189">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AC189">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="AD189">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE189">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF189">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG189">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>1.14</v>
+        <v>1.88</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31279,7 +31279,7 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O190">
         <v>3.5</v>
@@ -31442,7 +31442,7 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="O191">
         <v>3.6</v>
@@ -31973,7 +31973,7 @@
         <v>1.79</v>
       </c>
       <c r="AB194">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC194">
         <v>2.97</v>
@@ -32426,13 +32426,13 @@
         <v>3.7</v>
       </c>
       <c r="P197">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q197">
         <v>2.05</v>
       </c>
       <c r="R197">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S197">
         <v>1.3</v>
@@ -32441,22 +32441,22 @@
         <v>3.3</v>
       </c>
       <c r="U197">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V197">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W197">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X197">
         <v>1.01</v>
       </c>
       <c r="Y197">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z197">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="AA197">
         <v>1.66</v>
@@ -32465,19 +32465,19 @@
         <v>2.15</v>
       </c>
       <c r="AC197">
-        <v>2.42</v>
+        <v>2.7</v>
       </c>
       <c r="AD197">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE197">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF197">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG197">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Gimnástica Torrelavega</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O198">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P198">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q198">
-        <v>2.47</v>
+        <v>4.09</v>
       </c>
       <c r="R198">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S198">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T198">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="U198">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="V198">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W198">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X198">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z198">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA198">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB198">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC198">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD198">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE198">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF198">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG198">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AK198">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Gimnástica Torrelavega</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q199">
-        <v>4.09</v>
+        <v>2.5</v>
       </c>
       <c r="R199">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S199">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T199">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="U199">
-        <v>3</v>
+        <v>2.44</v>
       </c>
       <c r="V199">
+        <v>1.44</v>
+      </c>
+      <c r="W199">
+        <v>1.09</v>
+      </c>
+      <c r="X199">
+        <v>1.01</v>
+      </c>
+      <c r="Y199">
+        <v>1.22</v>
+      </c>
+      <c r="Z199">
+        <v>3.5</v>
+      </c>
+      <c r="AA199">
+        <v>1.75</v>
+      </c>
+      <c r="AB199">
+        <v>1.93</v>
+      </c>
+      <c r="AC199">
+        <v>2.83</v>
+      </c>
+      <c r="AD199">
         <v>1.33</v>
       </c>
-      <c r="W199">
-        <v>1.05</v>
-      </c>
-      <c r="X199">
-        <v>1.02</v>
-      </c>
-      <c r="Y199">
-        <v>1.3</v>
-      </c>
-      <c r="Z199">
-        <v>2.97</v>
-      </c>
-      <c r="AA199">
-        <v>1.98</v>
-      </c>
-      <c r="AB199">
-        <v>1.71</v>
-      </c>
-      <c r="AC199">
-        <v>3.42</v>
-      </c>
-      <c r="AD199">
-        <v>1.23</v>
-      </c>
       <c r="AE199">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AF199">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG199">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AK199">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.92</v>
+        <v>3.13</v>
       </c>
       <c r="O200">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P200">
-        <v>3.42</v>
+        <v>2.15</v>
       </c>
       <c r="Q200">
-        <v>2.5</v>
+        <v>4.03</v>
       </c>
       <c r="R200">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="S200">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T200">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="U200">
-        <v>2.44</v>
+        <v>2.95</v>
       </c>
       <c r="V200">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W200">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X200">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y200">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z200">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="AA200">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AB200">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AC200">
-        <v>2.83</v>
+        <v>3.95</v>
       </c>
       <c r="AD200">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AE200">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AF200">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG200">
-        <v>2.08</v>
+        <v>1.78</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK200">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>3.13</v>
+        <v>1.85</v>
       </c>
       <c r="O201">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P201">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q201">
-        <v>4.03</v>
+        <v>2.47</v>
       </c>
       <c r="R201">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S201">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T201">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="U201">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="V201">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W201">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X201">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y201">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z201">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="AA201">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AB201">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AC201">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AD201">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE201">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF201">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AG201">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK201">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -35683,10 +35683,10 @@
         <v>2.18</v>
       </c>
       <c r="O217">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P217">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="Q217">
         <v>2.9</v>
@@ -36223,7 +36223,7 @@
         <v>1.07</v>
       </c>
       <c r="AF220">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG220">
         <v>2.01</v>
@@ -36670,7 +36670,7 @@
         <v>2.21</v>
       </c>
       <c r="R223">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S223">
         <v>1.33</v>
@@ -38134,10 +38134,10 @@
         <v>3.2</v>
       </c>
       <c r="Q232">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R232">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S232">
         <v>1.38</v>
@@ -38361,7 +38361,7 @@
         <v>1.24</v>
       </c>
       <c r="AK233">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38940,7 +38940,7 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O237">
         <v>4</v>
@@ -39278,13 +39278,13 @@
         <v>3.5</v>
       </c>
       <c r="R239">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S239">
         <v>1.33</v>
       </c>
       <c r="T239">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U239">
         <v>2.53</v>
@@ -39438,7 +39438,7 @@
         <v>1.46</v>
       </c>
       <c r="Q240">
-        <v>5.35</v>
+        <v>4.47</v>
       </c>
       <c r="R240">
         <v>2.58</v>
@@ -39468,10 +39468,10 @@
         <v>4.45</v>
       </c>
       <c r="AA240">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB240">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC240">
         <v>2.33</v>
@@ -39755,7 +39755,7 @@
         </is>
       </c>
       <c r="N242">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O242">
         <v>5.25</v>
@@ -39800,10 +39800,10 @@
         <v>2.97</v>
       </c>
       <c r="AC242">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AD242">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE242">
         <v>1.33</v>
@@ -40081,58 +40081,58 @@
         </is>
       </c>
       <c r="N244">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="O244">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P244">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q244">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="R244">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S244">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T244">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="U244">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V244">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W244">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X244">
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z244">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA244">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB244">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC244">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AD244">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE244">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF244">
         <v>1.67</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK244">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -41113,7 +41113,7 @@
         <v>1.11</v>
       </c>
       <c r="AF250">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG250">
         <v>2.3</v>
@@ -41231,55 +41231,55 @@
         <v>4.55</v>
       </c>
       <c r="Q251">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R251">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S251">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T251">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U251">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V251">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W251">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y251">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z251">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA251">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB251">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC251">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD251">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE251">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF251">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG251">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
@@ -41292,10 +41292,10 @@
         </is>
       </c>
       <c r="AJ251">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK251">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL251">
         <v>0</v>
@@ -41560,7 +41560,7 @@
         <v>3.1</v>
       </c>
       <c r="R253">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S253">
         <v>1.25</v>
@@ -41581,16 +41581,16 @@
         <v>1.01</v>
       </c>
       <c r="Y253">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z253">
         <v>4.4</v>
       </c>
       <c r="AA253">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB253">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AC253">
         <v>2.44</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="O254">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="P254">
-        <v>4.67</v>
+        <v>3.8</v>
       </c>
       <c r="Q254">
         <v>0</v>
@@ -41874,22 +41874,22 @@
         </is>
       </c>
       <c r="N255">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="O255">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="P255">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="Q255">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R255">
         <v>2.1</v>
       </c>
       <c r="S255">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T255">
         <v>2.88</v>
@@ -41907,16 +41907,16 @@
         <v>1.01</v>
       </c>
       <c r="Y255">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z255">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AA255">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB255">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC255">
         <v>3.28</v>
@@ -42037,64 +42037,64 @@
         </is>
       </c>
       <c r="N256">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="O256">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P256">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="Q256">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="R256">
         <v>2</v>
       </c>
       <c r="S256">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T256">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="U256">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="V256">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W256">
         <v>1.04</v>
       </c>
       <c r="X256">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y256">
         <v>1.43</v>
       </c>
       <c r="Z256">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA256">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AB256">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC256">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD256">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE256">
         <v>1.02</v>
       </c>
       <c r="AF256">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG256">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>1.34</v>
       </c>
       <c r="T257">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U257">
         <v>2.53</v>
@@ -42242,7 +42242,7 @@
         <v>1.81</v>
       </c>
       <c r="AB257">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AC257">
         <v>2.84</v>
@@ -42270,7 +42270,7 @@
         </is>
       </c>
       <c r="AJ257">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AK257">
         <v>1.28</v>
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="O262">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P262">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="Q262">
         <v>3.76</v>
@@ -43033,7 +43033,7 @@
         <v>1.38</v>
       </c>
       <c r="T262">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U262">
         <v>2.75</v>
@@ -43054,7 +43054,7 @@
         <v>3.04</v>
       </c>
       <c r="AA262">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB262">
         <v>1.75</v>
@@ -43069,10 +43069,10 @@
         <v>1.05</v>
       </c>
       <c r="AF262">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG262">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH262" t="inlineStr">
         <is>
@@ -43380,10 +43380,10 @@
         <v>2.81</v>
       </c>
       <c r="AA264">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB264">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC264">
         <v>3.98</v>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK264">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="O265">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="P265">
-        <v>5.99</v>
+        <v>5</v>
       </c>
       <c r="Q265">
         <v>1.95</v>
@@ -43522,7 +43522,7 @@
         <v>1.3</v>
       </c>
       <c r="T265">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U265">
         <v>2.47</v>
@@ -43537,13 +43537,13 @@
         <v>1.02</v>
       </c>
       <c r="Y265">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z265">
-        <v>4</v>
+        <v>4.41</v>
       </c>
       <c r="AA265">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB265">
         <v>2.14</v>
@@ -43555,7 +43555,7 @@
         <v>1.37</v>
       </c>
       <c r="AE265">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF265">
         <v>1.7</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="O266">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P266">
-        <v>6.34</v>
+        <v>7</v>
       </c>
       <c r="Q266">
         <v>1.7</v>
@@ -43682,25 +43682,25 @@
         <v>2.5</v>
       </c>
       <c r="S266">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T266">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="U266">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="V266">
         <v>1.62</v>
       </c>
       <c r="W266">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X266">
         <v>1.02</v>
       </c>
       <c r="Y266">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z266">
         <v>5.25</v>
@@ -43712,19 +43712,19 @@
         <v>2.6</v>
       </c>
       <c r="AC266">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="AD266">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AE266">
         <v>1.2</v>
       </c>
       <c r="AF266">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG266">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>1.17</v>
       </c>
       <c r="AK266">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43833,16 +43833,16 @@
         <v>1.8</v>
       </c>
       <c r="O267">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P267">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="Q267">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R267">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S267">
         <v>1.39</v>
@@ -43857,7 +43857,7 @@
         <v>1.38</v>
       </c>
       <c r="W267">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X267">
         <v>1.01</v>
@@ -43869,16 +43869,16 @@
         <v>3.34</v>
       </c>
       <c r="AA267">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB267">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC267">
-        <v>3.51</v>
+        <v>3.14</v>
       </c>
       <c r="AD267">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE267">
         <v>1.06</v>
@@ -43887,7 +43887,7 @@
         <v>1.78</v>
       </c>
       <c r="AG267">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>1.26</v>
       </c>
       <c r="AK267">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43993,19 +43993,19 @@
         </is>
       </c>
       <c r="N268">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O268">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P268">
         <v>4.2</v>
       </c>
       <c r="Q268">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="R268">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="S268">
         <v>1.2</v>
@@ -44014,13 +44014,13 @@
         <v>4</v>
       </c>
       <c r="U268">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="V268">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W268">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X268">
         <v>1.01</v>
@@ -44029,25 +44029,25 @@
         <v>1.12</v>
       </c>
       <c r="Z268">
-        <v>5.86</v>
+        <v>5.79</v>
       </c>
       <c r="AA268">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB268">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="AC268">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AD268">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE268">
         <v>1.31</v>
       </c>
       <c r="AF268">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AG268">
         <v>2.62</v>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK268">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="O269">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="P269">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="Q269">
         <v>2.75</v>
@@ -44491,28 +44491,28 @@
         <v>1.7</v>
       </c>
       <c r="Q271">
-        <v>6</v>
+        <v>6.02</v>
       </c>
       <c r="R271">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S271">
         <v>1.36</v>
       </c>
       <c r="T271">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="U271">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V271">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W271">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y271">
         <v>1.27</v>
@@ -44521,10 +44521,10 @@
         <v>3.14</v>
       </c>
       <c r="AA271">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB271">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC271">
         <v>3.34</v>
@@ -44533,13 +44533,13 @@
         <v>1.24</v>
       </c>
       <c r="AE271">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF271">
         <v>1.98</v>
       </c>
       <c r="AG271">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK271">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O273">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P273">
-        <v>4.73</v>
+        <v>5.5</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44847,10 +44847,10 @@
         <v>0</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC273">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB274">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -45143,22 +45143,22 @@
         <v>1.67</v>
       </c>
       <c r="Q275">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="R275">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S275">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T275">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U275">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V275">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W275">
         <v>0</v>
@@ -45167,31 +45167,31 @@
         <v>0</v>
       </c>
       <c r="Y275">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z275">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC275">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD275">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE275">
         <v>0</v>
       </c>
       <c r="AF275">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG275">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK275">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45297,31 +45297,31 @@
         </is>
       </c>
       <c r="N276">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O276">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="P276">
-        <v>6.03</v>
+        <v>6.08</v>
       </c>
       <c r="Q276">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R276">
         <v>2.4</v>
       </c>
       <c r="S276">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T276">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U276">
         <v>2.4</v>
       </c>
       <c r="V276">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W276">
         <v>1.11</v>
@@ -45333,29 +45333,29 @@
         <v>1.2</v>
       </c>
       <c r="Z276">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="AA276">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB276">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC276">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD276">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE276">
         <v>1.15</v>
       </c>
       <c r="AF276">
+        <v>1.85</v>
+      </c>
+      <c r="AG276">
         <v>1.86</v>
       </c>
-      <c r="AG276">
-        <v>1.84</v>
-      </c>
       <c r="AH276" t="inlineStr">
         <is>
           <t>[]</t>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK276">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="O277">
-        <v>5.32</v>
+        <v>5.75</v>
       </c>
       <c r="P277">
-        <v>7.26</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q277">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="R277">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="S277">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="T277">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U277">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="V277">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="W277">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X277">
         <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z277">
-        <v>6.15</v>
+        <v>6.7</v>
       </c>
       <c r="AA277">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AB277">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AC277">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD277">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AE277">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF277">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG277">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK277">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,31 +45623,31 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="O278">
-        <v>6.15</v>
+        <v>4.25</v>
       </c>
       <c r="P278">
-        <v>8.449999999999999</v>
+        <v>5</v>
       </c>
       <c r="Q278">
-        <v>1.66</v>
+        <v>2.11</v>
       </c>
       <c r="R278">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="S278">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T278">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="U278">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="V278">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W278">
         <v>1.22</v>
@@ -45656,47 +45656,47 @@
         <v>1.01</v>
       </c>
       <c r="Y278">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z278">
-        <v>6.7</v>
+        <v>6.05</v>
       </c>
       <c r="AA278">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB278">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AC278">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD278">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AE278">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF278">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG278">
+        <v>2.66</v>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ278">
+        <v>1.15</v>
+      </c>
+      <c r="AK278">
         <v>2.3</v>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ278">
-        <v>1.14</v>
-      </c>
-      <c r="AK278">
-        <v>3.48</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -45786,16 +45786,16 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O279">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P279">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="Q279">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R279">
         <v>2.3</v>
@@ -45807,16 +45807,16 @@
         <v>3.5</v>
       </c>
       <c r="U279">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V279">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W279">
         <v>1.14</v>
       </c>
       <c r="X279">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y279">
         <v>1.17</v>
@@ -45825,10 +45825,10 @@
         <v>4.4</v>
       </c>
       <c r="AA279">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB279">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC279">
         <v>2.46</v>
@@ -45837,7 +45837,7 @@
         <v>1.43</v>
       </c>
       <c r="AE279">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AF279">
         <v>1.5</v>
@@ -45958,34 +45958,34 @@
         <v>3.3</v>
       </c>
       <c r="Q280">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R280">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S280">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T280">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U280">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V280">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W280">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X280">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y280">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z280">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA280">
         <v>2</v>
@@ -45994,19 +45994,19 @@
         <v>1.8</v>
       </c>
       <c r="AC280">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD280">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE280">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF280">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG280">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,10 +46019,10 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK280">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL280">
         <v>0</v>
@@ -46441,10 +46441,10 @@
         <v>1.66</v>
       </c>
       <c r="O283">
-        <v>4.31</v>
+        <v>4.2</v>
       </c>
       <c r="P283">
-        <v>5.49</v>
+        <v>4.5</v>
       </c>
       <c r="Q283">
         <v>2.19</v>
@@ -46465,7 +46465,7 @@
         <v>1.5</v>
       </c>
       <c r="W283">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X283">
         <v>1.01</v>
@@ -46480,10 +46480,10 @@
         <v>1.72</v>
       </c>
       <c r="AB283">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC283">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AD283">
         <v>1.44</v>
@@ -46508,10 +46508,10 @@
         </is>
       </c>
       <c r="AJ283">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK283">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AL283">
         <v>0</v>
@@ -46601,64 +46601,64 @@
         </is>
       </c>
       <c r="N284">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="O284">
-        <v>4.06</v>
+        <v>3.75</v>
       </c>
       <c r="P284">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q284">
         <v>2.31</v>
       </c>
       <c r="R284">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S284">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T284">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="U284">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="V284">
         <v>1.38</v>
       </c>
       <c r="W284">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X284">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y284">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z284">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AA284">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AB284">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC284">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD284">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE284">
         <v>1.05</v>
       </c>
       <c r="AF284">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG284">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46671,10 +46671,10 @@
         </is>
       </c>
       <c r="AJ284">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK284">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AL284">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="O285">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="P285">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="Q285">
         <v>2.5</v>
@@ -46803,10 +46803,10 @@
         <v>3.34</v>
       </c>
       <c r="AA285">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB285">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC285">
         <v>3.08</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O286">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P286">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q286">
         <v>3.56</v>
@@ -46969,7 +46969,7 @@
         <v>1.83</v>
       </c>
       <c r="AB286">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC286">
         <v>2.83</v>
@@ -47102,7 +47102,7 @@
         <v>4.33</v>
       </c>
       <c r="R287">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S287">
         <v>1.2</v>
@@ -47160,10 +47160,10 @@
         </is>
       </c>
       <c r="AJ287">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK287">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47416,16 +47416,16 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="O289">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="P289">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="Q289">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="R289">
         <v>1.9</v>
@@ -47434,7 +47434,7 @@
         <v>1.5</v>
       </c>
       <c r="T289">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="U289">
         <v>3.26</v>
@@ -47443,25 +47443,25 @@
         <v>1.28</v>
       </c>
       <c r="W289">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X289">
         <v>1.03</v>
       </c>
       <c r="Y289">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z289">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AA289">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AB289">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC289">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AD289">
         <v>1.13</v>
@@ -47470,10 +47470,10 @@
         <v>1.01</v>
       </c>
       <c r="AF289">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AG289">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK289">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,16 +47579,16 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O290">
         <v>3</v>
       </c>
       <c r="P290">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q290">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="R290">
         <v>1.99</v>
@@ -47597,7 +47597,7 @@
         <v>1.52</v>
       </c>
       <c r="T290">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U290">
         <v>3.5</v>
@@ -47606,7 +47606,7 @@
         <v>1.25</v>
       </c>
       <c r="W290">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X290">
         <v>1.05</v>
@@ -47742,7 +47742,7 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O291">
         <v>6.6</v>
@@ -47754,43 +47754,43 @@
         <v>1.54</v>
       </c>
       <c r="R291">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="S291">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T291">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U291">
         <v>2.07</v>
       </c>
       <c r="V291">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="W291">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X291">
         <v>1.01</v>
       </c>
       <c r="Y291">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z291">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA291">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AB291">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC291">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AD291">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AE291">
         <v>1.33</v>
@@ -47815,7 +47815,7 @@
         <v>1.12</v>
       </c>
       <c r="AK291">
-        <v>3.61</v>
+        <v>3.92</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.59</v>
+        <v>2.17</v>
       </c>
       <c r="O292">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="P292">
-        <v>5.31</v>
+        <v>3.35</v>
       </c>
       <c r="Q292">
-        <v>2.12</v>
+        <v>2.85</v>
       </c>
       <c r="R292">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="S292">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T292">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U292">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="V292">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="W292">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X292">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y292">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z292">
-        <v>3.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA292">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="AB292">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AC292">
-        <v>3.16</v>
+        <v>4.41</v>
       </c>
       <c r="AD292">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AE292">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF292">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG292">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK292">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="O293">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P293">
-        <v>3.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q293">
-        <v>2.85</v>
+        <v>3.87</v>
       </c>
       <c r="R293">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="S293">
         <v>1.44</v>
       </c>
       <c r="T293">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U293">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V293">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W293">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X293">
         <v>1.05</v>
       </c>
       <c r="Y293">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z293">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
       <c r="AA293">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AB293">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC293">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="AD293">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE293">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF293">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG293">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK293">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="O294">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="P294">
-        <v>2.71</v>
+        <v>4.35</v>
       </c>
       <c r="Q294">
-        <v>3.87</v>
+        <v>2.15</v>
       </c>
       <c r="R294">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S294">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T294">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U294">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="V294">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W294">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X294">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y294">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="Z294">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AA294">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AB294">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AC294">
-        <v>4.61</v>
+        <v>3.17</v>
       </c>
       <c r="AD294">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE294">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF294">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG294">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK294">
-        <v>1.34</v>
+        <v>2.23</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48394,34 +48394,34 @@
         </is>
       </c>
       <c r="N295">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="O295">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P295">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="Q295">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R295">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="S295">
         <v>1.13</v>
       </c>
       <c r="T295">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="U295">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V295">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="W295">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X295">
         <v>1.01</v>
@@ -48433,25 +48433,25 @@
         <v>4.33</v>
       </c>
       <c r="AA295">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AB295">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC295">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="AD295">
-        <v>1.86</v>
+        <v>2.19</v>
       </c>
       <c r="AE295">
         <v>1.4</v>
       </c>
       <c r="AF295">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AG295">
-        <v>2.75</v>
+        <v>3.48</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK295">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O297">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="P297">
-        <v>4.58</v>
+        <v>5.47</v>
       </c>
       <c r="Q297">
         <v>0</v>
@@ -48759,10 +48759,10 @@
         <v>0</v>
       </c>
       <c r="AA297">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB297">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC297">
         <v>0</v>
@@ -48883,64 +48883,64 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="O298">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P298">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q298">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="R298">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S298">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T298">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U298">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V298">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W298">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X298">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y298">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z298">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA298">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB298">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC298">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="AD298">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE298">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF298">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG298">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK298">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49055,22 +49055,22 @@
         <v>4.35</v>
       </c>
       <c r="Q299">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R299">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S299">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T299">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="U299">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V299">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W299">
         <v>0</v>
@@ -49079,31 +49079,31 @@
         <v>0</v>
       </c>
       <c r="Y299">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z299">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC299">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD299">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE299">
         <v>0</v>
       </c>
       <c r="AF299">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG299">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49116,10 +49116,10 @@
         </is>
       </c>
       <c r="AJ299">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK299">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AL299">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>7.02</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
+        <v>2.26</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
+        <v>3.25</v>
+      </c>
+      <c r="U6">
         <v>2.5</v>
       </c>
-      <c r="S6">
-        <v>1.25</v>
-      </c>
-      <c r="T6">
-        <v>3.24</v>
-      </c>
-      <c r="U6">
-        <v>2.25</v>
-      </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
+        <v>1.17</v>
+      </c>
+      <c r="Z6">
+        <v>3.96</v>
+      </c>
+      <c r="AA6">
+        <v>1.7</v>
+      </c>
+      <c r="AB6">
+        <v>2.12</v>
+      </c>
+      <c r="AC6">
+        <v>2.62</v>
+      </c>
+      <c r="AD6">
+        <v>1.42</v>
+      </c>
+      <c r="AE6">
         <v>1.15</v>
       </c>
-      <c r="Z6">
-        <v>4.3</v>
-      </c>
-      <c r="AA6">
-        <v>1.57</v>
-      </c>
-      <c r="AB6">
-        <v>2.25</v>
-      </c>
-      <c r="AC6">
-        <v>2.38</v>
-      </c>
-      <c r="AD6">
-        <v>1.46</v>
-      </c>
-      <c r="AE6">
-        <v>1.16</v>
-      </c>
       <c r="AF6">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>4</v>
+        <v>7.02</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="T11">
-        <v>3.6</v>
+        <v>2.34</v>
       </c>
       <c r="U11">
+        <v>3.3</v>
+      </c>
+      <c r="V11">
+        <v>1.29</v>
+      </c>
+      <c r="W11">
+        <v>1.01</v>
+      </c>
+      <c r="X11">
+        <v>1.05</v>
+      </c>
+      <c r="Y11">
+        <v>1.43</v>
+      </c>
+      <c r="Z11">
+        <v>2.46</v>
+      </c>
+      <c r="AA11">
         <v>2.4</v>
       </c>
-      <c r="V11">
-        <v>1.5</v>
-      </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>1.16</v>
-      </c>
-      <c r="Z11">
-        <v>4.15</v>
-      </c>
-      <c r="AA11">
+      <c r="AB11">
+        <v>1.53</v>
+      </c>
+      <c r="AC11">
+        <v>4.4</v>
+      </c>
+      <c r="AD11">
+        <v>1.14</v>
+      </c>
+      <c r="AE11">
+        <v>1.01</v>
+      </c>
+      <c r="AF11">
+        <v>2.02</v>
+      </c>
+      <c r="AG11">
+        <v>1.71</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.33</v>
+      </c>
+      <c r="AK11">
         <v>1.62</v>
-      </c>
-      <c r="AB11">
-        <v>2.2</v>
-      </c>
-      <c r="AC11">
-        <v>2.43</v>
-      </c>
-      <c r="AD11">
-        <v>1.44</v>
-      </c>
-      <c r="AE11">
-        <v>1.15</v>
-      </c>
-      <c r="AF11">
-        <v>1.66</v>
-      </c>
-      <c r="AG11">
-        <v>2.09</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.2</v>
-      </c>
-      <c r="AK11">
-        <v>2.29</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q12">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="R12">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>2.34</v>
+        <v>3.6</v>
       </c>
       <c r="U12">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>2.46</v>
+        <v>4.15</v>
       </c>
       <c r="AA12">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AB12">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
-        <v>4.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD12">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG12">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="U15">
         <v>2.42</v>
@@ -5706,7 +5706,7 @@
         <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="U33">
         <v>2.9</v>
@@ -5724,28 +5724,28 @@
         <v>1.33</v>
       </c>
       <c r="Z33">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="AD33">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AG33">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>2.18</v>
       </c>
       <c r="AB40">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC40">
         <v>3.94</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P41">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="R41">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="S41">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="U41">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="V41">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="Z41">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AA41">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AB41">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AC41">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="AD41">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE41">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG41">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK41">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O42">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>3.3</v>
+        <v>6.26</v>
       </c>
       <c r="Q42">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U42">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA42">
         <v>2.05</v>
       </c>
       <c r="AB42">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC42">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE42">
         <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AG42">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>6.26</v>
+        <v>3.53</v>
       </c>
       <c r="Q43">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="R43">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T43">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U43">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V43">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y43">
+        <v>1.44</v>
+      </c>
+      <c r="Z43">
+        <v>2.42</v>
+      </c>
+      <c r="AA43">
+        <v>2.41</v>
+      </c>
+      <c r="AB43">
+        <v>1.48</v>
+      </c>
+      <c r="AC43">
+        <v>4.6</v>
+      </c>
+      <c r="AD43">
+        <v>1.13</v>
+      </c>
+      <c r="AE43">
+        <v>1.01</v>
+      </c>
+      <c r="AF43">
+        <v>2.07</v>
+      </c>
+      <c r="AG43">
+        <v>1.66</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.28</v>
       </c>
-      <c r="Z43">
-        <v>3.05</v>
-      </c>
-      <c r="AA43">
-        <v>2.05</v>
-      </c>
-      <c r="AB43">
-        <v>1.75</v>
-      </c>
-      <c r="AC43">
-        <v>3.5</v>
-      </c>
-      <c r="AD43">
-        <v>1.22</v>
-      </c>
-      <c r="AE43">
-        <v>1.05</v>
-      </c>
-      <c r="AF43">
-        <v>2.14</v>
-      </c>
-      <c r="AG43">
-        <v>1.62</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.2</v>
-      </c>
       <c r="AK43">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
         <v>1.29</v>
@@ -8299,13 +8299,13 @@
         <v>1.9</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P49">
         <v>3.2</v>
       </c>
       <c r="Q49">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R49">
         <v>2.5</v>
@@ -8329,31 +8329,31 @@
         <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z49">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA49">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB49">
         <v>2.8</v>
       </c>
       <c r="AC49">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AD49">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AE49">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AF49">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG49">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8664,7 +8664,7 @@
         <v>1.89</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC51">
         <v>3.2</v>
@@ -9935,28 +9935,28 @@
         <v>2.7</v>
       </c>
       <c r="Q59">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R59">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T59">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U59">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V59">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
         <v>1.17</v>
@@ -9983,7 +9983,7 @@
         <v>1.53</v>
       </c>
       <c r="AG59">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>1.73</v>
       </c>
       <c r="Q60">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R60">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T60">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U60">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V60">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z60">
+        <v>2.75</v>
+      </c>
+      <c r="AA60">
+        <v>1.87</v>
+      </c>
+      <c r="AB60">
+        <v>1.8</v>
+      </c>
+      <c r="AC60">
         <v>3.2</v>
       </c>
-      <c r="AA60">
-        <v>1.92</v>
-      </c>
-      <c r="AB60">
-        <v>1.76</v>
-      </c>
-      <c r="AC60">
-        <v>3.34</v>
-      </c>
       <c r="AD60">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE60">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG60">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>2.79</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>2.12</v>
       </c>
       <c r="Q67">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="R67">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
         <v>1.29</v>
@@ -11251,13 +11251,13 @@
         <v>3.3</v>
       </c>
       <c r="U67">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="V67">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.03</v>
@@ -11269,22 +11269,22 @@
         <v>3.98</v>
       </c>
       <c r="AA67">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB67">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AC67">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="AD67">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF67">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
         <v>2.23</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AK67">
         <v>1.36</v>
@@ -11402,7 +11402,7 @@
         <v>11</v>
       </c>
       <c r="Q68">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R68">
         <v>2.73</v>
@@ -11432,16 +11432,16 @@
         <v>5.9</v>
       </c>
       <c r="AA68">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB68">
         <v>2.7</v>
       </c>
       <c r="AC68">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AD68">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE68">
         <v>1.26</v>
@@ -11450,7 +11450,7 @@
         <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK68">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11598,7 +11598,7 @@
         <v>1.95</v>
       </c>
       <c r="AB69">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC69">
         <v>2.97</v>
@@ -12054,19 +12054,19 @@
         <v>2.1</v>
       </c>
       <c r="Q72">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R72">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S72">
         <v>1.33</v>
       </c>
       <c r="T72">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U72">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V72">
         <v>1.4</v>
@@ -12078,31 +12078,31 @@
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AA72">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB72">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC72">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD72">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE72">
         <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG72">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK72">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -13847,28 +13847,28 @@
         <v>1.29</v>
       </c>
       <c r="Q83">
-        <v>6.5</v>
+        <v>6.91</v>
       </c>
       <c r="R83">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="S83">
         <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U83">
         <v>2.1</v>
       </c>
       <c r="V83">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y83">
         <v>1.09</v>
@@ -13895,7 +13895,7 @@
         <v>1.69</v>
       </c>
       <c r="AG83">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK83">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>2.89</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X89">
         <v>0</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15646,10 +15646,10 @@
         <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T94">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U94">
         <v>2.19</v>
@@ -15667,7 +15667,7 @@
         <v>1.15</v>
       </c>
       <c r="Z94">
-        <v>4.8</v>
+        <v>4.99</v>
       </c>
       <c r="AA94">
         <v>1.57</v>
@@ -15688,7 +15688,7 @@
         <v>1.44</v>
       </c>
       <c r="AG94">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="O95">
         <v>3.85</v>
@@ -15827,22 +15827,22 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z95">
-        <v>5.41</v>
+        <v>4.85</v>
       </c>
       <c r="AA95">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB95">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="AC95">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AD95">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE95">
         <v>1.22</v>
@@ -15851,7 +15851,7 @@
         <v>1.5</v>
       </c>
       <c r="AG95">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
+        <v>1.22</v>
+      </c>
+      <c r="AK95">
         <v>1.25</v>
-      </c>
-      <c r="AK95">
-        <v>1.19</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="O98">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P98">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="Q98">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="R98">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="S98">
         <v>1.22</v>
       </c>
       <c r="T98">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U98">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V98">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W98">
         <v>1.15</v>
@@ -16316,28 +16316,28 @@
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z98">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA98">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB98">
         <v>2.35</v>
       </c>
       <c r="AC98">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD98">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE98">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF98">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AG98">
         <v>2.05</v>
@@ -17282,7 +17282,7 @@
         <v>3.4</v>
       </c>
       <c r="U104">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V104">
         <v>1.65</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P105">
+        <v>2.75</v>
+      </c>
+      <c r="Q105">
         <v>2.8</v>
-      </c>
-      <c r="Q105">
-        <v>3.08</v>
       </c>
       <c r="R105">
         <v>2</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T105">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="U105">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="V105">
         <v>1.36</v>
       </c>
       <c r="W105">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z105">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA105">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB105">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC105">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AD105">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE105">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF105">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG105">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O106">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P106">
+        <v>2.62</v>
+      </c>
+      <c r="Q106">
+        <v>3</v>
+      </c>
+      <c r="R106">
+        <v>1.92</v>
+      </c>
+      <c r="S106">
+        <v>1.41</v>
+      </c>
+      <c r="T106">
         <v>2.75</v>
       </c>
-      <c r="Q106">
-        <v>3.24</v>
-      </c>
-      <c r="R106">
-        <v>1.94</v>
-      </c>
-      <c r="S106">
-        <v>1.39</v>
-      </c>
-      <c r="T106">
-        <v>2.61</v>
-      </c>
       <c r="U106">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="V106">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W106">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z106">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA106">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB106">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC106">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD106">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE106">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG106">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.28</v>
       </c>
       <c r="AK106">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17750,19 +17750,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="O107">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P107">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q107">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R107">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S107">
         <v>1.35</v>
@@ -17771,13 +17771,13 @@
         <v>2.76</v>
       </c>
       <c r="U107">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
         <v>1.38</v>
       </c>
       <c r="W107">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.01</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="O116">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P116">
-        <v>3.7</v>
+        <v>2.53</v>
       </c>
       <c r="Q116">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="R116">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S116">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T116">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U116">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V116">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z116">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="AA116">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AB116">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC116">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD116">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE116">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF116">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG116">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="O117">
+        <v>3.6</v>
+      </c>
+      <c r="P117">
         <v>3.7</v>
       </c>
-      <c r="P117">
-        <v>2.53</v>
-      </c>
       <c r="Q117">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="R117">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T117">
-        <v>3.28</v>
+        <v>2.85</v>
       </c>
       <c r="U117">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V117">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W117">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z117">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA117">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB117">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC117">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD117">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE117">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF117">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG117">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O131">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P131">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q131">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="R131">
         <v>2.13</v>
       </c>
       <c r="S131">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T131">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U131">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="V131">
         <v>1.36</v>
       </c>
       <c r="W131">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X131">
         <v>1.02</v>
       </c>
       <c r="Y131">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z131">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA131">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AB131">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC131">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD131">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE131">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF131">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AG131">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK131">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22190,10 +22190,10 @@
         <v>0</v>
       </c>
       <c r="AA134">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB134">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC134">
         <v>0</v>
@@ -22323,10 +22323,10 @@
         <v>1.75</v>
       </c>
       <c r="Q135">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="R135">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S135">
         <v>1.28</v>
@@ -22350,16 +22350,16 @@
         <v>1.18</v>
       </c>
       <c r="Z135">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA135">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB135">
         <v>2.07</v>
       </c>
       <c r="AC135">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="AD135">
         <v>1.41</v>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK135">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O136">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P136">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q136">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="R136">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="S136">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T136">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U136">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V136">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y136">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z136">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA136">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AB136">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC136">
-        <v>3.14</v>
+        <v>2.84</v>
       </c>
       <c r="AD136">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE136">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF136">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG136">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK136">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="O137">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P137">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q137">
-        <v>2.13</v>
+        <v>2.79</v>
       </c>
       <c r="R137">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="S137">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U137">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V137">
+        <v>1.36</v>
+      </c>
+      <c r="W137">
+        <v>1.07</v>
+      </c>
+      <c r="X137">
+        <v>1.01</v>
+      </c>
+      <c r="Y137">
+        <v>1.27</v>
+      </c>
+      <c r="Z137">
+        <v>3.14</v>
+      </c>
+      <c r="AA137">
+        <v>1.89</v>
+      </c>
+      <c r="AB137">
+        <v>1.78</v>
+      </c>
+      <c r="AC137">
+        <v>3.14</v>
+      </c>
+      <c r="AD137">
+        <v>1.27</v>
+      </c>
+      <c r="AE137">
+        <v>1.07</v>
+      </c>
+      <c r="AF137">
+        <v>1.72</v>
+      </c>
+      <c r="AG137">
+        <v>1.95</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>1.25</v>
+      </c>
+      <c r="AK137">
         <v>1.53</v>
-      </c>
-      <c r="W137">
-        <v>1.1</v>
-      </c>
-      <c r="X137">
-        <v>1</v>
-      </c>
-      <c r="Y137">
-        <v>1.18</v>
-      </c>
-      <c r="Z137">
-        <v>3.84</v>
-      </c>
-      <c r="AA137">
-        <v>1.71</v>
-      </c>
-      <c r="AB137">
-        <v>1.98</v>
-      </c>
-      <c r="AC137">
-        <v>2.84</v>
-      </c>
-      <c r="AD137">
-        <v>1.34</v>
-      </c>
-      <c r="AE137">
-        <v>1.09</v>
-      </c>
-      <c r="AF137">
-        <v>1.74</v>
-      </c>
-      <c r="AG137">
-        <v>2.05</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.17</v>
-      </c>
-      <c r="AK137">
-        <v>2.16</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22966,10 +22966,10 @@
         </is>
       </c>
       <c r="N139">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="O139">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P139">
         <v>2.05</v>
@@ -23129,16 +23129,16 @@
         </is>
       </c>
       <c r="N140">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O140">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P140">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q140">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="R140">
         <v>2.45</v>
@@ -23150,13 +23150,13 @@
         <v>3.5</v>
       </c>
       <c r="U140">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="V140">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W140">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X140">
         <v>1.01</v>
@@ -24605,10 +24605,10 @@
         <v>0</v>
       </c>
       <c r="Q149">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R149">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="S149">
         <v>1.16</v>
@@ -24617,10 +24617,10 @@
         <v>4.6</v>
       </c>
       <c r="U149">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V149">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W149">
         <v>1.24</v>
@@ -24632,28 +24632,28 @@
         <v>1.06</v>
       </c>
       <c r="Z149">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AA149">
         <v>1.3</v>
       </c>
       <c r="AB149">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AC149">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD149">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE149">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF149">
         <v>1.5</v>
       </c>
       <c r="AG149">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK149">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="N159">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O159">
         <v>4.6</v>
@@ -26265,7 +26265,7 @@
         <v>3.58</v>
       </c>
       <c r="AA159">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB159">
         <v>1.99</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="O169">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P169">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="Q169">
         <v>3.09</v>
@@ -27871,40 +27871,40 @@
         <v>2.25</v>
       </c>
       <c r="S169">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T169">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U169">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V169">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W169">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X169">
         <v>1.01</v>
       </c>
       <c r="Y169">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z169">
         <v>4.33</v>
       </c>
       <c r="AA169">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB169">
         <v>2.25</v>
       </c>
       <c r="AC169">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AD169">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE169">
         <v>1.15</v>
@@ -27913,7 +27913,7 @@
         <v>1.51</v>
       </c>
       <c r="AG169">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O170">
         <v>3.82</v>
@@ -30301,25 +30301,25 @@
         </is>
       </c>
       <c r="N184">
-        <v>6.31</v>
+        <v>5.5</v>
       </c>
       <c r="O184">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="P184">
         <v>1.39</v>
       </c>
       <c r="Q184">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="R184">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="S184">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T184">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="U184">
         <v>2.05</v>
@@ -30334,31 +30334,31 @@
         <v>1.01</v>
       </c>
       <c r="Y184">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z184">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA184">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB184">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AC184">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AD184">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE184">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF184">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG184">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -31285,10 +31285,10 @@
         <v>3.5</v>
       </c>
       <c r="P190">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q190">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R190">
         <v>2.24</v>
@@ -33111,7 +33111,7 @@
         <v>3.2</v>
       </c>
       <c r="AA201">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB201">
         <v>1.79</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O209">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="P209">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O212">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P212">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -36667,22 +36667,22 @@
         <v>4</v>
       </c>
       <c r="Q223">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="R223">
         <v>2.25</v>
       </c>
       <c r="S223">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T223">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="U223">
         <v>2.75</v>
       </c>
       <c r="V223">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W223">
         <v>1.08</v>
@@ -36691,31 +36691,31 @@
         <v>1.01</v>
       </c>
       <c r="Y223">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z223">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA223">
+        <v>1.86</v>
+      </c>
+      <c r="AB223">
         <v>1.81</v>
       </c>
-      <c r="AB223">
-        <v>1.86</v>
-      </c>
       <c r="AC223">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD223">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE223">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF223">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG223">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36731,7 +36731,7 @@
         <v>1.21</v>
       </c>
       <c r="AK223">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R228">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S228">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T228">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U228">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V228">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W228">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y228">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z228">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA228">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB228">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC228">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD228">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE228">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF228">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG228">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK228">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R229">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S229">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T229">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U229">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V229">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W229">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X229">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y229">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z229">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA229">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB229">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC229">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD229">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE229">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF229">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG229">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK229">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -38288,16 +38288,16 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="O233">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P233">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q233">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R233">
         <v>2.1</v>
@@ -38306,46 +38306,46 @@
         <v>1.44</v>
       </c>
       <c r="T233">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="U233">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V233">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W233">
         <v>1.03</v>
       </c>
       <c r="X233">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y233">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z233">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AA233">
         <v>2.1</v>
       </c>
       <c r="AB233">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC233">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AD233">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE233">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF233">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AG233">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38620,19 +38620,19 @@
         <v>3.45</v>
       </c>
       <c r="P235">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q235">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="R235">
         <v>2.19</v>
       </c>
       <c r="S235">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T235">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U235">
         <v>2.42</v>
@@ -38647,7 +38647,7 @@
         <v>1.03</v>
       </c>
       <c r="Y235">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z235">
         <v>3.98</v>
@@ -38659,7 +38659,7 @@
         <v>2.06</v>
       </c>
       <c r="AC235">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="AD235">
         <v>1.39</v>
@@ -38668,10 +38668,10 @@
         <v>1.12</v>
       </c>
       <c r="AF235">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG235">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -40253,7 +40253,7 @@
         <v>4.33</v>
       </c>
       <c r="Q245">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R245">
         <v>2.38</v>
@@ -40262,7 +40262,7 @@
         <v>1.25</v>
       </c>
       <c r="T245">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U245">
         <v>2.24</v>
@@ -40271,7 +40271,7 @@
         <v>1.57</v>
       </c>
       <c r="W245">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X245">
         <v>1.01</v>
@@ -40280,13 +40280,13 @@
         <v>1.12</v>
       </c>
       <c r="Z245">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="AA245">
         <v>1.57</v>
       </c>
       <c r="AB245">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC245">
         <v>2.4</v>
@@ -40295,13 +40295,13 @@
         <v>1.53</v>
       </c>
       <c r="AE245">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF245">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG245">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Omonia 29is Maiou</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G248">
@@ -40733,64 +40733,64 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="O248">
-        <v>3.22</v>
+        <v>3.42</v>
       </c>
       <c r="P248">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q248">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="R248">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S248">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T248">
-        <v>2.83</v>
+        <v>3.26</v>
       </c>
       <c r="U248">
-        <v>2.71</v>
+        <v>2.29</v>
       </c>
       <c r="V248">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W248">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X248">
         <v>1.01</v>
       </c>
       <c r="Y248">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z248">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA248">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB248">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AC248">
-        <v>3.34</v>
+        <v>2.52</v>
       </c>
       <c r="AD248">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AE248">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AF248">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG248">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK248">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Omonia 29is Maiou</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G249">
@@ -40896,64 +40896,64 @@
         </is>
       </c>
       <c r="N249">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O249">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="P249">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="Q249">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="R249">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="S249">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T249">
-        <v>3.26</v>
+        <v>2.83</v>
       </c>
       <c r="U249">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="V249">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W249">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X249">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y249">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="Z249">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA249">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB249">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AC249">
-        <v>2.52</v>
+        <v>3.34</v>
       </c>
       <c r="AD249">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE249">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF249">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AG249">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK249">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>6.58</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -43531,7 +43531,7 @@
         <v>1.46</v>
       </c>
       <c r="W265">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X265">
         <v>1.02</v>
@@ -45505,10 +45505,10 @@
         <v>3.08</v>
       </c>
       <c r="AC277">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD277">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE277">
         <v>1.36</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O279">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P279">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="Q279">
         <v>2.75</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,31 +47905,31 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="O292">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P292">
-        <v>3.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q292">
-        <v>2.85</v>
+        <v>3.87</v>
       </c>
       <c r="R292">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="S292">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T292">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U292">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="V292">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W292">
         <v>1.03</v>
@@ -47938,31 +47938,31 @@
         <v>1.05</v>
       </c>
       <c r="Y292">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z292">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AA292">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB292">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC292">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="AD292">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE292">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF292">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG292">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK292">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="O293">
+        <v>3.65</v>
+      </c>
+      <c r="P293">
+        <v>4.35</v>
+      </c>
+      <c r="Q293">
+        <v>2.15</v>
+      </c>
+      <c r="R293">
+        <v>2.2</v>
+      </c>
+      <c r="S293">
+        <v>1.36</v>
+      </c>
+      <c r="T293">
         <v>3</v>
       </c>
-      <c r="P293">
-        <v>2.37</v>
-      </c>
-      <c r="Q293">
-        <v>3.87</v>
-      </c>
-      <c r="R293">
-        <v>1.89</v>
-      </c>
-      <c r="S293">
-        <v>1.44</v>
-      </c>
-      <c r="T293">
-        <v>2.45</v>
-      </c>
       <c r="U293">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V293">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W293">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X293">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y293">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="Z293">
-        <v>2.52</v>
+        <v>3.28</v>
       </c>
       <c r="AA293">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AB293">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AC293">
-        <v>4.33</v>
+        <v>3.17</v>
       </c>
       <c r="AD293">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AE293">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF293">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG293">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK293">
-        <v>1.34</v>
+        <v>2.23</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="O294">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="P294">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="Q294">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="R294">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S294">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T294">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U294">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="V294">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W294">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X294">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y294">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z294">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="AA294">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AB294">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AC294">
-        <v>3.17</v>
+        <v>4.41</v>
       </c>
       <c r="AD294">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE294">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF294">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG294">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK294">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -49870,22 +49870,22 @@
         <v>2.88</v>
       </c>
       <c r="Q304">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R304">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S304">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T304">
-        <v>3.72</v>
+        <v>3.78</v>
       </c>
       <c r="U304">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="V304">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W304">
         <v>1.12</v>
@@ -49894,31 +49894,31 @@
         <v>1.01</v>
       </c>
       <c r="Y304">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z304">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA304">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB304">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AC304">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD304">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE304">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF304">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG304">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49931,10 +49931,10 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK304">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -50516,61 +50516,61 @@
         <v>1.85</v>
       </c>
       <c r="O308">
-        <v>4.2</v>
+        <v>4.02</v>
       </c>
       <c r="P308">
         <v>3.4</v>
       </c>
       <c r="Q308">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R308">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S308">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T308">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U308">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V308">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W308">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X308">
         <v>0</v>
       </c>
       <c r="Y308">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z308">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="AA308">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB308">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC308">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AD308">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF308">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG308">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH308" t="inlineStr">
         <is>
@@ -50583,10 +50583,10 @@
         </is>
       </c>
       <c r="AJ308">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK308">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL308">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -647,7 +647,7 @@
         <v>2.38</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S2">
         <v>1.4</v>
@@ -656,16 +656,16 @@
         <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.06</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -677,19 +677,19 @@
         <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD2">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE2">
         <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG2">
         <v>1.9</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -822,7 +822,7 @@
         <v>2.82</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -964,7 +964,7 @@
         <v>1.4</v>
       </c>
       <c r="O4">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="P4">
         <v>5.75</v>
@@ -988,7 +988,7 @@
         <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1148,7 +1148,7 @@
         <v>2.64</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1157,16 +1157,16 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB5">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC5">
         <v>3.08</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
         <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>7.02</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
         <v>3.24</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
+        <v>1.17</v>
+      </c>
+      <c r="Z7">
+        <v>3.96</v>
+      </c>
+      <c r="AA7">
+        <v>1.66</v>
+      </c>
+      <c r="AB7">
+        <v>2.05</v>
+      </c>
+      <c r="AC7">
+        <v>2.62</v>
+      </c>
+      <c r="AD7">
+        <v>1.42</v>
+      </c>
+      <c r="AE7">
         <v>1.15</v>
       </c>
-      <c r="Z7">
-        <v>4.3</v>
-      </c>
-      <c r="AA7">
-        <v>1.57</v>
-      </c>
-      <c r="AB7">
-        <v>2.25</v>
-      </c>
-      <c r="AC7">
-        <v>2.38</v>
-      </c>
-      <c r="AD7">
-        <v>1.46</v>
-      </c>
-      <c r="AE7">
-        <v>1.16</v>
-      </c>
       <c r="AF7">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
@@ -1803,37 +1803,37 @@
         <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
         <v>3.23</v>
       </c>
       <c r="AA9">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AB9">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
         <v>1.91</v>
@@ -1966,7 +1966,7 @@
         <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.04</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q11">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="U11">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>2.46</v>
+        <v>4.15</v>
       </c>
       <c r="AA11">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>4.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD11">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="Z12">
-        <v>4.15</v>
+        <v>2.46</v>
       </c>
       <c r="AA12">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC12">
-        <v>2.43</v>
+        <v>4.4</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AG12">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>2.29</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>1.77</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
         <v>3.7</v>
@@ -2443,7 +2443,7 @@
         <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T13">
         <v>3.2</v>
@@ -2479,7 +2479,7 @@
         <v>1.35</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -4405,13 +4405,13 @@
         <v>4.25</v>
       </c>
       <c r="U25">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4420,7 +4420,7 @@
         <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>6.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA25">
         <v>1.28</v>
@@ -4432,7 +4432,7 @@
         <v>1.79</v>
       </c>
       <c r="AD25">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AE25">
         <v>1.37</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5534,7 +5534,7 @@
         <v>5.58</v>
       </c>
       <c r="Q32">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R32">
         <v>2.07</v>
@@ -5579,10 +5579,10 @@
         <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
         <v>1.74</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>6.26</v>
       </c>
       <c r="Q41">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA41">
         <v>2.05</v>
       </c>
       <c r="AB41">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC41">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AG41">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>6.26</v>
+        <v>3.53</v>
       </c>
       <c r="Q42">
-        <v>2</v>
+        <v>2.77</v>
       </c>
       <c r="R42">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T42">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="U42">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y42">
+        <v>1.44</v>
+      </c>
+      <c r="Z42">
+        <v>2.42</v>
+      </c>
+      <c r="AA42">
+        <v>2.41</v>
+      </c>
+      <c r="AB42">
+        <v>1.48</v>
+      </c>
+      <c r="AC42">
+        <v>4.6</v>
+      </c>
+      <c r="AD42">
+        <v>1.13</v>
+      </c>
+      <c r="AE42">
+        <v>1.01</v>
+      </c>
+      <c r="AF42">
+        <v>2.07</v>
+      </c>
+      <c r="AG42">
+        <v>1.66</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.28</v>
       </c>
-      <c r="Z42">
-        <v>3.05</v>
-      </c>
-      <c r="AA42">
-        <v>2.05</v>
-      </c>
-      <c r="AB42">
-        <v>1.75</v>
-      </c>
-      <c r="AC42">
-        <v>3.5</v>
-      </c>
-      <c r="AD42">
-        <v>1.22</v>
-      </c>
-      <c r="AE42">
-        <v>1.05</v>
-      </c>
-      <c r="AF42">
-        <v>2.14</v>
-      </c>
-      <c r="AG42">
-        <v>1.62</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.2</v>
-      </c>
       <c r="AK42">
-        <v>2.5</v>
+        <v>1.61</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P43">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="R43">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="S43">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="T43">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="U43">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="V43">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="AC43">
-        <v>4.6</v>
+        <v>3.72</v>
       </c>
       <c r="AD43">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG43">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7991,7 +7991,7 @@
         <v>3.26</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="V47">
         <v>1.49</v>
@@ -8824,7 +8824,7 @@
         <v>3.08</v>
       </c>
       <c r="AA52">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB52">
         <v>1.86</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O54">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P54">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q54">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R54">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="S54">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
         <v>3.42</v>
       </c>
       <c r="U54">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V54">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W54">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z54">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA54">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB54">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC54">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AD54">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE54">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF54">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG54">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.08</v>
       </c>
       <c r="AK54">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10261,13 +10261,13 @@
         <v>7.5</v>
       </c>
       <c r="Q61">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R61">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="S61">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
         <v>4</v>
@@ -10276,7 +10276,7 @@
         <v>2.01</v>
       </c>
       <c r="V61">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
         <v>1.18</v>
@@ -10424,10 +10424,10 @@
         <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="R62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
         <v>1.35</v>
@@ -12220,7 +12220,7 @@
         <v>2.3</v>
       </c>
       <c r="R73">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S73">
         <v>1.19</v>
@@ -12229,7 +12229,7 @@
         <v>3.74</v>
       </c>
       <c r="U73">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="V73">
         <v>1.78</v>
@@ -12244,13 +12244,13 @@
         <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>6.23</v>
+        <v>6.2</v>
       </c>
       <c r="AA73">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AB73">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AC73">
         <v>1.88</v>
@@ -12374,7 +12374,7 @@
         <v>2.33</v>
       </c>
       <c r="O74">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="P74">
         <v>2.45</v>
@@ -12395,7 +12395,7 @@
         <v>2.16</v>
       </c>
       <c r="V74">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W74">
         <v>1.17</v>
@@ -14016,16 +14016,16 @@
         <v>2.35</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="U84">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="V84">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W84">
         <v>1.14</v>
@@ -14034,31 +14034,31 @@
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z84">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="AA84">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AB84">
         <v>2.49</v>
       </c>
       <c r="AC84">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AD84">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE84">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>2.04</v>
       </c>
       <c r="AB88">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC88">
         <v>3.42</v>
@@ -15000,10 +15000,10 @@
         <v>3.12</v>
       </c>
       <c r="U90">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V90">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W90">
         <v>1.1</v>
@@ -15015,7 +15015,7 @@
         <v>1.21</v>
       </c>
       <c r="Z90">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA90">
         <v>1.74</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q101">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R101">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S101">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T101">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U101">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="V101">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W101">
         <v>1.04</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z101">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA101">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AB101">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC101">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD101">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE101">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF101">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AG101">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
+        <v>1.37</v>
+      </c>
+      <c r="T102">
+        <v>2.68</v>
+      </c>
+      <c r="U102">
+        <v>2.75</v>
+      </c>
+      <c r="V102">
         <v>1.4</v>
-      </c>
-      <c r="T102">
-        <v>2.75</v>
-      </c>
-      <c r="U102">
-        <v>2.89</v>
-      </c>
-      <c r="V102">
-        <v>1.36</v>
       </c>
       <c r="W102">
         <v>1.04</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z102">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA102">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AB102">
+        <v>1.8</v>
+      </c>
+      <c r="AC102">
+        <v>3.14</v>
+      </c>
+      <c r="AD102">
+        <v>1.27</v>
+      </c>
+      <c r="AE102">
+        <v>1.06</v>
+      </c>
+      <c r="AF102">
         <v>1.69</v>
       </c>
-      <c r="AC102">
-        <v>3.42</v>
-      </c>
-      <c r="AD102">
-        <v>1.23</v>
-      </c>
-      <c r="AE102">
-        <v>1.05</v>
-      </c>
-      <c r="AF102">
-        <v>1.77</v>
-      </c>
       <c r="AG102">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18782,7 +18782,7 @@
         <v>1.11</v>
       </c>
       <c r="AF113">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG113">
         <v>2.21</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
         <v>2.3</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.42</v>
+        <v>2.09</v>
       </c>
       <c r="O116">
+        <v>3.6</v>
+      </c>
+      <c r="P116">
         <v>3.7</v>
       </c>
-      <c r="P116">
-        <v>2.53</v>
-      </c>
       <c r="Q116">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="R116">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S116">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T116">
-        <v>3.28</v>
+        <v>2.85</v>
       </c>
       <c r="U116">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V116">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W116">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z116">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA116">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AB116">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC116">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD116">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE116">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF116">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG116">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="O117">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P117">
-        <v>3.7</v>
+        <v>2.53</v>
       </c>
       <c r="Q117">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S117">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T117">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U117">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V117">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W117">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z117">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="AA117">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AB117">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC117">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD117">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF117">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19878,7 +19878,7 @@
         <v>2.12</v>
       </c>
       <c r="Q120">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R120">
         <v>2.3</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O122">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P122">
-        <v>4.3</v>
+        <v>4.55</v>
       </c>
       <c r="Q122">
         <v>2.05</v>
@@ -20757,7 +20757,7 @@
         <v>1.22</v>
       </c>
       <c r="AK125">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -21336,25 +21336,25 @@
         </is>
       </c>
       <c r="N129">
+        <v>1.67</v>
+      </c>
+      <c r="O129">
+        <v>3.7</v>
+      </c>
+      <c r="P129">
+        <v>4</v>
+      </c>
+      <c r="Q129">
+        <v>2.27</v>
+      </c>
+      <c r="R129">
         <v>2.22</v>
       </c>
-      <c r="O129">
-        <v>3.3</v>
-      </c>
-      <c r="P129">
-        <v>2.93</v>
-      </c>
-      <c r="Q129">
-        <v>2.15</v>
-      </c>
-      <c r="R129">
-        <v>2.44</v>
-      </c>
       <c r="S129">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T129">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U129">
         <v>2.5</v>
@@ -21363,7 +21363,7 @@
         <v>1.5</v>
       </c>
       <c r="W129">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X129">
         <v>1.02</v>
@@ -21372,28 +21372,28 @@
         <v>1.17</v>
       </c>
       <c r="Z129">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA129">
+        <v>1.61</v>
+      </c>
+      <c r="AB129">
+        <v>2.25</v>
+      </c>
+      <c r="AC129">
+        <v>2.59</v>
+      </c>
+      <c r="AD129">
+        <v>1.39</v>
+      </c>
+      <c r="AE129">
+        <v>1.12</v>
+      </c>
+      <c r="AF129">
         <v>1.6</v>
       </c>
-      <c r="AB129">
-        <v>2.2</v>
-      </c>
-      <c r="AC129">
-        <v>2.42</v>
-      </c>
-      <c r="AD129">
-        <v>1.49</v>
-      </c>
-      <c r="AE129">
-        <v>1.18</v>
-      </c>
-      <c r="AF129">
-        <v>1.63</v>
-      </c>
       <c r="AG129">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK129">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="O130">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="P130">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q130">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R130">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="S130">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T130">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="U130">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="V130">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="W130">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="X130">
         <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z130">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA130">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB130">
         <v>3</v>
       </c>
       <c r="AC130">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD130">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE130">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AF130">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AG130">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK130">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21825,58 +21825,58 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O132">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P132">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="Q132">
+        <v>2.3</v>
+      </c>
+      <c r="R132">
         <v>2.2</v>
       </c>
-      <c r="R132">
-        <v>2.3</v>
-      </c>
       <c r="S132">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T132">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="U132">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V132">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W132">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
         <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z132">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="AA132">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB132">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AC132">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="AD132">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE132">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF132">
         <v>1.7</v>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22504,7 +22504,7 @@
         <v>1.53</v>
       </c>
       <c r="W136">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X136">
         <v>1</v>
@@ -22516,13 +22516,13 @@
         <v>3.84</v>
       </c>
       <c r="AA136">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB136">
         <v>1.98</v>
       </c>
       <c r="AC136">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="AD136">
         <v>1.34</v>
@@ -26063,34 +26063,34 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="O158">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="P158">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q158">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R158">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="S158">
         <v>1.24</v>
       </c>
       <c r="T158">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U158">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V158">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W158">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X158">
         <v>1.01</v>
@@ -26117,10 +26117,10 @@
         <v>1.2</v>
       </c>
       <c r="AF158">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AG158">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AK158">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26606,7 +26606,7 @@
         <v>1.1</v>
       </c>
       <c r="AF161">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG161">
         <v>2.2</v>
@@ -28073,7 +28073,7 @@
         <v>1.15</v>
       </c>
       <c r="AF170">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG170">
         <v>1.82</v>
@@ -28997,7 +28997,7 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O176">
         <v>3.6</v>
@@ -29039,7 +29039,7 @@
         <v>1.43</v>
       </c>
       <c r="AB176">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC176">
         <v>2.17</v>
@@ -30992,7 +30992,7 @@
         <v>3.08</v>
       </c>
       <c r="AA188">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB188">
         <v>1.8</v>
@@ -31807,10 +31807,10 @@
         <v>2.56</v>
       </c>
       <c r="AA193">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AB193">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC193">
         <v>4.55</v>
@@ -34539,64 +34539,64 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R210">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S210">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T210">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U210">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V210">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W210">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X210">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y210">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z210">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE210">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF210">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG210">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH210" t="inlineStr">
         <is>
@@ -34609,10 +34609,10 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK210">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL210">
         <v>0</v>
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="O211">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="P211">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R211">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S211">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T211">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U211">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V211">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W211">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X211">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z211">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE211">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF211">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG211">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK211">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q212">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R212">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S212">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T212">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U212">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V212">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W212">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X212">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z212">
-        <v>0</v>
+        <v>5.59</v>
       </c>
       <c r="AA212">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB212">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC212">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD212">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE212">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF212">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG212">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK212">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.82</v>
+        <v>1.29</v>
       </c>
       <c r="O213">
-        <v>3.91</v>
+        <v>5.2</v>
       </c>
       <c r="P213">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R213">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S213">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T213">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U213">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V213">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W213">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X213">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z213">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE213">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF213">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG213">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK213">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R214">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S214">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T214">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U214">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V214">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W214">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X214">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z214">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AC214">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD214">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE214">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF214">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG214">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK214">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -39272,19 +39272,19 @@
         <v>3.3</v>
       </c>
       <c r="P239">
+        <v>2.22</v>
+      </c>
+      <c r="Q239">
+        <v>3.4</v>
+      </c>
+      <c r="R239">
         <v>2.2</v>
-      </c>
-      <c r="Q239">
-        <v>3.5</v>
-      </c>
-      <c r="R239">
-        <v>2.09</v>
       </c>
       <c r="S239">
         <v>1.33</v>
       </c>
       <c r="T239">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="U239">
         <v>2.53</v>
@@ -40081,10 +40081,10 @@
         </is>
       </c>
       <c r="N244">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O244">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P244">
         <v>2</v>
@@ -41590,7 +41590,7 @@
         <v>1.55</v>
       </c>
       <c r="AB253">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AC253">
         <v>2.44</v>
@@ -41913,7 +41913,7 @@
         <v>3.14</v>
       </c>
       <c r="AA255">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB255">
         <v>1.85</v>
@@ -43196,10 +43196,10 @@
         <v>1.3</v>
       </c>
       <c r="T263">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="U263">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V263">
         <v>1.5</v>
@@ -43217,22 +43217,22 @@
         <v>3</v>
       </c>
       <c r="AA263">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AB263">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="AC263">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD263">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE263">
         <v>1.09</v>
       </c>
       <c r="AF263">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG263">
         <v>1.95</v>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AK263">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43383,7 +43383,7 @@
         <v>2.13</v>
       </c>
       <c r="AB264">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC264">
         <v>3.98</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O266">
         <v>5</v>
       </c>
       <c r="P266">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q266">
         <v>1.7</v>
@@ -43682,49 +43682,49 @@
         <v>2.5</v>
       </c>
       <c r="S266">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T266">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U266">
         <v>2.32</v>
       </c>
       <c r="V266">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W266">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X266">
         <v>1.02</v>
       </c>
       <c r="Y266">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z266">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA266">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB266">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AC266">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="AD266">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE266">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF266">
         <v>1.73</v>
       </c>
       <c r="AG266">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O273">
         <v>3.4</v>
       </c>
       <c r="P273">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44847,10 +44847,10 @@
         <v>0</v>
       </c>
       <c r="AA273">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AB273">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC273">
         <v>0</v>
@@ -47102,7 +47102,7 @@
         <v>4.33</v>
       </c>
       <c r="R287">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S287">
         <v>1.2</v>
@@ -47111,7 +47111,7 @@
         <v>4</v>
       </c>
       <c r="U287">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V287">
         <v>1.67</v>
@@ -47135,16 +47135,16 @@
         <v>2.7</v>
       </c>
       <c r="AC287">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD287">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE287">
         <v>1.26</v>
       </c>
       <c r="AF287">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG287">
         <v>2.5</v>
@@ -47434,7 +47434,7 @@
         <v>1.5</v>
       </c>
       <c r="T289">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="U289">
         <v>3.26</v>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O290">
         <v>3</v>
       </c>
       <c r="P290">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q290">
         <v>2.8</v>
@@ -47633,10 +47633,10 @@
         <v>1</v>
       </c>
       <c r="AF290">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG290">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47760,16 +47760,16 @@
         <v>1.21</v>
       </c>
       <c r="T291">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="U291">
         <v>2.07</v>
       </c>
       <c r="V291">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W291">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X291">
         <v>1.01</v>
@@ -47781,25 +47781,25 @@
         <v>6.5</v>
       </c>
       <c r="AA291">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AB291">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AC291">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AD291">
+        <v>1.86</v>
+      </c>
+      <c r="AE291">
+        <v>1.3</v>
+      </c>
+      <c r="AF291">
+        <v>1.8</v>
+      </c>
+      <c r="AG291">
         <v>1.93</v>
-      </c>
-      <c r="AE291">
-        <v>1.33</v>
-      </c>
-      <c r="AF291">
-        <v>1.72</v>
-      </c>
-      <c r="AG291">
-        <v>2</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>1.12</v>
       </c>
       <c r="AK291">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O293">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P293">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q293">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="R293">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S293">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T293">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U293">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="V293">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W293">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X293">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y293">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z293">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="AA293">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AB293">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AC293">
-        <v>3.17</v>
+        <v>4.41</v>
       </c>
       <c r="AD293">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE293">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF293">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG293">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK293">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,64 +48231,64 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="O294">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="P294">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="Q294">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="R294">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S294">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="T294">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="U294">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="V294">
+        <v>1.37</v>
+      </c>
+      <c r="W294">
+        <v>1.04</v>
+      </c>
+      <c r="X294">
+        <v>1.01</v>
+      </c>
+      <c r="Y294">
         <v>1.28</v>
       </c>
-      <c r="W294">
-        <v>1.03</v>
-      </c>
-      <c r="X294">
-        <v>1.05</v>
-      </c>
-      <c r="Y294">
-        <v>1.4</v>
-      </c>
       <c r="Z294">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AA294">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="AB294">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="AC294">
-        <v>4.41</v>
+        <v>3.17</v>
       </c>
       <c r="AD294">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AE294">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF294">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG294">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH294" t="inlineStr">
         <is>
@@ -48301,10 +48301,10 @@
         </is>
       </c>
       <c r="AJ294">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK294">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="AL294">
         <v>0</v>
@@ -48883,16 +48883,16 @@
         </is>
       </c>
       <c r="N298">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O298">
         <v>2.95</v>
       </c>
       <c r="P298">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q298">
-        <v>4.38</v>
+        <v>4.17</v>
       </c>
       <c r="R298">
         <v>1.82</v>
@@ -48913,7 +48913,7 @@
         <v>1.01</v>
       </c>
       <c r="X298">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y298">
         <v>1.47</v>
@@ -48928,7 +48928,7 @@
         <v>1.5</v>
       </c>
       <c r="AC298">
-        <v>5.24</v>
+        <v>5.2</v>
       </c>
       <c r="AD298">
         <v>1.14</v>
@@ -48940,7 +48940,7 @@
         <v>2</v>
       </c>
       <c r="AG298">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AK298">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -50024,64 +50024,64 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="O305">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="P305">
-        <v>4.21</v>
+        <v>3.7</v>
       </c>
       <c r="Q305">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R305">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S305">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T305">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U305">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V305">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W305">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X305">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y305">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z305">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA305">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB305">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC305">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="AD305">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF305">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG305">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK305">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50187,64 +50187,64 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O306">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P306">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q306">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R306">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S306">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T306">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U306">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V306">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W306">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X306">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y306">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z306">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA306">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB306">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC306">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD306">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE306">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF306">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG306">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50257,10 +50257,10 @@
         </is>
       </c>
       <c r="AJ306">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK306">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50374,10 +50374,10 @@
         <v>2.2</v>
       </c>
       <c r="V307">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W307">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X307">
         <v>1.02</v>
@@ -50389,25 +50389,25 @@
         <v>5.1</v>
       </c>
       <c r="AA307">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AB307">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="AC307">
-        <v>2.29</v>
+        <v>1.99</v>
       </c>
       <c r="AD307">
         <v>1.43</v>
       </c>
       <c r="AE307">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF307">
         <v>1.33</v>
       </c>
       <c r="AG307">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="O309">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P309">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="Q309">
         <v>3.25</v>
@@ -50700,19 +50700,19 @@
         <v>3.2</v>
       </c>
       <c r="V309">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W309">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X309">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y309">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z309">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA309">
         <v>2.07</v>
@@ -50721,13 +50721,13 @@
         <v>1.64</v>
       </c>
       <c r="AC309">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AD309">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE309">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF309">
         <v>1.83</v>
@@ -50746,7 +50746,7 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK309">
         <v>1.36</v>
@@ -50848,13 +50848,13 @@
         <v>2.98</v>
       </c>
       <c r="Q310">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R310">
         <v>2.4</v>
       </c>
       <c r="S310">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T310">
         <v>3.9</v>
@@ -50866,7 +50866,7 @@
         <v>1.67</v>
       </c>
       <c r="W310">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X310">
         <v>1.02</v>
@@ -50878,7 +50878,7 @@
         <v>5.2</v>
       </c>
       <c r="AA310">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB310">
         <v>2.56</v>
@@ -50896,7 +50896,7 @@
         <v>1.4</v>
       </c>
       <c r="AG310">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>1.18</v>
       </c>
       <c r="AK310">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51002,13 +51002,13 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="O311">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P311">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="Q311">
         <v>3.6</v>
@@ -51168,7 +51168,7 @@
         <v>2.2</v>
       </c>
       <c r="O312">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P312">
         <v>2.8</v>
@@ -51183,13 +51183,13 @@
         <v>1.36</v>
       </c>
       <c r="T312">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U312">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V312">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W312">
         <v>1.07</v>
@@ -51198,16 +51198,16 @@
         <v>1.01</v>
       </c>
       <c r="Y312">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z312">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="AA312">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB312">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC312">
         <v>3.2</v>
@@ -51222,7 +51222,7 @@
         <v>1.7</v>
       </c>
       <c r="AG312">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK312">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="O313">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P313">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="Q313">
         <v>3.48</v>
@@ -51370,7 +51370,7 @@
         <v>1.88</v>
       </c>
       <c r="AB313">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC313">
         <v>2.97</v>
@@ -51666,7 +51666,7 @@
         <v>7.55</v>
       </c>
       <c r="R315">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S315">
         <v>1.24</v>
@@ -51681,16 +51681,16 @@
         <v>1.5</v>
       </c>
       <c r="W315">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X315">
         <v>1.02</v>
       </c>
       <c r="Y315">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z315">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA315">
         <v>1.56</v>
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="AJ315">
-        <v>1.14</v>
+        <v>3.1</v>
       </c>
       <c r="AK315">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AL315">
         <v>0</v>
@@ -51829,7 +51829,7 @@
         <v>2.4</v>
       </c>
       <c r="R316">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S316">
         <v>1.2</v>
@@ -51838,10 +51838,10 @@
         <v>4</v>
       </c>
       <c r="U316">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V316">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W316">
         <v>1.2</v>
@@ -51850,10 +51850,10 @@
         <v>1.01</v>
       </c>
       <c r="Y316">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z316">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA316">
         <v>1.36</v>
@@ -51871,10 +51871,10 @@
         <v>1.26</v>
       </c>
       <c r="AF316">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG316">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
@@ -51890,7 +51890,7 @@
         <v>1.18</v>
       </c>
       <c r="AK316">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AL316">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
         <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
         <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK6">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="O7">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>7.02</v>
+        <v>4</v>
       </c>
       <c r="Q7">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="R7">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
         <v>3.24</v>
       </c>
       <c r="U7">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.3</v>
+        <v>3.96</v>
       </c>
       <c r="AA7">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC7">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
         <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T11">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="Z11">
-        <v>4.15</v>
+        <v>2.46</v>
       </c>
       <c r="AA11">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC11">
-        <v>2.43</v>
+        <v>4.4</v>
       </c>
       <c r="AD11">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AG11">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
+        <v>1.57</v>
+      </c>
+      <c r="O12">
+        <v>3.95</v>
+      </c>
+      <c r="P12">
+        <v>4.5</v>
+      </c>
+      <c r="Q12">
+        <v>2.1</v>
+      </c>
+      <c r="R12">
+        <v>2.38</v>
+      </c>
+      <c r="S12">
+        <v>1.25</v>
+      </c>
+      <c r="T12">
+        <v>3.4</v>
+      </c>
+      <c r="U12">
+        <v>2.38</v>
+      </c>
+      <c r="V12">
+        <v>1.5</v>
+      </c>
+      <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.16</v>
+      </c>
+      <c r="Z12">
+        <v>4.15</v>
+      </c>
+      <c r="AA12">
+        <v>1.62</v>
+      </c>
+      <c r="AB12">
         <v>2.2</v>
       </c>
-      <c r="O12">
-        <v>3</v>
-      </c>
-      <c r="P12">
-        <v>3.1</v>
-      </c>
-      <c r="Q12">
-        <v>2.88</v>
-      </c>
-      <c r="R12">
-        <v>1.85</v>
-      </c>
-      <c r="S12">
-        <v>1.45</v>
-      </c>
-      <c r="T12">
-        <v>2.55</v>
-      </c>
-      <c r="U12">
-        <v>3.3</v>
-      </c>
-      <c r="V12">
-        <v>1.29</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>1.43</v>
-      </c>
-      <c r="Z12">
-        <v>2.46</v>
-      </c>
-      <c r="AA12">
-        <v>2.34</v>
-      </c>
-      <c r="AB12">
-        <v>1.53</v>
-      </c>
       <c r="AC12">
-        <v>4.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD12">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG12">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R15">
         <v>2.3</v>
@@ -2772,40 +2772,40 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AA15">
         <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AC15">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD15">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE15">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
         <v>1.57</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK15">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3252,71 +3252,71 @@
         <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R18">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="S18">
+        <v>1.44</v>
+      </c>
+      <c r="T18">
+        <v>2.63</v>
+      </c>
+      <c r="U18">
+        <v>3.12</v>
+      </c>
+      <c r="V18">
+        <v>1.28</v>
+      </c>
+      <c r="W18">
+        <v>1.03</v>
+      </c>
+      <c r="X18">
+        <v>1.06</v>
+      </c>
+      <c r="Y18">
         <v>1.37</v>
       </c>
-      <c r="T18">
-        <v>2.69</v>
-      </c>
-      <c r="U18">
-        <v>2.86</v>
-      </c>
-      <c r="V18">
-        <v>1.33</v>
-      </c>
-      <c r="W18">
-        <v>1.06</v>
-      </c>
-      <c r="X18">
-        <v>1.03</v>
-      </c>
-      <c r="Y18">
+      <c r="Z18">
+        <v>2.66</v>
+      </c>
+      <c r="AA18">
+        <v>2.27</v>
+      </c>
+      <c r="AB18">
+        <v>1.54</v>
+      </c>
+      <c r="AC18">
+        <v>4.25</v>
+      </c>
+      <c r="AD18">
+        <v>1.15</v>
+      </c>
+      <c r="AE18">
+        <v>1.02</v>
+      </c>
+      <c r="AF18">
+        <v>1.91</v>
+      </c>
+      <c r="AG18">
+        <v>1.78</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
         <v>1.3</v>
       </c>
-      <c r="Z18">
-        <v>2.97</v>
-      </c>
-      <c r="AA18">
-        <v>2.05</v>
-      </c>
-      <c r="AB18">
-        <v>1.66</v>
-      </c>
-      <c r="AC18">
-        <v>3.7</v>
-      </c>
-      <c r="AD18">
-        <v>1.2</v>
-      </c>
-      <c r="AE18">
-        <v>1.03</v>
-      </c>
-      <c r="AF18">
-        <v>1.8</v>
-      </c>
-      <c r="AG18">
-        <v>1.89</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.26</v>
-      </c>
       <c r="AK18">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="R19">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
         <v>3</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="V19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
         <v>1.08</v>
@@ -3439,31 +3439,31 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB19">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
         <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>4.59</v>
       </c>
       <c r="Q20">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="U20">
         <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.04</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
         <v>2.05</v>
@@ -3614,19 +3614,19 @@
         <v>1.75</v>
       </c>
       <c r="AC20">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD20">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>1.68</v>
       </c>
       <c r="Q21">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="R21">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="S21">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="T21">
-        <v>2.89</v>
+        <v>2.61</v>
       </c>
       <c r="U21">
-        <v>2.64</v>
+        <v>2.85</v>
       </c>
       <c r="V21">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="AA21">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AB21">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
-        <v>2.97</v>
+        <v>3.42</v>
       </c>
       <c r="AD21">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE21">
         <v>1.07</v>
       </c>
       <c r="AF21">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AG21">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,22 +3904,22 @@
         <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R22">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="S22">
         <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
         <v>1.04</v>
@@ -3928,31 +3928,31 @@
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="AA22">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="AB22">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>3.58</v>
+        <v>3.95</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
         <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>3.41</v>
+        <v>3.58</v>
       </c>
       <c r="R23">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U23">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="AA23">
         <v>1.8</v>
@@ -4103,19 +4103,19 @@
         <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.81</v>
+        <v>2.64</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.11</v>
+        <v>2.53</v>
       </c>
       <c r="O24">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="P24">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="Q24">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
         <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z24">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="AD24">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AG24">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,22 +5045,22 @@
         <v>3.06</v>
       </c>
       <c r="Q29">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="R29">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="S29">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
         <v>1.05</v>
@@ -5069,31 +5069,31 @@
         <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC29">
-        <v>3.48</v>
+        <v>3.78</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
         <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG29">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.26</v>
+        <v>3.64</v>
       </c>
       <c r="O30">
-        <v>3.26</v>
+        <v>3.31</v>
       </c>
       <c r="P30">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5371,13 +5371,13 @@
         <v>2.63</v>
       </c>
       <c r="Q31">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
         <v>2</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T31">
         <v>2.75</v>
@@ -5392,7 +5392,7 @@
         <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
         <v>1.32</v>
@@ -5404,10 +5404,10 @@
         <v>2.15</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC31">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AD31">
         <v>1.2</v>
@@ -5416,10 +5416,10 @@
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AG31">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,22 +5534,22 @@
         <v>5.58</v>
       </c>
       <c r="Q32">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="R32">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="U32">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W32">
         <v>1.04</v>
@@ -5558,31 +5558,31 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z32">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA32">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
         <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AG32">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="R33">
         <v>2.06</v>
@@ -5709,10 +5709,10 @@
         <v>2.58</v>
       </c>
       <c r="U33">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <v>1.04</v>
@@ -5721,10 +5721,10 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
@@ -5733,19 +5733,19 @@
         <v>1.66</v>
       </c>
       <c r="AC33">
-        <v>3.72</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AG33">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK33">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="R34">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U34">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X34">
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB34">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC34">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD34">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK34">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="R35">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T35">
         <v>2.75</v>
       </c>
       <c r="U35">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V35">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W35">
+        <v>1.03</v>
+      </c>
+      <c r="X35">
         <v>1.04</v>
       </c>
-      <c r="X35">
+      <c r="Y35">
+        <v>1.35</v>
+      </c>
+      <c r="Z35">
+        <v>2.78</v>
+      </c>
+      <c r="AA35">
+        <v>2.15</v>
+      </c>
+      <c r="AB35">
+        <v>1.66</v>
+      </c>
+      <c r="AC35">
+        <v>4.1</v>
+      </c>
+      <c r="AD35">
+        <v>1.16</v>
+      </c>
+      <c r="AE35">
         <v>1.03</v>
       </c>
-      <c r="Y35">
-        <v>1.32</v>
-      </c>
-      <c r="Z35">
-        <v>2.88</v>
-      </c>
-      <c r="AA35">
-        <v>2.1</v>
-      </c>
-      <c r="AB35">
-        <v>1.63</v>
-      </c>
-      <c r="AC35">
-        <v>3.86</v>
-      </c>
-      <c r="AD35">
-        <v>1.18</v>
-      </c>
-      <c r="AE35">
-        <v>1.04</v>
-      </c>
       <c r="AF35">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>2.32</v>
       </c>
       <c r="Q36">
-        <v>3.54</v>
+        <v>3.42</v>
       </c>
       <c r="R36">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U36">
         <v>2.65</v>
@@ -6210,31 +6210,31 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AB36">
         <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
         <v>1.35</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.04</v>
+      </c>
+      <c r="O41">
+        <v>3</v>
+      </c>
+      <c r="P41">
+        <v>3.53</v>
+      </c>
+      <c r="Q41">
+        <v>2.55</v>
+      </c>
+      <c r="R41">
+        <v>1.91</v>
+      </c>
+      <c r="S41">
         <v>1.5</v>
       </c>
-      <c r="O41">
-        <v>3.8</v>
-      </c>
-      <c r="P41">
-        <v>6.26</v>
-      </c>
-      <c r="Q41">
-        <v>2</v>
-      </c>
-      <c r="R41">
-        <v>2.2</v>
-      </c>
-      <c r="S41">
-        <v>1.36</v>
-      </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y41">
+        <v>1.5</v>
+      </c>
+      <c r="Z41">
+        <v>2.47</v>
+      </c>
+      <c r="AA41">
+        <v>2.5</v>
+      </c>
+      <c r="AB41">
+        <v>1.5</v>
+      </c>
+      <c r="AC41">
+        <v>4.65</v>
+      </c>
+      <c r="AD41">
+        <v>1.12</v>
+      </c>
+      <c r="AE41">
+        <v>1.03</v>
+      </c>
+      <c r="AF41">
+        <v>2.19</v>
+      </c>
+      <c r="AG41">
+        <v>1.59</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.28</v>
       </c>
-      <c r="Z41">
-        <v>3.05</v>
-      </c>
-      <c r="AA41">
-        <v>2.05</v>
-      </c>
-      <c r="AB41">
-        <v>1.75</v>
-      </c>
-      <c r="AC41">
-        <v>3.5</v>
-      </c>
-      <c r="AD41">
-        <v>1.22</v>
-      </c>
-      <c r="AE41">
-        <v>1.05</v>
-      </c>
-      <c r="AF41">
-        <v>2.14</v>
-      </c>
-      <c r="AG41">
-        <v>1.62</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.2</v>
-      </c>
       <c r="AK41">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P42">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
-        <v>2.77</v>
+        <v>3.07</v>
       </c>
       <c r="R42">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="S42">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="U42">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="V42">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="Z42">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="AA42">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AC42">
-        <v>4.6</v>
+        <v>3.76</v>
       </c>
       <c r="AD42">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AG42">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
+        <v>1.5</v>
+      </c>
+      <c r="O43">
+        <v>3.8</v>
+      </c>
+      <c r="P43">
+        <v>6.26</v>
+      </c>
+      <c r="Q43">
         <v>2.03</v>
       </c>
-      <c r="O43">
-        <v>3.22</v>
-      </c>
-      <c r="P43">
-        <v>3.3</v>
-      </c>
-      <c r="Q43">
-        <v>2.72</v>
-      </c>
       <c r="R43">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="S43">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="U43">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z43">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA43">
         <v>2.05</v>
       </c>
       <c r="AB43">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC43">
-        <v>3.72</v>
+        <v>3.08</v>
       </c>
       <c r="AD43">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF43">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG43">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,55 +7490,55 @@
         <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="V44">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z44">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="AA44">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB44">
         <v>2.25</v>
       </c>
       <c r="AC44">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD44">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF44">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>1.61</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P47">
         <v>4.33</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Q50">
-        <v>2.29</v>
+        <v>2.06</v>
       </c>
       <c r="R50">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S50">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>2.64</v>
+        <v>2.85</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="V50">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W50">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="AA50">
         <v>1.9</v>
       </c>
       <c r="AB50">
+        <v>1.96</v>
+      </c>
+      <c r="AC50">
+        <v>2.7</v>
+      </c>
+      <c r="AD50">
+        <v>1.36</v>
+      </c>
+      <c r="AE50">
+        <v>1.1</v>
+      </c>
+      <c r="AF50">
         <v>1.78</v>
       </c>
-      <c r="AC50">
-        <v>3.2</v>
-      </c>
-      <c r="AD50">
-        <v>1.26</v>
-      </c>
-      <c r="AE50">
-        <v>1.06</v>
-      </c>
-      <c r="AF50">
-        <v>1.82</v>
-      </c>
       <c r="AG50">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8628,74 +8628,74 @@
         <v>3.1</v>
       </c>
       <c r="P51">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q51">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R51">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U51">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V51">
         <v>1.36</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC51">
-        <v>3.34</v>
+        <v>3.04</v>
       </c>
       <c r="AD51">
+        <v>1.29</v>
+      </c>
+      <c r="AE51">
+        <v>1.07</v>
+      </c>
+      <c r="AF51">
+        <v>1.64</v>
+      </c>
+      <c r="AG51">
+        <v>2.04</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.24</v>
       </c>
-      <c r="AE51">
-        <v>1.04</v>
-      </c>
-      <c r="AF51">
-        <v>1.72</v>
-      </c>
-      <c r="AG51">
-        <v>1.96</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.25</v>
-      </c>
       <c r="AK51">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,55 +8957,55 @@
         <v>3.59</v>
       </c>
       <c r="Q53">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="R53">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S53">
+        <v>1.4</v>
+      </c>
+      <c r="T53">
+        <v>2.45</v>
+      </c>
+      <c r="U53">
+        <v>3.12</v>
+      </c>
+      <c r="V53">
+        <v>1.28</v>
+      </c>
+      <c r="W53">
+        <v>1.04</v>
+      </c>
+      <c r="X53">
+        <v>1.05</v>
+      </c>
+      <c r="Y53">
         <v>1.39</v>
       </c>
-      <c r="T53">
-        <v>2.61</v>
-      </c>
-      <c r="U53">
-        <v>3</v>
-      </c>
-      <c r="V53">
-        <v>1.32</v>
-      </c>
-      <c r="W53">
-        <v>1.05</v>
-      </c>
-      <c r="X53">
-        <v>1.02</v>
-      </c>
-      <c r="Y53">
-        <v>1.3</v>
-      </c>
       <c r="Z53">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA53">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB53">
         <v>1.72</v>
       </c>
       <c r="AC53">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD53">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF53">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG53">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9132,10 +9132,10 @@
         <v>3.42</v>
       </c>
       <c r="U54">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V54">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
         <v>1.13</v>
@@ -9331,7 +9331,7 @@
         <v>1.83</v>
       </c>
       <c r="AG55">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -10424,22 +10424,22 @@
         <v>2.7</v>
       </c>
       <c r="Q62">
-        <v>2.73</v>
+        <v>3.17</v>
       </c>
       <c r="R62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
         <v>1.35</v>
       </c>
       <c r="T62">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U62">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W62">
         <v>1.07</v>
@@ -10460,7 +10460,7 @@
         <v>1.83</v>
       </c>
       <c r="AC62">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="AD62">
         <v>1.27</v>
@@ -10469,10 +10469,10 @@
         <v>1.07</v>
       </c>
       <c r="AF62">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG62">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="O63">
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q63">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="R63">
         <v>2.3</v>
@@ -10611,7 +10611,7 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
         <v>4.75</v>
@@ -10620,13 +10620,13 @@
         <v>1.54</v>
       </c>
       <c r="AB63">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AC63">
         <v>2.3</v>
       </c>
       <c r="AD63">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE63">
         <v>1.16</v>
@@ -10651,7 +10651,7 @@
         <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>1.5</v>
       </c>
       <c r="Q65">
-        <v>7.47</v>
+        <v>6</v>
       </c>
       <c r="R65">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T65">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="U65">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z65">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="AA65">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB65">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC65">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="AD65">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF65">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AG65">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11097,7 +11097,7 @@
         <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
         <v>1.18</v>
@@ -11918,7 +11918,7 @@
         <v>1.3</v>
       </c>
       <c r="Z71">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AA71">
         <v>1.79</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O73">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q73">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R73">
         <v>2.62</v>
@@ -12226,13 +12226,13 @@
         <v>1.19</v>
       </c>
       <c r="T73">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="U73">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="V73">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W73">
         <v>1.16</v>
@@ -12241,22 +12241,22 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="AA73">
         <v>1.33</v>
       </c>
       <c r="AB73">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AC73">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AD73">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE73">
         <v>1.31</v>
@@ -12265,7 +12265,7 @@
         <v>1.36</v>
       </c>
       <c r="AG73">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>2.33</v>
       </c>
       <c r="O74">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P74">
         <v>2.45</v>
@@ -12392,10 +12392,10 @@
         <v>4</v>
       </c>
       <c r="U74">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="V74">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W74">
         <v>1.17</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="O85">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="P85">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="Q85">
         <v>3</v>
@@ -14197,10 +14197,10 @@
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z85">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="AA85">
         <v>1.97</v>
@@ -15018,7 +15018,7 @@
         <v>3.75</v>
       </c>
       <c r="AA90">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB90">
         <v>2.27</v>
@@ -15151,7 +15151,7 @@
         <v>2.7</v>
       </c>
       <c r="Q91">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
         <v>2.25</v>
@@ -16944,19 +16944,19 @@
         <v>2.37</v>
       </c>
       <c r="Q102">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U102">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="V102">
         <v>1.36</v>
@@ -16971,28 +16971,28 @@
         <v>1.31</v>
       </c>
       <c r="Z102">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA102">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AB102">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AC102">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD102">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE102">
         <v>1.05</v>
       </c>
       <c r="AF102">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG102">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK102">
         <v>1.4</v>
@@ -17107,16 +17107,16 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R103">
         <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T103">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="U103">
         <v>2.75</v>
@@ -17125,37 +17125,37 @@
         <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z103">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
         <v>1.8</v>
       </c>
       <c r="AC103">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD103">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF103">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG103">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>2.44</v>
       </c>
       <c r="Q105">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="R105">
         <v>2.4</v>
@@ -17445,7 +17445,7 @@
         <v>3.4</v>
       </c>
       <c r="U105">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V105">
         <v>1.65</v>
@@ -17475,7 +17475,7 @@
         <v>1.66</v>
       </c>
       <c r="AE105">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -18118,7 +18118,7 @@
         <v>1.51</v>
       </c>
       <c r="AB109">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC109">
         <v>2.35</v>
@@ -18149,7 +18149,7 @@
         <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18251,7 +18251,7 @@
         <v>1.8</v>
       </c>
       <c r="R110">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S110">
         <v>1.22</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK110">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18897,7 +18897,7 @@
         <v>3.3</v>
       </c>
       <c r="P114">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q114">
         <v>3.2</v>
@@ -19069,10 +19069,10 @@
         <v>2.1</v>
       </c>
       <c r="S115">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T115">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U115">
         <v>2.71</v>
@@ -19380,7 +19380,7 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="O117">
         <v>3.6</v>
@@ -19419,10 +19419,10 @@
         <v>3.74</v>
       </c>
       <c r="AA117">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB117">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC117">
         <v>2.88</v>
@@ -19549,10 +19549,10 @@
         <v>3.7</v>
       </c>
       <c r="P118">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="Q118">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="R118">
         <v>2.21</v>
@@ -19585,7 +19585,7 @@
         <v>1.7</v>
       </c>
       <c r="AB118">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AC118">
         <v>2.46</v>
@@ -19616,7 +19616,7 @@
         <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O123">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P123">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="Q123">
         <v>2.05</v>
@@ -20684,22 +20684,22 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O125">
         <v>3.8</v>
       </c>
       <c r="P125">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q125">
         <v>4.4</v>
       </c>
       <c r="R125">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S125">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T125">
         <v>3.6</v>
@@ -20714,7 +20714,7 @@
         <v>1.12</v>
       </c>
       <c r="X125">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
         <v>1.17</v>
@@ -20729,16 +20729,16 @@
         <v>2.21</v>
       </c>
       <c r="AC125">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="AD125">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE125">
         <v>1.17</v>
       </c>
       <c r="AF125">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG125">
         <v>2.18</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK125">
         <v>1.22</v>
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="O126">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="P126">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="Q126">
-        <v>3.7</v>
+        <v>4.67</v>
       </c>
       <c r="R126">
         <v>2.25</v>
       </c>
       <c r="S126">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T126">
-        <v>3.46</v>
+        <v>3.55</v>
       </c>
       <c r="U126">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V126">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W126">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y126">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z126">
-        <v>4.54</v>
+        <v>4.61</v>
       </c>
       <c r="AA126">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB126">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC126">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD126">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE126">
         <v>1.19</v>
       </c>
       <c r="AF126">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG126">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.98</v>
+        <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21988,13 +21988,13 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O133">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P133">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q133">
         <v>2.3</v>
@@ -22042,10 +22042,10 @@
         <v>1.1</v>
       </c>
       <c r="AF133">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG133">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O137">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P137">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q137">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="R137">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U137">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V137">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W137">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X137">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z137">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA137">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB137">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC137">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="AD137">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE137">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF137">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG137">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK137">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,80 +22803,80 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="O138">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P138">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q138">
-        <v>2.13</v>
+        <v>2.79</v>
       </c>
       <c r="R138">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S138">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T138">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U138">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V138">
+        <v>1.36</v>
+      </c>
+      <c r="W138">
+        <v>1.08</v>
+      </c>
+      <c r="X138">
+        <v>1.03</v>
+      </c>
+      <c r="Y138">
+        <v>1.27</v>
+      </c>
+      <c r="Z138">
+        <v>3.14</v>
+      </c>
+      <c r="AA138">
+        <v>1.89</v>
+      </c>
+      <c r="AB138">
+        <v>1.78</v>
+      </c>
+      <c r="AC138">
+        <v>3.14</v>
+      </c>
+      <c r="AD138">
+        <v>1.29</v>
+      </c>
+      <c r="AE138">
+        <v>1.07</v>
+      </c>
+      <c r="AF138">
+        <v>1.72</v>
+      </c>
+      <c r="AG138">
+        <v>1.95</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>1.25</v>
+      </c>
+      <c r="AK138">
         <v>1.53</v>
-      </c>
-      <c r="W138">
-        <v>1.11</v>
-      </c>
-      <c r="X138">
-        <v>1</v>
-      </c>
-      <c r="Y138">
-        <v>1.18</v>
-      </c>
-      <c r="Z138">
-        <v>3.84</v>
-      </c>
-      <c r="AA138">
-        <v>1.7</v>
-      </c>
-      <c r="AB138">
-        <v>1.98</v>
-      </c>
-      <c r="AC138">
-        <v>2.76</v>
-      </c>
-      <c r="AD138">
-        <v>1.34</v>
-      </c>
-      <c r="AE138">
-        <v>1.09</v>
-      </c>
-      <c r="AF138">
-        <v>1.74</v>
-      </c>
-      <c r="AG138">
-        <v>2.05</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>1.17</v>
-      </c>
-      <c r="AK138">
-        <v>2.16</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23144,7 +23144,7 @@
         <v>2.26</v>
       </c>
       <c r="S140">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T140">
         <v>3.2</v>
@@ -23648,7 +23648,7 @@
         <v>1.09</v>
       </c>
       <c r="X143">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y143">
         <v>1.19</v>
@@ -25257,55 +25257,55 @@
         <v>0</v>
       </c>
       <c r="Q153">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="R153">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S153">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T153">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="U153">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V153">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W153">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y153">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z153">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="AA153">
         <v>1.66</v>
       </c>
       <c r="AB153">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AC153">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="AD153">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE153">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF153">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG153">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK153">
         <v>1.85</v>
@@ -25435,7 +25435,7 @@
         <v>2.2</v>
       </c>
       <c r="V154">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W154">
         <v>1.17</v>
@@ -25574,37 +25574,37 @@
         </is>
       </c>
       <c r="N155">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O155">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="P155">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Q155">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R155">
         <v>2</v>
       </c>
       <c r="S155">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T155">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="U155">
         <v>3.3</v>
       </c>
       <c r="V155">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W155">
         <v>1.02</v>
       </c>
       <c r="X155">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y155">
         <v>1.39</v>
@@ -25613,13 +25613,13 @@
         <v>2.59</v>
       </c>
       <c r="AA155">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AB155">
         <v>1.61</v>
       </c>
       <c r="AC155">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD155">
         <v>1.16</v>
@@ -25628,7 +25628,7 @@
         <v>1.02</v>
       </c>
       <c r="AF155">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG155">
         <v>1.73</v>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK155">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25900,80 +25900,80 @@
         </is>
       </c>
       <c r="N157">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O157">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P157">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q157">
+        <v>1.33</v>
+      </c>
+      <c r="R157">
+        <v>3.18</v>
+      </c>
+      <c r="S157">
+        <v>1.14</v>
+      </c>
+      <c r="T157">
+        <v>4</v>
+      </c>
+      <c r="U157">
+        <v>1.95</v>
+      </c>
+      <c r="V157">
+        <v>1.8</v>
+      </c>
+      <c r="W157">
+        <v>1.2</v>
+      </c>
+      <c r="X157">
+        <v>1</v>
+      </c>
+      <c r="Y157">
+        <v>1.06</v>
+      </c>
+      <c r="Z157">
+        <v>8.35</v>
+      </c>
+      <c r="AA157">
+        <v>1.3</v>
+      </c>
+      <c r="AB157">
+        <v>2.97</v>
+      </c>
+      <c r="AC157">
+        <v>1.93</v>
+      </c>
+      <c r="AD157">
+        <v>1.83</v>
+      </c>
+      <c r="AE157">
         <v>1.36</v>
       </c>
-      <c r="R157">
-        <v>2.91</v>
-      </c>
-      <c r="S157">
-        <v>1.19</v>
-      </c>
-      <c r="T157">
-        <v>3.74</v>
-      </c>
-      <c r="U157">
-        <v>1.93</v>
-      </c>
-      <c r="V157">
-        <v>1.85</v>
-      </c>
-      <c r="W157">
-        <v>1.18</v>
-      </c>
-      <c r="X157">
+      <c r="AF157">
+        <v>2.48</v>
+      </c>
+      <c r="AG157">
+        <v>1.45</v>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ157">
         <v>1.01</v>
       </c>
-      <c r="Y157">
-        <v>1.05</v>
-      </c>
-      <c r="Z157">
-        <v>9.1</v>
-      </c>
-      <c r="AA157">
-        <v>1.31</v>
-      </c>
-      <c r="AB157">
-        <v>3.08</v>
-      </c>
-      <c r="AC157">
-        <v>1.82</v>
-      </c>
-      <c r="AD157">
-        <v>1.99</v>
-      </c>
-      <c r="AE157">
-        <v>1.44</v>
-      </c>
-      <c r="AF157">
-        <v>2.25</v>
-      </c>
-      <c r="AG157">
-        <v>1.54</v>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ157">
-        <v>1.02</v>
-      </c>
       <c r="AK157">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26462,7 +26462,7 @@
         <v>3.4</v>
       </c>
       <c r="AK160">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26884,7 +26884,7 @@
         <v>4.2</v>
       </c>
       <c r="P163">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="Q163">
         <v>2.05</v>
@@ -28716,7 +28716,7 @@
         <v>1.66</v>
       </c>
       <c r="AC174">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="AD174">
         <v>1.19</v>
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P176">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q176">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R176">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S176">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T176">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U176">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V176">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W176">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X176">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y176">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z176">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA176">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB176">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC176">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD176">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE176">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF176">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG176">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK176">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29362,7 +29362,7 @@
         <v>4.2</v>
       </c>
       <c r="AA178">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB178">
         <v>2.22</v>
@@ -29540,7 +29540,7 @@
         <v>1.27</v>
       </c>
       <c r="AF179">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG179">
         <v>1.9</v>
@@ -29688,7 +29688,7 @@
         <v>4.45</v>
       </c>
       <c r="AA180">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB180">
         <v>2.33</v>
@@ -29821,7 +29821,7 @@
         <v>1.63</v>
       </c>
       <c r="Q181">
-        <v>4.07</v>
+        <v>4.17</v>
       </c>
       <c r="R181">
         <v>2.34</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="O188">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="P188">
-        <v>3.44</v>
+        <v>5.31</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31125,55 +31125,55 @@
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R189">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T189">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U189">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V189">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W189">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X189">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y189">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z189">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA189">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB189">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC189">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD189">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE189">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF189">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG189">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK189">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31288,16 +31288,16 @@
         <v>4.4</v>
       </c>
       <c r="Q190">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="R190">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="S190">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T190">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U190">
         <v>2.9</v>
@@ -31312,22 +31312,22 @@
         <v>1.03</v>
       </c>
       <c r="Y190">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z190">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA190">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB190">
         <v>1.63</v>
       </c>
       <c r="AC190">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AD190">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE190">
         <v>1.04</v>
@@ -31336,7 +31336,7 @@
         <v>1.95</v>
       </c>
       <c r="AG190">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK190">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31484,7 +31484,7 @@
         <v>1.6</v>
       </c>
       <c r="AB191">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC191">
         <v>2.28</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="O192">
         <v>3.6</v>
       </c>
       <c r="P192">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="Q192">
         <v>2.8</v>
@@ -31768,7 +31768,7 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="O193">
         <v>6</v>
@@ -31940,16 +31940,16 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="R194">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="S194">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T194">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="U194">
         <v>3.3</v>
@@ -31964,13 +31964,13 @@
         <v>1.06</v>
       </c>
       <c r="Y194">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z194">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="AA194">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AB194">
         <v>1.51</v>
@@ -31985,10 +31985,10 @@
         <v>1.01</v>
       </c>
       <c r="AF194">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AG194">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK194">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32106,19 +32106,19 @@
         <v>2.63</v>
       </c>
       <c r="R195">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="S195">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T195">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U195">
         <v>2.75</v>
       </c>
       <c r="V195">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W195">
         <v>1.08</v>
@@ -32127,31 +32127,31 @@
         <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z195">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA195">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB195">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC195">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD195">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE195">
         <v>1.09</v>
       </c>
       <c r="AF195">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AG195">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32167,7 +32167,7 @@
         <v>1.26</v>
       </c>
       <c r="AK195">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32266,16 +32266,16 @@
         <v>4.76</v>
       </c>
       <c r="Q196">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="R196">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S196">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T196">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U196">
         <v>2.88</v>
@@ -32302,19 +32302,19 @@
         <v>1.71</v>
       </c>
       <c r="AC196">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD196">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE196">
         <v>1.05</v>
       </c>
       <c r="AF196">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AG196">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK196">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32583,7 +32583,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="O198">
         <v>3.7</v>
@@ -32622,7 +32622,7 @@
         <v>4.15</v>
       </c>
       <c r="AA198">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB198">
         <v>2.15</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK198">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R199">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S199">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T199">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U199">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V199">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W199">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X199">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y199">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z199">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA199">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB199">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC199">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD199">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE199">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF199">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG199">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK199">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33072,43 +33072,43 @@
         </is>
       </c>
       <c r="N201">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="O201">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P201">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q201">
-        <v>4.03</v>
+        <v>4.97</v>
       </c>
       <c r="R201">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="S201">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="T201">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="U201">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="V201">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W201">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X201">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y201">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z201">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="AA201">
         <v>2.25</v>
@@ -33117,35 +33117,35 @@
         <v>1.61</v>
       </c>
       <c r="AC201">
-        <v>3.95</v>
+        <v>4.33</v>
       </c>
       <c r="AD201">
+        <v>1.14</v>
+      </c>
+      <c r="AE201">
+        <v>1.01</v>
+      </c>
+      <c r="AF201">
+        <v>2.05</v>
+      </c>
+      <c r="AG201">
+        <v>1.67</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ201">
+        <v>1.28</v>
+      </c>
+      <c r="AK201">
         <v>1.17</v>
-      </c>
-      <c r="AE201">
-        <v>1.03</v>
-      </c>
-      <c r="AF201">
-        <v>1.91</v>
-      </c>
-      <c r="AG201">
-        <v>1.78</v>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ201">
-        <v>1.26</v>
-      </c>
-      <c r="AK201">
-        <v>1.27</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33244,55 +33244,55 @@
         <v>3.7</v>
       </c>
       <c r="Q202">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="R202">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S202">
         <v>1.35</v>
       </c>
       <c r="T202">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
       <c r="U202">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="V202">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W202">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X202">
         <v>1.01</v>
       </c>
       <c r="Y202">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z202">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA202">
         <v>1.95</v>
       </c>
       <c r="AB202">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AC202">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD202">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE202">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF202">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG202">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33305,10 +33305,10 @@
         </is>
       </c>
       <c r="AJ202">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK202">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="AL202">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="O203">
-        <v>3.54</v>
+        <v>3.26</v>
       </c>
       <c r="P203">
-        <v>4.19</v>
+        <v>3.58</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -35363,19 +35363,19 @@
         <v>2.48</v>
       </c>
       <c r="Q215">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R215">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S215">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T215">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="U215">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V215">
         <v>1.4</v>
@@ -35387,47 +35387,47 @@
         <v>1.01</v>
       </c>
       <c r="Y215">
+        <v>1.21</v>
+      </c>
+      <c r="Z215">
+        <v>3.58</v>
+      </c>
+      <c r="AA215">
+        <v>1.8</v>
+      </c>
+      <c r="AB215">
+        <v>1.91</v>
+      </c>
+      <c r="AC215">
+        <v>2.88</v>
+      </c>
+      <c r="AD215">
+        <v>1.32</v>
+      </c>
+      <c r="AE215">
+        <v>1.08</v>
+      </c>
+      <c r="AF215">
+        <v>1.65</v>
+      </c>
+      <c r="AG215">
+        <v>2.1</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ215">
         <v>1.27</v>
       </c>
-      <c r="Z215">
-        <v>3.14</v>
-      </c>
-      <c r="AA215">
-        <v>1.97</v>
-      </c>
-      <c r="AB215">
-        <v>1.77</v>
-      </c>
-      <c r="AC215">
-        <v>3.34</v>
-      </c>
-      <c r="AD215">
-        <v>1.24</v>
-      </c>
-      <c r="AE215">
-        <v>1.04</v>
-      </c>
-      <c r="AF215">
-        <v>1.74</v>
-      </c>
-      <c r="AG215">
-        <v>1.95</v>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ215">
-        <v>1.28</v>
-      </c>
       <c r="AK215">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35535,7 +35535,7 @@
         <v>1.35</v>
       </c>
       <c r="T216">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="U216">
         <v>2.88</v>
@@ -35556,7 +35556,7 @@
         <v>3.82</v>
       </c>
       <c r="AA216">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB216">
         <v>1.85</v>
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK216">
         <v>1.62</v>
@@ -35722,7 +35722,7 @@
         <v>1.82</v>
       </c>
       <c r="AB217">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC217">
         <v>3.04</v>
@@ -36658,64 +36658,64 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="O223">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P223">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q223">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="R223">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S223">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T223">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="U223">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V223">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W223">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X223">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y223">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z223">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="AA223">
         <v>1.8</v>
       </c>
       <c r="AB223">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AC223">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="AD223">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE223">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF223">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG223">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AH223" t="inlineStr">
         <is>
@@ -36728,10 +36728,10 @@
         </is>
       </c>
       <c r="AJ223">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK223">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AL223">
         <v>0</v>
@@ -36827,7 +36827,7 @@
         <v>4.05</v>
       </c>
       <c r="P224">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="Q224">
         <v>6.1</v>
@@ -36860,7 +36860,7 @@
         <v>3.4</v>
       </c>
       <c r="AA224">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB224">
         <v>1.97</v>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AK224">
         <v>1.1</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>5.33</v>
+        <v>4.8</v>
       </c>
       <c r="O225">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P225">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q225">
         <v>5.65</v>
@@ -37829,7 +37829,7 @@
         <v>1.06</v>
       </c>
       <c r="X230">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y230">
         <v>1.25</v>
@@ -37971,7 +37971,7 @@
         <v>3.54</v>
       </c>
       <c r="Q231">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R231">
         <v>2</v>
@@ -37992,34 +37992,34 @@
         <v>1.06</v>
       </c>
       <c r="X231">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y231">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z231">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA231">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AB231">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC231">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD231">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE231">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF231">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG231">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>1.3</v>
       </c>
       <c r="AK231">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38125,16 +38125,16 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O232">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P232">
+        <v>2.8</v>
+      </c>
+      <c r="Q232">
         <v>3</v>
-      </c>
-      <c r="Q232">
-        <v>2.88</v>
       </c>
       <c r="R232">
         <v>2</v>
@@ -38152,37 +38152,37 @@
         <v>1.33</v>
       </c>
       <c r="W232">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X232">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y232">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z232">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AA232">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AB232">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC232">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="AD232">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE232">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF232">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG232">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>1.27</v>
       </c>
       <c r="AK232">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="O233">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P233">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q233">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R233">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S233">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T233">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="U233">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="V233">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W233">
+        <v>1.06</v>
+      </c>
+      <c r="X233">
         <v>1.03</v>
       </c>
-      <c r="X233">
-        <v>1.04</v>
-      </c>
       <c r="Y233">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z233">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="AA233">
         <v>2.1</v>
       </c>
       <c r="AB233">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AC233">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD233">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE233">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF233">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG233">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38460,10 +38460,10 @@
         <v>2.02</v>
       </c>
       <c r="Q234">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R234">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S234">
         <v>1.2</v>
@@ -38499,10 +38499,10 @@
         <v>2.02</v>
       </c>
       <c r="AD234">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE234">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF234">
         <v>1.33</v>
@@ -38943,7 +38943,7 @@
         <v>1.68</v>
       </c>
       <c r="O237">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="P237">
         <v>4.54</v>
@@ -39133,7 +39133,7 @@
         <v>1.12</v>
       </c>
       <c r="X238">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y238">
         <v>1.16</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="O240">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P240">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q240">
         <v>4.47</v>
@@ -39779,7 +39779,7 @@
         <v>2</v>
       </c>
       <c r="V242">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W242">
         <v>1.2</v>
@@ -40090,16 +40090,16 @@
         <v>2</v>
       </c>
       <c r="Q244">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R244">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S244">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T244">
-        <v>3.14</v>
+        <v>2.78</v>
       </c>
       <c r="U244">
         <v>2.62</v>
@@ -40108,28 +40108,28 @@
         <v>1.4</v>
       </c>
       <c r="W244">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X244">
         <v>1.01</v>
       </c>
       <c r="Y244">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z244">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA244">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB244">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC244">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AD244">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE244">
         <v>1.08</v>
@@ -40151,10 +40151,10 @@
         </is>
       </c>
       <c r="AJ244">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK244">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL244">
         <v>0</v>
@@ -40416,52 +40416,52 @@
         <v>4.75</v>
       </c>
       <c r="Q246">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R246">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S246">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T246">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="U246">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V246">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W246">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X246">
         <v>1.02</v>
       </c>
       <c r="Y246">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z246">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="AA246">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AB246">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC246">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD246">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE246">
         <v>1.05</v>
       </c>
       <c r="AF246">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG246">
         <v>1.75</v>
@@ -40480,7 +40480,7 @@
         <v>1.21</v>
       </c>
       <c r="AK246">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40579,55 +40579,55 @@
         <v>2.23</v>
       </c>
       <c r="Q247">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="R247">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T247">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U247">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V247">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W247">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X247">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y247">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z247">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA247">
         <v>1.6</v>
       </c>
       <c r="AB247">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AC247">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="AD247">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE247">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF247">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG247">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40640,10 +40640,10 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK247">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AL247">
         <v>0</v>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK249">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41059,64 +41059,64 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="O250">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="P250">
-        <v>4.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q250">
         <v>2.25</v>
       </c>
       <c r="R250">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S250">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T250">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U250">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="V250">
         <v>1.4</v>
       </c>
       <c r="W250">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X250">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z250">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA250">
         <v>1.85</v>
       </c>
       <c r="AB250">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AC250">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AD250">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE250">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF250">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG250">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK250">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41385,64 +41385,64 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.68</v>
+        <v>2.1</v>
       </c>
       <c r="O252">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P252">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q252">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R252">
         <v>2.3</v>
       </c>
       <c r="S252">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T252">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="U252">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="V252">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W252">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X252">
         <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z252">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA252">
         <v>1.65</v>
       </c>
       <c r="AB252">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AC252">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AD252">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE252">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF252">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG252">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41455,10 +41455,10 @@
         </is>
       </c>
       <c r="AJ252">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK252">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,7 +41548,7 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O253">
         <v>3.96</v>
@@ -41913,7 +41913,7 @@
         <v>2.62</v>
       </c>
       <c r="AA255">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AB255">
         <v>1.6</v>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="AJ255">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK255">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42094,7 +42094,7 @@
         <v>1.62</v>
       </c>
       <c r="AG256">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH256" t="inlineStr">
         <is>
@@ -43187,22 +43187,22 @@
         <v>3.41</v>
       </c>
       <c r="Q263">
-        <v>2.68</v>
+        <v>2.77</v>
       </c>
       <c r="R263">
         <v>2</v>
       </c>
       <c r="S263">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="T263">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U263">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V263">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W263">
         <v>1.04</v>
@@ -43211,31 +43211,31 @@
         <v>1.03</v>
       </c>
       <c r="Y263">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z263">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AA263">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB263">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC263">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="AD263">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE263">
         <v>1.03</v>
       </c>
       <c r="AF263">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG263">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK263">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43359,13 +43359,13 @@
         <v>1.3</v>
       </c>
       <c r="T264">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U264">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="V264">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W264">
         <v>1.12</v>
@@ -43377,19 +43377,19 @@
         <v>1.21</v>
       </c>
       <c r="Z264">
-        <v>4.41</v>
+        <v>4.47</v>
       </c>
       <c r="AA264">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB264">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AC264">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AD264">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AE264">
         <v>1.18</v>
@@ -44319,64 +44319,64 @@
         </is>
       </c>
       <c r="N270">
-        <v>4.54</v>
+        <v>6.5</v>
       </c>
       <c r="O270">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P270">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Q270">
-        <v>6.08</v>
+        <v>6.84</v>
       </c>
       <c r="R270">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="S270">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T270">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="U270">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V270">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W270">
         <v>1.06</v>
       </c>
       <c r="X270">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y270">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z270">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA270">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB270">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC270">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD270">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE270">
         <v>1.06</v>
       </c>
       <c r="AF270">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AG270">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK270">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -44651,7 +44651,7 @@
         <v>3.4</v>
       </c>
       <c r="P272">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -45164,7 +45164,7 @@
         <v>1.11</v>
       </c>
       <c r="X275">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y275">
         <v>1.2</v>
@@ -45460,7 +45460,7 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O277">
         <v>4.25</v>
@@ -45484,10 +45484,10 @@
         <v>1.93</v>
       </c>
       <c r="V277">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W277">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X277">
         <v>1.01</v>
@@ -45653,7 +45653,7 @@
         <v>1.14</v>
       </c>
       <c r="X278">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y278">
         <v>1.17</v>
@@ -45693,7 +45693,7 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK278">
         <v>1.6</v>
@@ -45786,64 +45786,64 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="O279">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P279">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q279">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="R279">
         <v>2.1</v>
       </c>
       <c r="S279">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="T279">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U279">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V279">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W279">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X279">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y279">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z279">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA279">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB279">
         <v>1.8</v>
       </c>
       <c r="AC279">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD279">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE279">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF279">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG279">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -46305,7 +46305,7 @@
         <v>1.11</v>
       </c>
       <c r="X282">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y282">
         <v>1.16</v>
@@ -46468,7 +46468,7 @@
         <v>1.04</v>
       </c>
       <c r="X283">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y283">
         <v>1.27</v>
@@ -47265,7 +47265,7 @@
         <v>3.42</v>
       </c>
       <c r="R288">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S288">
         <v>1.5</v>
@@ -47304,7 +47304,7 @@
         <v>1.13</v>
       </c>
       <c r="AE288">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF288">
         <v>1.98</v>
@@ -47591,7 +47591,7 @@
         <v>1.54</v>
       </c>
       <c r="R290">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="S290">
         <v>1.21</v>
@@ -47624,7 +47624,7 @@
         <v>2.76</v>
       </c>
       <c r="AC290">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AD290">
         <v>1.86</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,64 +47905,64 @@
         </is>
       </c>
       <c r="N292">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O292">
+        <v>3.65</v>
+      </c>
+      <c r="P292">
+        <v>4.35</v>
+      </c>
+      <c r="Q292">
+        <v>2.15</v>
+      </c>
+      <c r="R292">
+        <v>2.2</v>
+      </c>
+      <c r="S292">
+        <v>1.36</v>
+      </c>
+      <c r="T292">
         <v>3</v>
       </c>
-      <c r="P292">
-        <v>3.25</v>
-      </c>
-      <c r="Q292">
-        <v>2.85</v>
-      </c>
-      <c r="R292">
-        <v>2.06</v>
-      </c>
-      <c r="S292">
-        <v>1.5</v>
-      </c>
-      <c r="T292">
-        <v>2.38</v>
-      </c>
       <c r="U292">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="V292">
+        <v>1.37</v>
+      </c>
+      <c r="W292">
+        <v>1.04</v>
+      </c>
+      <c r="X292">
+        <v>1.01</v>
+      </c>
+      <c r="Y292">
         <v>1.28</v>
       </c>
-      <c r="W292">
-        <v>1.03</v>
-      </c>
-      <c r="X292">
-        <v>1.05</v>
-      </c>
-      <c r="Y292">
-        <v>1.4</v>
-      </c>
       <c r="Z292">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AA292">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="AB292">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="AC292">
-        <v>4.41</v>
+        <v>3.17</v>
       </c>
       <c r="AD292">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AE292">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF292">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG292">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK292">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O293">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P293">
-        <v>4.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q293">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="R293">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S293">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="T293">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U293">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="V293">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W293">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X293">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y293">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z293">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="AA293">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AB293">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AC293">
-        <v>3.17</v>
+        <v>4.41</v>
       </c>
       <c r="AD293">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE293">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF293">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG293">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK293">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48720,19 +48720,19 @@
         </is>
       </c>
       <c r="N297">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O297">
         <v>2.95</v>
       </c>
       <c r="P297">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q297">
         <v>3.9</v>
       </c>
       <c r="R297">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="S297">
         <v>1.5</v>
@@ -48750,7 +48750,7 @@
         <v>1.01</v>
       </c>
       <c r="X297">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y297">
         <v>1.47</v>
@@ -48765,13 +48765,13 @@
         <v>1.5</v>
       </c>
       <c r="AC297">
-        <v>5.17</v>
+        <v>5.26</v>
       </c>
       <c r="AD297">
         <v>1.14</v>
       </c>
       <c r="AE297">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF297">
         <v>2</v>
@@ -49698,19 +49698,19 @@
         </is>
       </c>
       <c r="N303">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="O303">
-        <v>3.72</v>
+        <v>3.5</v>
       </c>
       <c r="P303">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q303">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R303">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="S303">
         <v>1.25</v>
@@ -49719,13 +49719,13 @@
         <v>3.7</v>
       </c>
       <c r="U303">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="V303">
         <v>1.59</v>
       </c>
       <c r="W303">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X303">
         <v>1.02</v>
@@ -49734,25 +49734,25 @@
         <v>1.16</v>
       </c>
       <c r="Z303">
-        <v>5.3</v>
+        <v>4.95</v>
       </c>
       <c r="AA303">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB303">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AC303">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="AD303">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AE303">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF303">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG303">
         <v>2.5</v>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK303">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -49864,7 +49864,7 @@
         <v>1.98</v>
       </c>
       <c r="O304">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P304">
         <v>3.7</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O305">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P305">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="Q305">
         <v>2.38</v>
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O307">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="P307">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q307">
         <v>2.3</v>
@@ -50368,13 +50368,13 @@
         <v>1.17</v>
       </c>
       <c r="T307">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="U307">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V307">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W307">
         <v>1.2</v>
@@ -50392,16 +50392,16 @@
         <v>1.4</v>
       </c>
       <c r="AB307">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="AC307">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AD307">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AE307">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF307">
         <v>1.36</v>
@@ -50881,7 +50881,7 @@
         <v>1.7</v>
       </c>
       <c r="AB310">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AC310">
         <v>2.56</v>
@@ -51165,7 +51165,7 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="O312">
         <v>3.6</v>
@@ -51328,7 +51328,7 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O313">
         <v>2.75</v>
@@ -51666,7 +51666,7 @@
         <v>2.4</v>
       </c>
       <c r="R315">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S315">
         <v>1.17</v>
@@ -51675,40 +51675,40 @@
         <v>4.5</v>
       </c>
       <c r="U315">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V315">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W315">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X315">
         <v>1.01</v>
       </c>
       <c r="Y315">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z315">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA315">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB315">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AC315">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD315">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE315">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF315">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG315">
         <v>3</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -656,7 +656,7 @@
         <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.36</v>
@@ -801,7 +801,7 @@
         <v>2.75</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
         <v>2.45</v>
@@ -816,10 +816,10 @@
         <v>1.38</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -837,10 +837,10 @@
         <v>3.04</v>
       </c>
       <c r="AA3">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB3">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
         <v>3.42</v>
@@ -1619,7 +1619,7 @@
         <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q8">
         <v>2.82</v>
@@ -1655,13 +1655,13 @@
         <v>2.02</v>
       </c>
       <c r="AB8">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC8">
         <v>3.48</v>
       </c>
       <c r="AD8">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
         <v>1.04</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
         <v>3.25</v>
@@ -1830,10 +1830,10 @@
         <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>1.57</v>
+      </c>
+      <c r="O11">
+        <v>3.95</v>
+      </c>
+      <c r="P11">
+        <v>4.5</v>
+      </c>
+      <c r="Q11">
+        <v>2.1</v>
+      </c>
+      <c r="R11">
+        <v>2.38</v>
+      </c>
+      <c r="S11">
+        <v>1.25</v>
+      </c>
+      <c r="T11">
+        <v>3.4</v>
+      </c>
+      <c r="U11">
+        <v>2.38</v>
+      </c>
+      <c r="V11">
+        <v>1.5</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.16</v>
+      </c>
+      <c r="Z11">
+        <v>4.15</v>
+      </c>
+      <c r="AA11">
+        <v>1.62</v>
+      </c>
+      <c r="AB11">
         <v>2.2</v>
       </c>
-      <c r="O11">
-        <v>3</v>
-      </c>
-      <c r="P11">
-        <v>3.1</v>
-      </c>
-      <c r="Q11">
-        <v>2.88</v>
-      </c>
-      <c r="R11">
-        <v>1.85</v>
-      </c>
-      <c r="S11">
-        <v>1.45</v>
-      </c>
-      <c r="T11">
-        <v>2.55</v>
-      </c>
-      <c r="U11">
-        <v>3.3</v>
-      </c>
-      <c r="V11">
-        <v>1.29</v>
-      </c>
-      <c r="W11">
-        <v>1.03</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>1.43</v>
-      </c>
-      <c r="Z11">
-        <v>2.46</v>
-      </c>
-      <c r="AA11">
-        <v>2.34</v>
-      </c>
-      <c r="AB11">
-        <v>1.53</v>
-      </c>
       <c r="AC11">
-        <v>4.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD11">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="Z12">
-        <v>4.15</v>
+        <v>2.46</v>
       </c>
       <c r="AA12">
-        <v>1.62</v>
+        <v>2.34</v>
       </c>
       <c r="AB12">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AC12">
-        <v>2.43</v>
+        <v>4.4</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="AG12">
-        <v>2.09</v>
+        <v>1.69</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
         <v>2.48</v>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R18">
         <v>1.88</v>
@@ -3421,10 +3421,10 @@
         <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
         <v>2.58</v>
@@ -3436,7 +3436,7 @@
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
         <v>1.24</v>
@@ -3460,10 +3460,10 @@
         <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>2.35</v>
       </c>
       <c r="R20">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
         <v>1.33</v>
@@ -3590,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
         <v>1.36</v>
@@ -3608,7 +3608,7 @@
         <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
         <v>1.75</v>
@@ -3626,7 +3626,7 @@
         <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
         <v>1.87</v>
@@ -3741,7 +3741,7 @@
         <v>1.68</v>
       </c>
       <c r="Q21">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="R21">
         <v>2.01</v>
@@ -3753,10 +3753,10 @@
         <v>2.61</v>
       </c>
       <c r="U21">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="V21">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W21">
         <v>1.06</v>
@@ -3765,16 +3765,16 @@
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z21">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="AA21">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB21">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC21">
         <v>3.42</v>
@@ -3783,7 +3783,7 @@
         <v>1.23</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
         <v>1.82</v>
@@ -3805,7 +3805,7 @@
         <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         <v>2.62</v>
       </c>
       <c r="AA22">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
         <v>1.66</v>
@@ -4067,10 +4067,10 @@
         <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
         <v>1.27</v>
@@ -4079,16 +4079,16 @@
         <v>3.18</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.17</v>
@@ -4100,7 +4100,7 @@
         <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AC23">
         <v>2.64</v>
@@ -4115,7 +4115,7 @@
         <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>2.35</v>
       </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
         <v>1.29</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="O26">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="R26">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T26">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="U26">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z26">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA26">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AB26">
         <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG26">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="O30">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,37 +5362,37 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2.63</v>
+        <v>5.58</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
         <v>2.75</v>
       </c>
       <c r="U31">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
         <v>1.04</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
         <v>1.32</v>
@@ -5407,19 +5407,19 @@
         <v>1.66</v>
       </c>
       <c r="AC31">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE31">
         <v>1.04</v>
       </c>
       <c r="AF31">
-        <v>1.86</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q33">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
         <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="V33">
         <v>1.33</v>
@@ -5718,34 +5718,34 @@
         <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="AG33">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U34">
         <v>2.5</v>
@@ -5878,7 +5878,7 @@
         <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -5905,10 +5905,10 @@
         <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,19 +6023,19 @@
         <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S35">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U35">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V35">
         <v>1.3</v>
@@ -6068,7 +6068,7 @@
         <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG35">
         <v>1.79</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK35">
         <v>1.44</v>
@@ -6186,10 +6186,10 @@
         <v>2.32</v>
       </c>
       <c r="Q36">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R36">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
         <v>1.36</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="O37">
         <v>3.24</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
+        <v>3.8</v>
+      </c>
+      <c r="P41">
+        <v>6.26</v>
+      </c>
+      <c r="Q41">
+        <v>2.03</v>
+      </c>
+      <c r="R41">
+        <v>2.25</v>
+      </c>
+      <c r="S41">
+        <v>1.36</v>
+      </c>
+      <c r="T41">
         <v>3</v>
       </c>
-      <c r="P41">
-        <v>3.53</v>
-      </c>
-      <c r="Q41">
-        <v>2.55</v>
-      </c>
-      <c r="R41">
-        <v>1.91</v>
-      </c>
-      <c r="S41">
-        <v>1.5</v>
-      </c>
-      <c r="T41">
+      <c r="U41">
+        <v>2.88</v>
+      </c>
+      <c r="V41">
+        <v>1.36</v>
+      </c>
+      <c r="W41">
+        <v>1.08</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.24</v>
+      </c>
+      <c r="Z41">
+        <v>3.08</v>
+      </c>
+      <c r="AA41">
+        <v>1.86</v>
+      </c>
+      <c r="AB41">
+        <v>1.75</v>
+      </c>
+      <c r="AC41">
+        <v>3.08</v>
+      </c>
+      <c r="AD41">
+        <v>1.28</v>
+      </c>
+      <c r="AE41">
+        <v>1.09</v>
+      </c>
+      <c r="AF41">
+        <v>1.85</v>
+      </c>
+      <c r="AG41">
+        <v>1.83</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.17</v>
+      </c>
+      <c r="AK41">
         <v>2.5</v>
-      </c>
-      <c r="U41">
-        <v>3.5</v>
-      </c>
-      <c r="V41">
-        <v>1.25</v>
-      </c>
-      <c r="W41">
-        <v>1.01</v>
-      </c>
-      <c r="X41">
-        <v>1.07</v>
-      </c>
-      <c r="Y41">
-        <v>1.5</v>
-      </c>
-      <c r="Z41">
-        <v>2.47</v>
-      </c>
-      <c r="AA41">
-        <v>2.5</v>
-      </c>
-      <c r="AB41">
-        <v>1.5</v>
-      </c>
-      <c r="AC41">
-        <v>4.65</v>
-      </c>
-      <c r="AD41">
-        <v>1.12</v>
-      </c>
-      <c r="AE41">
-        <v>1.03</v>
-      </c>
-      <c r="AF41">
-        <v>2.19</v>
-      </c>
-      <c r="AG41">
-        <v>1.59</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.28</v>
-      </c>
-      <c r="AK41">
-        <v>1.76</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
+        <v>2.04</v>
+      </c>
+      <c r="O43">
+        <v>3</v>
+      </c>
+      <c r="P43">
+        <v>3.53</v>
+      </c>
+      <c r="Q43">
+        <v>2.5</v>
+      </c>
+      <c r="R43">
+        <v>1.91</v>
+      </c>
+      <c r="S43">
         <v>1.5</v>
       </c>
-      <c r="O43">
-        <v>3.8</v>
-      </c>
-      <c r="P43">
-        <v>6.26</v>
-      </c>
-      <c r="Q43">
-        <v>2.03</v>
-      </c>
-      <c r="R43">
-        <v>2.25</v>
-      </c>
-      <c r="S43">
-        <v>1.33</v>
-      </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Z43">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="AA43">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AB43">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC43">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AD43">
+        <v>1.12</v>
+      </c>
+      <c r="AE43">
+        <v>1.03</v>
+      </c>
+      <c r="AF43">
+        <v>2.19</v>
+      </c>
+      <c r="AG43">
+        <v>1.59</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.28</v>
       </c>
-      <c r="AE43">
-        <v>1.09</v>
-      </c>
-      <c r="AF43">
-        <v>1.95</v>
-      </c>
-      <c r="AG43">
-        <v>1.75</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.17</v>
-      </c>
       <c r="AK43">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R44">
         <v>2.2</v>
@@ -7520,10 +7520,10 @@
         <v>3.58</v>
       </c>
       <c r="AA44">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC44">
         <v>2.88</v>
@@ -7647,7 +7647,7 @@
         <v>2.3</v>
       </c>
       <c r="O45">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
         <v>2.7</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O47">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q47">
         <v>2.05</v>
@@ -7991,7 +7991,7 @@
         <v>3.26</v>
       </c>
       <c r="U47">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
         <v>1.5</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.84</v>
       </c>
       <c r="AK48">
         <v>1.3</v>
@@ -8299,7 +8299,7 @@
         <v>1.9</v>
       </c>
       <c r="O49">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="P49">
         <v>3.2</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O50">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q50">
         <v>2.06</v>
@@ -8489,7 +8489,7 @@
         <v>1.06</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y50">
         <v>1.2</v>
@@ -8637,16 +8637,16 @@
         <v>2.1</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
         <v>1.06</v>
@@ -8664,7 +8664,7 @@
         <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
         <v>3.04</v>
@@ -8969,13 +8969,13 @@
         <v>2.45</v>
       </c>
       <c r="U53">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="V53">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X53">
         <v>1.05</v>
@@ -9002,7 +9002,7 @@
         <v>1.03</v>
       </c>
       <c r="AF53">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG53">
         <v>1.79</v>
@@ -9117,13 +9117,13 @@
         <v>5.75</v>
       </c>
       <c r="P54">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q54">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="R54">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="S54">
         <v>1.25</v>
@@ -9132,7 +9132,7 @@
         <v>3.42</v>
       </c>
       <c r="U54">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="V54">
         <v>1.57</v>
@@ -9141,13 +9141,13 @@
         <v>1.13</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
         <v>1.13</v>
       </c>
       <c r="Z54">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA54">
         <v>1.49</v>
@@ -9162,10 +9162,10 @@
         <v>1.53</v>
       </c>
       <c r="AE54">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF54">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG54">
         <v>1.65</v>
@@ -9184,7 +9184,7 @@
         <v>1.08</v>
       </c>
       <c r="AK54">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9331,7 +9331,7 @@
         <v>1.83</v>
       </c>
       <c r="AG55">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
+        <v>2.1</v>
+      </c>
+      <c r="O59">
+        <v>3.1</v>
+      </c>
+      <c r="P59">
+        <v>2.9</v>
+      </c>
+      <c r="Q59">
+        <v>2.6</v>
+      </c>
+      <c r="R59">
         <v>2.2</v>
       </c>
-      <c r="O59">
-        <v>3.5</v>
-      </c>
-      <c r="P59">
-        <v>2.7</v>
-      </c>
-      <c r="Q59">
-        <v>2.77</v>
-      </c>
-      <c r="R59">
-        <v>2.19</v>
-      </c>
       <c r="S59">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T59">
-        <v>3.08</v>
+        <v>2.64</v>
       </c>
       <c r="U59">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V59">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z59">
-        <v>3.96</v>
+        <v>3.78</v>
       </c>
       <c r="AA59">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AC59">
         <v>2.52</v>
       </c>
       <c r="AD59">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE59">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG59">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,55 +10098,55 @@
         <v>1.73</v>
       </c>
       <c r="Q60">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="R60">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S60">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.86</v>
+        <v>2.58</v>
       </c>
       <c r="U60">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V60">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
+        <v>1.22</v>
+      </c>
+      <c r="Z60">
+        <v>2.63</v>
+      </c>
+      <c r="AA60">
+        <v>1.95</v>
+      </c>
+      <c r="AB60">
+        <v>1.73</v>
+      </c>
+      <c r="AC60">
+        <v>2.7</v>
+      </c>
+      <c r="AD60">
         <v>1.2</v>
-      </c>
-      <c r="Z60">
-        <v>2.75</v>
-      </c>
-      <c r="AA60">
-        <v>1.87</v>
-      </c>
-      <c r="AB60">
-        <v>1.8</v>
-      </c>
-      <c r="AC60">
-        <v>3.2</v>
-      </c>
-      <c r="AD60">
-        <v>1.22</v>
       </c>
       <c r="AE60">
         <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG60">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="O63">
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="Q63">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="R63">
         <v>2.3</v>
@@ -10635,7 +10635,7 @@
         <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10916,10 +10916,10 @@
         <v>6</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
         <v>2.95</v>
@@ -10931,7 +10931,7 @@
         <v>1.4</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
         <v>1.02</v>
@@ -10958,10 +10958,10 @@
         <v>1.09</v>
       </c>
       <c r="AF65">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG65">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>2.12</v>
       </c>
       <c r="Q67">
-        <v>3.47</v>
+        <v>3.41</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S67">
         <v>1.29</v>
@@ -11260,13 +11260,13 @@
         <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
         <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA67">
         <v>1.65</v>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
         <v>1.36</v>
@@ -11897,10 +11897,10 @@
         <v>2.1</v>
       </c>
       <c r="S71">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T71">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U71">
         <v>2.88</v>
@@ -12054,55 +12054,55 @@
         <v>2.1</v>
       </c>
       <c r="Q72">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R72">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S72">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="U72">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="V72">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z72">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="AA72">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB72">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC72">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="AD72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE72">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF72">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG72">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AK72">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12220,7 +12220,7 @@
         <v>2.2</v>
       </c>
       <c r="R73">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S73">
         <v>1.19</v>
@@ -12229,10 +12229,10 @@
         <v>3.75</v>
       </c>
       <c r="U73">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V73">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W73">
         <v>1.16</v>
@@ -12244,10 +12244,10 @@
         <v>1.1</v>
       </c>
       <c r="Z73">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="AA73">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB73">
         <v>2.83</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK73">
         <v>1.8</v>
@@ -12392,7 +12392,7 @@
         <v>4</v>
       </c>
       <c r="U74">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="V74">
         <v>1.62</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O76">
         <v>4</v>
       </c>
       <c r="P76">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="Q76">
         <v>2.1</v>
@@ -12770,7 +12770,7 @@
         <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O83">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P83">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q83">
-        <v>6.91</v>
+        <v>6.5</v>
       </c>
       <c r="R83">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T83">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="U83">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="V83">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="W83">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Z83">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA83">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AB83">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AC83">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AD83">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AE83">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG83">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK83">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14185,13 +14185,13 @@
         <v>2.68</v>
       </c>
       <c r="U85">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V85">
         <v>1.36</v>
       </c>
       <c r="W85">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
         <v>1.01</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK85">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15000,10 +15000,10 @@
         <v>3.12</v>
       </c>
       <c r="U90">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V90">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W90">
         <v>1.1</v>
@@ -15012,7 +15012,7 @@
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z90">
         <v>3.75</v>
@@ -15148,7 +15148,7 @@
         <v>3.3</v>
       </c>
       <c r="P91">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q91">
         <v>2.7</v>
@@ -15199,7 +15199,7 @@
         <v>1.57</v>
       </c>
       <c r="AG91">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15305,28 +15305,28 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="O92">
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q92">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R92">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T92">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U92">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V92">
         <v>1.5</v>
@@ -15338,28 +15338,28 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z92">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AA92">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB92">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC92">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD92">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE92">
         <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG92">
         <v>2.25</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK92">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15637,10 +15637,10 @@
         <v>3.4</v>
       </c>
       <c r="P94">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q94">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R94">
         <v>2.3</v>
@@ -15655,7 +15655,7 @@
         <v>2.19</v>
       </c>
       <c r="V94">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W94">
         <v>1.12</v>
@@ -15670,7 +15670,7 @@
         <v>4.99</v>
       </c>
       <c r="AA94">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB94">
         <v>2.25</v>
@@ -15794,31 +15794,31 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.23</v>
+        <v>3.6</v>
       </c>
       <c r="O95">
         <v>3.85</v>
       </c>
       <c r="P95">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q95">
         <v>4</v>
       </c>
       <c r="R95">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="S95">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
         <v>4</v>
       </c>
       <c r="U95">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="V95">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W95">
         <v>1.14</v>
@@ -15839,10 +15839,10 @@
         <v>2.41</v>
       </c>
       <c r="AC95">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="AD95">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE95">
         <v>1.22</v>
@@ -16446,34 +16446,34 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P99">
-        <v>4.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q99">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="R99">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S99">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T99">
         <v>3.34</v>
       </c>
       <c r="U99">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V99">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
         <v>1.01</v>
@@ -16482,16 +16482,16 @@
         <v>1.13</v>
       </c>
       <c r="Z99">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA99">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB99">
         <v>2.35</v>
       </c>
       <c r="AC99">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AD99">
         <v>1.52</v>
@@ -16500,10 +16500,10 @@
         <v>1.16</v>
       </c>
       <c r="AF99">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG99">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16935,16 +16935,16 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="O102">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P102">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="Q102">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R102">
         <v>2.1</v>
@@ -16953,13 +16953,13 @@
         <v>1.36</v>
       </c>
       <c r="T102">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U102">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
         <v>1.04</v>
@@ -16974,10 +16974,10 @@
         <v>2.97</v>
       </c>
       <c r="AA102">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AB102">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC102">
         <v>3.34</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,22 +17107,22 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R103">
         <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T103">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="U103">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W103">
         <v>1.03</v>
@@ -17131,16 +17131,16 @@
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z103">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AA103">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC103">
         <v>3.34</v>
@@ -17294,13 +17294,13 @@
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z104">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA104">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB104">
         <v>2.3</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O105">
         <v>3.5</v>
@@ -17445,7 +17445,7 @@
         <v>3.4</v>
       </c>
       <c r="U105">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V105">
         <v>1.65</v>
@@ -17463,10 +17463,10 @@
         <v>5.5</v>
       </c>
       <c r="AA105">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB105">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC105">
         <v>2.34</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O106">
         <v>3.2</v>
       </c>
       <c r="P106">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q106">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R106">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S106">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T106">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="U106">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="V106">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
         <v>1</v>
       </c>
       <c r="Y106">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z106">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA106">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB106">
         <v>1.8</v>
       </c>
       <c r="AC106">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD106">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE106">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG106">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
+        <v>1.7</v>
+      </c>
+      <c r="O107">
+        <v>3.5</v>
+      </c>
+      <c r="P107">
+        <v>4</v>
+      </c>
+      <c r="Q107">
         <v>2.3</v>
       </c>
-      <c r="O107">
-        <v>3.1</v>
-      </c>
-      <c r="P107">
-        <v>2.62</v>
-      </c>
-      <c r="Q107">
-        <v>3</v>
-      </c>
       <c r="R107">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="S107">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T107">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="U107">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V107">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W107">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y107">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="Z107">
-        <v>2.83</v>
+        <v>3.8</v>
       </c>
       <c r="AA107">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AB107">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC107">
-        <v>3.68</v>
+        <v>2.74</v>
       </c>
       <c r="AD107">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE107">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF107">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AG107">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,80 +17913,80 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="O108">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P108">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="Q108">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="S108">
+        <v>1.41</v>
+      </c>
+      <c r="T108">
+        <v>2.63</v>
+      </c>
+      <c r="U108">
+        <v>3.2</v>
+      </c>
+      <c r="V108">
+        <v>1.3</v>
+      </c>
+      <c r="W108">
+        <v>1.04</v>
+      </c>
+      <c r="X108">
+        <v>1.03</v>
+      </c>
+      <c r="Y108">
         <v>1.35</v>
       </c>
-      <c r="T108">
-        <v>2.76</v>
-      </c>
-      <c r="U108">
-        <v>2.75</v>
-      </c>
-      <c r="V108">
-        <v>1.38</v>
-      </c>
-      <c r="W108">
-        <v>1.08</v>
-      </c>
-      <c r="X108">
-        <v>1.01</v>
-      </c>
-      <c r="Y108">
-        <v>1.22</v>
-      </c>
       <c r="Z108">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="AA108">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="AB108">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AC108">
-        <v>2.97</v>
+        <v>3.94</v>
       </c>
       <c r="AD108">
+        <v>1.17</v>
+      </c>
+      <c r="AE108">
+        <v>1.02</v>
+      </c>
+      <c r="AF108">
+        <v>1.88</v>
+      </c>
+      <c r="AG108">
+        <v>1.79</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ108">
         <v>1.3</v>
       </c>
-      <c r="AE108">
-        <v>1.07</v>
-      </c>
-      <c r="AF108">
-        <v>1.72</v>
-      </c>
-      <c r="AG108">
-        <v>1.96</v>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ108">
-        <v>1.22</v>
-      </c>
       <c r="AK108">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18085,10 +18085,10 @@
         <v>2.7</v>
       </c>
       <c r="Q109">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R109">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S109">
         <v>1.26</v>
@@ -18260,10 +18260,10 @@
         <v>3.9</v>
       </c>
       <c r="U110">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V110">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W110">
         <v>1.14</v>
@@ -18278,10 +18278,10 @@
         <v>5.4</v>
       </c>
       <c r="AA110">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB110">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC110">
         <v>2.13</v>
@@ -18577,13 +18577,13 @@
         <v>2.45</v>
       </c>
       <c r="R112">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="S112">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T112">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U112">
         <v>1.82</v>
@@ -18619,7 +18619,7 @@
         <v>1.36</v>
       </c>
       <c r="AF112">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AG112">
         <v>3.21</v>
@@ -18737,25 +18737,25 @@
         <v>3.1</v>
       </c>
       <c r="Q113">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R113">
         <v>2.65</v>
       </c>
       <c r="S113">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="T113">
         <v>4.8</v>
       </c>
       <c r="U113">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V113">
         <v>1.95</v>
       </c>
       <c r="W113">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X113">
         <v>1.01</v>
@@ -18764,7 +18764,7 @@
         <v>1.05</v>
       </c>
       <c r="Z113">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA113">
         <v>1.28</v>
@@ -18945,7 +18945,7 @@
         <v>1.11</v>
       </c>
       <c r="AF114">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG114">
         <v>2.21</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O117">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P117">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q117">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S117">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T117">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U117">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V117">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W117">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X117">
         <v>1.01</v>
       </c>
       <c r="Y117">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z117">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="AA117">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AB117">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="AC117">
-        <v>2.88</v>
+        <v>2.46</v>
       </c>
       <c r="AD117">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE117">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF117">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG117">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.86</v>
+        <v>1.55</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O118">
+        <v>3.6</v>
+      </c>
+      <c r="P118">
         <v>3.7</v>
       </c>
-      <c r="P118">
+      <c r="Q118">
+        <v>2.5</v>
+      </c>
+      <c r="R118">
+        <v>2.3</v>
+      </c>
+      <c r="S118">
+        <v>1.35</v>
+      </c>
+      <c r="T118">
+        <v>2.85</v>
+      </c>
+      <c r="U118">
         <v>2.75</v>
       </c>
-      <c r="Q118">
-        <v>2.71</v>
-      </c>
-      <c r="R118">
-        <v>2.21</v>
-      </c>
-      <c r="S118">
-        <v>1.29</v>
-      </c>
-      <c r="T118">
-        <v>3.28</v>
-      </c>
-      <c r="U118">
-        <v>2.4</v>
-      </c>
       <c r="V118">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W118">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z118">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="AA118">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AB118">
-        <v>2.34</v>
+        <v>2.05</v>
       </c>
       <c r="AC118">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD118">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AE118">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF118">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG118">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>1.25</v>
       </c>
       <c r="AK118">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19724,10 +19724,10 @@
         <v>1.37</v>
       </c>
       <c r="T119">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U119">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V119">
         <v>1.4</v>
@@ -19742,16 +19742,16 @@
         <v>1.29</v>
       </c>
       <c r="Z119">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="AA119">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB119">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AC119">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="AD119">
         <v>1.25</v>
@@ -20032,10 +20032,10 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="O121">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="P121">
         <v>2.12</v>
@@ -20056,7 +20056,7 @@
         <v>2.23</v>
       </c>
       <c r="V121">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W121">
         <v>1.13</v>
@@ -20358,7 +20358,7 @@
         </is>
       </c>
       <c r="N123">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O123">
         <v>3.9</v>
@@ -20379,7 +20379,7 @@
         <v>3.3</v>
       </c>
       <c r="U123">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V123">
         <v>1.5</v>
@@ -20431,7 +20431,7 @@
         <v>1.16</v>
       </c>
       <c r="AK123">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20693,28 +20693,28 @@
         <v>1.75</v>
       </c>
       <c r="Q125">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="R125">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S125">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T125">
         <v>3.6</v>
       </c>
       <c r="U125">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V125">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W125">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y125">
         <v>1.17</v>
@@ -20726,22 +20726,22 @@
         <v>1.58</v>
       </c>
       <c r="AB125">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC125">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AD125">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE125">
         <v>1.17</v>
       </c>
       <c r="AF125">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG125">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20847,31 +20847,31 @@
         </is>
       </c>
       <c r="N126">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O126">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P126">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q126">
-        <v>4.67</v>
+        <v>4.35</v>
       </c>
       <c r="R126">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S126">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T126">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="U126">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="V126">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W126">
         <v>1.12</v>
@@ -20883,28 +20883,28 @@
         <v>1.14</v>
       </c>
       <c r="Z126">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="AA126">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB126">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AC126">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AD126">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE126">
         <v>1.19</v>
       </c>
       <c r="AF126">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG126">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>1.22</v>
       </c>
       <c r="AK126">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21825,19 +21825,19 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="O132">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P132">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q132">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="R132">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="S132">
         <v>1.36</v>
@@ -21846,10 +21846,10 @@
         <v>2.73</v>
       </c>
       <c r="U132">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="V132">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W132">
         <v>1.07</v>
@@ -21858,31 +21858,31 @@
         <v>1.02</v>
       </c>
       <c r="Y132">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z132">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA132">
         <v>1.95</v>
       </c>
       <c r="AB132">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC132">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD132">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE132">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF132">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AG132">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK132">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,80 +22640,80 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="O137">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P137">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q137">
-        <v>2.13</v>
+        <v>2.79</v>
       </c>
       <c r="R137">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S137">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T137">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U137">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V137">
+        <v>1.36</v>
+      </c>
+      <c r="W137">
+        <v>1.08</v>
+      </c>
+      <c r="X137">
+        <v>1.03</v>
+      </c>
+      <c r="Y137">
+        <v>1.27</v>
+      </c>
+      <c r="Z137">
+        <v>3.14</v>
+      </c>
+      <c r="AA137">
+        <v>1.89</v>
+      </c>
+      <c r="AB137">
+        <v>1.78</v>
+      </c>
+      <c r="AC137">
+        <v>3.14</v>
+      </c>
+      <c r="AD137">
+        <v>1.29</v>
+      </c>
+      <c r="AE137">
+        <v>1.07</v>
+      </c>
+      <c r="AF137">
+        <v>1.72</v>
+      </c>
+      <c r="AG137">
+        <v>1.95</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>1.25</v>
+      </c>
+      <c r="AK137">
         <v>1.53</v>
-      </c>
-      <c r="W137">
-        <v>1.11</v>
-      </c>
-      <c r="X137">
-        <v>1</v>
-      </c>
-      <c r="Y137">
-        <v>1.18</v>
-      </c>
-      <c r="Z137">
-        <v>3.84</v>
-      </c>
-      <c r="AA137">
-        <v>1.7</v>
-      </c>
-      <c r="AB137">
-        <v>1.98</v>
-      </c>
-      <c r="AC137">
-        <v>2.76</v>
-      </c>
-      <c r="AD137">
-        <v>1.34</v>
-      </c>
-      <c r="AE137">
-        <v>1.09</v>
-      </c>
-      <c r="AF137">
-        <v>1.74</v>
-      </c>
-      <c r="AG137">
-        <v>2.05</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>1.17</v>
-      </c>
-      <c r="AK137">
-        <v>2.16</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="O138">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P138">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q138">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="R138">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S138">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T138">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U138">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V138">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W138">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X138">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z138">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA138">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB138">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC138">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="AD138">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF138">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG138">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK138">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -23171,7 +23171,7 @@
         <v>1.73</v>
       </c>
       <c r="AB140">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AC140">
         <v>2.53</v>
@@ -23362,7 +23362,7 @@
         </is>
       </c>
       <c r="AJ141">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK141">
         <v>1.06</v>
@@ -23618,19 +23618,19 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="O143">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="P143">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="Q143">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="R143">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S143">
         <v>1.33</v>
@@ -23645,22 +23645,22 @@
         <v>1.49</v>
       </c>
       <c r="W143">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X143">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y143">
         <v>1.19</v>
       </c>
       <c r="Z143">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AA143">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB143">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC143">
         <v>2.69</v>
@@ -23672,10 +23672,10 @@
         <v>1.11</v>
       </c>
       <c r="AF143">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG143">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK143">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O151">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P151">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25592,16 +25592,16 @@
         <v>1.5</v>
       </c>
       <c r="T155">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U155">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V155">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W155">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X155">
         <v>1.05</v>
@@ -25616,7 +25616,7 @@
         <v>2.27</v>
       </c>
       <c r="AB155">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AC155">
         <v>4.1</v>
@@ -25647,7 +25647,7 @@
         <v>1.36</v>
       </c>
       <c r="AK155">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25909,22 +25909,22 @@
         <v>41</v>
       </c>
       <c r="Q157">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="R157">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="S157">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T157">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="U157">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V157">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W157">
         <v>1.2</v>
@@ -25933,31 +25933,31 @@
         <v>1</v>
       </c>
       <c r="Y157">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z157">
-        <v>8.35</v>
+        <v>7.2</v>
       </c>
       <c r="AA157">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AB157">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AC157">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AD157">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AE157">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF157">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AG157">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>1.01</v>
       </c>
       <c r="AK157">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O169">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P169">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="O170">
         <v>3.5</v>
@@ -28028,7 +28028,7 @@
         <v>2.1</v>
       </c>
       <c r="Q170">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="R170">
         <v>2.25</v>
@@ -28040,7 +28040,7 @@
         <v>3.24</v>
       </c>
       <c r="U170">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V170">
         <v>1.57</v>
@@ -28064,7 +28064,7 @@
         <v>2.25</v>
       </c>
       <c r="AC170">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AD170">
         <v>1.55</v>
@@ -28076,7 +28076,7 @@
         <v>1.51</v>
       </c>
       <c r="AG170">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28197,10 +28197,10 @@
         <v>2.4</v>
       </c>
       <c r="S171">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T171">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U171">
         <v>2.3</v>
@@ -28212,7 +28212,7 @@
         <v>1.11</v>
       </c>
       <c r="X171">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y171">
         <v>1.2</v>
@@ -28692,7 +28692,7 @@
         <v>2.75</v>
       </c>
       <c r="U174">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="V174">
         <v>1.32</v>
@@ -28704,7 +28704,7 @@
         <v>1.02</v>
       </c>
       <c r="Y174">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z174">
         <v>2.68</v>
@@ -28713,7 +28713,7 @@
         <v>2.3</v>
       </c>
       <c r="AB174">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC174">
         <v>3.6</v>
@@ -29006,10 +29006,10 @@
         <v>2.45</v>
       </c>
       <c r="Q176">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R176">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S176">
         <v>1.38</v>
@@ -29018,10 +29018,10 @@
         <v>2.65</v>
       </c>
       <c r="U176">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="V176">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W176">
         <v>1.05</v>
@@ -29036,13 +29036,13 @@
         <v>2.97</v>
       </c>
       <c r="AA176">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AB176">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC176">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD176">
         <v>1.22</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AK176">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29528,10 +29528,10 @@
         <v>1.4</v>
       </c>
       <c r="AB179">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AC179">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AD179">
         <v>1.75</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AK179">
         <v>1.02</v>
@@ -29658,10 +29658,10 @@
         <v>2.4</v>
       </c>
       <c r="Q180">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R180">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S180">
         <v>1.24</v>
@@ -29688,13 +29688,13 @@
         <v>4.45</v>
       </c>
       <c r="AA180">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB180">
         <v>2.33</v>
       </c>
       <c r="AC180">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AD180">
         <v>1.5</v>
@@ -29703,10 +29703,10 @@
         <v>1.18</v>
       </c>
       <c r="AF180">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG180">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK180">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29845,10 +29845,10 @@
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z181">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="AA181">
         <v>1.6</v>
@@ -30307,7 +30307,7 @@
         <v>4.05</v>
       </c>
       <c r="P184">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q184">
         <v>3.75</v>
@@ -30697,7 +30697,7 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK186">
         <v>1.53</v>
@@ -31125,55 +31125,55 @@
         <v>0</v>
       </c>
       <c r="Q189">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R189">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S189">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T189">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U189">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V189">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W189">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X189">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y189">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z189">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA189">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB189">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC189">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD189">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE189">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF189">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG189">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK189">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="O192">
         <v>3.6</v>
@@ -31629,7 +31629,7 @@
         <v>2.05</v>
       </c>
       <c r="V192">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="W192">
         <v>1.17</v>
@@ -31768,7 +31768,7 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="O193">
         <v>6</v>
@@ -31822,7 +31822,7 @@
         <v>1.38</v>
       </c>
       <c r="AF193">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG193">
         <v>2.25</v>
@@ -31940,55 +31940,55 @@
         <v>0</v>
       </c>
       <c r="Q194">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S194">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="T194">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U194">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V194">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W194">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X194">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y194">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z194">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="AA194">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB194">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC194">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD194">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE194">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF194">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG194">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK194">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32103,55 +32103,55 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S195">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T195">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U195">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V195">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W195">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y195">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z195">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA195">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB195">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC195">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD195">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE195">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF195">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG195">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK195">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32266,22 +32266,22 @@
         <v>4.76</v>
       </c>
       <c r="Q196">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R196">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="S196">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T196">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="U196">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="V196">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W196">
         <v>1.05</v>
@@ -32290,31 +32290,31 @@
         <v>1.02</v>
       </c>
       <c r="Y196">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z196">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA196">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB196">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC196">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AD196">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE196">
         <v>1.05</v>
       </c>
       <c r="AF196">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG196">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK196">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32474,10 +32474,10 @@
         <v>1.04</v>
       </c>
       <c r="AF197">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG197">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>4</v>
       </c>
       <c r="Q198">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R198">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S198">
         <v>1.3</v>
@@ -32628,7 +32628,7 @@
         <v>2.15</v>
       </c>
       <c r="AC198">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="AD198">
         <v>1.42</v>
@@ -32755,55 +32755,55 @@
         <v>0</v>
       </c>
       <c r="Q199">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R199">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S199">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T199">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U199">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V199">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W199">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X199">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y199">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z199">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA199">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB199">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC199">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD199">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE199">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF199">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG199">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK199">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33081,22 +33081,22 @@
         <v>2.1</v>
       </c>
       <c r="Q201">
-        <v>4.97</v>
+        <v>4.76</v>
       </c>
       <c r="R201">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S201">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T201">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="U201">
         <v>3.25</v>
       </c>
       <c r="V201">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W201">
         <v>1.02</v>
@@ -33105,10 +33105,10 @@
         <v>1.06</v>
       </c>
       <c r="Y201">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z201">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="AA201">
         <v>2.25</v>
@@ -33117,7 +33117,7 @@
         <v>1.61</v>
       </c>
       <c r="AC201">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AD201">
         <v>1.14</v>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK201">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33244,16 +33244,16 @@
         <v>3.7</v>
       </c>
       <c r="Q202">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R202">
         <v>2.2</v>
       </c>
       <c r="S202">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T202">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
       <c r="U202">
         <v>2.75</v>
@@ -33271,19 +33271,19 @@
         <v>1.23</v>
       </c>
       <c r="Z202">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA202">
         <v>1.95</v>
       </c>
       <c r="AB202">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC202">
         <v>2.97</v>
       </c>
       <c r="AD202">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE202">
         <v>1.09</v>
@@ -33292,7 +33292,7 @@
         <v>1.78</v>
       </c>
       <c r="AG202">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>3.26</v>
       </c>
       <c r="P203">
-        <v>3.58</v>
+        <v>3.67</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="R209">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S209">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T209">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U209">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V209">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W209">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y209">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z209">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE209">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF209">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG209">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK209">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O210">
         <v>3.5</v>
       </c>
       <c r="P210">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="Q210">
         <v>2.84</v>
@@ -34560,10 +34560,10 @@
         <v>4.4</v>
       </c>
       <c r="U210">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V210">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W210">
         <v>1.22</v>
@@ -34593,7 +34593,7 @@
         <v>1.37</v>
       </c>
       <c r="AF210">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG210">
         <v>3.14</v>
@@ -34609,7 +34609,7 @@
         </is>
       </c>
       <c r="AJ210">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AK210">
         <v>1.5</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O211">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="P211">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="Q211">
         <v>2.55</v>
@@ -34729,7 +34729,7 @@
         <v>1.84</v>
       </c>
       <c r="W211">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X211">
         <v>1.01</v>
@@ -34756,7 +34756,7 @@
         <v>1.33</v>
       </c>
       <c r="AF211">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AG211">
         <v>3.1</v>
@@ -34775,7 +34775,7 @@
         <v>1.2</v>
       </c>
       <c r="AK211">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34913,7 +34913,7 @@
         <v>2.09</v>
       </c>
       <c r="AD212">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE212">
         <v>1.25</v>
@@ -35037,7 +35037,7 @@
         <v>6.6</v>
       </c>
       <c r="Q213">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R213">
         <v>3.22</v>
@@ -35046,7 +35046,7 @@
         <v>1.11</v>
       </c>
       <c r="T213">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="U213">
         <v>1.77</v>
@@ -35055,7 +35055,7 @@
         <v>1.95</v>
       </c>
       <c r="W213">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X213">
         <v>1.01</v>
@@ -35076,16 +35076,16 @@
         <v>1.65</v>
       </c>
       <c r="AD213">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AE213">
         <v>1.45</v>
       </c>
       <c r="AF213">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG213">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK213">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35191,31 +35191,31 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="O214">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P214">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="Q214">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R214">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="S214">
         <v>1.17</v>
       </c>
       <c r="T214">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="U214">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V214">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="W214">
         <v>1.25</v>
@@ -35224,28 +35224,28 @@
         <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z214">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="AA214">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB214">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="AC214">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AD214">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE214">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF214">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG214">
         <v>2.8</v>
@@ -35264,7 +35264,7 @@
         <v>1.18</v>
       </c>
       <c r="AK214">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35363,10 +35363,10 @@
         <v>2.48</v>
       </c>
       <c r="Q215">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R215">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S215">
         <v>1.31</v>
@@ -35393,25 +35393,25 @@
         <v>3.58</v>
       </c>
       <c r="AA215">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB215">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC215">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD215">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE215">
         <v>1.08</v>
       </c>
       <c r="AF215">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG215">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK215">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -36658,13 +36658,13 @@
         </is>
       </c>
       <c r="N223">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O223">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P223">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q223">
         <v>2.07</v>
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O228">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P228">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="Q228">
         <v>2.8</v>
@@ -37512,10 +37512,10 @@
         <v>3.58</v>
       </c>
       <c r="AA228">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB228">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC228">
         <v>2.83</v>
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O229">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P229">
         <v>2.6</v>
       </c>
       <c r="Q229">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="R229">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S229">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T229">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U229">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V229">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W229">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X229">
         <v>1.03</v>
       </c>
       <c r="Y229">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z229">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA229">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AB229">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC229">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD229">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE229">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF229">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AG229">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK229">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37799,31 +37799,31 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="O230">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="P230">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q230">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="R230">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S230">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T230">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="U230">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V230">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W230">
         <v>1.06</v>
@@ -37838,25 +37838,25 @@
         <v>3.44</v>
       </c>
       <c r="AA230">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB230">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AC230">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AD230">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE230">
         <v>1.07</v>
       </c>
       <c r="AF230">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="AG230">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK230">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -38019,7 +38019,7 @@
         <v>1.78</v>
       </c>
       <c r="AG231">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O232">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P232">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q232">
         <v>3</v>
@@ -38288,7 +38288,7 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O233">
         <v>3.2</v>
@@ -38300,7 +38300,7 @@
         <v>2.4</v>
       </c>
       <c r="R233">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S233">
         <v>1.42</v>
@@ -38361,7 +38361,7 @@
         <v>1.24</v>
       </c>
       <c r="AK233">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38460,10 +38460,10 @@
         <v>2.02</v>
       </c>
       <c r="Q234">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R234">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S234">
         <v>1.2</v>
@@ -38499,7 +38499,7 @@
         <v>2.02</v>
       </c>
       <c r="AD234">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE234">
         <v>1.35</v>
@@ -38521,7 +38521,7 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AK234">
         <v>1.38</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O236">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P236">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="Q236">
         <v>0</v>
@@ -38940,16 +38940,16 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O237">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P237">
         <v>4.54</v>
       </c>
       <c r="Q237">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R237">
         <v>2.3</v>
@@ -39124,10 +39124,10 @@
         <v>3.25</v>
       </c>
       <c r="U238">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="V238">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W238">
         <v>1.12</v>
@@ -39284,13 +39284,13 @@
         <v>1.33</v>
       </c>
       <c r="T239">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="U239">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="V239">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W239">
         <v>1.05</v>
@@ -39323,7 +39323,7 @@
         <v>1.65</v>
       </c>
       <c r="AG239">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH239" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>4.47</v>
       </c>
       <c r="R240">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="S240">
         <v>1.22</v>
@@ -39450,10 +39450,10 @@
         <v>3.7</v>
       </c>
       <c r="U240">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="V240">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W240">
         <v>1.14</v>
@@ -39462,16 +39462,16 @@
         <v>1.02</v>
       </c>
       <c r="Y240">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z240">
         <v>4.45</v>
       </c>
       <c r="AA240">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB240">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC240">
         <v>2.33</v>
@@ -39480,10 +39480,10 @@
         <v>1.52</v>
       </c>
       <c r="AE240">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF240">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG240">
         <v>2.2</v>
@@ -39499,7 +39499,7 @@
         </is>
       </c>
       <c r="AJ240">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AK240">
         <v>1.15</v>
@@ -40087,7 +40087,7 @@
         <v>3.3</v>
       </c>
       <c r="P244">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q244">
         <v>4</v>
@@ -40286,7 +40286,7 @@
         <v>1.57</v>
       </c>
       <c r="AB245">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC245">
         <v>2.4</v>
@@ -40446,7 +40446,7 @@
         <v>3.09</v>
       </c>
       <c r="AA246">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB246">
         <v>1.72</v>
@@ -40627,7 +40627,7 @@
         <v>1.57</v>
       </c>
       <c r="AG247">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH247" t="inlineStr">
         <is>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O249">
         <v>3.7</v>
       </c>
       <c r="P249">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="Q249">
         <v>2.39</v>
@@ -40914,10 +40914,10 @@
         <v>1.33</v>
       </c>
       <c r="T249">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U249">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="V249">
         <v>1.47</v>
@@ -40938,13 +40938,13 @@
         <v>1.8</v>
       </c>
       <c r="AB249">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AC249">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="AD249">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE249">
         <v>1.11</v>
@@ -41059,49 +41059,49 @@
         </is>
       </c>
       <c r="N250">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="O250">
+        <v>3.3</v>
+      </c>
+      <c r="P250">
         <v>3.45</v>
       </c>
-      <c r="P250">
-        <v>4.1</v>
-      </c>
       <c r="Q250">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R250">
         <v>2.15</v>
       </c>
       <c r="S250">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T250">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U250">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="V250">
         <v>1.4</v>
       </c>
       <c r="W250">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X250">
         <v>1.02</v>
       </c>
       <c r="Y250">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z250">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA250">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB250">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC250">
         <v>3.2</v>
@@ -41113,10 +41113,10 @@
         <v>1.06</v>
       </c>
       <c r="AF250">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG250">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK250">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41394,55 +41394,55 @@
         <v>2.9</v>
       </c>
       <c r="Q252">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R252">
         <v>2.3</v>
       </c>
       <c r="S252">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T252">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U252">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="V252">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W252">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X252">
         <v>1.01</v>
       </c>
       <c r="Y252">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z252">
-        <v>4.3</v>
+        <v>4.68</v>
       </c>
       <c r="AA252">
         <v>1.65</v>
       </c>
       <c r="AB252">
-        <v>2.17</v>
+        <v>2.34</v>
       </c>
       <c r="AC252">
-        <v>2.58</v>
+        <v>2.35</v>
       </c>
       <c r="AD252">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AE252">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF252">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG252">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH252" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>1.25</v>
       </c>
       <c r="AK252">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41732,7 +41732,7 @@
         <v>2.88</v>
       </c>
       <c r="U254">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V254">
         <v>1.36</v>
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="O255">
         <v>3.1</v>
@@ -41901,13 +41901,13 @@
         <v>1.29</v>
       </c>
       <c r="W255">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X255">
         <v>1.04</v>
       </c>
       <c r="Y255">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z255">
         <v>2.62</v>
@@ -41916,7 +41916,7 @@
         <v>2.27</v>
       </c>
       <c r="AB255">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC255">
         <v>4.15</v>
@@ -41947,7 +41947,7 @@
         <v>1.33</v>
       </c>
       <c r="AK255">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL255">
         <v>0</v>
@@ -42855,10 +42855,10 @@
         <v>2.85</v>
       </c>
       <c r="O261">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P261">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="Q261">
         <v>3.76</v>
@@ -43187,37 +43187,37 @@
         <v>3.41</v>
       </c>
       <c r="Q263">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="R263">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S263">
         <v>1.48</v>
       </c>
       <c r="T263">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U263">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="V263">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W263">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X263">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y263">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z263">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA263">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AB263">
         <v>1.65</v>
@@ -43229,13 +43229,13 @@
         <v>1.16</v>
       </c>
       <c r="AE263">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF263">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG263">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1.3</v>
       </c>
       <c r="AK263">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43356,13 +43356,13 @@
         <v>2.38</v>
       </c>
       <c r="S264">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T264">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U264">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="V264">
         <v>1.48</v>
@@ -43414,7 +43414,7 @@
         <v>1.11</v>
       </c>
       <c r="AK264">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O266">
         <v>3.5</v>
@@ -43830,19 +43830,19 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="O267">
         <v>4.1</v>
       </c>
       <c r="P267">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q267">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R267">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S267">
         <v>1.2</v>
@@ -43851,13 +43851,13 @@
         <v>4</v>
       </c>
       <c r="U267">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="V267">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W267">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X267">
         <v>1.01</v>
@@ -43866,28 +43866,28 @@
         <v>1.12</v>
       </c>
       <c r="Z267">
-        <v>5.79</v>
+        <v>3.75</v>
       </c>
       <c r="AA267">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB267">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="AC267">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AD267">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AE267">
         <v>1.31</v>
       </c>
       <c r="AF267">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AG267">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AK267">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43993,65 +43993,65 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="O268">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P268">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="Q268">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="R268">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="S268">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T268">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="U268">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="V268">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="W268">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X268">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y268">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z268">
-        <v>2.93</v>
+        <v>2.77</v>
       </c>
       <c r="AA268">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AB268">
+        <v>1.57</v>
+      </c>
+      <c r="AC268">
+        <v>4.45</v>
+      </c>
+      <c r="AD268">
+        <v>1.16</v>
+      </c>
+      <c r="AE268">
+        <v>1.01</v>
+      </c>
+      <c r="AF268">
+        <v>2.02</v>
+      </c>
+      <c r="AG268">
         <v>1.71</v>
       </c>
-      <c r="AC268">
-        <v>3.78</v>
-      </c>
-      <c r="AD268">
-        <v>1.21</v>
-      </c>
-      <c r="AE268">
-        <v>1.03</v>
-      </c>
-      <c r="AF268">
-        <v>1.87</v>
-      </c>
-      <c r="AG268">
-        <v>1.83</v>
-      </c>
       <c r="AH268" t="inlineStr">
         <is>
           <t>[]</t>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AK268">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44651,7 +44651,7 @@
         <v>3.4</v>
       </c>
       <c r="P272">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Q272">
         <v>0</v>
@@ -44980,22 +44980,22 @@
         <v>1.67</v>
       </c>
       <c r="Q274">
-        <v>4.72</v>
+        <v>3.05</v>
       </c>
       <c r="R274">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="S274">
         <v>1.24</v>
       </c>
       <c r="T274">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="U274">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="V274">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W274">
         <v>0</v>
@@ -45007,28 +45007,28 @@
         <v>1.25</v>
       </c>
       <c r="Z274">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="AA274">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB274">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC274">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="AD274">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE274">
         <v>0</v>
       </c>
       <c r="AF274">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG274">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK274">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45143,7 +45143,7 @@
         <v>6.08</v>
       </c>
       <c r="Q275">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R275">
         <v>2.4</v>
@@ -45170,28 +45170,28 @@
         <v>1.2</v>
       </c>
       <c r="Z275">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="AA275">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB275">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC275">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD275">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE275">
         <v>1.15</v>
       </c>
       <c r="AF275">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG275">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>1.83</v>
       </c>
       <c r="V276">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="W276">
         <v>1.24</v>
@@ -45345,7 +45345,7 @@
         <v>1.79</v>
       </c>
       <c r="AD276">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE276">
         <v>1.36</v>
@@ -45460,13 +45460,13 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="O277">
         <v>4.25</v>
       </c>
       <c r="P277">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q277">
         <v>2.11</v>
@@ -45810,10 +45810,10 @@
         <v>2.99</v>
       </c>
       <c r="V279">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W279">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X279">
         <v>1.02</v>
@@ -45843,7 +45843,7 @@
         <v>1.82</v>
       </c>
       <c r="AG279">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK279">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45961,7 +45961,7 @@
         <v>2.9</v>
       </c>
       <c r="R280">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="S280">
         <v>1.74</v>
@@ -45973,7 +45973,7 @@
         <v>4.3</v>
       </c>
       <c r="V280">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W280">
         <v>1.02</v>
@@ -46003,10 +46003,10 @@
         <v>1.02</v>
       </c>
       <c r="AF280">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AG280">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH280" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         </is>
       </c>
       <c r="AJ280">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK280">
         <v>1.62</v>
@@ -46121,7 +46121,7 @@
         <v>3.1</v>
       </c>
       <c r="Q281">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R281">
         <v>1.86</v>
@@ -46130,7 +46130,7 @@
         <v>1.44</v>
       </c>
       <c r="T281">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U281">
         <v>3.15</v>
@@ -46148,19 +46148,19 @@
         <v>1.47</v>
       </c>
       <c r="Z281">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AA281">
         <v>2.7</v>
       </c>
       <c r="AB281">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AC281">
         <v>4.5</v>
       </c>
       <c r="AD281">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE281">
         <v>1.01</v>
@@ -46345,7 +46345,7 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK282">
         <v>2.15</v>
@@ -46477,7 +46477,7 @@
         <v>3.3</v>
       </c>
       <c r="AA283">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB283">
         <v>1.89</v>
@@ -47105,7 +47105,7 @@
         <v>2.09</v>
       </c>
       <c r="S287">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T287">
         <v>2.5</v>
@@ -47132,13 +47132,13 @@
         <v>2.4</v>
       </c>
       <c r="AB287">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC287">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="AD287">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE287">
         <v>1.01</v>
@@ -47147,7 +47147,7 @@
         <v>2.45</v>
       </c>
       <c r="AG287">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="O288">
         <v>2.85</v>
@@ -47265,7 +47265,7 @@
         <v>3.42</v>
       </c>
       <c r="R288">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S288">
         <v>1.5</v>
@@ -47323,7 +47323,7 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK288">
         <v>1.44</v>
@@ -47470,7 +47470,7 @@
         <v>1</v>
       </c>
       <c r="AF289">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG289">
         <v>1.7</v>
@@ -47597,13 +47597,13 @@
         <v>1.21</v>
       </c>
       <c r="T290">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U290">
         <v>2.07</v>
       </c>
       <c r="V290">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="W290">
         <v>1.2</v>
@@ -47618,13 +47618,13 @@
         <v>6.5</v>
       </c>
       <c r="AA290">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB290">
         <v>2.76</v>
       </c>
       <c r="AC290">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="AD290">
         <v>1.86</v>
@@ -47763,7 +47763,7 @@
         <v>2.45</v>
       </c>
       <c r="U291">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V291">
         <v>1.3</v>
@@ -47796,7 +47796,7 @@
         <v>1.03</v>
       </c>
       <c r="AF291">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG291">
         <v>1.73</v>
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G292">
@@ -47905,80 +47905,80 @@
         </is>
       </c>
       <c r="N292">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O292">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P292">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q292">
-        <v>2.15</v>
+        <v>2.85</v>
       </c>
       <c r="R292">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S292">
+        <v>1.5</v>
+      </c>
+      <c r="T292">
+        <v>2.38</v>
+      </c>
+      <c r="U292">
+        <v>3.24</v>
+      </c>
+      <c r="V292">
+        <v>1.28</v>
+      </c>
+      <c r="W292">
+        <v>1.03</v>
+      </c>
+      <c r="X292">
+        <v>1.05</v>
+      </c>
+      <c r="Y292">
+        <v>1.4</v>
+      </c>
+      <c r="Z292">
+        <v>2.56</v>
+      </c>
+      <c r="AA292">
+        <v>2.31</v>
+      </c>
+      <c r="AB292">
+        <v>1.56</v>
+      </c>
+      <c r="AC292">
+        <v>4.41</v>
+      </c>
+      <c r="AD292">
+        <v>1.2</v>
+      </c>
+      <c r="AE292">
+        <v>1.02</v>
+      </c>
+      <c r="AF292">
+        <v>2</v>
+      </c>
+      <c r="AG292">
+        <v>1.75</v>
+      </c>
+      <c r="AH292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ292">
         <v>1.36</v>
       </c>
-      <c r="T292">
-        <v>3</v>
-      </c>
-      <c r="U292">
-        <v>2.75</v>
-      </c>
-      <c r="V292">
-        <v>1.37</v>
-      </c>
-      <c r="W292">
-        <v>1.04</v>
-      </c>
-      <c r="X292">
-        <v>1.01</v>
-      </c>
-      <c r="Y292">
-        <v>1.28</v>
-      </c>
-      <c r="Z292">
-        <v>3.28</v>
-      </c>
-      <c r="AA292">
-        <v>1.91</v>
-      </c>
-      <c r="AB292">
-        <v>1.93</v>
-      </c>
-      <c r="AC292">
-        <v>3.17</v>
-      </c>
-      <c r="AD292">
-        <v>1.34</v>
-      </c>
-      <c r="AE292">
-        <v>1.07</v>
-      </c>
-      <c r="AF292">
-        <v>1.85</v>
-      </c>
-      <c r="AG292">
-        <v>1.83</v>
-      </c>
-      <c r="AH292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ292">
-        <v>1.22</v>
-      </c>
       <c r="AK292">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,64 +48068,64 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O293">
+        <v>3.65</v>
+      </c>
+      <c r="P293">
+        <v>4.35</v>
+      </c>
+      <c r="Q293">
+        <v>2.15</v>
+      </c>
+      <c r="R293">
+        <v>2.2</v>
+      </c>
+      <c r="S293">
+        <v>1.35</v>
+      </c>
+      <c r="T293">
         <v>3</v>
       </c>
-      <c r="P293">
-        <v>3.25</v>
-      </c>
-      <c r="Q293">
-        <v>2.85</v>
-      </c>
-      <c r="R293">
-        <v>2.06</v>
-      </c>
-      <c r="S293">
-        <v>1.5</v>
-      </c>
-      <c r="T293">
-        <v>2.38</v>
-      </c>
       <c r="U293">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="V293">
+        <v>1.37</v>
+      </c>
+      <c r="W293">
+        <v>1.04</v>
+      </c>
+      <c r="X293">
+        <v>1.01</v>
+      </c>
+      <c r="Y293">
         <v>1.28</v>
       </c>
-      <c r="W293">
-        <v>1.03</v>
-      </c>
-      <c r="X293">
-        <v>1.05</v>
-      </c>
-      <c r="Y293">
-        <v>1.4</v>
-      </c>
       <c r="Z293">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AA293">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="AB293">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="AC293">
-        <v>4.41</v>
+        <v>3.17</v>
       </c>
       <c r="AD293">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AE293">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF293">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG293">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK293">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48246,7 +48246,7 @@
         <v>2.64</v>
       </c>
       <c r="S294">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T294">
         <v>4.75</v>
@@ -48720,43 +48720,43 @@
         </is>
       </c>
       <c r="N297">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O297">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P297">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q297">
         <v>3.9</v>
       </c>
       <c r="R297">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S297">
         <v>1.5</v>
       </c>
       <c r="T297">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="U297">
         <v>3.5</v>
       </c>
       <c r="V297">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W297">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X297">
         <v>1.1</v>
       </c>
       <c r="Y297">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="Z297">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AA297">
         <v>2.5</v>
@@ -48774,10 +48774,10 @@
         <v>1.01</v>
       </c>
       <c r="AF297">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG297">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AH297" t="inlineStr">
         <is>
@@ -48790,10 +48790,10 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AK297">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AL297">
         <v>0</v>
@@ -49698,13 +49698,13 @@
         </is>
       </c>
       <c r="N303">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O303">
         <v>3.5</v>
       </c>
       <c r="P303">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q303">
         <v>2.48</v>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK303">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -50033,16 +50033,16 @@
         <v>4.4</v>
       </c>
       <c r="Q305">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R305">
         <v>2</v>
       </c>
       <c r="S305">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="T305">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="U305">
         <v>3.5</v>
@@ -50054,34 +50054,34 @@
         <v>1.02</v>
       </c>
       <c r="X305">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y305">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z305">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AA305">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AB305">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AC305">
-        <v>4.65</v>
+        <v>5.09</v>
       </c>
       <c r="AD305">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE305">
         <v>1.02</v>
       </c>
       <c r="AF305">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG305">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK305">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50350,19 +50350,19 @@
         </is>
       </c>
       <c r="N307">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O307">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="P307">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="Q307">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R307">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S307">
         <v>1.17</v>
@@ -50383,13 +50383,13 @@
         <v>0</v>
       </c>
       <c r="Y307">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z307">
-        <v>6.41</v>
+        <v>6.73</v>
       </c>
       <c r="AA307">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB307">
         <v>2.9</v>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK307">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50516,7 +50516,7 @@
         <v>2.6</v>
       </c>
       <c r="O308">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P308">
         <v>2.5</v>
@@ -50528,10 +50528,10 @@
         <v>2</v>
       </c>
       <c r="S308">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T308">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U308">
         <v>3.2</v>
@@ -51059,7 +51059,7 @@
         <v>1.7</v>
       </c>
       <c r="AG311">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>1.28</v>
       </c>
       <c r="AK311">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51168,10 +51168,10 @@
         <v>3.2</v>
       </c>
       <c r="O312">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P312">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q312">
         <v>3.48</v>
@@ -51337,22 +51337,22 @@
         <v>3.6</v>
       </c>
       <c r="Q313">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R313">
         <v>1.79</v>
       </c>
       <c r="S313">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T313">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U313">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="V313">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W313">
         <v>1.04</v>
@@ -51370,13 +51370,13 @@
         <v>2.87</v>
       </c>
       <c r="AB313">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC313">
-        <v>5.55</v>
+        <v>5.74</v>
       </c>
       <c r="AD313">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AE313">
         <v>1.03</v>
@@ -51675,7 +51675,7 @@
         <v>4.5</v>
       </c>
       <c r="U315">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V315">
         <v>1.72</v>
@@ -51687,10 +51687,10 @@
         <v>1.01</v>
       </c>
       <c r="Y315">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z315">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA315">
         <v>1.36</v>
@@ -51699,13 +51699,13 @@
         <v>2.83</v>
       </c>
       <c r="AC315">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD315">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE315">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF315">
         <v>1.36</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -2775,7 +2775,7 @@
         <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
         <v>1.43</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
         <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R16">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S16">
         <v>1.2</v>
@@ -3252,22 +3252,22 @@
         <v>2.26</v>
       </c>
       <c r="Q18">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R18">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S18">
         <v>1.44</v>
       </c>
       <c r="T18">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="V18">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W18">
         <v>1.03</v>
@@ -3282,13 +3282,13 @@
         <v>2.66</v>
       </c>
       <c r="AA18">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AB18">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AC18">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD18">
         <v>1.15</v>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         <v>1.68</v>
       </c>
       <c r="Q21">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="R21">
         <v>2.01</v>
@@ -3786,10 +3786,10 @@
         <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4073,65 +4073,65 @@
         <v>2.3</v>
       </c>
       <c r="S23">
+        <v>1.24</v>
+      </c>
+      <c r="T23">
+        <v>3.38</v>
+      </c>
+      <c r="U23">
+        <v>2.24</v>
+      </c>
+      <c r="V23">
+        <v>1.6</v>
+      </c>
+      <c r="W23">
+        <v>1.13</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.14</v>
+      </c>
+      <c r="Z23">
+        <v>4.4</v>
+      </c>
+      <c r="AA23">
+        <v>1.52</v>
+      </c>
+      <c r="AB23">
+        <v>2.38</v>
+      </c>
+      <c r="AC23">
+        <v>2.3</v>
+      </c>
+      <c r="AD23">
+        <v>1.49</v>
+      </c>
+      <c r="AE23">
+        <v>1.17</v>
+      </c>
+      <c r="AF23">
+        <v>1.48</v>
+      </c>
+      <c r="AG23">
+        <v>2.4</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="T23">
-        <v>3.3</v>
-      </c>
-      <c r="U23">
-        <v>2.37</v>
-      </c>
-      <c r="V23">
-        <v>1.54</v>
-      </c>
-      <c r="W23">
-        <v>1.12</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
-        <v>1.17</v>
-      </c>
-      <c r="Z23">
-        <v>3.98</v>
-      </c>
-      <c r="AA23">
-        <v>1.62</v>
-      </c>
-      <c r="AB23">
-        <v>2.22</v>
-      </c>
-      <c r="AC23">
-        <v>2.56</v>
-      </c>
-      <c r="AD23">
-        <v>1.46</v>
-      </c>
-      <c r="AE23">
-        <v>1.14</v>
-      </c>
-      <c r="AF23">
-        <v>1.53</v>
-      </c>
-      <c r="AG23">
-        <v>2.3</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.3</v>
-      </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA24">
         <v>1.75</v>
@@ -4275,10 +4275,10 @@
         <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG24">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
         <v>2.02</v>
@@ -4586,7 +4586,7 @@
         <v>2.88</v>
       </c>
       <c r="AA26">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AB26">
         <v>1.79</v>
@@ -4882,16 +4882,16 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="S28">
         <v>1.44</v>
       </c>
       <c r="T28">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="U28">
         <v>3</v>
@@ -4906,13 +4906,13 @@
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AB28">
         <v>1.8</v>
@@ -4927,10 +4927,10 @@
         <v>1.03</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG28">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,10 +5045,10 @@
         <v>3.06</v>
       </c>
       <c r="Q29">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.4</v>
@@ -5075,7 +5075,7 @@
         <v>2.92</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
         <v>1.64</v>
@@ -5205,7 +5205,7 @@
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Atlético Paso</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,28 +5525,28 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S32">
         <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="V32">
         <v>1.33</v>
@@ -5555,34 +5555,34 @@
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.32</v>
       </c>
       <c r="Z32">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AA32">
         <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC32">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD32">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE32">
         <v>1.04</v>
       </c>
       <c r="AF32">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Paso</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q33">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
         <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
+        <v>1.07</v>
+      </c>
+      <c r="X33">
         <v>1.04</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
       </c>
       <c r="Y33">
         <v>1.32</v>
       </c>
       <c r="Z33">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
         <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="AG33">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>2.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6195,13 +6195,13 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U36">
         <v>2.65</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.08</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>1.5</v>
+      </c>
+      <c r="O41">
+        <v>3.8</v>
+      </c>
+      <c r="P41">
+        <v>6.26</v>
+      </c>
+      <c r="Q41">
         <v>2.03</v>
       </c>
-      <c r="O41">
-        <v>3.22</v>
-      </c>
-      <c r="P41">
-        <v>3.3</v>
-      </c>
-      <c r="Q41">
-        <v>3.07</v>
-      </c>
       <c r="R41">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="U41">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V41">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA41">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC41">
-        <v>3.76</v>
+        <v>3.08</v>
       </c>
       <c r="AD41">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG41">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P42">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
-        <v>2.5</v>
+        <v>3.07</v>
       </c>
       <c r="R42">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S42">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U42">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="V42">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z42">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="AA42">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AC42">
-        <v>4.65</v>
+        <v>3.76</v>
       </c>
       <c r="AD42">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AG42">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
+        <v>2.04</v>
+      </c>
+      <c r="O43">
+        <v>3</v>
+      </c>
+      <c r="P43">
+        <v>3.53</v>
+      </c>
+      <c r="Q43">
+        <v>2.5</v>
+      </c>
+      <c r="R43">
+        <v>1.91</v>
+      </c>
+      <c r="S43">
         <v>1.5</v>
       </c>
-      <c r="O43">
-        <v>3.8</v>
-      </c>
-      <c r="P43">
-        <v>6.26</v>
-      </c>
-      <c r="Q43">
-        <v>2.03</v>
-      </c>
-      <c r="R43">
-        <v>2.25</v>
-      </c>
-      <c r="S43">
-        <v>1.36</v>
-      </c>
       <c r="T43">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y43">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Z43">
-        <v>3.08</v>
+        <v>2.47</v>
       </c>
       <c r="AA43">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="AB43">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AC43">
-        <v>3.08</v>
+        <v>4.65</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AE43">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AG43">
+        <v>1.59</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.3</v>
+      </c>
+      <c r="AK43">
         <v>1.83</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.17</v>
-      </c>
-      <c r="AK43">
-        <v>2.5</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R44">
         <v>2.2</v>
@@ -7976,7 +7976,7 @@
         <v>4</v>
       </c>
       <c r="P47">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q47">
         <v>2.15</v>
@@ -7988,10 +7988,10 @@
         <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
         <v>1.5</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.64</v>
+        <v>2.83</v>
       </c>
       <c r="O48">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="P48">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q48">
         <v>3.5</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.84</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
         <v>1.3</v>
@@ -8471,7 +8471,7 @@
         <v>2.06</v>
       </c>
       <c r="R50">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.33</v>
@@ -8830,7 +8830,7 @@
         <v>1.86</v>
       </c>
       <c r="AC52">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="AD52">
         <v>1.26</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O54">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="P54">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q54">
         <v>1.55</v>
@@ -9126,7 +9126,7 @@
         <v>2.75</v>
       </c>
       <c r="S54">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
         <v>3.42</v>
@@ -9138,7 +9138,7 @@
         <v>1.57</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X54">
         <v>1.02</v>
@@ -9184,7 +9184,7 @@
         <v>1.08</v>
       </c>
       <c r="AK54">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>1.91</v>
       </c>
       <c r="O55">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P55">
         <v>4.22</v>
@@ -10581,7 +10581,7 @@
         <v>2.3</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="P63">
         <v>2.7</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q64">
         <v>2.77</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="O67">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P67">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="Q67">
         <v>1.82</v>
@@ -12386,19 +12386,19 @@
         <v>2.63</v>
       </c>
       <c r="S74">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T74">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="U74">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="V74">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="W74">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X74">
         <v>1.01</v>
@@ -12428,7 +12428,7 @@
         <v>1.25</v>
       </c>
       <c r="AG74">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>4</v>
       </c>
       <c r="U75">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V75">
         <v>1.62</v>
@@ -12863,7 +12863,7 @@
         <v>1.7</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P77">
         <v>4.33</v>
@@ -13032,55 +13032,55 @@
         <v>2.75</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14336,28 +14336,28 @@
         <v>2.67</v>
       </c>
       <c r="Q86">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S86">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T86">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="U86">
         <v>2.8</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W86">
         <v>1.08</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
         <v>1.31</v>
@@ -14366,10 +14366,10 @@
         <v>3.18</v>
       </c>
       <c r="AA86">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB86">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AC86">
         <v>3.62</v>
@@ -14400,7 +14400,7 @@
         <v>1.33</v>
       </c>
       <c r="AK86">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15187,10 +15187,10 @@
         <v>2.27</v>
       </c>
       <c r="AC91">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="AD91">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE91">
         <v>1.14</v>
@@ -15359,7 +15359,7 @@
         <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG92">
         <v>2.25</v>
@@ -15378,7 +15378,7 @@
         <v>1.39</v>
       </c>
       <c r="AK92">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O93">
         <v>3.4</v>
@@ -15483,13 +15483,13 @@
         <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V93">
         <v>1.5</v>
@@ -15507,10 +15507,10 @@
         <v>3.8</v>
       </c>
       <c r="AA93">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB93">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC93">
         <v>2.62</v>
@@ -17282,7 +17282,7 @@
         <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V104">
         <v>1.36</v>
@@ -17660,7 +17660,7 @@
         <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17768,7 +17768,7 @@
         <v>1.24</v>
       </c>
       <c r="T107">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U107">
         <v>2.13</v>
@@ -18417,7 +18417,7 @@
         <v>2.45</v>
       </c>
       <c r="S111">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T111">
         <v>3.8</v>
@@ -19256,10 +19256,10 @@
         <v>4.09</v>
       </c>
       <c r="AA116">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB116">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC116">
         <v>2.84</v>
@@ -19271,7 +19271,7 @@
         <v>1.11</v>
       </c>
       <c r="AF116">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG116">
         <v>2.21</v>
@@ -19567,7 +19567,7 @@
         <v>2.25</v>
       </c>
       <c r="V118">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W118">
         <v>1.16</v>
@@ -19616,7 +19616,7 @@
         <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19869,10 +19869,10 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O120">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P120">
         <v>2.53</v>
@@ -19884,7 +19884,7 @@
         <v>2.24</v>
       </c>
       <c r="S120">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T120">
         <v>3.22</v>
@@ -20038,13 +20038,13 @@
         <v>3.42</v>
       </c>
       <c r="P121">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="Q121">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="R121">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S121">
         <v>1.37</v>
@@ -20204,55 +20204,55 @@
         <v>4.34</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O125">
         <v>3.9</v>
@@ -20741,7 +20741,7 @@
         <v>1.73</v>
       </c>
       <c r="AG125">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="N127">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O127">
         <v>3.8</v>
@@ -21067,7 +21067,7 @@
         <v>1.53</v>
       </c>
       <c r="AG127">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>3.46</v>
       </c>
       <c r="U128">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V128">
         <v>1.54</v>
@@ -21336,31 +21336,31 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="O129">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="P129">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="Q129">
         <v>3.25</v>
       </c>
       <c r="R129">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S129">
         <v>1.43</v>
       </c>
       <c r="T129">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="U129">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="V129">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W129">
         <v>1.03</v>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="N130">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O130">
         <v>6</v>
@@ -21508,55 +21508,55 @@
         <v>1.22</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X130">
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -22323,7 +22323,7 @@
         <v>3.85</v>
       </c>
       <c r="Q135">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R135">
         <v>2.2</v>
@@ -22387,7 +22387,7 @@
         <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O139">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P139">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q139">
         <v>2.13</v>
@@ -23129,13 +23129,13 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O140">
         <v>3.2</v>
       </c>
       <c r="P140">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Q140">
         <v>2.79</v>
@@ -23947,10 +23947,10 @@
         <v>2.29</v>
       </c>
       <c r="O145">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P145">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="Q145">
         <v>2.84</v>
@@ -23980,7 +23980,7 @@
         <v>1.19</v>
       </c>
       <c r="Z145">
-        <v>3.98</v>
+        <v>4.24</v>
       </c>
       <c r="AA145">
         <v>1.73</v>
@@ -24282,7 +24282,7 @@
         <v>2.33</v>
       </c>
       <c r="R147">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="S147">
         <v>1.25</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK147">
         <v>1.91</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,80 +25248,80 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.4</v>
+        <v>4.99</v>
       </c>
       <c r="O153">
+        <v>3.2</v>
+      </c>
+      <c r="P153">
+        <v>1.67</v>
+      </c>
+      <c r="Q153">
+        <v>5.99</v>
+      </c>
+      <c r="R153">
+        <v>1.89</v>
+      </c>
+      <c r="S153">
+        <v>1.48</v>
+      </c>
+      <c r="T153">
+        <v>2.33</v>
+      </c>
+      <c r="U153">
+        <v>3.73</v>
+      </c>
+      <c r="V153">
+        <v>1.21</v>
+      </c>
+      <c r="W153">
+        <v>0</v>
+      </c>
+      <c r="X153">
+        <v>0</v>
+      </c>
+      <c r="Y153">
+        <v>1.48</v>
+      </c>
+      <c r="Z153">
+        <v>2.39</v>
+      </c>
+      <c r="AA153">
         <v>2.66</v>
       </c>
-      <c r="P153">
-        <v>3.15</v>
-      </c>
-      <c r="Q153">
-        <v>3.44</v>
-      </c>
-      <c r="R153">
-        <v>1.69</v>
-      </c>
-      <c r="S153">
-        <v>1.66</v>
-      </c>
-      <c r="T153">
-        <v>1.99</v>
-      </c>
-      <c r="U153">
-        <v>0</v>
-      </c>
-      <c r="V153">
-        <v>0</v>
-      </c>
-      <c r="W153">
-        <v>0</v>
-      </c>
-      <c r="X153">
-        <v>0</v>
-      </c>
-      <c r="Y153">
-        <v>1.76</v>
-      </c>
-      <c r="Z153">
-        <v>1.91</v>
-      </c>
-      <c r="AA153">
-        <v>3.6</v>
-      </c>
       <c r="AB153">
+        <v>1.4</v>
+      </c>
+      <c r="AC153">
+        <v>0</v>
+      </c>
+      <c r="AD153">
+        <v>0</v>
+      </c>
+      <c r="AE153">
+        <v>0</v>
+      </c>
+      <c r="AF153">
+        <v>2.1</v>
+      </c>
+      <c r="AG153">
+        <v>1.62</v>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ153">
         <v>1.23</v>
       </c>
-      <c r="AC153">
-        <v>0</v>
-      </c>
-      <c r="AD153">
-        <v>0</v>
-      </c>
-      <c r="AE153">
-        <v>0</v>
-      </c>
-      <c r="AF153">
-        <v>2.72</v>
-      </c>
-      <c r="AG153">
-        <v>1.38</v>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ153">
-        <v>1.34</v>
-      </c>
       <c r="AK153">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,31 +25411,31 @@
         </is>
       </c>
       <c r="N154">
-        <v>4.99</v>
+        <v>2.4</v>
       </c>
       <c r="O154">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="P154">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="Q154">
-        <v>5.99</v>
+        <v>3.44</v>
       </c>
       <c r="R154">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="S154">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="T154">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="U154">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="V154">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W154">
         <v>0</v>
@@ -25444,16 +25444,16 @@
         <v>0</v>
       </c>
       <c r="Y154">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="Z154">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="AA154">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="AB154">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AC154">
         <v>0</v>
@@ -25465,10 +25465,10 @@
         <v>0</v>
       </c>
       <c r="AF154">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="AG154">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AK154">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK159">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26887,55 +26887,55 @@
         <v>5</v>
       </c>
       <c r="Q163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R163">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S163">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T163">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U163">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V163">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W163">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X163">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y163">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA163">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB163">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC163">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD163">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE163">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF163">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG163">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK163">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27213,55 +27213,55 @@
         <v>4.65</v>
       </c>
       <c r="Q165">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="R165">
         <v>2.5</v>
       </c>
       <c r="S165">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T165">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="U165">
         <v>2.23</v>
       </c>
       <c r="V165">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W165">
         <v>1.13</v>
       </c>
       <c r="X165">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y165">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z165">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA165">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB165">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC165">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AD165">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE165">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF165">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG165">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH165" t="inlineStr">
         <is>
@@ -27274,10 +27274,10 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK165">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AL165">
         <v>0</v>
@@ -27865,55 +27865,55 @@
         <v>4.34</v>
       </c>
       <c r="Q169">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R169">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S169">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T169">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U169">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V169">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W169">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X169">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y169">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z169">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA169">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB169">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC169">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD169">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE169">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF169">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG169">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK169">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28846,7 +28846,7 @@
         <v>2.39</v>
       </c>
       <c r="R175">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="S175">
         <v>1.36</v>
@@ -28904,7 +28904,7 @@
         </is>
       </c>
       <c r="AJ175">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK175">
         <v>1.97</v>
@@ -29009,7 +29009,7 @@
         <v>2.85</v>
       </c>
       <c r="R176">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S176">
         <v>1.44</v>
@@ -29344,13 +29344,13 @@
         <v>2.8</v>
       </c>
       <c r="U178">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V178">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W178">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X178">
         <v>1.03</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK179">
         <v>1.65</v>
@@ -29688,10 +29688,10 @@
         <v>4.2</v>
       </c>
       <c r="AA180">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB180">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC180">
         <v>2.42</v>
@@ -29818,13 +29818,13 @@
         <v>6</v>
       </c>
       <c r="P181">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q181">
         <v>8.35</v>
       </c>
       <c r="R181">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="S181">
         <v>1.16</v>
@@ -29839,7 +29839,7 @@
         <v>1.74</v>
       </c>
       <c r="W181">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X181">
         <v>1.01</v>
@@ -29866,10 +29866,10 @@
         <v>1.27</v>
       </c>
       <c r="AF181">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG181">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.1</v>
+        <v>3.66</v>
       </c>
       <c r="AK181">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29993,16 +29993,16 @@
         <v>1.24</v>
       </c>
       <c r="T182">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U182">
         <v>2.19</v>
       </c>
       <c r="V182">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W182">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X182">
         <v>1.01</v>
@@ -30029,7 +30029,7 @@
         <v>1.18</v>
       </c>
       <c r="AF182">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG182">
         <v>2.55</v>
@@ -30144,13 +30144,13 @@
         <v>3.9</v>
       </c>
       <c r="P183">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Q183">
         <v>4.38</v>
       </c>
       <c r="R183">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="S183">
         <v>1.29</v>
@@ -30627,19 +30627,19 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O186">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P186">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="Q186">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R186">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="S186">
         <v>1.14</v>
@@ -30648,10 +30648,10 @@
         <v>4.8</v>
       </c>
       <c r="U186">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V186">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="W186">
         <v>1.2</v>
@@ -30663,7 +30663,7 @@
         <v>1.06</v>
       </c>
       <c r="Z186">
-        <v>6.3</v>
+        <v>6.84</v>
       </c>
       <c r="AA186">
         <v>1.36</v>
@@ -30672,13 +30672,13 @@
         <v>3.1</v>
       </c>
       <c r="AC186">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD186">
         <v>1.82</v>
       </c>
       <c r="AE186">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF186">
         <v>1.35</v>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>1.23</v>
+        <v>1.91</v>
       </c>
       <c r="AK186">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30962,55 +30962,55 @@
         <v>2.96</v>
       </c>
       <c r="Q188">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="R188">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S188">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="T188">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="U188">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V188">
+        <v>1.44</v>
+      </c>
+      <c r="W188">
+        <v>1.11</v>
+      </c>
+      <c r="X188">
+        <v>1.02</v>
+      </c>
+      <c r="Y188">
+        <v>1.23</v>
+      </c>
+      <c r="Z188">
+        <v>3.95</v>
+      </c>
+      <c r="AA188">
+        <v>1.76</v>
+      </c>
+      <c r="AB188">
+        <v>2.03</v>
+      </c>
+      <c r="AC188">
+        <v>2.83</v>
+      </c>
+      <c r="AD188">
         <v>1.4</v>
       </c>
-      <c r="W188">
-        <v>1.08</v>
-      </c>
-      <c r="X188">
-        <v>1</v>
-      </c>
-      <c r="Y188">
-        <v>1.25</v>
-      </c>
-      <c r="Z188">
-        <v>3.6</v>
-      </c>
-      <c r="AA188">
-        <v>1.79</v>
-      </c>
-      <c r="AB188">
-        <v>1.88</v>
-      </c>
-      <c r="AC188">
-        <v>2.92</v>
-      </c>
-      <c r="AD188">
-        <v>1.31</v>
-      </c>
       <c r="AE188">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF188">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG188">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>1.54</v>
       </c>
       <c r="O189">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P189">
         <v>5.31</v>
@@ -31608,13 +31608,13 @@
         <v>2.5</v>
       </c>
       <c r="O192">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P192">
         <v>2.4</v>
       </c>
       <c r="Q192">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="R192">
         <v>2.4</v>
@@ -31629,7 +31629,7 @@
         <v>2.32</v>
       </c>
       <c r="V192">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W192">
         <v>1.13</v>
@@ -31768,16 +31768,16 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O193">
         <v>3.8</v>
       </c>
       <c r="P193">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="Q193">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R193">
         <v>2.6</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G195">
@@ -32103,56 +32103,56 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R195">
+        <v>2.03</v>
+      </c>
+      <c r="S195">
+        <v>1.35</v>
+      </c>
+      <c r="T195">
+        <v>2.86</v>
+      </c>
+      <c r="U195">
+        <v>2.7</v>
+      </c>
+      <c r="V195">
+        <v>1.4</v>
+      </c>
+      <c r="W195">
+        <v>1.08</v>
+      </c>
+      <c r="X195">
+        <v>1.02</v>
+      </c>
+      <c r="Y195">
+        <v>1.25</v>
+      </c>
+      <c r="Z195">
+        <v>3.28</v>
+      </c>
+      <c r="AA195">
+        <v>1.85</v>
+      </c>
+      <c r="AB195">
+        <v>1.95</v>
+      </c>
+      <c r="AC195">
+        <v>3.05</v>
+      </c>
+      <c r="AD195">
+        <v>1.28</v>
+      </c>
+      <c r="AE195">
+        <v>1.09</v>
+      </c>
+      <c r="AF195">
+        <v>1.75</v>
+      </c>
+      <c r="AG195">
         <v>2</v>
       </c>
-      <c r="S195">
-        <v>1.44</v>
-      </c>
-      <c r="T195">
-        <v>2.43</v>
-      </c>
-      <c r="U195">
-        <v>3.3</v>
-      </c>
-      <c r="V195">
-        <v>1.27</v>
-      </c>
-      <c r="W195">
-        <v>1.02</v>
-      </c>
-      <c r="X195">
-        <v>1.06</v>
-      </c>
-      <c r="Y195">
-        <v>1.43</v>
-      </c>
-      <c r="Z195">
-        <v>2.68</v>
-      </c>
-      <c r="AA195">
-        <v>2.36</v>
-      </c>
-      <c r="AB195">
-        <v>1.51</v>
-      </c>
-      <c r="AC195">
-        <v>4.55</v>
-      </c>
-      <c r="AD195">
-        <v>1.13</v>
-      </c>
-      <c r="AE195">
-        <v>1.01</v>
-      </c>
-      <c r="AF195">
-        <v>2.04</v>
-      </c>
-      <c r="AG195">
-        <v>1.68</v>
-      </c>
       <c r="AH195" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK195">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G196">
@@ -32266,55 +32266,55 @@
         <v>0</v>
       </c>
       <c r="Q196">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R196">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S196">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T196">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="U196">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="V196">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="W196">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y196">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Z196">
-        <v>3.28</v>
+        <v>2.68</v>
       </c>
       <c r="AA196">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AB196">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="AC196">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="AD196">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AE196">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF196">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AG196">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK196">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32429,7 +32429,7 @@
         <v>3.67</v>
       </c>
       <c r="Q197">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="R197">
         <v>2</v>
@@ -32945,10 +32945,10 @@
         <v>1.35</v>
       </c>
       <c r="Z200">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AA200">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB200">
         <v>1.61</v>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK200">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33410,7 +33410,7 @@
         <v>2.39</v>
       </c>
       <c r="R203">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S203">
         <v>1.36</v>
@@ -34865,19 +34865,19 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="O212">
         <v>3.3</v>
       </c>
       <c r="P212">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q212">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R212">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="S212">
         <v>1.31</v>
@@ -34892,7 +34892,7 @@
         <v>1.4</v>
       </c>
       <c r="W212">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X212">
         <v>1.01</v>
@@ -34907,7 +34907,7 @@
         <v>2</v>
       </c>
       <c r="AB212">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AC212">
         <v>2.92</v>
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="O216">
         <v>3.4</v>
       </c>
       <c r="P216">
-        <v>3.03</v>
+        <v>2.87</v>
       </c>
       <c r="Q216">
         <v>2.9</v>
@@ -35538,10 +35538,10 @@
         <v>3.2</v>
       </c>
       <c r="U216">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V216">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W216">
         <v>1.11</v>
@@ -35852,55 +35852,55 @@
         <v>2.2</v>
       </c>
       <c r="Q218">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="R218">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S218">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T218">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U218">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="V218">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W218">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y218">
         <v>1.27</v>
       </c>
       <c r="Z218">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AA218">
         <v>1.9</v>
       </c>
       <c r="AB218">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AC218">
-        <v>3.07</v>
+        <v>3.28</v>
       </c>
       <c r="AD218">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE218">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF218">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG218">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK218">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36006,80 +36006,80 @@
         </is>
       </c>
       <c r="N219">
-        <v>2.86</v>
+        <v>2.41</v>
       </c>
       <c r="O219">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P219">
-        <v>2.39</v>
+        <v>2.71</v>
       </c>
       <c r="Q219">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R219">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U219">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="V219">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W219">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X219">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y219">
+        <v>1.28</v>
+      </c>
+      <c r="Z219">
+        <v>3.08</v>
+      </c>
+      <c r="AA219">
+        <v>1.93</v>
+      </c>
+      <c r="AB219">
+        <v>1.75</v>
+      </c>
+      <c r="AC219">
+        <v>3.28</v>
+      </c>
+      <c r="AD219">
+        <v>1.25</v>
+      </c>
+      <c r="AE219">
+        <v>1.06</v>
+      </c>
+      <c r="AF219">
+        <v>1.73</v>
+      </c>
+      <c r="AG219">
+        <v>1.95</v>
+      </c>
+      <c r="AH219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ219">
         <v>1.26</v>
       </c>
-      <c r="Z219">
-        <v>3.4</v>
-      </c>
-      <c r="AA219">
-        <v>1.89</v>
-      </c>
-      <c r="AB219">
-        <v>1.91</v>
-      </c>
-      <c r="AC219">
-        <v>3.02</v>
-      </c>
-      <c r="AD219">
-        <v>1.34</v>
-      </c>
-      <c r="AE219">
-        <v>1.1</v>
-      </c>
-      <c r="AF219">
-        <v>0</v>
-      </c>
-      <c r="AG219">
-        <v>2.07</v>
-      </c>
-      <c r="AH219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI219" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ219">
-        <v>0</v>
-      </c>
       <c r="AK219">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36184,7 +36184,7 @@
         <v>2.3</v>
       </c>
       <c r="S220">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T220">
         <v>3.12</v>
@@ -36516,7 +36516,7 @@
         <v>2.51</v>
       </c>
       <c r="U222">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="V222">
         <v>1.28</v>
@@ -36863,10 +36863,10 @@
         <v>1.46</v>
       </c>
       <c r="AB224">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AC224">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD224">
         <v>1.56</v>
@@ -36875,10 +36875,10 @@
         <v>1.2</v>
       </c>
       <c r="AF224">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG224">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AH224" t="inlineStr">
         <is>
@@ -36891,10 +36891,10 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK224">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL224">
         <v>0</v>
@@ -37310,10 +37310,10 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="O227">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P227">
         <v>7.1</v>
@@ -37663,7 +37663,7 @@
         <v>1.33</v>
       </c>
       <c r="W229">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X229">
         <v>1.02</v>
@@ -38451,16 +38451,16 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O234">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P234">
-        <v>4.54</v>
+        <v>3.97</v>
       </c>
       <c r="Q234">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="R234">
         <v>2.45</v>
@@ -38656,10 +38656,10 @@
         <v>1.67</v>
       </c>
       <c r="AB235">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC235">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD235">
         <v>1.4</v>
@@ -38795,10 +38795,10 @@
         <v>1.33</v>
       </c>
       <c r="T236">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="U236">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V236">
         <v>1.45</v>
@@ -38943,7 +38943,7 @@
         <v>5</v>
       </c>
       <c r="O237">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P237">
         <v>1.5</v>
@@ -39112,55 +39112,55 @@
         <v>4</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z238">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG238">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH238" t="inlineStr">
         <is>
@@ -39173,10 +39173,10 @@
         </is>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL238">
         <v>0</v>
@@ -39278,7 +39278,7 @@
         <v>6.21</v>
       </c>
       <c r="R239">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="S239">
         <v>1.17</v>
@@ -39305,10 +39305,10 @@
         <v>6.5</v>
       </c>
       <c r="AA239">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB239">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC239">
         <v>1.98</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O241">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P241">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q241">
         <v>4</v>
@@ -39628,25 +39628,25 @@
         <v>1.25</v>
       </c>
       <c r="Z241">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA241">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AB241">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC241">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AD241">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE241">
         <v>1.08</v>
       </c>
       <c r="AF241">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG241">
         <v>2.03</v>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
+        <v>1.29</v>
+      </c>
+      <c r="AK241">
         <v>1.25</v>
-      </c>
-      <c r="AK241">
-        <v>1.29</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -40317,7 +40317,7 @@
         <v>1.28</v>
       </c>
       <c r="AK245">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>3.2</v>
       </c>
       <c r="AA246">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB246">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AC246">
         <v>3.34</v>
@@ -40582,7 +40582,7 @@
         <v>2.39</v>
       </c>
       <c r="R247">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S247">
         <v>1.33</v>
@@ -40600,28 +40600,28 @@
         <v>1.11</v>
       </c>
       <c r="X247">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y247">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z247">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="AA247">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB247">
         <v>2.12</v>
       </c>
       <c r="AC247">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="AD247">
         <v>1.44</v>
       </c>
       <c r="AE247">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF247">
         <v>1.65</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="O248">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P248">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q248">
         <v>2.4</v>
@@ -40751,7 +40751,7 @@
         <v>1.4</v>
       </c>
       <c r="T248">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="U248">
         <v>2.7</v>
@@ -40766,16 +40766,16 @@
         <v>1.02</v>
       </c>
       <c r="Y248">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z248">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA248">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB248">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC248">
         <v>3.2</v>
@@ -40787,10 +40787,10 @@
         <v>1.06</v>
       </c>
       <c r="AF248">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG248">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH248" t="inlineStr">
         <is>
@@ -40803,10 +40803,10 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK248">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -40905,55 +40905,55 @@
         <v>6.58</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R249">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S249">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T249">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U249">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V249">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W249">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X249">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y249">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z249">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA249">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB249">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC249">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD249">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE249">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF249">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG249">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -40966,10 +40966,10 @@
         </is>
       </c>
       <c r="AJ249">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK249">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AL249">
         <v>0</v>
@@ -41059,16 +41059,16 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O250">
         <v>3.45</v>
       </c>
       <c r="P250">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q250">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="R250">
         <v>2.22</v>
@@ -41098,10 +41098,10 @@
         <v>4.6</v>
       </c>
       <c r="AA250">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB250">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AC250">
         <v>2.35</v>
@@ -41113,10 +41113,10 @@
         <v>1.21</v>
       </c>
       <c r="AF250">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG250">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41129,10 +41129,10 @@
         </is>
       </c>
       <c r="AJ250">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AK250">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41403,7 +41403,7 @@
         <v>1.42</v>
       </c>
       <c r="T252">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U252">
         <v>2.88</v>
@@ -41427,7 +41427,7 @@
         <v>2</v>
       </c>
       <c r="AB252">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC252">
         <v>3.28</v>
@@ -41548,16 +41548,16 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="O253">
         <v>3.1</v>
       </c>
       <c r="P253">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q253">
-        <v>2.49</v>
+        <v>2.76</v>
       </c>
       <c r="R253">
         <v>2</v>
@@ -41569,43 +41569,43 @@
         <v>2.63</v>
       </c>
       <c r="U253">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V253">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W253">
         <v>1.05</v>
       </c>
       <c r="X253">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y253">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z253">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AA253">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB253">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC253">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="AD253">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE253">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF253">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG253">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH253" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>1.33</v>
       </c>
       <c r="AK253">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -41747,22 +41747,22 @@
         <v>1.22</v>
       </c>
       <c r="Z254">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA254">
         <v>1.81</v>
       </c>
       <c r="AB254">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC254">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AD254">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE254">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF254">
         <v>1.62</v>
@@ -42535,19 +42535,19 @@
         <v>2.33</v>
       </c>
       <c r="Q259">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="R259">
         <v>2.05</v>
       </c>
       <c r="S259">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T259">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U259">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V259">
         <v>1.38</v>
@@ -42556,34 +42556,34 @@
         <v>1.06</v>
       </c>
       <c r="X259">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y259">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z259">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA259">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB259">
+        <v>1.74</v>
+      </c>
+      <c r="AC259">
+        <v>3.6</v>
+      </c>
+      <c r="AD259">
+        <v>1.25</v>
+      </c>
+      <c r="AE259">
+        <v>1.06</v>
+      </c>
+      <c r="AF259">
         <v>1.75</v>
       </c>
-      <c r="AC259">
-        <v>3.34</v>
-      </c>
-      <c r="AD259">
-        <v>1.24</v>
-      </c>
-      <c r="AE259">
-        <v>1.05</v>
-      </c>
-      <c r="AF259">
-        <v>1.73</v>
-      </c>
       <c r="AG259">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH259" t="inlineStr">
         <is>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK259">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42861,10 +42861,10 @@
         <v>3.41</v>
       </c>
       <c r="Q261">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R261">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S261">
         <v>1.48</v>
@@ -42925,7 +42925,7 @@
         <v>1.25</v>
       </c>
       <c r="AK261">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43030,19 +43030,19 @@
         <v>2.38</v>
       </c>
       <c r="S262">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T262">
         <v>3.4</v>
       </c>
       <c r="U262">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="V262">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W262">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X262">
         <v>1.02</v>
@@ -43088,7 +43088,7 @@
         <v>1.22</v>
       </c>
       <c r="AK262">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL262">
         <v>0</v>
@@ -43193,7 +43193,7 @@
         <v>2.5</v>
       </c>
       <c r="S263">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T263">
         <v>3.75</v>
@@ -43220,7 +43220,7 @@
         <v>1.57</v>
       </c>
       <c r="AB263">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC263">
         <v>2.36</v>
@@ -43350,13 +43350,13 @@
         <v>4.1</v>
       </c>
       <c r="Q264">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R264">
         <v>2.2</v>
       </c>
       <c r="S264">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T264">
         <v>2.92</v>
@@ -43411,10 +43411,10 @@
         </is>
       </c>
       <c r="AJ264">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AK264">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43513,7 +43513,7 @@
         <v>3.9</v>
       </c>
       <c r="Q265">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R265">
         <v>2.69</v>
@@ -43546,7 +43546,7 @@
         <v>1.4</v>
       </c>
       <c r="AB265">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AC265">
         <v>2.03</v>
@@ -43574,7 +43574,7 @@
         </is>
       </c>
       <c r="AJ265">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK265">
         <v>2</v>
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="O266">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P266">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q266">
         <v>2.91</v>
@@ -43685,7 +43685,7 @@
         <v>1.55</v>
       </c>
       <c r="T266">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="U266">
         <v>3.52</v>
@@ -43706,13 +43706,13 @@
         <v>2.59</v>
       </c>
       <c r="AA266">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AB266">
         <v>1.57</v>
       </c>
       <c r="AC266">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AD266">
         <v>1.16</v>
@@ -43830,61 +43830,61 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="O267">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P267">
-        <v>4.19</v>
+        <v>4.87</v>
       </c>
       <c r="Q267">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="R267">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S267">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T267">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U267">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="V267">
+        <v>1.3</v>
+      </c>
+      <c r="W267">
+        <v>1.06</v>
+      </c>
+      <c r="X267">
+        <v>1.06</v>
+      </c>
+      <c r="Y267">
         <v>1.32</v>
       </c>
-      <c r="W267">
-        <v>1.07</v>
-      </c>
-      <c r="X267">
-        <v>0</v>
-      </c>
-      <c r="Y267">
-        <v>1.35</v>
-      </c>
       <c r="Z267">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AA267">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB267">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC267">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AD267">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE267">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF267">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG267">
         <v>1.75</v>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK267">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44014,7 +44014,7 @@
         <v>2.64</v>
       </c>
       <c r="U268">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="V268">
         <v>1.32</v>
@@ -44032,10 +44032,10 @@
         <v>3.08</v>
       </c>
       <c r="AA268">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB268">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC268">
         <v>3.42</v>
@@ -44165,55 +44165,55 @@
         <v>2.73</v>
       </c>
       <c r="Q269">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R269">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S269">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T269">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U269">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V269">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W269">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y269">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z269">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA269">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB269">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC269">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD269">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE269">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF269">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG269">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK269">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="O271">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="P271">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44847,10 +44847,10 @@
         <v>4.31</v>
       </c>
       <c r="AA273">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB273">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AC273">
         <v>2.59</v>
@@ -44865,7 +44865,7 @@
         <v>1.85</v>
       </c>
       <c r="AG273">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>1.17</v>
       </c>
       <c r="AK273">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -44974,7 +44974,7 @@
         <v>1.33</v>
       </c>
       <c r="O274">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="P274">
         <v>8.699999999999999</v>
@@ -45010,16 +45010,16 @@
         <v>6.7</v>
       </c>
       <c r="AA274">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB274">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC274">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AD274">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE274">
         <v>1.36</v>
@@ -45152,7 +45152,7 @@
         <v>1.2</v>
       </c>
       <c r="T275">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="U275">
         <v>1.93</v>
@@ -45173,16 +45173,16 @@
         <v>6.05</v>
       </c>
       <c r="AA275">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB275">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AC275">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD275">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AE275">
         <v>1.33</v>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK275">
         <v>2.3</v>
@@ -45336,10 +45336,10 @@
         <v>4.4</v>
       </c>
       <c r="AA276">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB276">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AC276">
         <v>2.46</v>
@@ -45367,7 +45367,7 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK276">
         <v>1.6</v>
@@ -45499,10 +45499,10 @@
         <v>3.05</v>
       </c>
       <c r="AA277">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AB277">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC277">
         <v>3.5</v>
@@ -45677,7 +45677,7 @@
         <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AG278">
         <v>1.5</v>
@@ -45840,7 +45840,7 @@
         <v>1.01</v>
       </c>
       <c r="AF279">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG279">
         <v>1.67</v>
@@ -45952,7 +45952,7 @@
         <v>1.67</v>
       </c>
       <c r="O280">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P280">
         <v>4.5</v>
@@ -45982,10 +45982,10 @@
         <v>1.01</v>
       </c>
       <c r="Y280">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z280">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA280">
         <v>1.72</v>
@@ -45994,13 +45994,13 @@
         <v>2.2</v>
       </c>
       <c r="AC280">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD280">
         <v>1.44</v>
       </c>
       <c r="AE280">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF280">
         <v>1.65</v>
@@ -46127,7 +46127,7 @@
         <v>2.2</v>
       </c>
       <c r="S281">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T281">
         <v>2.81</v>
@@ -46151,7 +46151,7 @@
         <v>3.3</v>
       </c>
       <c r="AA281">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB281">
         <v>1.89</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O283">
-        <v>3.52</v>
+        <v>3.19</v>
       </c>
       <c r="P283">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q283">
         <v>3.56</v>
@@ -46477,7 +46477,7 @@
         <v>3.58</v>
       </c>
       <c r="AA283">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB283">
         <v>2</v>
@@ -46637,7 +46637,7 @@
         <v>1.08</v>
       </c>
       <c r="Z284">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA284">
         <v>1.44</v>
@@ -46655,7 +46655,7 @@
         <v>1.26</v>
       </c>
       <c r="AF284">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG284">
         <v>2.5</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O286">
         <v>2.85</v>
       </c>
       <c r="P286">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q286">
         <v>3.42</v>
@@ -47283,7 +47283,7 @@
         <v>1.2</v>
       </c>
       <c r="X288">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="Y288">
         <v>1.08</v>
@@ -47295,7 +47295,7 @@
         <v>1.4</v>
       </c>
       <c r="AB288">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="AC288">
         <v>2.13</v>
@@ -47326,7 +47326,7 @@
         <v>1.12</v>
       </c>
       <c r="AK288">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -48077,55 +48077,55 @@
         <v>2.24</v>
       </c>
       <c r="Q293">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="R293">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S293">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T293">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U293">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="V293">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="W293">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X293">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y293">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z293">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AA293">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AB293">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AC293">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AD293">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AE293">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF293">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG293">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AH293" t="inlineStr">
         <is>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK293">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48394,31 +48394,31 @@
         </is>
       </c>
       <c r="N295">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="O295">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P295">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="Q295">
         <v>3.9</v>
       </c>
       <c r="R295">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S295">
         <v>1.5</v>
       </c>
       <c r="T295">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="U295">
         <v>3.5</v>
       </c>
       <c r="V295">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W295">
         <v>1.04</v>
@@ -48430,28 +48430,28 @@
         <v>1.45</v>
       </c>
       <c r="Z295">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="AA295">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AB295">
         <v>1.5</v>
       </c>
       <c r="AC295">
-        <v>5.01</v>
+        <v>4.44</v>
       </c>
       <c r="AD295">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE295">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF295">
         <v>2.1</v>
       </c>
       <c r="AG295">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AK295">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -49375,7 +49375,7 @@
         <v>1.94</v>
       </c>
       <c r="O301">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="P301">
         <v>2.7</v>
@@ -49574,7 +49574,7 @@
         <v>2.29</v>
       </c>
       <c r="AA302">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AB302">
         <v>1.38</v>
@@ -49701,10 +49701,10 @@
         <v>1.78</v>
       </c>
       <c r="O303">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P303">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q303">
         <v>2.4</v>
@@ -50030,7 +50030,7 @@
         <v>4.02</v>
       </c>
       <c r="P305">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="Q305">
         <v>2.45</v>
@@ -50048,7 +50048,7 @@
         <v>1.92</v>
       </c>
       <c r="V305">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W305">
         <v>1.2</v>
@@ -50359,10 +50359,10 @@
         <v>2.98</v>
       </c>
       <c r="Q307">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R307">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S307">
         <v>1.21</v>
@@ -50386,28 +50386,28 @@
         <v>1.1</v>
       </c>
       <c r="Z307">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AA307">
         <v>1.4</v>
       </c>
       <c r="AB307">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AC307">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AD307">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE307">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF307">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG307">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK307">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50746,7 +50746,7 @@
         </is>
       </c>
       <c r="AJ309">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK309">
         <v>1.6</v>
@@ -50912,7 +50912,7 @@
         <v>1.28</v>
       </c>
       <c r="AK310">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL310">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -825,7 +825,7 @@
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
         <v>1.01</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,58 +961,58 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="O4">
-        <v>4.6</v>
+        <v>3.33</v>
       </c>
       <c r="P4">
-        <v>5.75</v>
+        <v>3.23</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="R4">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z4">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="AD4">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>2.81</v>
+        <v>1.87</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,58 +1124,58 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>3.33</v>
+        <v>4.6</v>
       </c>
       <c r="P5">
-        <v>3.23</v>
+        <v>5.75</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB5">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC5">
-        <v>3.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD5">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK5">
-        <v>1.87</v>
+        <v>2.81</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O9">
         <v>3.25</v>
@@ -1815,10 +1815,10 @@
         <v>3.23</v>
       </c>
       <c r="AA9">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
         <v>3.5</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="P11">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R11">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="T11">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
+        <v>1.43</v>
+      </c>
+      <c r="Z11">
+        <v>2.46</v>
+      </c>
+      <c r="AA11">
+        <v>2.29</v>
+      </c>
+      <c r="AB11">
+        <v>1.53</v>
+      </c>
+      <c r="AC11">
+        <v>4.8</v>
+      </c>
+      <c r="AD11">
         <v>1.15</v>
       </c>
-      <c r="Z11">
-        <v>4.65</v>
-      </c>
-      <c r="AA11">
-        <v>1.65</v>
-      </c>
-      <c r="AB11">
-        <v>2.2</v>
-      </c>
-      <c r="AC11">
-        <v>2.43</v>
-      </c>
-      <c r="AD11">
-        <v>1.51</v>
-      </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
+        <v>1.57</v>
+      </c>
+      <c r="O12">
+        <v>4.05</v>
+      </c>
+      <c r="P12">
+        <v>4.6</v>
+      </c>
+      <c r="Q12">
+        <v>2.05</v>
+      </c>
+      <c r="R12">
+        <v>2.39</v>
+      </c>
+      <c r="S12">
+        <v>1.25</v>
+      </c>
+      <c r="T12">
+        <v>3.4</v>
+      </c>
+      <c r="U12">
+        <v>2.38</v>
+      </c>
+      <c r="V12">
+        <v>1.5</v>
+      </c>
+      <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.15</v>
+      </c>
+      <c r="Z12">
+        <v>4.65</v>
+      </c>
+      <c r="AA12">
+        <v>1.65</v>
+      </c>
+      <c r="AB12">
         <v>2.2</v>
       </c>
-      <c r="O12">
-        <v>3</v>
-      </c>
-      <c r="P12">
-        <v>3.1</v>
-      </c>
-      <c r="Q12">
-        <v>2.88</v>
-      </c>
-      <c r="R12">
-        <v>1.85</v>
-      </c>
-      <c r="S12">
-        <v>1.52</v>
-      </c>
-      <c r="T12">
-        <v>2.31</v>
-      </c>
-      <c r="U12">
-        <v>3.25</v>
-      </c>
-      <c r="V12">
-        <v>1.29</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>1.43</v>
-      </c>
-      <c r="Z12">
-        <v>2.46</v>
-      </c>
-      <c r="AA12">
-        <v>2.29</v>
-      </c>
-      <c r="AB12">
-        <v>1.53</v>
-      </c>
       <c r="AC12">
-        <v>4.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD12">
+        <v>1.51</v>
+      </c>
+      <c r="AE12">
         <v>1.15</v>
       </c>
-      <c r="AE12">
-        <v>1.01</v>
-      </c>
       <c r="AF12">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>2.26</v>
       </c>
       <c r="R16">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="S16">
         <v>1.2</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q17">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R17">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="S17">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="V17">
         <v>1.57</v>
@@ -3113,47 +3113,47 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
+        <v>2.3</v>
+      </c>
+      <c r="AC17">
         <v>2.38</v>
-      </c>
-      <c r="AC17">
-        <v>2.43</v>
       </c>
       <c r="AD17">
         <v>1.48</v>
       </c>
       <c r="AE17">
+        <v>1.21</v>
+      </c>
+      <c r="AF17">
+        <v>1.52</v>
+      </c>
+      <c r="AG17">
+        <v>2.27</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.2</v>
       </c>
-      <c r="AF17">
-        <v>1.53</v>
-      </c>
-      <c r="AG17">
-        <v>2.38</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.18</v>
-      </c>
       <c r="AK17">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>2.66</v>
       </c>
       <c r="AA18">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AB18">
         <v>1.56</v>
@@ -3608,10 +3608,10 @@
         <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
         <v>2.92</v>
@@ -4073,49 +4073,49 @@
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W23">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AB23">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC23">
+        <v>2.42</v>
+      </c>
+      <c r="AD23">
+        <v>1.44</v>
+      </c>
+      <c r="AE23">
+        <v>1.15</v>
+      </c>
+      <c r="AF23">
+        <v>1.53</v>
+      </c>
+      <c r="AG23">
         <v>2.3</v>
-      </c>
-      <c r="AD23">
-        <v>1.49</v>
-      </c>
-      <c r="AE23">
-        <v>1.17</v>
-      </c>
-      <c r="AF23">
-        <v>1.48</v>
-      </c>
-      <c r="AG23">
-        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>3</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -4915,7 +4915,7 @@
         <v>2.08</v>
       </c>
       <c r="AB28">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC28">
         <v>3.58</v>
@@ -5202,10 +5202,10 @@
         <v>3.64</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <v>1.07</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="T34">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
+        <v>1.36</v>
+      </c>
+      <c r="Z34">
+        <v>2.7</v>
+      </c>
+      <c r="AA34">
+        <v>2.2</v>
+      </c>
+      <c r="AB34">
+        <v>1.57</v>
+      </c>
+      <c r="AC34">
+        <v>4.15</v>
+      </c>
+      <c r="AD34">
+        <v>1.16</v>
+      </c>
+      <c r="AE34">
         <v>1.03</v>
       </c>
-      <c r="Y34">
-        <v>1.18</v>
-      </c>
-      <c r="Z34">
-        <v>3.84</v>
-      </c>
-      <c r="AA34">
-        <v>1.71</v>
-      </c>
-      <c r="AB34">
-        <v>1.98</v>
-      </c>
-      <c r="AC34">
-        <v>2.74</v>
-      </c>
-      <c r="AD34">
-        <v>1.35</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.89</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="O35">
+        <v>3.18</v>
+      </c>
+      <c r="P35">
+        <v>2.32</v>
+      </c>
+      <c r="Q35">
+        <v>3.3</v>
+      </c>
+      <c r="R35">
+        <v>2.15</v>
+      </c>
+      <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
+        <v>2.9</v>
+      </c>
+      <c r="U35">
+        <v>2.65</v>
+      </c>
+      <c r="V35">
+        <v>1.4</v>
+      </c>
+      <c r="W35">
+        <v>1.08</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.27</v>
+      </c>
+      <c r="Z35">
+        <v>3.14</v>
+      </c>
+      <c r="AA35">
+        <v>1.97</v>
+      </c>
+      <c r="AB35">
+        <v>1.77</v>
+      </c>
+      <c r="AC35">
         <v>3.2</v>
       </c>
-      <c r="P35">
-        <v>2.25</v>
-      </c>
-      <c r="Q35">
-        <v>3</v>
-      </c>
-      <c r="R35">
-        <v>2.05</v>
-      </c>
-      <c r="S35">
-        <v>1.44</v>
-      </c>
-      <c r="T35">
-        <v>2.63</v>
-      </c>
-      <c r="U35">
-        <v>3.1</v>
-      </c>
-      <c r="V35">
-        <v>1.3</v>
-      </c>
-      <c r="W35">
-        <v>1.03</v>
-      </c>
-      <c r="X35">
-        <v>1.04</v>
-      </c>
-      <c r="Y35">
-        <v>1.35</v>
-      </c>
-      <c r="Z35">
-        <v>2.78</v>
-      </c>
-      <c r="AA35">
-        <v>2.15</v>
-      </c>
-      <c r="AB35">
-        <v>1.66</v>
-      </c>
-      <c r="AC35">
-        <v>4.1</v>
-      </c>
       <c r="AD35">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
+        <v>1.26</v>
+      </c>
+      <c r="AK35">
         <v>1.4</v>
-      </c>
-      <c r="AK35">
-        <v>1.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="O36">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.32</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T36">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V36">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA36">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AB36">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AC36">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AD36">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
         <v>1.71</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="P41">
-        <v>6.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
-        <v>2.03</v>
+        <v>3.07</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="U41">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z41">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA41">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>3.08</v>
+        <v>3.76</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>1.5</v>
+      </c>
+      <c r="O42">
+        <v>3.8</v>
+      </c>
+      <c r="P42">
+        <v>6.26</v>
+      </c>
+      <c r="Q42">
         <v>2.03</v>
       </c>
-      <c r="O42">
-        <v>3.22</v>
-      </c>
-      <c r="P42">
-        <v>3.3</v>
-      </c>
-      <c r="Q42">
-        <v>3.07</v>
-      </c>
       <c r="R42">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="U42">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AA42">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AB42">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC42">
-        <v>3.76</v>
+        <v>3.08</v>
       </c>
       <c r="AD42">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>3.58</v>
       </c>
       <c r="AA44">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB44">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC44">
         <v>2.88</v>
@@ -7532,7 +7532,7 @@
         <v>1.32</v>
       </c>
       <c r="AE44">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
         <v>1.61</v>
@@ -7650,7 +7650,7 @@
         <v>3</v>
       </c>
       <c r="P45">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O47">
         <v>4</v>
@@ -7988,10 +7988,10 @@
         <v>1.29</v>
       </c>
       <c r="T47">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="V47">
         <v>1.5</v>
@@ -8154,7 +8154,7 @@
         <v>3.55</v>
       </c>
       <c r="U48">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V48">
         <v>1.69</v>
@@ -8302,13 +8302,13 @@
         <v>3.83</v>
       </c>
       <c r="P49">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="Q49">
         <v>2.36</v>
       </c>
       <c r="R49">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S49">
         <v>1.2</v>
@@ -8317,7 +8317,7 @@
         <v>4.1</v>
       </c>
       <c r="U49">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V49">
         <v>1.7</v>
@@ -8498,10 +8498,10 @@
         <v>3.72</v>
       </c>
       <c r="AA50">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AC50">
         <v>2.7</v>
@@ -8794,7 +8794,7 @@
         <v>2.65</v>
       </c>
       <c r="Q52">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="R52">
         <v>2.21</v>
@@ -8830,7 +8830,7 @@
         <v>1.86</v>
       </c>
       <c r="AC52">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="AD52">
         <v>1.26</v>
@@ -9153,7 +9153,7 @@
         <v>1.49</v>
       </c>
       <c r="AB54">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AC54">
         <v>2.29</v>
@@ -9999,7 +9999,7 @@
         <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10107,43 +10107,43 @@
         <v>1.36</v>
       </c>
       <c r="T60">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="U60">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W60">
         <v>1.06</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA60">
         <v>1.95</v>
       </c>
       <c r="AB60">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC60">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD60">
         <v>1.2</v>
       </c>
       <c r="AE60">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF60">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG60">
         <v>1.7</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O63">
         <v>3.34</v>
       </c>
       <c r="P63">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q63">
         <v>3.17</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11921,7 +11921,7 @@
         <v>2.81</v>
       </c>
       <c r="AA71">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB71">
         <v>1.66</v>
@@ -12072,7 +12072,7 @@
         <v>1.36</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X72">
         <v>1.02</v>
@@ -12217,40 +12217,40 @@
         <v>2.1</v>
       </c>
       <c r="Q73">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="R73">
+        <v>2.04</v>
+      </c>
+      <c r="S73">
+        <v>1.33</v>
+      </c>
+      <c r="T73">
+        <v>2.22</v>
+      </c>
+      <c r="U73">
+        <v>2.8</v>
+      </c>
+      <c r="V73">
+        <v>1.36</v>
+      </c>
+      <c r="W73">
+        <v>1.07</v>
+      </c>
+      <c r="X73">
+        <v>1.03</v>
+      </c>
+      <c r="Y73">
+        <v>1.25</v>
+      </c>
+      <c r="Z73">
+        <v>2.55</v>
+      </c>
+      <c r="AA73">
         <v>1.95</v>
       </c>
-      <c r="S73">
-        <v>1.36</v>
-      </c>
-      <c r="T73">
-        <v>2.73</v>
-      </c>
-      <c r="U73">
-        <v>2.69</v>
-      </c>
-      <c r="V73">
-        <v>1.37</v>
-      </c>
-      <c r="W73">
-        <v>1.06</v>
-      </c>
-      <c r="X73">
-        <v>1.02</v>
-      </c>
-      <c r="Y73">
-        <v>1.22</v>
-      </c>
-      <c r="Z73">
-        <v>3.18</v>
-      </c>
-      <c r="AA73">
-        <v>1.94</v>
-      </c>
       <c r="AB73">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AC73">
         <v>3.34</v>
@@ -12259,13 +12259,13 @@
         <v>1.2</v>
       </c>
       <c r="AE73">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF73">
         <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK73">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>6.35</v>
       </c>
       <c r="AA74">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AC74">
         <v>1.87</v>
@@ -12537,7 +12537,7 @@
         <v>2.45</v>
       </c>
       <c r="O75">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="P75">
         <v>2.55</v>
@@ -14010,55 +14010,55 @@
         <v>1.3</v>
       </c>
       <c r="Q84">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="R84">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="S84">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U84">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="W84">
+        <v>1.12</v>
+      </c>
+      <c r="X84">
+        <v>1.02</v>
+      </c>
+      <c r="Y84">
         <v>1.11</v>
       </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.12</v>
-      </c>
       <c r="Z84">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA84">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AB84">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AC84">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AD84">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AE84">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF84">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG84">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK84">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14348,22 +14348,22 @@
         <v>2.61</v>
       </c>
       <c r="U86">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="V86">
         <v>1.35</v>
       </c>
       <c r="W86">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Z86">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="AA86">
         <v>1.99</v>
@@ -15480,7 +15480,7 @@
         <v>2.55</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
         <v>1.3</v>
@@ -15507,7 +15507,7 @@
         <v>3.8</v>
       </c>
       <c r="AA93">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB93">
         <v>2.12</v>
@@ -15525,7 +15525,7 @@
         <v>1.59</v>
       </c>
       <c r="AG93">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15803,13 +15803,13 @@
         <v>2.38</v>
       </c>
       <c r="Q95">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="R95">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S95">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T95">
         <v>3.25</v>
@@ -15833,7 +15833,7 @@
         <v>4.99</v>
       </c>
       <c r="AA95">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB95">
         <v>2.25</v>
@@ -15864,7 +15864,7 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
         <v>1.49</v>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="O96">
         <v>3.85</v>
@@ -15966,7 +15966,7 @@
         <v>1.8</v>
       </c>
       <c r="Q96">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="R96">
         <v>2.23</v>
@@ -15981,7 +15981,7 @@
         <v>2.09</v>
       </c>
       <c r="V96">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W96">
         <v>1.14</v>
@@ -16002,7 +16002,7 @@
         <v>2.41</v>
       </c>
       <c r="AC96">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AD96">
         <v>1.61</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P101">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q101">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="R101">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="S101">
         <v>1.25</v>
       </c>
       <c r="T101">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U101">
         <v>2.27</v>
       </c>
       <c r="V101">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W101">
         <v>1.1</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z101">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA101">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AB101">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC101">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AD101">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE101">
         <v>1.16</v>
       </c>
       <c r="AF101">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG101">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17282,7 +17282,7 @@
         <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V104">
         <v>1.36</v>
@@ -17300,10 +17300,10 @@
         <v>2.97</v>
       </c>
       <c r="AA104">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB104">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC104">
         <v>3.34</v>
@@ -17433,7 +17433,7 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R105">
         <v>2.1</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17777,7 +17777,7 @@
         <v>1.65</v>
       </c>
       <c r="W107">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X107">
         <v>1.01</v>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O108">
         <v>3</v>
@@ -17925,7 +17925,7 @@
         <v>2.73</v>
       </c>
       <c r="R108">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S108">
         <v>1.41</v>
@@ -17952,10 +17952,10 @@
         <v>2.74</v>
       </c>
       <c r="AA108">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB108">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC108">
         <v>3.94</v>
@@ -17970,7 +17970,7 @@
         <v>1.88</v>
       </c>
       <c r="AG108">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>1.72</v>
       </c>
       <c r="AB110">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC110">
         <v>2.74</v>
@@ -18420,10 +18420,10 @@
         <v>1.25</v>
       </c>
       <c r="T111">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U111">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="V111">
         <v>1.6</v>
@@ -18568,7 +18568,7 @@
         <v>1.31</v>
       </c>
       <c r="O112">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P112">
         <v>6.5</v>
@@ -18607,7 +18607,7 @@
         <v>1.47</v>
       </c>
       <c r="AB112">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC112">
         <v>2.13</v>
@@ -18734,7 +18734,7 @@
         <v>4.9</v>
       </c>
       <c r="P113">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q113">
         <v>5.55</v>
@@ -18909,13 +18909,13 @@
         <v>1.17</v>
       </c>
       <c r="T114">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U114">
         <v>1.82</v>
       </c>
       <c r="V114">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="W114">
         <v>1.22</v>
@@ -18933,7 +18933,7 @@
         <v>1.3</v>
       </c>
       <c r="AB114">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC114">
         <v>1.86</v>
@@ -18948,7 +18948,7 @@
         <v>1.35</v>
       </c>
       <c r="AG114">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>3.3</v>
       </c>
       <c r="P116">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -19271,7 +19271,7 @@
         <v>1.11</v>
       </c>
       <c r="AF116">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG116">
         <v>2.21</v>
@@ -19567,13 +19567,13 @@
         <v>2.25</v>
       </c>
       <c r="V118">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W118">
         <v>1.16</v>
       </c>
       <c r="X118">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
         <v>1.15</v>
@@ -19585,10 +19585,10 @@
         <v>1.54</v>
       </c>
       <c r="AB118">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AC118">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AD118">
         <v>1.53</v>
@@ -19597,10 +19597,10 @@
         <v>1.18</v>
       </c>
       <c r="AF118">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG118">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>1.22</v>
       </c>
       <c r="AK118">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="O119">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P119">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="Q119">
         <v>2.38</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O120">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="P120">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="Q120">
         <v>2.69</v>
@@ -20035,10 +20035,10 @@
         <v>2.91</v>
       </c>
       <c r="O121">
-        <v>3.42</v>
+        <v>3.43</v>
       </c>
       <c r="P121">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q121">
         <v>3.31</v>
@@ -20367,10 +20367,10 @@
         <v>2.12</v>
       </c>
       <c r="Q123">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R123">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S123">
         <v>1.28</v>
@@ -20397,7 +20397,7 @@
         <v>4.5</v>
       </c>
       <c r="AA123">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB123">
         <v>2.4</v>
@@ -20708,10 +20708,10 @@
         <v>2.59</v>
       </c>
       <c r="V125">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W125">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X125">
         <v>1</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK125">
         <v>2.25</v>
@@ -21345,7 +21345,7 @@
         <v>2.55</v>
       </c>
       <c r="Q129">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R129">
         <v>2.05</v>
@@ -22169,16 +22169,16 @@
         <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U134">
         <v>2.79</v>
       </c>
       <c r="V134">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X134">
         <v>1.02</v>
@@ -22193,7 +22193,7 @@
         <v>1.95</v>
       </c>
       <c r="AB134">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC134">
         <v>3.14</v>
@@ -22205,10 +22205,10 @@
         <v>1.07</v>
       </c>
       <c r="AF134">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG134">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O135">
         <v>3.25</v>
@@ -22384,7 +22384,7 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK135">
         <v>1.83</v>
@@ -22824,10 +22824,10 @@
         <v>3.12</v>
       </c>
       <c r="U138">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="V138">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W138">
         <v>1.1</v>
@@ -23005,7 +23005,7 @@
         <v>3.84</v>
       </c>
       <c r="AA139">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB139">
         <v>1.98</v>
@@ -23186,7 +23186,7 @@
         <v>1.72</v>
       </c>
       <c r="AG140">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23651,13 +23651,13 @@
         <v>1.01</v>
       </c>
       <c r="Y143">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z143">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA143">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB143">
         <v>2.29</v>
@@ -23669,13 +23669,13 @@
         <v>1.48</v>
       </c>
       <c r="AE143">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF143">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG143">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK143">
         <v>1.06</v>
@@ -23947,16 +23947,16 @@
         <v>2.29</v>
       </c>
       <c r="O145">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P145">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="Q145">
         <v>2.84</v>
       </c>
       <c r="R145">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="S145">
         <v>1.33</v>
@@ -23980,7 +23980,7 @@
         <v>1.19</v>
       </c>
       <c r="Z145">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="AA145">
         <v>1.73</v>
@@ -24273,10 +24273,10 @@
         <v>1.8</v>
       </c>
       <c r="O147">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P147">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q147">
         <v>2.33</v>
@@ -25740,7 +25740,7 @@
         <v>1.68</v>
       </c>
       <c r="O156">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="P156">
         <v>4.44</v>
@@ -26754,7 +26754,7 @@
         <v>3.58</v>
       </c>
       <c r="AA162">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB162">
         <v>1.99</v>
@@ -27095,7 +27095,7 @@
         <v>1.1</v>
       </c>
       <c r="AF164">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG164">
         <v>2.2</v>
@@ -27243,10 +27243,10 @@
         <v>4.8</v>
       </c>
       <c r="AA165">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB165">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC165">
         <v>2.38</v>
@@ -28345,10 +28345,10 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="O172">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P172">
         <v>2.1</v>
@@ -28372,7 +28372,7 @@
         <v>1.57</v>
       </c>
       <c r="W172">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X172">
         <v>1.01</v>
@@ -28381,25 +28381,25 @@
         <v>1.14</v>
       </c>
       <c r="Z172">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AA172">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB172">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC172">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AD172">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE172">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF172">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AG172">
         <v>2.45</v>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK172">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O173">
         <v>3.82</v>
@@ -28550,7 +28550,7 @@
         <v>1.73</v>
       </c>
       <c r="AB173">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC173">
         <v>2.65</v>
@@ -29018,7 +29018,7 @@
         <v>2.75</v>
       </c>
       <c r="U176">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="V176">
         <v>1.32</v>
@@ -29495,7 +29495,7 @@
         <v>2.8</v>
       </c>
       <c r="Q179">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R179">
         <v>2.5</v>
@@ -29510,7 +29510,7 @@
         <v>2.05</v>
       </c>
       <c r="V179">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W179">
         <v>1.18</v>
@@ -29519,10 +29519,10 @@
         <v>1.02</v>
       </c>
       <c r="Y179">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z179">
-        <v>5.67</v>
+        <v>5.53</v>
       </c>
       <c r="AA179">
         <v>1.43</v>
@@ -29531,10 +29531,10 @@
         <v>2.6</v>
       </c>
       <c r="AC179">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD179">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE179">
         <v>1.22</v>
@@ -30029,7 +30029,7 @@
         <v>1.18</v>
       </c>
       <c r="AF182">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG182">
         <v>2.55</v>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK182">
         <v>1.47</v>
@@ -30144,7 +30144,7 @@
         <v>3.9</v>
       </c>
       <c r="P183">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Q183">
         <v>4.38</v>
@@ -30627,19 +30627,19 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O186">
         <v>3.95</v>
       </c>
       <c r="P186">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
       </c>
       <c r="R186">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S186">
         <v>1.14</v>
@@ -30648,10 +30648,10 @@
         <v>4.8</v>
       </c>
       <c r="U186">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V186">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W186">
         <v>1.2</v>
@@ -30669,13 +30669,13 @@
         <v>1.36</v>
       </c>
       <c r="AB186">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC186">
         <v>1.86</v>
       </c>
       <c r="AD186">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE186">
         <v>1.32</v>
@@ -30700,7 +30700,7 @@
         <v>1.91</v>
       </c>
       <c r="AK186">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30802,7 +30802,7 @@
         <v>5.6</v>
       </c>
       <c r="R187">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="S187">
         <v>1.2</v>
@@ -31315,7 +31315,7 @@
         <v>1.3</v>
       </c>
       <c r="Z190">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AA190">
         <v>2</v>
@@ -31774,7 +31774,7 @@
         <v>3.8</v>
       </c>
       <c r="P193">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="Q193">
         <v>2.62</v>
@@ -31789,7 +31789,7 @@
         <v>3.9</v>
       </c>
       <c r="U193">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V193">
         <v>1.74</v>
@@ -32136,7 +32136,7 @@
         <v>1.85</v>
       </c>
       <c r="AB195">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC195">
         <v>3.05</v>
@@ -32327,7 +32327,7 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK196">
         <v>1.63</v>
@@ -32438,7 +32438,7 @@
         <v>1.4</v>
       </c>
       <c r="T197">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="U197">
         <v>3.08</v>
@@ -32447,7 +32447,7 @@
         <v>1.33</v>
       </c>
       <c r="W197">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X197">
         <v>1.03</v>
@@ -32474,10 +32474,10 @@
         <v>1.04</v>
       </c>
       <c r="AF197">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG197">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32752,7 +32752,7 @@
         <v>3.7</v>
       </c>
       <c r="P199">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q199">
         <v>2.15</v>
@@ -32791,7 +32791,7 @@
         <v>2.15</v>
       </c>
       <c r="AC199">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="AD199">
         <v>1.42</v>
@@ -33142,7 +33142,7 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK201">
         <v>1.66</v>
@@ -33274,10 +33274,10 @@
         <v>2.43</v>
       </c>
       <c r="AA202">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AB202">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AC202">
         <v>4.45</v>
@@ -33407,19 +33407,19 @@
         <v>3.7</v>
       </c>
       <c r="Q203">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="R203">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S203">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T203">
         <v>2.9</v>
       </c>
       <c r="U203">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="V203">
         <v>1.36</v>
@@ -33428,34 +33428,34 @@
         <v>1.07</v>
       </c>
       <c r="X203">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y203">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z203">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA203">
         <v>1.95</v>
       </c>
       <c r="AB203">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC203">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD203">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE203">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF203">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG203">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH203" t="inlineStr">
         <is>
@@ -33468,10 +33468,10 @@
         </is>
       </c>
       <c r="AJ203">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK203">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AL203">
         <v>0</v>
@@ -33600,10 +33600,10 @@
         <v>0</v>
       </c>
       <c r="AA204">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB204">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AC204">
         <v>0</v>
@@ -33926,7 +33926,7 @@
         <v>6.45</v>
       </c>
       <c r="AA206">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB206">
         <v>3.1</v>
@@ -34062,7 +34062,7 @@
         <v>2.37</v>
       </c>
       <c r="R207">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="S207">
         <v>1.13</v>
@@ -34086,16 +34086,16 @@
         <v>1.11</v>
       </c>
       <c r="Z207">
-        <v>6.38</v>
+        <v>6.34</v>
       </c>
       <c r="AA207">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB207">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AC207">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD207">
         <v>1.83</v>
@@ -34234,7 +34234,7 @@
         <v>4.1</v>
       </c>
       <c r="U208">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V208">
         <v>1.68</v>
@@ -34270,7 +34270,7 @@
         <v>1.42</v>
       </c>
       <c r="AG208">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK208">
         <v>1.88</v>
@@ -34397,13 +34397,13 @@
         <v>4.8</v>
       </c>
       <c r="U209">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V209">
         <v>1.95</v>
       </c>
       <c r="W209">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X209">
         <v>1</v>
@@ -34415,10 +34415,10 @@
         <v>8.4</v>
       </c>
       <c r="AA209">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB209">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AC209">
         <v>1.65</v>
@@ -34430,10 +34430,10 @@
         <v>1.52</v>
       </c>
       <c r="AF209">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG209">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>1.95</v>
       </c>
       <c r="W210">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X210">
         <v>1.01</v>
@@ -34578,13 +34578,13 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AA210">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB210">
         <v>3.58</v>
       </c>
       <c r="AC210">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD210">
         <v>2.12</v>
@@ -34744,7 +34744,7 @@
         <v>1.3</v>
       </c>
       <c r="AB211">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="AC211">
         <v>1.76</v>
@@ -34889,7 +34889,7 @@
         <v>2.62</v>
       </c>
       <c r="V212">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W212">
         <v>1.1</v>
@@ -34904,7 +34904,7 @@
         <v>3.58</v>
       </c>
       <c r="AA212">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AB212">
         <v>2.02</v>
@@ -35031,7 +35031,7 @@
         <v>2.22</v>
       </c>
       <c r="O213">
-        <v>3.43</v>
+        <v>3.15</v>
       </c>
       <c r="P213">
         <v>3.1</v>
@@ -35261,7 +35261,7 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK214">
         <v>1.29</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O215">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P215">
-        <v>3.17</v>
+        <v>2.87</v>
       </c>
       <c r="Q215">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R215">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S215">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T215">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U215">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V215">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W215">
         <v>1.11</v>
       </c>
       <c r="X215">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y215">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z215">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA215">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AB215">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AC215">
-        <v>2.54</v>
+        <v>3.04</v>
       </c>
       <c r="AD215">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AE215">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF215">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AG215">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK215">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,80 +35517,80 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O216">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P216">
-        <v>2.87</v>
+        <v>3.17</v>
       </c>
       <c r="Q216">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R216">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S216">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T216">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U216">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V216">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W216">
         <v>1.11</v>
       </c>
       <c r="X216">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y216">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z216">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA216">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AB216">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC216">
-        <v>3.04</v>
+        <v>2.54</v>
       </c>
       <c r="AD216">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE216">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF216">
+        <v>1.51</v>
+      </c>
+      <c r="AG216">
+        <v>2.42</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ216">
+        <v>1.36</v>
+      </c>
+      <c r="AK216">
         <v>1.66</v>
-      </c>
-      <c r="AG216">
-        <v>2.12</v>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ216">
-        <v>1.35</v>
-      </c>
-      <c r="AK216">
-        <v>1.63</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>2.2</v>
       </c>
       <c r="Q218">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R218">
         <v>2.06</v>
@@ -35870,7 +35870,7 @@
         <v>1.37</v>
       </c>
       <c r="W218">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X218">
         <v>1</v>
@@ -36048,7 +36048,7 @@
         <v>1.93</v>
       </c>
       <c r="AB219">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC219">
         <v>3.28</v>
@@ -36347,7 +36347,7 @@
         <v>2.16</v>
       </c>
       <c r="S221">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T221">
         <v>3.09</v>
@@ -36402,7 +36402,7 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AK221">
         <v>1.15</v>
@@ -36891,7 +36891,7 @@
         </is>
       </c>
       <c r="AJ224">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK224">
         <v>2.6</v>
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O225">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P225">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q225">
         <v>2.8</v>
@@ -37023,10 +37023,10 @@
         <v>3.58</v>
       </c>
       <c r="AA225">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB225">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC225">
         <v>2.83</v>
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="O226">
         <v>3</v>
       </c>
       <c r="P226">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q226">
         <v>3.44</v>
@@ -37201,7 +37201,7 @@
         <v>1.04</v>
       </c>
       <c r="AF226">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG226">
         <v>1.82</v>
@@ -37220,7 +37220,7 @@
         <v>1.26</v>
       </c>
       <c r="AK226">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37310,10 +37310,10 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O227">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="P227">
         <v>7.1</v>
@@ -37983,7 +37983,7 @@
         <v>4</v>
       </c>
       <c r="U231">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V231">
         <v>1.73</v>
@@ -38004,7 +38004,7 @@
         <v>1.39</v>
       </c>
       <c r="AB231">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AC231">
         <v>1.9</v>
@@ -38146,7 +38146,7 @@
         <v>3.08</v>
       </c>
       <c r="U232">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V232">
         <v>1.45</v>
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O234">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P234">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="Q234">
         <v>2.04</v>
@@ -38466,7 +38466,7 @@
         <v>2.45</v>
       </c>
       <c r="S234">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T234">
         <v>3.38</v>
@@ -38493,7 +38493,7 @@
         <v>1.64</v>
       </c>
       <c r="AB234">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC234">
         <v>2.38</v>
@@ -38795,10 +38795,10 @@
         <v>1.33</v>
       </c>
       <c r="T236">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U236">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V236">
         <v>1.45</v>
@@ -38943,7 +38943,7 @@
         <v>5</v>
       </c>
       <c r="O237">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P237">
         <v>1.5</v>
@@ -39607,19 +39607,19 @@
         <v>2.15</v>
       </c>
       <c r="S241">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T241">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="U241">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V241">
         <v>1.4</v>
       </c>
       <c r="W241">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X241">
         <v>1.01</v>
@@ -39791,7 +39791,7 @@
         <v>1.12</v>
       </c>
       <c r="Z242">
-        <v>4.69</v>
+        <v>4.7</v>
       </c>
       <c r="AA242">
         <v>1.57</v>
@@ -39806,7 +39806,7 @@
         <v>1.53</v>
       </c>
       <c r="AE242">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF242">
         <v>1.57</v>
@@ -39936,7 +39936,7 @@
         <v>1.36</v>
       </c>
       <c r="T243">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U243">
         <v>3</v>
@@ -40283,7 +40283,7 @@
         <v>3.84</v>
       </c>
       <c r="AA245">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB245">
         <v>2.03</v>
@@ -40570,10 +40570,10 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O247">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P247">
         <v>3.52</v>
@@ -40742,7 +40742,7 @@
         <v>3.35</v>
       </c>
       <c r="Q248">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R248">
         <v>2.15</v>
@@ -40778,10 +40778,10 @@
         <v>1.76</v>
       </c>
       <c r="AC248">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD248">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE248">
         <v>1.06</v>
@@ -40803,7 +40803,7 @@
         </is>
       </c>
       <c r="AJ248">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK248">
         <v>1.75</v>
@@ -41225,7 +41225,7 @@
         <v>1.77</v>
       </c>
       <c r="O251">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="P251">
         <v>3.8</v>
@@ -41427,7 +41427,7 @@
         <v>2</v>
       </c>
       <c r="AB252">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC252">
         <v>3.28</v>
@@ -41548,7 +41548,7 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O253">
         <v>3.1</v>
@@ -41557,7 +41557,7 @@
         <v>3.4</v>
       </c>
       <c r="Q253">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="R253">
         <v>2</v>
@@ -41581,16 +41581,16 @@
         <v>1.05</v>
       </c>
       <c r="Y253">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z253">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA253">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB253">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC253">
         <v>4.34</v>
@@ -41621,7 +41621,7 @@
         <v>1.33</v>
       </c>
       <c r="AK253">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL253">
         <v>0</v>
@@ -42861,7 +42861,7 @@
         <v>3.41</v>
       </c>
       <c r="Q261">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R261">
         <v>2</v>
@@ -42925,7 +42925,7 @@
         <v>1.25</v>
       </c>
       <c r="AK261">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL261">
         <v>0</v>
@@ -43217,7 +43217,7 @@
         <v>5</v>
       </c>
       <c r="AA263">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB263">
         <v>2.45</v>
@@ -43347,7 +43347,7 @@
         <v>3.5</v>
       </c>
       <c r="P264">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q264">
         <v>2.34</v>
@@ -43507,7 +43507,7 @@
         <v>1.71</v>
       </c>
       <c r="O265">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P265">
         <v>3.9</v>
@@ -43531,7 +43531,7 @@
         <v>1.7</v>
       </c>
       <c r="W265">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X265">
         <v>1.01</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O266">
         <v>3.1</v>
@@ -43685,7 +43685,7 @@
         <v>1.55</v>
       </c>
       <c r="T266">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="U266">
         <v>3.52</v>
@@ -43706,13 +43706,13 @@
         <v>2.59</v>
       </c>
       <c r="AA266">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AB266">
         <v>1.57</v>
       </c>
       <c r="AC266">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="AD266">
         <v>1.16</v>
@@ -43737,7 +43737,7 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AK266">
         <v>1.71</v>
@@ -43839,55 +43839,55 @@
         <v>4.87</v>
       </c>
       <c r="Q267">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="R267">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S267">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T267">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U267">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V267">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W267">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X267">
         <v>1.06</v>
       </c>
       <c r="Y267">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z267">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA267">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB267">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC267">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD267">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE267">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF267">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG267">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH267" t="inlineStr">
         <is>
@@ -43900,10 +43900,10 @@
         </is>
       </c>
       <c r="AJ267">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK267">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -44174,7 +44174,7 @@
         <v>1.3</v>
       </c>
       <c r="T269">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U269">
         <v>2.45</v>
@@ -44183,7 +44183,7 @@
         <v>1.44</v>
       </c>
       <c r="W269">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X269">
         <v>1</v>
@@ -44485,7 +44485,7 @@
         <v>1.22</v>
       </c>
       <c r="O271">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="P271">
         <v>12</v>
@@ -44654,10 +44654,10 @@
         <v>1.67</v>
       </c>
       <c r="Q272">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R272">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S272">
         <v>1.24</v>
@@ -44669,10 +44669,10 @@
         <v>2.43</v>
       </c>
       <c r="V272">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W272">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X272">
         <v>0</v>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK272">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44808,10 +44808,10 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O273">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P273">
         <v>6.08</v>
@@ -44865,7 +44865,7 @@
         <v>1.85</v>
       </c>
       <c r="AG273">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44971,10 +44971,10 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="O274">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="P274">
         <v>8.699999999999999</v>
@@ -45134,7 +45134,7 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="O275">
         <v>4.25</v>
@@ -45155,7 +45155,7 @@
         <v>3.98</v>
       </c>
       <c r="U275">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V275">
         <v>1.74</v>
@@ -45324,7 +45324,7 @@
         <v>1.57</v>
       </c>
       <c r="W276">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X276">
         <v>1.01</v>
@@ -45632,43 +45632,43 @@
         <v>3.6</v>
       </c>
       <c r="Q278">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R278">
         <v>1.71</v>
       </c>
       <c r="S278">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="T278">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U278">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="V278">
         <v>1.15</v>
       </c>
       <c r="W278">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X278">
         <v>1.12</v>
       </c>
       <c r="Y278">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Z278">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AA278">
         <v>3.5</v>
       </c>
       <c r="AB278">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC278">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="AD278">
         <v>1.05</v>
@@ -45693,7 +45693,7 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AK278">
         <v>1.62</v>
@@ -45786,28 +45786,28 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O279">
         <v>2.87</v>
       </c>
       <c r="P279">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q279">
         <v>3.04</v>
       </c>
       <c r="R279">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="S279">
         <v>1.44</v>
       </c>
       <c r="T279">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="U279">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="V279">
         <v>1.3</v>
@@ -45816,25 +45816,25 @@
         <v>1.05</v>
       </c>
       <c r="X279">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y279">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z279">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AA279">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB279">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC279">
         <v>4.5</v>
       </c>
       <c r="AD279">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE279">
         <v>1.01</v>
@@ -46124,7 +46124,7 @@
         <v>2.31</v>
       </c>
       <c r="R281">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S281">
         <v>1.36</v>
@@ -47455,10 +47455,10 @@
         <v>2.52</v>
       </c>
       <c r="AA289">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB289">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC289">
         <v>4.33</v>
@@ -47585,7 +47585,7 @@
         <v>3.65</v>
       </c>
       <c r="P290">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q290">
         <v>2.15</v>
@@ -47618,10 +47618,10 @@
         <v>3.28</v>
       </c>
       <c r="AA290">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB290">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC290">
         <v>3.17</v>
@@ -47636,7 +47636,7 @@
         <v>1.85</v>
       </c>
       <c r="AG290">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47748,13 +47748,13 @@
         <v>3</v>
       </c>
       <c r="P291">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q291">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="R291">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="S291">
         <v>1.5</v>
@@ -47769,7 +47769,7 @@
         <v>1.28</v>
       </c>
       <c r="W291">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X291">
         <v>1.05</v>
@@ -47781,10 +47781,10 @@
         <v>2.56</v>
       </c>
       <c r="AA291">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AB291">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC291">
         <v>4.41</v>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK291">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL291">
         <v>0</v>
@@ -50260,7 +50260,7 @@
         <v>1.33</v>
       </c>
       <c r="AK306">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL306">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G4">
@@ -961,58 +961,58 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="O4">
-        <v>3.33</v>
+        <v>4.6</v>
       </c>
       <c r="P4">
-        <v>3.23</v>
+        <v>6.7</v>
       </c>
       <c r="Q4">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U4">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z4">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AA4">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC4">
-        <v>3.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
         <v>1.75</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK4">
-        <v>1.87</v>
+        <v>2.81</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,58 +1124,58 @@
         </is>
       </c>
       <c r="N5">
+        <v>1.93</v>
+      </c>
+      <c r="O5">
+        <v>3.33</v>
+      </c>
+      <c r="P5">
+        <v>3.23</v>
+      </c>
+      <c r="Q5">
+        <v>2.5</v>
+      </c>
+      <c r="R5">
+        <v>2.2</v>
+      </c>
+      <c r="S5">
+        <v>1.33</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>2.64</v>
+      </c>
+      <c r="V5">
         <v>1.4</v>
       </c>
-      <c r="O5">
-        <v>4.6</v>
-      </c>
-      <c r="P5">
-        <v>5.75</v>
-      </c>
-      <c r="Q5">
-        <v>1.75</v>
-      </c>
-      <c r="R5">
-        <v>2.34</v>
-      </c>
-      <c r="S5">
-        <v>1.22</v>
-      </c>
-      <c r="T5">
-        <v>3.8</v>
-      </c>
-      <c r="U5">
-        <v>2.25</v>
-      </c>
-      <c r="V5">
-        <v>1.57</v>
-      </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC5">
-        <v>2.33</v>
+        <v>3.08</v>
       </c>
       <c r="AD5">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>2.81</v>
+        <v>1.87</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,10 +1296,10 @@
         <v>7.02</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
         <v>1.25</v>
@@ -1329,7 +1329,7 @@
         <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
         <v>2.61</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="P7">
         <v>4.15</v>
@@ -1489,7 +1489,7 @@
         <v>3.96</v>
       </c>
       <c r="AA7">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
         <v>2.15</v>
@@ -1498,10 +1498,10 @@
         <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
         <v>1.65</v>
@@ -1978,10 +1978,10 @@
         <v>3.47</v>
       </c>
       <c r="AA10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB10">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
         <v>3.42</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
         <v>1.79</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q11">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>2.39</v>
       </c>
       <c r="S11">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="U11">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="Z11">
-        <v>2.46</v>
+        <v>4.65</v>
       </c>
       <c r="AA11">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
-        <v>4.8</v>
+        <v>2.43</v>
       </c>
       <c r="AD11">
+        <v>1.51</v>
+      </c>
+      <c r="AE11">
         <v>1.15</v>
       </c>
-      <c r="AE11">
-        <v>1.01</v>
-      </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="O12">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="P12">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>2.39</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="T12">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
+        <v>1.44</v>
+      </c>
+      <c r="Z12">
+        <v>2.46</v>
+      </c>
+      <c r="AA12">
+        <v>2.29</v>
+      </c>
+      <c r="AB12">
+        <v>1.53</v>
+      </c>
+      <c r="AC12">
+        <v>4.8</v>
+      </c>
+      <c r="AD12">
         <v>1.15</v>
       </c>
-      <c r="Z12">
-        <v>4.65</v>
-      </c>
-      <c r="AA12">
-        <v>1.65</v>
-      </c>
-      <c r="AB12">
-        <v>2.2</v>
-      </c>
-      <c r="AC12">
-        <v>2.43</v>
-      </c>
-      <c r="AD12">
-        <v>1.51</v>
-      </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2461,16 +2461,16 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AA13">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC13">
         <v>2.74</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.82</v>
+        <v>4.59</v>
       </c>
       <c r="Q19">
-        <v>2.81</v>
+        <v>2.35</v>
       </c>
       <c r="R19">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T19">
         <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.59</v>
+        <v>2.82</v>
       </c>
       <c r="Q20">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
         <v>3.1</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD20">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4390,10 +4390,10 @@
         <v>3.65</v>
       </c>
       <c r="P25">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q25">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R25">
         <v>2.5</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,80 +6992,80 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O41">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="Q41">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="R41">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T41">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U41">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="V41">
+        <v>1.25</v>
+      </c>
+      <c r="W41">
+        <v>1.01</v>
+      </c>
+      <c r="X41">
+        <v>1.07</v>
+      </c>
+      <c r="Y41">
+        <v>1.5</v>
+      </c>
+      <c r="Z41">
+        <v>2.47</v>
+      </c>
+      <c r="AA41">
+        <v>2.5</v>
+      </c>
+      <c r="AB41">
+        <v>1.47</v>
+      </c>
+      <c r="AC41">
+        <v>4.65</v>
+      </c>
+      <c r="AD41">
+        <v>1.12</v>
+      </c>
+      <c r="AE41">
+        <v>1.03</v>
+      </c>
+      <c r="AF41">
+        <v>2.19</v>
+      </c>
+      <c r="AG41">
+        <v>1.59</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ41">
         <v>1.3</v>
       </c>
-      <c r="W41">
-        <v>1.04</v>
-      </c>
-      <c r="X41">
-        <v>1.03</v>
-      </c>
-      <c r="Y41">
-        <v>1.31</v>
-      </c>
-      <c r="Z41">
-        <v>2.92</v>
-      </c>
-      <c r="AA41">
-        <v>2.1</v>
-      </c>
-      <c r="AB41">
-        <v>1.7</v>
-      </c>
-      <c r="AC41">
-        <v>3.76</v>
-      </c>
-      <c r="AD41">
-        <v>1.19</v>
-      </c>
-      <c r="AE41">
-        <v>1.04</v>
-      </c>
-      <c r="AF41">
-        <v>1.81</v>
-      </c>
-      <c r="AG41">
-        <v>1.88</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.26</v>
-      </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P43">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>3.07</v>
       </c>
       <c r="R43">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S43">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U43">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="V43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="AA43">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB43">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AC43">
-        <v>4.65</v>
+        <v>3.76</v>
       </c>
       <c r="AD43">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AG43">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>4</v>
       </c>
       <c r="U62">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="V62">
         <v>1.73</v>
@@ -14206,7 +14206,7 @@
         <v>1.42</v>
       </c>
       <c r="AB85">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC85">
         <v>2.19</v>
@@ -14221,7 +14221,7 @@
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>3.6</v>
       </c>
       <c r="U107">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V107">
         <v>1.65</v>
@@ -17792,7 +17792,7 @@
         <v>1.53</v>
       </c>
       <c r="AB107">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC107">
         <v>2.34</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="O114">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P114">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q114">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="R114">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="S114">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T114">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U114">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V114">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="W114">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z114">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA114">
+        <v>1.28</v>
+      </c>
+      <c r="AB114">
+        <v>3.6</v>
+      </c>
+      <c r="AC114">
+        <v>1.72</v>
+      </c>
+      <c r="AD114">
+        <v>2.09</v>
+      </c>
+      <c r="AE114">
+        <v>1.48</v>
+      </c>
+      <c r="AF114">
         <v>1.3</v>
       </c>
-      <c r="AB114">
-        <v>3.4</v>
-      </c>
-      <c r="AC114">
-        <v>1.86</v>
-      </c>
-      <c r="AD114">
-        <v>1.96</v>
-      </c>
-      <c r="AE114">
-        <v>1.36</v>
-      </c>
-      <c r="AF114">
-        <v>1.35</v>
-      </c>
       <c r="AG114">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK114">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="O115">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P115">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="Q115">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="R115">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="S115">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T115">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U115">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V115">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="W115">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X115">
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z115">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AA115">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB115">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC115">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AD115">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="AE115">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AF115">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AG115">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK115">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O119">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="P119">
-        <v>3.56</v>
+        <v>2.73</v>
       </c>
       <c r="Q119">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="R119">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S119">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T119">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="U119">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V119">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W119">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X119">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y119">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z119">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="AA119">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB119">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC119">
-        <v>2.96</v>
+        <v>2.62</v>
       </c>
       <c r="AD119">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AE119">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF119">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG119">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK119">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
+        <v>2.03</v>
+      </c>
+      <c r="O120">
+        <v>3.45</v>
+      </c>
+      <c r="P120">
+        <v>3.56</v>
+      </c>
+      <c r="Q120">
+        <v>2.38</v>
+      </c>
+      <c r="R120">
         <v>2.3</v>
       </c>
-      <c r="O120">
-        <v>3.56</v>
-      </c>
-      <c r="P120">
-        <v>2.73</v>
-      </c>
-      <c r="Q120">
-        <v>2.69</v>
-      </c>
-      <c r="R120">
-        <v>2.24</v>
-      </c>
       <c r="S120">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="U120">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V120">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W120">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z120">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA120">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AB120">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC120">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="AD120">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AE120">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG120">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>4.15</v>
       </c>
       <c r="AA132">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB132">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC132">
         <v>2.49</v>
@@ -21988,31 +21988,31 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="O133">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="P133">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q133">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="R133">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="S133">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="T133">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="U133">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="V133">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W133">
         <v>1.16</v>
@@ -22042,10 +22042,10 @@
         <v>1.32</v>
       </c>
       <c r="AF133">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AG133">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>1.01</v>
       </c>
       <c r="AK133">
-        <v>5.55</v>
+        <v>5.15</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,61 +22966,61 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="O139">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P139">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="Q139">
-        <v>2.13</v>
+        <v>2.79</v>
       </c>
       <c r="R139">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="S139">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T139">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U139">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="V139">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X139">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z139">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="AA139">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AB139">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC139">
-        <v>2.76</v>
+        <v>3.14</v>
       </c>
       <c r="AD139">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE139">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF139">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG139">
         <v>2.05</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK139">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,61 +23129,61 @@
         </is>
       </c>
       <c r="N140">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="O140">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P140">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="Q140">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="R140">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S140">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T140">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U140">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V140">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W140">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X140">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y140">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z140">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA140">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB140">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC140">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="AD140">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE140">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF140">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG140">
         <v>2.05</v>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK140">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23473,7 +23473,7 @@
         <v>1.29</v>
       </c>
       <c r="T142">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U142">
         <v>2.4</v>
@@ -23512,7 +23512,7 @@
         <v>1.57</v>
       </c>
       <c r="AG142">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>1.62</v>
       </c>
       <c r="W161">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X161">
         <v>1.01</v>
@@ -26591,10 +26591,10 @@
         <v>4.75</v>
       </c>
       <c r="AA161">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB161">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AC161">
         <v>2.33</v>
@@ -26609,7 +26609,7 @@
         <v>1.7</v>
       </c>
       <c r="AG161">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK161">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="O165">
         <v>4.2</v>
@@ -27225,7 +27225,7 @@
         <v>3.55</v>
       </c>
       <c r="U165">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="V165">
         <v>1.62</v>
@@ -27274,7 +27274,7 @@
         </is>
       </c>
       <c r="AJ165">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK165">
         <v>2.27</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,64 +27693,64 @@
         </is>
       </c>
       <c r="N168">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O168">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P168">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="Q168">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R168">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S168">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T168">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U168">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V168">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W168">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X168">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y168">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z168">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA168">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB168">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC168">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD168">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE168">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF168">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG168">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,10 +27763,10 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK168">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O169">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P169">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="Q169">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R169">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S169">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T169">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U169">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V169">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W169">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X169">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y169">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z169">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA169">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB169">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AC169">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD169">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE169">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF169">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG169">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK169">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O173">
         <v>3.82</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O186">
         <v>3.95</v>
       </c>
       <c r="P186">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
@@ -30663,13 +30663,13 @@
         <v>1.06</v>
       </c>
       <c r="Z186">
-        <v>6.84</v>
+        <v>6.87</v>
       </c>
       <c r="AA186">
         <v>1.36</v>
       </c>
       <c r="AB186">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AC186">
         <v>1.86</v>
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O192">
         <v>3.7</v>
       </c>
       <c r="P192">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q192">
         <v>2.83</v>
@@ -31768,7 +31768,7 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O193">
         <v>3.8</v>
@@ -31789,7 +31789,7 @@
         <v>3.9</v>
       </c>
       <c r="U193">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V193">
         <v>1.74</v>
@@ -32918,55 +32918,55 @@
         <v>0</v>
       </c>
       <c r="Q200">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S200">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T200">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U200">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V200">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W200">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X200">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y200">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z200">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AA200">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB200">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC200">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AD200">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE200">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF200">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG200">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK200">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33096,7 +33096,7 @@
         <v>2.34</v>
       </c>
       <c r="V201">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W201">
         <v>1.09</v>
@@ -33111,7 +33111,7 @@
         <v>3.78</v>
       </c>
       <c r="AA201">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AB201">
         <v>2</v>
@@ -33262,7 +33262,7 @@
         <v>1.27</v>
       </c>
       <c r="W202">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X202">
         <v>1.06</v>
@@ -33292,7 +33292,7 @@
         <v>2.05</v>
       </c>
       <c r="AG202">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>1.95</v>
       </c>
       <c r="AB203">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC203">
         <v>3.14</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,64 +34050,64 @@
         </is>
       </c>
       <c r="N207">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="O207">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P207">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q207">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="R207">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="S207">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T207">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U207">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V207">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="W207">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X207">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y207">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z207">
-        <v>6.34</v>
+        <v>5.59</v>
       </c>
       <c r="AA207">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB207">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="AC207">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AD207">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AE207">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF207">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG207">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
@@ -34120,10 +34120,10 @@
         </is>
       </c>
       <c r="AJ207">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK207">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,80 +34213,80 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.86</v>
+        <v>6.1</v>
       </c>
       <c r="O208">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="P208">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="Q208">
-        <v>2.31</v>
+        <v>4.81</v>
       </c>
       <c r="R208">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="S208">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T208">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U208">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="V208">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="W208">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X208">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y208">
+        <v>1.01</v>
+      </c>
+      <c r="Z208">
+        <v>8.4</v>
+      </c>
+      <c r="AA208">
+        <v>1.25</v>
+      </c>
+      <c r="AB208">
+        <v>4</v>
+      </c>
+      <c r="AC208">
+        <v>1.65</v>
+      </c>
+      <c r="AD208">
+        <v>2.21</v>
+      </c>
+      <c r="AE208">
+        <v>1.52</v>
+      </c>
+      <c r="AF208">
+        <v>1.4</v>
+      </c>
+      <c r="AG208">
+        <v>2.7</v>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ208">
         <v>1.09</v>
       </c>
-      <c r="Z208">
-        <v>5.59</v>
-      </c>
-      <c r="AA208">
-        <v>1.39</v>
-      </c>
-      <c r="AB208">
-        <v>2.59</v>
-      </c>
-      <c r="AC208">
-        <v>2.09</v>
-      </c>
-      <c r="AD208">
-        <v>1.68</v>
-      </c>
-      <c r="AE208">
-        <v>1.25</v>
-      </c>
-      <c r="AF208">
-        <v>1.42</v>
-      </c>
-      <c r="AG208">
-        <v>2.62</v>
-      </c>
-      <c r="AH208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ208">
-        <v>1.21</v>
-      </c>
       <c r="AK208">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,64 +34376,64 @@
         </is>
       </c>
       <c r="N209">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="O209">
-        <v>4.95</v>
+        <v>3.68</v>
       </c>
       <c r="P209">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q209">
-        <v>4.81</v>
+        <v>2.37</v>
       </c>
       <c r="R209">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="S209">
         <v>1.13</v>
       </c>
       <c r="T209">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U209">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="V209">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="W209">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X209">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z209">
-        <v>8.4</v>
+        <v>6.34</v>
       </c>
       <c r="AA209">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AB209">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="AC209">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AD209">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AE209">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AF209">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG209">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK209">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,80 +35354,80 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O215">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P215">
-        <v>2.87</v>
+        <v>3.17</v>
       </c>
       <c r="Q215">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R215">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="S215">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T215">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U215">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V215">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W215">
         <v>1.11</v>
       </c>
       <c r="X215">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y215">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z215">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA215">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AB215">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC215">
-        <v>3.04</v>
+        <v>2.54</v>
       </c>
       <c r="AD215">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE215">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF215">
+        <v>1.51</v>
+      </c>
+      <c r="AG215">
+        <v>2.42</v>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ215">
+        <v>1.36</v>
+      </c>
+      <c r="AK215">
         <v>1.66</v>
-      </c>
-      <c r="AG215">
-        <v>2.12</v>
-      </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ215">
-        <v>1.35</v>
-      </c>
-      <c r="AK215">
-        <v>1.63</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O216">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P216">
-        <v>3.17</v>
+        <v>2.87</v>
       </c>
       <c r="Q216">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R216">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S216">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T216">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U216">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V216">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W216">
         <v>1.11</v>
       </c>
       <c r="X216">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z216">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA216">
+        <v>1.82</v>
+      </c>
+      <c r="AB216">
+        <v>1.93</v>
+      </c>
+      <c r="AC216">
+        <v>3.04</v>
+      </c>
+      <c r="AD216">
+        <v>1.32</v>
+      </c>
+      <c r="AE216">
+        <v>1.07</v>
+      </c>
+      <c r="AF216">
         <v>1.66</v>
       </c>
-      <c r="AB216">
-        <v>2.25</v>
-      </c>
-      <c r="AC216">
-        <v>2.54</v>
-      </c>
-      <c r="AD216">
-        <v>1.53</v>
-      </c>
-      <c r="AE216">
-        <v>1.17</v>
-      </c>
-      <c r="AF216">
-        <v>1.51</v>
-      </c>
       <c r="AG216">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK216">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -37488,7 +37488,7 @@
         <v>2</v>
       </c>
       <c r="S228">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T228">
         <v>2.75</v>
@@ -39933,7 +39933,7 @@
         <v>2.05</v>
       </c>
       <c r="S243">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T243">
         <v>2.8</v>
@@ -39957,7 +39957,7 @@
         <v>3.09</v>
       </c>
       <c r="AA243">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AB243">
         <v>1.72</v>
@@ -42743,7 +42743,7 @@
         <v>1.09</v>
       </c>
       <c r="AF260">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG260">
         <v>1.95</v>
@@ -43054,7 +43054,7 @@
         <v>4.47</v>
       </c>
       <c r="AA262">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB262">
         <v>2.15</v>
@@ -43085,7 +43085,7 @@
         </is>
       </c>
       <c r="AJ262">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK262">
         <v>2.63</v>
@@ -44865,7 +44865,7 @@
         <v>1.85</v>
       </c>
       <c r="AG273">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -45149,13 +45149,13 @@
         <v>2.54</v>
       </c>
       <c r="S275">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T275">
         <v>3.98</v>
       </c>
       <c r="U275">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V275">
         <v>1.74</v>
@@ -45176,7 +45176,7 @@
         <v>1.36</v>
       </c>
       <c r="AB275">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC275">
         <v>1.88</v>
@@ -45191,7 +45191,7 @@
         <v>1.44</v>
       </c>
       <c r="AG275">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>2.31</v>
       </c>
       <c r="R281">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S281">
         <v>1.36</v>
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,64 +47579,64 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O290">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="P290">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q290">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R290">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S290">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="T290">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U290">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="V290">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="W290">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X290">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y290">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z290">
-        <v>3.28</v>
+        <v>2.56</v>
       </c>
       <c r="AA290">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AB290">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC290">
-        <v>3.17</v>
+        <v>4.41</v>
       </c>
       <c r="AD290">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE290">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF290">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG290">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH290" t="inlineStr">
         <is>
@@ -47649,10 +47649,10 @@
         </is>
       </c>
       <c r="AJ290">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK290">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL290">
         <v>0</v>
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,64 +47742,64 @@
         </is>
       </c>
       <c r="N291">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O291">
+        <v>3.65</v>
+      </c>
+      <c r="P291">
+        <v>4.6</v>
+      </c>
+      <c r="Q291">
+        <v>2.15</v>
+      </c>
+      <c r="R291">
+        <v>2.2</v>
+      </c>
+      <c r="S291">
+        <v>1.35</v>
+      </c>
+      <c r="T291">
         <v>3</v>
       </c>
-      <c r="P291">
-        <v>3.25</v>
-      </c>
-      <c r="Q291">
-        <v>2.6</v>
-      </c>
-      <c r="R291">
-        <v>1.91</v>
-      </c>
-      <c r="S291">
-        <v>1.5</v>
-      </c>
-      <c r="T291">
-        <v>2.38</v>
-      </c>
       <c r="U291">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="V291">
+        <v>1.37</v>
+      </c>
+      <c r="W291">
+        <v>1.04</v>
+      </c>
+      <c r="X291">
+        <v>1.01</v>
+      </c>
+      <c r="Y291">
         <v>1.28</v>
       </c>
-      <c r="W291">
-        <v>1.05</v>
-      </c>
-      <c r="X291">
-        <v>1.05</v>
-      </c>
-      <c r="Y291">
-        <v>1.4</v>
-      </c>
       <c r="Z291">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AA291">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AB291">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC291">
-        <v>4.41</v>
+        <v>3.17</v>
       </c>
       <c r="AD291">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AE291">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF291">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG291">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -47812,10 +47812,10 @@
         </is>
       </c>
       <c r="AJ291">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK291">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AL291">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="P6">
-        <v>7.02</v>
+        <v>4.15</v>
       </c>
       <c r="Q6">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="R6">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T6">
         <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.3</v>
+        <v>3.96</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AD6">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="O7">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>4.15</v>
+        <v>7.02</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
         <v>3.24</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AD7">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>1.97</v>
+        <v>2.88</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>4.59</v>
+        <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
         <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>4.59</v>
       </c>
       <c r="Q20">
-        <v>2.81</v>
+        <v>2.35</v>
       </c>
       <c r="R20">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
         <v>3.1</v>
       </c>
       <c r="U20">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4100,7 +4100,7 @@
         <v>1.64</v>
       </c>
       <c r="AB23">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC23">
         <v>2.42</v>
@@ -4275,7 +4275,7 @@
         <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
         <v>2.21</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,22 +4873,22 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q28">
-        <v>4.22</v>
+        <v>2.8</v>
       </c>
       <c r="R28">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
         <v>2.7</v>
@@ -4897,37 +4897,37 @@
         <v>3</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
         <v>1.33</v>
       </c>
       <c r="Z28">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA28">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB28">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF28">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG28">
         <v>1.85</v>
@@ -4946,7 +4946,7 @@
         <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6346,7 +6346,7 @@
         <v>3.24</v>
       </c>
       <c r="P37">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P41">
-        <v>3.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q41">
-        <v>2.5</v>
+        <v>3.07</v>
       </c>
       <c r="R41">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="S41">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U41">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="V41">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="Z41">
-        <v>2.47</v>
+        <v>2.92</v>
       </c>
       <c r="AA41">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AB41">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>4.65</v>
+        <v>3.76</v>
       </c>
       <c r="AD41">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AG41">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,80 +7318,80 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O43">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>3.3</v>
+        <v>3.53</v>
       </c>
       <c r="Q43">
-        <v>3.07</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T43">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="V43">
+        <v>1.25</v>
+      </c>
+      <c r="W43">
+        <v>1.01</v>
+      </c>
+      <c r="X43">
+        <v>1.07</v>
+      </c>
+      <c r="Y43">
+        <v>1.5</v>
+      </c>
+      <c r="Z43">
+        <v>2.47</v>
+      </c>
+      <c r="AA43">
+        <v>2.5</v>
+      </c>
+      <c r="AB43">
+        <v>1.47</v>
+      </c>
+      <c r="AC43">
+        <v>4.65</v>
+      </c>
+      <c r="AD43">
+        <v>1.12</v>
+      </c>
+      <c r="AE43">
+        <v>1.03</v>
+      </c>
+      <c r="AF43">
+        <v>2.19</v>
+      </c>
+      <c r="AG43">
+        <v>1.59</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
         <v>1.3</v>
       </c>
-      <c r="W43">
-        <v>1.04</v>
-      </c>
-      <c r="X43">
-        <v>1.03</v>
-      </c>
-      <c r="Y43">
-        <v>1.31</v>
-      </c>
-      <c r="Z43">
-        <v>2.92</v>
-      </c>
-      <c r="AA43">
-        <v>2.1</v>
-      </c>
-      <c r="AB43">
-        <v>1.7</v>
-      </c>
-      <c r="AC43">
-        <v>3.76</v>
-      </c>
-      <c r="AD43">
-        <v>1.19</v>
-      </c>
-      <c r="AE43">
-        <v>1.04</v>
-      </c>
-      <c r="AF43">
-        <v>1.81</v>
-      </c>
-      <c r="AG43">
-        <v>1.88</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.26</v>
-      </c>
       <c r="AK43">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O47">
         <v>4</v>
@@ -7991,7 +7991,7 @@
         <v>3.26</v>
       </c>
       <c r="U47">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
         <v>1.5</v>
@@ -8628,7 +8628,7 @@
         <v>3.1</v>
       </c>
       <c r="P51">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q51">
         <v>2.88</v>
@@ -8649,7 +8649,7 @@
         <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="O54">
         <v>6.25</v>
@@ -12389,7 +12389,7 @@
         <v>1.14</v>
       </c>
       <c r="T74">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="U74">
         <v>1.75</v>
@@ -12712,7 +12712,7 @@
         <v>2.5</v>
       </c>
       <c r="S76">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
         <v>4.25</v>
@@ -15471,7 +15471,7 @@
         <v>1.95</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P93">
         <v>3.2</v>
@@ -15492,7 +15492,7 @@
         <v>2.39</v>
       </c>
       <c r="V93">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W93">
         <v>1.08</v>
@@ -18574,7 +18574,7 @@
         <v>6.5</v>
       </c>
       <c r="Q112">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R112">
         <v>2.51</v>
@@ -18610,7 +18610,7 @@
         <v>2.55</v>
       </c>
       <c r="AC112">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="AD112">
         <v>1.61</v>
@@ -19259,7 +19259,7 @@
         <v>1.7</v>
       </c>
       <c r="AB116">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC116">
         <v>2.84</v>
@@ -19271,7 +19271,7 @@
         <v>1.11</v>
       </c>
       <c r="AF116">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG116">
         <v>2.21</v>
@@ -19434,10 +19434,10 @@
         <v>1.06</v>
       </c>
       <c r="AF117">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG117">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>2.25</v>
       </c>
       <c r="V118">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W118">
         <v>1.16</v>
@@ -19582,10 +19582,10 @@
         <v>4.65</v>
       </c>
       <c r="AA118">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AB118">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AC118">
         <v>2.46</v>
@@ -19594,10 +19594,10 @@
         <v>1.53</v>
       </c>
       <c r="AE118">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF118">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG118">
         <v>2.2</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
+        <v>2.03</v>
+      </c>
+      <c r="O119">
+        <v>3.45</v>
+      </c>
+      <c r="P119">
+        <v>3.56</v>
+      </c>
+      <c r="Q119">
+        <v>2.38</v>
+      </c>
+      <c r="R119">
         <v>2.3</v>
       </c>
-      <c r="O119">
-        <v>3.56</v>
-      </c>
-      <c r="P119">
-        <v>2.73</v>
-      </c>
-      <c r="Q119">
-        <v>2.69</v>
-      </c>
-      <c r="R119">
-        <v>2.24</v>
-      </c>
       <c r="S119">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T119">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="U119">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="V119">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W119">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X119">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y119">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z119">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="AA119">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AB119">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC119">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="AD119">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AE119">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF119">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG119">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK119">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O120">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="P120">
-        <v>3.56</v>
+        <v>2.73</v>
       </c>
       <c r="Q120">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="R120">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S120">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T120">
-        <v>2.83</v>
+        <v>3.22</v>
       </c>
       <c r="U120">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="V120">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W120">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z120">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="AA120">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB120">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC120">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="AD120">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AE120">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF120">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG120">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK120">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>1.71</v>
       </c>
       <c r="AG121">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20479,22 +20479,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G124">
@@ -20517,68 +20517,68 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O125">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P125">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q125">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R125">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S125">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T125">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U125">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V125">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W125">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y125">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z125">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA125">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB125">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD125">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE125">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF125">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK125">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q126">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R126">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S126">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T126">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U126">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V126">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W126">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X126">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y126">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z126">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC126">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD126">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE126">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF126">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG126">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AK126">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20968,22 +20968,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,61 +21010,61 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.7</v>
+        <v>3.87</v>
       </c>
       <c r="O127">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P127">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="Q127">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="R127">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="S127">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T127">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="U127">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="V127">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W127">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X127">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z127">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
       <c r="AA127">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB127">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AC127">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AD127">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE127">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AF127">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG127">
         <v>2.25</v>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>2.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK127">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21131,22 +21131,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,80 +21173,80 @@
         </is>
       </c>
       <c r="N128">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O128">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="P128">
-        <v>1.52</v>
+        <v>2.55</v>
       </c>
       <c r="Q128">
-        <v>4.35</v>
+        <v>3.3</v>
       </c>
       <c r="R128">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S128">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="T128">
-        <v>3.46</v>
+        <v>2.54</v>
       </c>
       <c r="U128">
-        <v>2.27</v>
+        <v>2.81</v>
       </c>
       <c r="V128">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W128">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X128">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y128">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z128">
-        <v>4.51</v>
+        <v>2.97</v>
       </c>
       <c r="AA128">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="AB128">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="AC128">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="AD128">
+        <v>1.25</v>
+      </c>
+      <c r="AE128">
+        <v>1.04</v>
+      </c>
+      <c r="AF128">
+        <v>1.77</v>
+      </c>
+      <c r="AG128">
+        <v>1.94</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>1.43</v>
+      </c>
+      <c r="AK128">
         <v>1.44</v>
-      </c>
-      <c r="AE128">
-        <v>1.19</v>
-      </c>
-      <c r="AF128">
-        <v>1.57</v>
-      </c>
-      <c r="AG128">
-        <v>2.25</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>1.22</v>
-      </c>
-      <c r="AK128">
-        <v>1.13</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21294,22 +21294,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G129">
@@ -21336,64 +21336,64 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.6</v>
+        <v>8.5</v>
       </c>
       <c r="O129">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="P129">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="Q129">
-        <v>3.3</v>
+        <v>8.25</v>
       </c>
       <c r="R129">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="S129">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="T129">
-        <v>2.54</v>
+        <v>4.45</v>
       </c>
       <c r="U129">
-        <v>2.81</v>
+        <v>1.86</v>
       </c>
       <c r="V129">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="W129">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="X129">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y129">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="Z129">
-        <v>2.97</v>
+        <v>6.5</v>
       </c>
       <c r="AA129">
-        <v>2.08</v>
+        <v>1.29</v>
       </c>
       <c r="AB129">
-        <v>1.72</v>
+        <v>3.04</v>
       </c>
       <c r="AC129">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="AD129">
-        <v>1.25</v>
+        <v>1.86</v>
       </c>
       <c r="AE129">
-        <v>1.04</v>
+        <v>1.35</v>
       </c>
       <c r="AF129">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG129">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="AK129">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O130">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P130">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q130">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="R130">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S130">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T130">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="U130">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V130">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="W130">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X130">
         <v>0</v>
       </c>
       <c r="Y130">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z130">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA130">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB130">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AC130">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD130">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE130">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF130">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG130">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK130">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="O132">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="P132">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="Q132">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="R132">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="S132">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T132">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="U132">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="V132">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W132">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X132">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y132">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Z132">
-        <v>4.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA132">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="AB132">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AC132">
-        <v>2.49</v>
+        <v>1.86</v>
       </c>
       <c r="AD132">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="AE132">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AF132">
-        <v>1.61</v>
+        <v>2.13</v>
       </c>
       <c r="AG132">
-        <v>2.13</v>
+        <v>1.59</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AK132">
-        <v>2</v>
+        <v>5.15</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.12</v>
+        <v>1.7</v>
       </c>
       <c r="O133">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>13</v>
+        <v>4.33</v>
       </c>
       <c r="Q133">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="R133">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="S133">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T133">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="U133">
-        <v>2.01</v>
+        <v>2.79</v>
       </c>
       <c r="V133">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="W133">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X133">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="Z133">
-        <v>6.05</v>
+        <v>3.14</v>
       </c>
       <c r="AA133">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="AB133">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AC133">
-        <v>1.86</v>
+        <v>3.14</v>
       </c>
       <c r="AD133">
-        <v>1.81</v>
+        <v>1.27</v>
       </c>
       <c r="AE133">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AF133">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>5.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,28 +22151,28 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O134">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P134">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="Q134">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R134">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S134">
         <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U134">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V134">
         <v>1.4</v>
@@ -22184,31 +22184,31 @@
         <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z134">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="AA134">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB134">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC134">
-        <v>3.14</v>
+        <v>2.69</v>
       </c>
       <c r="AD134">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE134">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF134">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG134">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK134">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="O135">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="P135">
-        <v>3.85</v>
+        <v>7.55</v>
       </c>
       <c r="Q135">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R135">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S135">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T135">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U135">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V135">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W135">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y135">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z135">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AA135">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB135">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC135">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD135">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE135">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF135">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG135">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK135">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q137">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R137">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S137">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T137">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U137">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V137">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W137">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y137">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z137">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA137">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB137">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AC137">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD137">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE137">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF137">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG137">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK137">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>3.87</v>
+        <v>2.07</v>
       </c>
       <c r="O138">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="P138">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q138">
-        <v>3.8</v>
+        <v>2.79</v>
       </c>
       <c r="R138">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S138">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T138">
-        <v>3.12</v>
+        <v>2.72</v>
       </c>
       <c r="U138">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V138">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W138">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y138">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z138">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA138">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AB138">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AC138">
-        <v>2.53</v>
+        <v>3.14</v>
       </c>
       <c r="AD138">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AE138">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF138">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AG138">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK138">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,61 +22966,61 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="O139">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P139">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="Q139">
-        <v>2.79</v>
+        <v>2.13</v>
       </c>
       <c r="R139">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T139">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U139">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V139">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W139">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X139">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y139">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z139">
-        <v>3.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA139">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AB139">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC139">
-        <v>3.14</v>
+        <v>2.76</v>
       </c>
       <c r="AD139">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AE139">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF139">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG139">
         <v>2.05</v>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK139">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G140">
@@ -23129,64 +23129,64 @@
         </is>
       </c>
       <c r="N140">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="O140">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="P140">
-        <v>4.7</v>
+        <v>7.75</v>
       </c>
       <c r="Q140">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="R140">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S140">
         <v>1.3</v>
       </c>
       <c r="T140">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="U140">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="V140">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="W140">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X140">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y140">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z140">
-        <v>3.84</v>
+        <v>4.4</v>
       </c>
       <c r="AA140">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB140">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC140">
-        <v>2.76</v>
+        <v>2.33</v>
       </c>
       <c r="AD140">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE140">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF140">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AG140">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
@@ -23199,10 +23199,10 @@
         </is>
       </c>
       <c r="AJ140">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK140">
-        <v>2.16</v>
+        <v>2.85</v>
       </c>
       <c r="AL140">
         <v>0</v>
@@ -23250,22 +23250,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G141">
@@ -23292,80 +23292,80 @@
         </is>
       </c>
       <c r="N141">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="O141">
-        <v>4.33</v>
+        <v>3.66</v>
       </c>
       <c r="P141">
-        <v>7.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q141">
-        <v>1.82</v>
+        <v>3.8</v>
       </c>
       <c r="R141">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="S141">
+        <v>1.29</v>
+      </c>
+      <c r="T141">
+        <v>3.4</v>
+      </c>
+      <c r="U141">
+        <v>2.4</v>
+      </c>
+      <c r="V141">
+        <v>1.55</v>
+      </c>
+      <c r="W141">
+        <v>1.09</v>
+      </c>
+      <c r="X141">
+        <v>1.01</v>
+      </c>
+      <c r="Y141">
+        <v>1.17</v>
+      </c>
+      <c r="Z141">
+        <v>4.6</v>
+      </c>
+      <c r="AA141">
+        <v>1.73</v>
+      </c>
+      <c r="AB141">
+        <v>2.28</v>
+      </c>
+      <c r="AC141">
+        <v>2.53</v>
+      </c>
+      <c r="AD141">
+        <v>1.46</v>
+      </c>
+      <c r="AE141">
+        <v>1.13</v>
+      </c>
+      <c r="AF141">
+        <v>1.57</v>
+      </c>
+      <c r="AG141">
+        <v>2.3</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
+        <v>1.22</v>
+      </c>
+      <c r="AK141">
         <v>1.3</v>
-      </c>
-      <c r="T141">
-        <v>3.08</v>
-      </c>
-      <c r="U141">
-        <v>2.31</v>
-      </c>
-      <c r="V141">
-        <v>1.51</v>
-      </c>
-      <c r="W141">
-        <v>1.1</v>
-      </c>
-      <c r="X141">
-        <v>1.02</v>
-      </c>
-      <c r="Y141">
-        <v>1.14</v>
-      </c>
-      <c r="Z141">
-        <v>4.4</v>
-      </c>
-      <c r="AA141">
-        <v>1.57</v>
-      </c>
-      <c r="AB141">
-        <v>2.25</v>
-      </c>
-      <c r="AC141">
-        <v>2.33</v>
-      </c>
-      <c r="AD141">
-        <v>1.48</v>
-      </c>
-      <c r="AE141">
-        <v>1.17</v>
-      </c>
-      <c r="AF141">
-        <v>1.83</v>
-      </c>
-      <c r="AG141">
-        <v>1.83</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>1.13</v>
-      </c>
-      <c r="AK141">
-        <v>2.85</v>
       </c>
       <c r="AL141">
         <v>0</v>
@@ -23408,12 +23408,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G142">
@@ -23455,80 +23455,80 @@
         </is>
       </c>
       <c r="N142">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O142">
-        <v>3.66</v>
+        <v>4.05</v>
       </c>
       <c r="P142">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="Q142">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="R142">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="S142">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T142">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U142">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="V142">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W142">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X142">
         <v>1.01</v>
       </c>
       <c r="Y142">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z142">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA142">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB142">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AC142">
-        <v>2.53</v>
+        <v>2.33</v>
       </c>
       <c r="AD142">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE142">
+        <v>1.18</v>
+      </c>
+      <c r="AF142">
+        <v>1.65</v>
+      </c>
+      <c r="AG142">
+        <v>2.1</v>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ142">
         <v>1.13</v>
       </c>
-      <c r="AF142">
-        <v>1.57</v>
-      </c>
-      <c r="AG142">
-        <v>2.3</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>1.22</v>
-      </c>
       <c r="AK142">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23559,7 +23559,7 @@
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>2026-10-18 10:00:00</t>
+          <t>2026-10-18 10:05:00</t>
         </is>
       </c>
     </row>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Khor fakkan</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G143">
@@ -23614,68 +23614,68 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N143">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q143">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R143">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S143">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T143">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U143">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="V143">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W143">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X143">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y143">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z143">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA143">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB143">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AC143">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD143">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE143">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF143">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG143">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK143">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23734,12 +23734,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Khor fakkan</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G144">
@@ -23777,68 +23777,68 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N144">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O144">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P144">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q144">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R144">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S144">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T144">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U144">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V144">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W144">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z144">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AA144">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB144">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC144">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD144">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE144">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF144">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG144">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK144">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23885,7 +23885,7 @@
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>2026-10-18 10:05:00</t>
+          <t>2026-10-18 10:15:00</t>
         </is>
       </c>
     </row>
@@ -23897,12 +23897,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P145">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q145">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="R145">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S145">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T145">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U145">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V145">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W145">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X145">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y145">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z145">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="AA145">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB145">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AC145">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD145">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE145">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF145">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG145">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK145">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24048,7 +24048,7 @@
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>2026-10-18 10:15:00</t>
+          <t>2026-10-18 10:30:00</t>
         </is>
       </c>
     </row>
@@ -24065,7 +24065,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,64 +24107,64 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q146">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R146">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S146">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T146">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U146">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V146">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W146">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X146">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y146">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z146">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA146">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB146">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC146">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD146">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE146">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF146">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG146">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK146">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G147">
@@ -24270,64 +24270,64 @@
         </is>
       </c>
       <c r="N147">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O147">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P147">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q147">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="R147">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S147">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T147">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U147">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V147">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W147">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X147">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y147">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z147">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA147">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB147">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AC147">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD147">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE147">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF147">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG147">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24340,10 +24340,10 @@
         </is>
       </c>
       <c r="AJ147">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK147">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G148">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G149">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G151">
@@ -24931,55 +24931,55 @@
         <v>0</v>
       </c>
       <c r="Q151">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R151">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S151">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T151">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U151">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V151">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W151">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X151">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y151">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z151">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA151">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB151">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC151">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD151">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE151">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF151">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG151">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -24992,10 +24992,10 @@
         </is>
       </c>
       <c r="AJ151">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK151">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AL151">
         <v>0</v>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,64 +25085,64 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q152">
-        <v>1.71</v>
+        <v>5.99</v>
       </c>
       <c r="R152">
-        <v>2.78</v>
+        <v>1.89</v>
       </c>
       <c r="S152">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="T152">
-        <v>4.6</v>
+        <v>2.33</v>
       </c>
       <c r="U152">
-        <v>1.9</v>
+        <v>3.73</v>
       </c>
       <c r="V152">
-        <v>1.77</v>
+        <v>1.21</v>
       </c>
       <c r="W152">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X152">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y152">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="Z152">
-        <v>7</v>
+        <v>2.39</v>
       </c>
       <c r="AA152">
-        <v>1.3</v>
+        <v>2.66</v>
       </c>
       <c r="AB152">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC152">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD152">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE152">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF152">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG152">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
@@ -25155,10 +25155,10 @@
         </is>
       </c>
       <c r="AJ152">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK152">
-        <v>2.98</v>
+        <v>1.09</v>
       </c>
       <c r="AL152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,31 +25248,31 @@
         </is>
       </c>
       <c r="N153">
-        <v>4.99</v>
+        <v>2.4</v>
       </c>
       <c r="O153">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="P153">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="Q153">
-        <v>5.99</v>
+        <v>3.44</v>
       </c>
       <c r="R153">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="S153">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
       <c r="T153">
-        <v>2.33</v>
+        <v>1.99</v>
       </c>
       <c r="U153">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="V153">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W153">
         <v>0</v>
@@ -25281,16 +25281,16 @@
         <v>0</v>
       </c>
       <c r="Y153">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="Z153">
-        <v>2.39</v>
+        <v>1.91</v>
       </c>
       <c r="AA153">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="AB153">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AC153">
         <v>0</v>
@@ -25302,10 +25302,10 @@
         <v>0</v>
       </c>
       <c r="AF153">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="AG153">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AK153">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,64 +25411,64 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.4</v>
+        <v>1.81</v>
       </c>
       <c r="O154">
-        <v>2.66</v>
+        <v>3.55</v>
       </c>
       <c r="P154">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q154">
-        <v>3.44</v>
+        <v>2.3</v>
       </c>
       <c r="R154">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="S154">
-        <v>1.66</v>
+        <v>1.27</v>
       </c>
       <c r="T154">
-        <v>1.99</v>
+        <v>3.18</v>
       </c>
       <c r="U154">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V154">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W154">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X154">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y154">
-        <v>1.76</v>
+        <v>1.15</v>
       </c>
       <c r="Z154">
-        <v>1.91</v>
+        <v>4.25</v>
       </c>
       <c r="AA154">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB154">
-        <v>1.23</v>
+        <v>2.17</v>
       </c>
       <c r="AC154">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD154">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE154">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF154">
-        <v>2.72</v>
+        <v>1.53</v>
       </c>
       <c r="AG154">
-        <v>1.38</v>
+        <v>2.29</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AK154">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G155">
@@ -25574,80 +25574,80 @@
         </is>
       </c>
       <c r="N155">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="O155">
-        <v>3.55</v>
+        <v>4.26</v>
       </c>
       <c r="P155">
-        <v>3.5</v>
+        <v>4.44</v>
       </c>
       <c r="Q155">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R155">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S155">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="T155">
-        <v>3.18</v>
+        <v>3.84</v>
       </c>
       <c r="U155">
+        <v>2.09</v>
+      </c>
+      <c r="V155">
+        <v>1.78</v>
+      </c>
+      <c r="W155">
+        <v>1.17</v>
+      </c>
+      <c r="X155">
+        <v>1.01</v>
+      </c>
+      <c r="Y155">
+        <v>1.09</v>
+      </c>
+      <c r="Z155">
+        <v>5.25</v>
+      </c>
+      <c r="AA155">
+        <v>1.43</v>
+      </c>
+      <c r="AB155">
+        <v>2.62</v>
+      </c>
+      <c r="AC155">
         <v>2.25</v>
       </c>
-      <c r="V155">
-        <v>1.57</v>
-      </c>
-      <c r="W155">
-        <v>1.1</v>
-      </c>
-      <c r="X155">
-        <v>1.03</v>
-      </c>
-      <c r="Y155">
-        <v>1.15</v>
-      </c>
-      <c r="Z155">
-        <v>4.25</v>
-      </c>
-      <c r="AA155">
-        <v>1.55</v>
-      </c>
-      <c r="AB155">
-        <v>2.17</v>
-      </c>
-      <c r="AC155">
-        <v>2.41</v>
-      </c>
       <c r="AD155">
+        <v>1.74</v>
+      </c>
+      <c r="AE155">
+        <v>1.25</v>
+      </c>
+      <c r="AF155">
         <v>1.48</v>
       </c>
-      <c r="AE155">
+      <c r="AG155">
+        <v>2.55</v>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ155">
         <v>1.16</v>
       </c>
-      <c r="AF155">
-        <v>1.53</v>
-      </c>
-      <c r="AG155">
-        <v>2.29</v>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ155">
-        <v>1.19</v>
-      </c>
       <c r="AK155">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,64 +25737,64 @@
         </is>
       </c>
       <c r="N156">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="O156">
-        <v>4.26</v>
+        <v>3.1</v>
       </c>
       <c r="P156">
-        <v>4.44</v>
+        <v>3</v>
       </c>
       <c r="Q156">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="R156">
+        <v>2</v>
+      </c>
+      <c r="S156">
+        <v>1.5</v>
+      </c>
+      <c r="T156">
         <v>2.5</v>
       </c>
-      <c r="S156">
-        <v>1.22</v>
-      </c>
-      <c r="T156">
-        <v>3.84</v>
-      </c>
       <c r="U156">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="V156">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="W156">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X156">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y156">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="Z156">
-        <v>5.25</v>
+        <v>2.59</v>
       </c>
       <c r="AA156">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="AB156">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC156">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="AD156">
-        <v>1.74</v>
+        <v>1.16</v>
       </c>
       <c r="AE156">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="AF156">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AG156">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,10 +25807,10 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK156">
-        <v>2.21</v>
+        <v>1.51</v>
       </c>
       <c r="AL156">
         <v>0</v>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-10-18 10:30:00</t>
+          <t>2026-10-18 11:00:00</t>
         </is>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Portel</t>
         </is>
       </c>
       <c r="G157">
@@ -25900,64 +25900,64 @@
         </is>
       </c>
       <c r="N157">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O157">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q157">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R157">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S157">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T157">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U157">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V157">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W157">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X157">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y157">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z157">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA157">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB157">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC157">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD157">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE157">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF157">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG157">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
@@ -25970,10 +25970,10 @@
         </is>
       </c>
       <c r="AJ157">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK157">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL157">
         <v>0</v>
@@ -26021,7 +26021,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Portel</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,64 +26063,64 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q158">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R158">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S158">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T158">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U158">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V158">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W158">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X158">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y158">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z158">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA158">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB158">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC158">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD158">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE158">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF158">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG158">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH158" t="inlineStr">
         <is>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK158">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,80 +26226,80 @@
         </is>
       </c>
       <c r="N159">
-        <v>1.06</v>
+        <v>2.23</v>
       </c>
       <c r="O159">
-        <v>10</v>
+        <v>2.97</v>
       </c>
       <c r="P159">
-        <v>41</v>
+        <v>3.05</v>
       </c>
       <c r="Q159">
+        <v>3.14</v>
+      </c>
+      <c r="R159">
+        <v>1.97</v>
+      </c>
+      <c r="S159">
+        <v>1.53</v>
+      </c>
+      <c r="T159">
+        <v>2.42</v>
+      </c>
+      <c r="U159">
+        <v>3.55</v>
+      </c>
+      <c r="V159">
+        <v>1.22</v>
+      </c>
+      <c r="W159">
+        <v>1.01</v>
+      </c>
+      <c r="X159">
+        <v>1.05</v>
+      </c>
+      <c r="Y159">
+        <v>1.48</v>
+      </c>
+      <c r="Z159">
+        <v>2.58</v>
+      </c>
+      <c r="AA159">
+        <v>2.54</v>
+      </c>
+      <c r="AB159">
+        <v>1.49</v>
+      </c>
+      <c r="AC159">
+        <v>4.85</v>
+      </c>
+      <c r="AD159">
+        <v>1.16</v>
+      </c>
+      <c r="AE159">
+        <v>1</v>
+      </c>
+      <c r="AF159">
+        <v>2.08</v>
+      </c>
+      <c r="AG159">
+        <v>1.67</v>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ159">
         <v>1.29</v>
       </c>
-      <c r="R159">
-        <v>3.42</v>
-      </c>
-      <c r="S159">
-        <v>1.14</v>
-      </c>
-      <c r="T159">
-        <v>4.5</v>
-      </c>
-      <c r="U159">
-        <v>1.85</v>
-      </c>
-      <c r="V159">
-        <v>1.83</v>
-      </c>
-      <c r="W159">
-        <v>1.2</v>
-      </c>
-      <c r="X159">
-        <v>1.01</v>
-      </c>
-      <c r="Y159">
-        <v>1.03</v>
-      </c>
-      <c r="Z159">
-        <v>7.2</v>
-      </c>
-      <c r="AA159">
-        <v>1.26</v>
-      </c>
-      <c r="AB159">
-        <v>3.2</v>
-      </c>
-      <c r="AC159">
-        <v>1.85</v>
-      </c>
-      <c r="AD159">
-        <v>1.9</v>
-      </c>
-      <c r="AE159">
-        <v>1.4</v>
-      </c>
-      <c r="AF159">
-        <v>2.6</v>
-      </c>
-      <c r="AG159">
-        <v>1.41</v>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ159">
-        <v>1.05</v>
-      </c>
       <c r="AK159">
-        <v>8</v>
+        <v>1.57</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26347,22 +26347,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,64 +26389,64 @@
         </is>
       </c>
       <c r="N160">
-        <v>2.23</v>
+        <v>1.36</v>
       </c>
       <c r="O160">
-        <v>2.97</v>
+        <v>4.5</v>
       </c>
       <c r="P160">
-        <v>3.05</v>
+        <v>6.1</v>
       </c>
       <c r="Q160">
-        <v>3.14</v>
+        <v>1.75</v>
       </c>
       <c r="R160">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="S160">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="T160">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="U160">
-        <v>3.55</v>
+        <v>2.15</v>
       </c>
       <c r="V160">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="W160">
+        <v>1.14</v>
+      </c>
+      <c r="X160">
         <v>1.01</v>
       </c>
-      <c r="X160">
-        <v>1.05</v>
-      </c>
       <c r="Y160">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="Z160">
-        <v>2.58</v>
+        <v>4.75</v>
       </c>
       <c r="AA160">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB160">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="AC160">
-        <v>4.85</v>
+        <v>2.33</v>
       </c>
       <c r="AD160">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AE160">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="AF160">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="AG160">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK160">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G161">
@@ -26548,68 +26548,68 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N161">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O161">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P161">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q161">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R161">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S161">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T161">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U161">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V161">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W161">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X161">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y161">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z161">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA161">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB161">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC161">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD161">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE161">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF161">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG161">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK161">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="O162">
         <v>4.6</v>
       </c>
       <c r="P162">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Q162">
         <v>7.5</v>
@@ -28252,7 +28252,7 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK171">
         <v>0</v>
@@ -28840,7 +28840,7 @@
         <v>3.2</v>
       </c>
       <c r="P175">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="Q175">
         <v>2.39</v>
@@ -28852,7 +28852,7 @@
         <v>1.36</v>
       </c>
       <c r="T175">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U175">
         <v>2.88</v>
@@ -29504,7 +29504,7 @@
         <v>1.22</v>
       </c>
       <c r="T179">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="U179">
         <v>2.05</v>
@@ -29513,7 +29513,7 @@
         <v>1.65</v>
       </c>
       <c r="W179">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X179">
         <v>1.02</v>
@@ -29655,7 +29655,7 @@
         <v>6</v>
       </c>
       <c r="P180">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Q180">
         <v>1.63</v>
@@ -29854,7 +29854,7 @@
         <v>1.4</v>
       </c>
       <c r="AB181">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AC181">
         <v>1.98</v>
@@ -30144,7 +30144,7 @@
         <v>3.9</v>
       </c>
       <c r="P183">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q183">
         <v>4.38</v>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AK183">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -31288,55 +31288,55 @@
         <v>0</v>
       </c>
       <c r="Q190">
-        <v>5.06</v>
+        <v>0</v>
       </c>
       <c r="R190">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S190">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T190">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="U190">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V190">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W190">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X190">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y190">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z190">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AA190">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB190">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC190">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD190">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE190">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF190">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG190">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK190">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G195">
@@ -32103,71 +32103,71 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="R195">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="S195">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T195">
-        <v>2.86</v>
+        <v>2.43</v>
       </c>
       <c r="U195">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="V195">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="W195">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y195">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Z195">
-        <v>3.28</v>
+        <v>2.68</v>
       </c>
       <c r="AA195">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="AB195">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AC195">
-        <v>3.05</v>
+        <v>4.55</v>
       </c>
       <c r="AD195">
+        <v>1.13</v>
+      </c>
+      <c r="AE195">
+        <v>1.01</v>
+      </c>
+      <c r="AF195">
+        <v>2.04</v>
+      </c>
+      <c r="AG195">
+        <v>1.7</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ195">
         <v>1.28</v>
       </c>
-      <c r="AE195">
-        <v>1.09</v>
-      </c>
-      <c r="AF195">
-        <v>1.75</v>
-      </c>
-      <c r="AG195">
-        <v>2</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ195">
-        <v>1.22</v>
-      </c>
       <c r="AK195">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G196">
@@ -32266,56 +32266,56 @@
         <v>0</v>
       </c>
       <c r="Q196">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R196">
+        <v>2.03</v>
+      </c>
+      <c r="S196">
+        <v>1.35</v>
+      </c>
+      <c r="T196">
+        <v>2.86</v>
+      </c>
+      <c r="U196">
+        <v>2.7</v>
+      </c>
+      <c r="V196">
+        <v>1.4</v>
+      </c>
+      <c r="W196">
+        <v>1.08</v>
+      </c>
+      <c r="X196">
+        <v>1.02</v>
+      </c>
+      <c r="Y196">
+        <v>1.25</v>
+      </c>
+      <c r="Z196">
+        <v>3.28</v>
+      </c>
+      <c r="AA196">
+        <v>1.85</v>
+      </c>
+      <c r="AB196">
+        <v>1.85</v>
+      </c>
+      <c r="AC196">
+        <v>3.05</v>
+      </c>
+      <c r="AD196">
+        <v>1.28</v>
+      </c>
+      <c r="AE196">
+        <v>1.09</v>
+      </c>
+      <c r="AF196">
+        <v>1.75</v>
+      </c>
+      <c r="AG196">
         <v>2</v>
       </c>
-      <c r="S196">
-        <v>1.44</v>
-      </c>
-      <c r="T196">
-        <v>2.43</v>
-      </c>
-      <c r="U196">
-        <v>3.3</v>
-      </c>
-      <c r="V196">
-        <v>1.27</v>
-      </c>
-      <c r="W196">
-        <v>1.05</v>
-      </c>
-      <c r="X196">
-        <v>1.06</v>
-      </c>
-      <c r="Y196">
-        <v>1.43</v>
-      </c>
-      <c r="Z196">
-        <v>2.68</v>
-      </c>
-      <c r="AA196">
-        <v>2.36</v>
-      </c>
-      <c r="AB196">
-        <v>1.51</v>
-      </c>
-      <c r="AC196">
-        <v>4.55</v>
-      </c>
-      <c r="AD196">
-        <v>1.13</v>
-      </c>
-      <c r="AE196">
-        <v>1.01</v>
-      </c>
-      <c r="AF196">
-        <v>2.04</v>
-      </c>
-      <c r="AG196">
-        <v>1.7</v>
-      </c>
       <c r="AH196" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK196">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32438,7 +32438,7 @@
         <v>1.4</v>
       </c>
       <c r="T197">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U197">
         <v>3.08</v>
@@ -32598,10 +32598,10 @@
         <v>2.04</v>
       </c>
       <c r="S198">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T198">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U198">
         <v>2.77</v>
@@ -35070,7 +35070,7 @@
         <v>1.83</v>
       </c>
       <c r="AB213">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC213">
         <v>3.09</v>
@@ -35215,7 +35215,7 @@
         <v>2.75</v>
       </c>
       <c r="V214">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W214">
         <v>1.08</v>
@@ -35236,7 +35236,7 @@
         <v>1.97</v>
       </c>
       <c r="AC214">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="AD214">
         <v>1.3</v>
@@ -35538,10 +35538,10 @@
         <v>3.2</v>
       </c>
       <c r="U216">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V216">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W216">
         <v>1.11</v>
@@ -35852,55 +35852,55 @@
         <v>2.2</v>
       </c>
       <c r="Q218">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R218">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="S218">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T218">
         <v>2.88</v>
       </c>
       <c r="U218">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V218">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W218">
         <v>1.06</v>
       </c>
       <c r="X218">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y218">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z218">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA218">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB218">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AC218">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD218">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE218">
         <v>1.05</v>
       </c>
       <c r="AF218">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG218">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>1.25</v>
       </c>
       <c r="AK218">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36015,22 +36015,22 @@
         <v>2.71</v>
       </c>
       <c r="Q219">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R219">
         <v>2.1</v>
       </c>
       <c r="S219">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T219">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U219">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V219">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W219">
         <v>1.05</v>
@@ -36039,31 +36039,31 @@
         <v>1.02</v>
       </c>
       <c r="Y219">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z219">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA219">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB219">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC219">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD219">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE219">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF219">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG219">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH219" t="inlineStr">
         <is>
@@ -36076,10 +36076,10 @@
         </is>
       </c>
       <c r="AJ219">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK219">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL219">
         <v>0</v>
@@ -36350,13 +36350,13 @@
         <v>1.35</v>
       </c>
       <c r="T221">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="U221">
         <v>2.83</v>
       </c>
       <c r="V221">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W221">
         <v>1.06</v>
@@ -36510,10 +36510,10 @@
         <v>2.03</v>
       </c>
       <c r="S222">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T222">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="U222">
         <v>3.1</v>
@@ -36549,10 +36549,10 @@
         <v>1.03</v>
       </c>
       <c r="AF222">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AG222">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36845,7 +36845,7 @@
         <v>2.16</v>
       </c>
       <c r="V224">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W224">
         <v>1.15</v>
@@ -37268,7 +37268,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,64 +37310,64 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="O227">
-        <v>4.34</v>
+        <v>3.06</v>
       </c>
       <c r="P227">
-        <v>7.1</v>
+        <v>3.54</v>
       </c>
       <c r="Q227">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="R227">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="S227">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T227">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="U227">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V227">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W227">
         <v>1.06</v>
       </c>
       <c r="X227">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y227">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z227">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
       <c r="AA227">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB227">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AC227">
-        <v>3.13</v>
+        <v>3.5</v>
       </c>
       <c r="AD227">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE227">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF227">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="AG227">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK227">
-        <v>2.74</v>
+        <v>1.5</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O228">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P228">
-        <v>3.54</v>
+        <v>2.87</v>
       </c>
       <c r="Q228">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R228">
         <v>2</v>
       </c>
       <c r="S228">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T228">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="U228">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V228">
         <v>1.33</v>
       </c>
       <c r="W228">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X228">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z228">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA228">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB228">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC228">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="AD228">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE228">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF228">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG228">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK228">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,65 +37636,65 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O229">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P229">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="Q229">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="R229">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S229">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T229">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U229">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V229">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W229">
         <v>1.07</v>
       </c>
       <c r="X229">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y229">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z229">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AA229">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AB229">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AC229">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="AD229">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AE229">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF229">
+        <v>1.8</v>
+      </c>
+      <c r="AG229">
         <v>1.85</v>
       </c>
-      <c r="AG229">
-        <v>1.8</v>
-      </c>
       <c r="AH229" t="inlineStr">
         <is>
           <t>[]</t>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK229">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="O230">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P230">
-        <v>4.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q230">
-        <v>2.4</v>
+        <v>3.48</v>
       </c>
       <c r="R230">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="S230">
+        <v>1.2</v>
+      </c>
+      <c r="T230">
+        <v>4.6</v>
+      </c>
+      <c r="U230">
+        <v>2.07</v>
+      </c>
+      <c r="V230">
+        <v>1.73</v>
+      </c>
+      <c r="W230">
+        <v>1.22</v>
+      </c>
+      <c r="X230">
+        <v>1.02</v>
+      </c>
+      <c r="Y230">
+        <v>1.06</v>
+      </c>
+      <c r="Z230">
+        <v>7</v>
+      </c>
+      <c r="AA230">
+        <v>1.38</v>
+      </c>
+      <c r="AB230">
+        <v>3</v>
+      </c>
+      <c r="AC230">
+        <v>2.07</v>
+      </c>
+      <c r="AD230">
+        <v>1.87</v>
+      </c>
+      <c r="AE230">
         <v>1.36</v>
       </c>
-      <c r="T230">
-        <v>2.75</v>
-      </c>
-      <c r="U230">
-        <v>2.8</v>
-      </c>
-      <c r="V230">
-        <v>1.32</v>
-      </c>
-      <c r="W230">
-        <v>1.07</v>
-      </c>
-      <c r="X230">
-        <v>1.03</v>
-      </c>
-      <c r="Y230">
-        <v>1.31</v>
-      </c>
-      <c r="Z230">
-        <v>2.92</v>
-      </c>
-      <c r="AA230">
-        <v>2.1</v>
-      </c>
-      <c r="AB230">
-        <v>1.68</v>
-      </c>
-      <c r="AC230">
-        <v>3.42</v>
-      </c>
-      <c r="AD230">
-        <v>1.23</v>
-      </c>
-      <c r="AE230">
-        <v>1.05</v>
-      </c>
       <c r="AF230">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AG230">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK230">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37915,12 +37915,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,65 +37962,65 @@
         </is>
       </c>
       <c r="N231">
-        <v>3.2</v>
+        <v>1.46</v>
       </c>
       <c r="O231">
-        <v>3.9</v>
+        <v>4.34</v>
       </c>
       <c r="P231">
-        <v>2.02</v>
+        <v>7.1</v>
       </c>
       <c r="Q231">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="R231">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S231">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="T231">
-        <v>4</v>
+        <v>2.93</v>
       </c>
       <c r="U231">
-        <v>2.06</v>
+        <v>2.77</v>
       </c>
       <c r="V231">
+        <v>1.42</v>
+      </c>
+      <c r="W231">
+        <v>1.06</v>
+      </c>
+      <c r="X231">
+        <v>1.01</v>
+      </c>
+      <c r="Y231">
+        <v>1.24</v>
+      </c>
+      <c r="Z231">
+        <v>3.52</v>
+      </c>
+      <c r="AA231">
+        <v>1.94</v>
+      </c>
+      <c r="AB231">
+        <v>2</v>
+      </c>
+      <c r="AC231">
+        <v>3.13</v>
+      </c>
+      <c r="AD231">
+        <v>1.36</v>
+      </c>
+      <c r="AE231">
+        <v>1.12</v>
+      </c>
+      <c r="AF231">
+        <v>1.99</v>
+      </c>
+      <c r="AG231">
         <v>1.73</v>
       </c>
-      <c r="W231">
-        <v>1.2</v>
-      </c>
-      <c r="X231">
-        <v>1.02</v>
-      </c>
-      <c r="Y231">
-        <v>1.1</v>
-      </c>
-      <c r="Z231">
-        <v>6.5</v>
-      </c>
-      <c r="AA231">
-        <v>1.39</v>
-      </c>
-      <c r="AB231">
-        <v>3</v>
-      </c>
-      <c r="AC231">
-        <v>1.9</v>
-      </c>
-      <c r="AD231">
-        <v>1.87</v>
-      </c>
-      <c r="AE231">
-        <v>1.36</v>
-      </c>
-      <c r="AF231">
-        <v>1.33</v>
-      </c>
-      <c r="AG231">
-        <v>3</v>
-      </c>
       <c r="AH231" t="inlineStr">
         <is>
           <t>[]</t>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="AK231">
-        <v>1.38</v>
+        <v>2.74</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>2026-10-18 12:30:00</t>
+          <t>2026-10-18 12:45:00</t>
         </is>
       </c>
     </row>
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O237">
         <v>4.2</v>
       </c>
       <c r="P237">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q237">
         <v>4.47</v>
@@ -38994,7 +38994,7 @@
         <v>1.19</v>
       </c>
       <c r="AF237">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG237">
         <v>2.2</v>
@@ -39601,10 +39601,10 @@
         <v>1.94</v>
       </c>
       <c r="Q241">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R241">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S241">
         <v>1.36</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="O248">
         <v>3.25</v>
       </c>
       <c r="P248">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="Q248">
         <v>2.5</v>
@@ -40806,7 +40806,7 @@
         <v>1.24</v>
       </c>
       <c r="AK248">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL248">
         <v>0</v>
@@ -41071,31 +41071,31 @@
         <v>2.71</v>
       </c>
       <c r="R250">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S250">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T250">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U250">
-        <v>2.22</v>
+        <v>1.96</v>
       </c>
       <c r="V250">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W250">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X250">
         <v>1.01</v>
       </c>
       <c r="Y250">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z250">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA250">
         <v>1.57</v>
@@ -41104,19 +41104,19 @@
         <v>2.25</v>
       </c>
       <c r="AC250">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AD250">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="AE250">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AF250">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AG250">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>1.39</v>
       </c>
       <c r="AK250">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL250">
         <v>0</v>
@@ -41427,7 +41427,7 @@
         <v>2</v>
       </c>
       <c r="AB252">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AC252">
         <v>3.28</v>
@@ -41458,7 +41458,7 @@
         <v>1.3</v>
       </c>
       <c r="AK252">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AL252">
         <v>0</v>
@@ -41548,7 +41548,7 @@
         </is>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O253">
         <v>3.1</v>
@@ -41720,7 +41720,7 @@
         <v>2.15</v>
       </c>
       <c r="Q254">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="R254">
         <v>2.38</v>
@@ -41784,7 +41784,7 @@
         <v>1.33</v>
       </c>
       <c r="AK254">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL254">
         <v>0</v>
@@ -42529,25 +42529,25 @@
         <v>2.85</v>
       </c>
       <c r="O259">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="P259">
         <v>2.33</v>
       </c>
       <c r="Q259">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="R259">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S259">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T259">
         <v>2.59</v>
       </c>
       <c r="U259">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V259">
         <v>1.38</v>
@@ -42565,10 +42565,10 @@
         <v>3.25</v>
       </c>
       <c r="AA259">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB259">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC259">
         <v>3.6</v>
@@ -42577,7 +42577,7 @@
         <v>1.25</v>
       </c>
       <c r="AE259">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF259">
         <v>1.75</v>
@@ -42596,10 +42596,10 @@
         </is>
       </c>
       <c r="AJ259">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AK259">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL259">
         <v>0</v>
@@ -42867,10 +42867,10 @@
         <v>2</v>
       </c>
       <c r="S261">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T261">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="U261">
         <v>3.06</v>
@@ -42894,7 +42894,7 @@
         <v>2.22</v>
       </c>
       <c r="AB261">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC261">
         <v>4.1</v>
@@ -43350,7 +43350,7 @@
         <v>3.9</v>
       </c>
       <c r="Q264">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="R264">
         <v>2.2</v>
@@ -43414,7 +43414,7 @@
         <v>1.15</v>
       </c>
       <c r="AK264">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AL264">
         <v>0</v>
@@ -43507,7 +43507,7 @@
         <v>1.71</v>
       </c>
       <c r="O265">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P265">
         <v>3.9</v>
@@ -43519,16 +43519,16 @@
         <v>2.69</v>
       </c>
       <c r="S265">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T265">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U265">
         <v>1.79</v>
       </c>
       <c r="V265">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W265">
         <v>1.16</v>
@@ -43577,7 +43577,7 @@
         <v>1.2</v>
       </c>
       <c r="AK265">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43620,27 +43620,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,64 +43667,64 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="O266">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="P266">
-        <v>3.45</v>
+        <v>4.87</v>
       </c>
       <c r="Q266">
-        <v>2.91</v>
+        <v>2.21</v>
       </c>
       <c r="R266">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="S266">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="T266">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="U266">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="V266">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W266">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X266">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y266">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Z266">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="AA266">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AB266">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC266">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD266">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE266">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF266">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AG266">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43737,10 +43737,10 @@
         </is>
       </c>
       <c r="AJ266">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK266">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-10-18 14:45:00</t>
+          <t>2026-10-18 15:00:00</t>
         </is>
       </c>
     </row>
@@ -43788,22 +43788,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,43 +43830,43 @@
         </is>
       </c>
       <c r="N267">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="O267">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="P267">
-        <v>4.87</v>
+        <v>1.44</v>
       </c>
       <c r="Q267">
-        <v>2.21</v>
+        <v>6.84</v>
       </c>
       <c r="R267">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="S267">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T267">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="U267">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V267">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W267">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X267">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y267">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z267">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA267">
         <v>2.1</v>
@@ -43875,35 +43875,35 @@
         <v>1.73</v>
       </c>
       <c r="AC267">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD267">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE267">
+        <v>1.06</v>
+      </c>
+      <c r="AF267">
+        <v>2.09</v>
+      </c>
+      <c r="AG267">
+        <v>1.65</v>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ267">
+        <v>1.17</v>
+      </c>
+      <c r="AK267">
         <v>1.04</v>
-      </c>
-      <c r="AF267">
-        <v>1.98</v>
-      </c>
-      <c r="AG267">
-        <v>1.72</v>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ267">
-        <v>1.22</v>
-      </c>
-      <c r="AK267">
-        <v>2.1</v>
       </c>
       <c r="AL267">
         <v>0</v>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,64 +43993,64 @@
         </is>
       </c>
       <c r="N268">
-        <v>6.5</v>
+        <v>2.39</v>
       </c>
       <c r="O268">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="P268">
+        <v>2.73</v>
+      </c>
+      <c r="Q268">
+        <v>2.75</v>
+      </c>
+      <c r="R268">
+        <v>2.25</v>
+      </c>
+      <c r="S268">
+        <v>1.3</v>
+      </c>
+      <c r="T268">
+        <v>3.08</v>
+      </c>
+      <c r="U268">
+        <v>2.45</v>
+      </c>
+      <c r="V268">
         <v>1.44</v>
       </c>
-      <c r="Q268">
-        <v>6.84</v>
-      </c>
-      <c r="R268">
-        <v>2.11</v>
-      </c>
-      <c r="S268">
-        <v>1.38</v>
-      </c>
-      <c r="T268">
-        <v>2.64</v>
-      </c>
-      <c r="U268">
-        <v>2.9</v>
-      </c>
-      <c r="V268">
+      <c r="W268">
+        <v>1.08</v>
+      </c>
+      <c r="X268">
+        <v>1</v>
+      </c>
+      <c r="Y268">
+        <v>1.21</v>
+      </c>
+      <c r="Z268">
+        <v>3.58</v>
+      </c>
+      <c r="AA268">
+        <v>1.75</v>
+      </c>
+      <c r="AB268">
+        <v>2.05</v>
+      </c>
+      <c r="AC268">
+        <v>2.88</v>
+      </c>
+      <c r="AD268">
         <v>1.32</v>
       </c>
-      <c r="W268">
-        <v>1.06</v>
-      </c>
-      <c r="X268">
-        <v>1.02</v>
-      </c>
-      <c r="Y268">
-        <v>1.28</v>
-      </c>
-      <c r="Z268">
-        <v>3.08</v>
-      </c>
-      <c r="AA268">
-        <v>2.1</v>
-      </c>
-      <c r="AB268">
-        <v>1.73</v>
-      </c>
-      <c r="AC268">
-        <v>3.42</v>
-      </c>
-      <c r="AD268">
-        <v>1.23</v>
-      </c>
       <c r="AE268">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF268">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="AG268">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AH268" t="inlineStr">
         <is>
@@ -44063,10 +44063,10 @@
         </is>
       </c>
       <c r="AJ268">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK268">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="AL268">
         <v>0</v>
@@ -44114,22 +44114,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,64 +44156,64 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.39</v>
+        <v>1.57</v>
       </c>
       <c r="O269">
-        <v>3.49</v>
+        <v>3.12</v>
       </c>
       <c r="P269">
-        <v>2.73</v>
+        <v>6.5</v>
       </c>
       <c r="Q269">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R269">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S269">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T269">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U269">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V269">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W269">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y269">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z269">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA269">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="AB269">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AC269">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD269">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE269">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF269">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG269">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK269">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,49 +44319,49 @@
         </is>
       </c>
       <c r="N270">
+        <v>1.22</v>
+      </c>
+      <c r="O270">
+        <v>5.55</v>
+      </c>
+      <c r="P270">
+        <v>12</v>
+      </c>
+      <c r="Q270">
+        <v>0</v>
+      </c>
+      <c r="R270">
+        <v>0</v>
+      </c>
+      <c r="S270">
+        <v>0</v>
+      </c>
+      <c r="T270">
+        <v>0</v>
+      </c>
+      <c r="U270">
+        <v>0</v>
+      </c>
+      <c r="V270">
+        <v>0</v>
+      </c>
+      <c r="W270">
+        <v>0</v>
+      </c>
+      <c r="X270">
+        <v>0</v>
+      </c>
+      <c r="Y270">
+        <v>0</v>
+      </c>
+      <c r="Z270">
+        <v>0</v>
+      </c>
+      <c r="AA270">
         <v>1.57</v>
       </c>
-      <c r="O270">
-        <v>3.24</v>
-      </c>
-      <c r="P270">
-        <v>6.4</v>
-      </c>
-      <c r="Q270">
-        <v>0</v>
-      </c>
-      <c r="R270">
-        <v>0</v>
-      </c>
-      <c r="S270">
-        <v>0</v>
-      </c>
-      <c r="T270">
-        <v>0</v>
-      </c>
-      <c r="U270">
-        <v>0</v>
-      </c>
-      <c r="V270">
-        <v>0</v>
-      </c>
-      <c r="W270">
-        <v>0</v>
-      </c>
-      <c r="X270">
-        <v>0</v>
-      </c>
-      <c r="Y270">
-        <v>0</v>
-      </c>
-      <c r="Z270">
-        <v>0</v>
-      </c>
-      <c r="AA270">
-        <v>2.87</v>
-      </c>
       <c r="AB270">
-        <v>1.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC270">
         <v>0</v>
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>1.22</v>
+        <v>4.26</v>
       </c>
       <c r="O271">
-        <v>5.55</v>
+        <v>3.63</v>
       </c>
       <c r="P271">
-        <v>12</v>
+        <v>1.67</v>
       </c>
       <c r="Q271">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R271">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S271">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T271">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U271">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V271">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W271">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X271">
         <v>0</v>
       </c>
       <c r="Y271">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z271">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AA271">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AB271">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AC271">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD271">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE271">
         <v>0</v>
       </c>
       <c r="AF271">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG271">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK271">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>4.26</v>
+        <v>2.12</v>
       </c>
       <c r="O272">
-        <v>3.63</v>
+        <v>3.1</v>
       </c>
       <c r="P272">
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="Q272">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="R272">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S272">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="T272">
-        <v>3.34</v>
+        <v>2.54</v>
       </c>
       <c r="U272">
-        <v>2.43</v>
+        <v>3.52</v>
       </c>
       <c r="V272">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W272">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X272">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y272">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Z272">
-        <v>3.39</v>
+        <v>2.59</v>
       </c>
       <c r="AA272">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="AB272">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC272">
-        <v>3.57</v>
+        <v>4.45</v>
       </c>
       <c r="AD272">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE272">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF272">
-        <v>1.73</v>
+        <v>2.02</v>
       </c>
       <c r="AG272">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AK272">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -45632,16 +45632,16 @@
         <v>3.6</v>
       </c>
       <c r="Q278">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="R278">
+        <v>1.81</v>
+      </c>
+      <c r="S278">
         <v>1.71</v>
       </c>
-      <c r="S278">
-        <v>1.72</v>
-      </c>
       <c r="T278">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U278">
         <v>4.25</v>
@@ -45656,10 +45656,10 @@
         <v>1.12</v>
       </c>
       <c r="Y278">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z278">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AA278">
         <v>3.5</v>
@@ -45668,10 +45668,10 @@
         <v>1.28</v>
       </c>
       <c r="AC278">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="AD278">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE278">
         <v>1.02</v>
@@ -45680,7 +45680,7 @@
         <v>2.54</v>
       </c>
       <c r="AG278">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45795,34 +45795,34 @@
         <v>3.2</v>
       </c>
       <c r="Q279">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="R279">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="S279">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T279">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="U279">
         <v>3.4</v>
       </c>
       <c r="V279">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W279">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X279">
         <v>1.11</v>
       </c>
       <c r="Y279">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Z279">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="AA279">
         <v>2.5</v>
@@ -45834,7 +45834,7 @@
         <v>4.5</v>
       </c>
       <c r="AD279">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE279">
         <v>1.01</v>
@@ -45843,7 +45843,7 @@
         <v>2.05</v>
       </c>
       <c r="AG279">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH279" t="inlineStr">
         <is>
@@ -45856,10 +45856,10 @@
         </is>
       </c>
       <c r="AJ279">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK279">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL279">
         <v>0</v>
@@ -45949,7 +45949,7 @@
         </is>
       </c>
       <c r="N280">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="O280">
         <v>4</v>
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="O282">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P282">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="Q282">
         <v>2.5</v>
@@ -46441,10 +46441,10 @@
         <v>2.87</v>
       </c>
       <c r="O283">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="P283">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q283">
         <v>3.56</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O285">
         <v>3.5</v>
       </c>
       <c r="P285">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q285">
         <v>2.17</v>
@@ -46779,7 +46779,7 @@
         <v>2.09</v>
       </c>
       <c r="S285">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="T285">
         <v>2.5</v>
@@ -46788,7 +46788,7 @@
         <v>3.12</v>
       </c>
       <c r="V285">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W285">
         <v>1.05</v>
@@ -46806,7 +46806,7 @@
         <v>2.4</v>
       </c>
       <c r="AB285">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC285">
         <v>4.35</v>
@@ -46821,7 +46821,7 @@
         <v>2.45</v>
       </c>
       <c r="AG285">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O286">
         <v>2.85</v>
@@ -47111,10 +47111,10 @@
         <v>2.29</v>
       </c>
       <c r="U287">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V287">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W287">
         <v>1.02</v>
@@ -47144,7 +47144,7 @@
         <v>1</v>
       </c>
       <c r="AF287">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AG287">
         <v>1.7</v>
@@ -48083,7 +48083,7 @@
         <v>2.1</v>
       </c>
       <c r="S293">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T293">
         <v>2.79</v>
@@ -48092,10 +48092,10 @@
         <v>2.65</v>
       </c>
       <c r="V293">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W293">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X293">
         <v>1.04</v>
@@ -48138,10 +48138,10 @@
         </is>
       </c>
       <c r="AJ293">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AK293">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL293">
         <v>0</v>
@@ -48270,10 +48270,10 @@
         <v>0</v>
       </c>
       <c r="AA294">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AB294">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC294">
         <v>0</v>
@@ -48394,19 +48394,19 @@
         </is>
       </c>
       <c r="N295">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O295">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P295">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q295">
-        <v>3.9</v>
+        <v>4.94</v>
       </c>
       <c r="R295">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="S295">
         <v>1.5</v>
@@ -48415,13 +48415,13 @@
         <v>2.5</v>
       </c>
       <c r="U295">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V295">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W295">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X295">
         <v>1.1</v>
@@ -48430,28 +48430,28 @@
         <v>1.45</v>
       </c>
       <c r="Z295">
+        <v>2.52</v>
+      </c>
+      <c r="AA295">
         <v>2.33</v>
       </c>
-      <c r="AA295">
-        <v>2.5</v>
-      </c>
       <c r="AB295">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC295">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="AD295">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE295">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF295">
         <v>2.1</v>
       </c>
       <c r="AG295">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,10 +48464,10 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AK295">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48673,7 +48673,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48836,7 +48836,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -48999,7 +48999,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,7 +49162,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-10-18 17:30:00</t>
+          <t>2026-10-18 17:00:00</t>
         </is>
       </c>
     </row>
@@ -49378,7 +49378,7 @@
         <v>3.5</v>
       </c>
       <c r="P301">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q301">
         <v>2.48</v>
@@ -49414,7 +49414,7 @@
         <v>1.47</v>
       </c>
       <c r="AB301">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC301">
         <v>2.27</v>
@@ -49704,19 +49704,19 @@
         <v>3.1</v>
       </c>
       <c r="P303">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q303">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R303">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S303">
         <v>1.53</v>
       </c>
       <c r="T303">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U303">
         <v>3.5</v>
@@ -49728,16 +49728,16 @@
         <v>1.02</v>
       </c>
       <c r="X303">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y303">
         <v>1.47</v>
       </c>
       <c r="Z303">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="AA303">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB303">
         <v>1.47</v>
@@ -49746,7 +49746,7 @@
         <v>5.09</v>
       </c>
       <c r="AD303">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE303">
         <v>1.02</v>
@@ -49755,7 +49755,7 @@
         <v>2.25</v>
       </c>
       <c r="AG303">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -49768,10 +49768,10 @@
         </is>
       </c>
       <c r="AJ303">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK303">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL303">
         <v>0</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="O305">
         <v>4.02</v>
       </c>
       <c r="P305">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="Q305">
         <v>2.45</v>
@@ -50039,7 +50039,7 @@
         <v>2.6</v>
       </c>
       <c r="S305">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T305">
         <v>4.1</v>
@@ -50078,7 +50078,7 @@
         <v>1.33</v>
       </c>
       <c r="AF305">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AG305">
         <v>3</v>
@@ -50094,10 +50094,10 @@
         </is>
       </c>
       <c r="AJ305">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK305">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50359,16 +50359,16 @@
         <v>2.98</v>
       </c>
       <c r="Q307">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="R307">
         <v>2.4</v>
       </c>
       <c r="S307">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T307">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U307">
         <v>2.1</v>
@@ -50392,7 +50392,7 @@
         <v>1.4</v>
       </c>
       <c r="AB307">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC307">
         <v>2.08</v>
@@ -50420,10 +50420,10 @@
         </is>
       </c>
       <c r="AJ307">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK307">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL307">
         <v>0</v>
@@ -50676,7 +50676,7 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O309">
         <v>2.75</v>
@@ -50685,25 +50685,25 @@
         <v>3.5</v>
       </c>
       <c r="Q309">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="R309">
         <v>1.79</v>
       </c>
       <c r="S309">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T309">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U309">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="V309">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W309">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X309">
         <v>1.08</v>
@@ -50715,16 +50715,16 @@
         <v>2.2</v>
       </c>
       <c r="AA309">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AB309">
         <v>1.4</v>
       </c>
       <c r="AC309">
-        <v>5.74</v>
+        <v>5.55</v>
       </c>
       <c r="AD309">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE309">
         <v>1.03</v>
@@ -50912,7 +50912,7 @@
         <v>1.28</v>
       </c>
       <c r="AK310">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51361,25 +51361,25 @@
         <v>1.01</v>
       </c>
       <c r="Y313">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z313">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA313">
         <v>1.36</v>
       </c>
       <c r="AB313">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AC313">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD313">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE313">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF313">
         <v>1.36</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -644,28 +644,28 @@
         <v>4.24</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="R2">
         <v>2.12</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T2">
         <v>2.66</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="V2">
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -677,7 +677,7 @@
         <v>1.87</v>
       </c>
       <c r="AB2">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
         <v>3.2</v>
@@ -686,13 +686,13 @@
         <v>1.26</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
         <v>1.81</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -807,22 +807,22 @@
         <v>2.45</v>
       </c>
       <c r="Q3">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
         <v>2.01</v>
       </c>
       <c r="S3">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T3">
         <v>2.56</v>
       </c>
       <c r="U3">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -837,7 +837,7 @@
         <v>3.04</v>
       </c>
       <c r="AA3">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB3">
         <v>1.73</v>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK3">
         <v>1.4</v>
@@ -1299,22 +1299,22 @@
         <v>1.87</v>
       </c>
       <c r="R6">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T6">
         <v>3.24</v>
       </c>
       <c r="U6">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
         <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1323,28 +1323,28 @@
         <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB6">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AC6">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AD6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK6">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="O7">
         <v>3.83</v>
@@ -1459,19 +1459,19 @@
         <v>4.15</v>
       </c>
       <c r="Q7">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V7">
         <v>1.5</v>
@@ -1489,19 +1489,19 @@
         <v>3.96</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC7">
         <v>2.62</v>
       </c>
       <c r="AD7">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
         <v>1.65</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
         <v>1.97</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
         <v>3.72</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S9">
         <v>1.41</v>
@@ -1797,28 +1797,28 @@
         <v>2.9</v>
       </c>
       <c r="U9">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
         <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.23</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
         <v>3.5</v>
@@ -1830,11 +1830,11 @@
         <v>1.04</v>
       </c>
       <c r="AF9">
+        <v>1.87</v>
+      </c>
+      <c r="AG9">
         <v>1.83</v>
       </c>
-      <c r="AG9">
-        <v>1.85</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.13</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <v>3.1</v>
+      </c>
+      <c r="Q10">
+        <v>2.88</v>
+      </c>
+      <c r="R10">
+        <v>1.85</v>
+      </c>
+      <c r="S10">
+        <v>1.52</v>
+      </c>
+      <c r="T10">
+        <v>2.31</v>
+      </c>
+      <c r="U10">
+        <v>3.25</v>
+      </c>
+      <c r="V10">
+        <v>1.3</v>
+      </c>
+      <c r="W10">
+        <v>1.03</v>
+      </c>
+      <c r="X10">
+        <v>1.05</v>
+      </c>
+      <c r="Y10">
+        <v>1.44</v>
+      </c>
+      <c r="Z10">
+        <v>2.46</v>
+      </c>
+      <c r="AA10">
+        <v>2.29</v>
+      </c>
+      <c r="AB10">
         <v>1.53</v>
       </c>
-      <c r="O10">
-        <v>4.05</v>
-      </c>
-      <c r="P10">
+      <c r="AC10">
         <v>4.8</v>
       </c>
-      <c r="Q10">
-        <v>2.05</v>
-      </c>
-      <c r="R10">
-        <v>2.39</v>
-      </c>
-      <c r="S10">
-        <v>1.25</v>
-      </c>
-      <c r="T10">
-        <v>3.4</v>
-      </c>
-      <c r="U10">
-        <v>2.38</v>
-      </c>
-      <c r="V10">
-        <v>1.5</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
+      <c r="AD10">
         <v>1.15</v>
       </c>
-      <c r="Z10">
-        <v>4.65</v>
-      </c>
-      <c r="AA10">
-        <v>1.61</v>
-      </c>
-      <c r="AB10">
-        <v>2.3</v>
-      </c>
-      <c r="AC10">
-        <v>2.43</v>
-      </c>
-      <c r="AD10">
-        <v>1.51</v>
-      </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG10">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="U11">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="V11">
+        <v>1.36</v>
+      </c>
+      <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
         <v>1.3</v>
       </c>
-      <c r="W11">
-        <v>1.03</v>
-      </c>
-      <c r="X11">
-        <v>1.05</v>
-      </c>
-      <c r="Y11">
-        <v>1.44</v>
-      </c>
       <c r="Z11">
-        <v>2.46</v>
+        <v>3.47</v>
       </c>
       <c r="AA11">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>4.8</v>
+        <v>3.42</v>
       </c>
       <c r="AD11">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="P12">
+        <v>4.8</v>
+      </c>
+      <c r="Q12">
+        <v>2.05</v>
+      </c>
+      <c r="R12">
+        <v>2.39</v>
+      </c>
+      <c r="S12">
+        <v>1.25</v>
+      </c>
+      <c r="T12">
         <v>3.4</v>
       </c>
-      <c r="Q12">
-        <v>2.56</v>
-      </c>
-      <c r="R12">
-        <v>2.1</v>
-      </c>
-      <c r="S12">
-        <v>1.38</v>
-      </c>
-      <c r="T12">
-        <v>2.82</v>
-      </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>3.47</v>
+        <v>4.65</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AB12">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC12">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG12">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,16 +2437,16 @@
         <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
         <v>1.31</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U13">
         <v>2.63</v>
@@ -2455,7 +2455,7 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2485,7 +2485,7 @@
         <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>2.2</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="Q15">
         <v>2.7</v>
@@ -2778,7 +2778,7 @@
         <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2926,10 +2926,10 @@
         <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
         <v>1.2</v>
@@ -2950,31 +2950,31 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AA16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC16">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD16">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>4.8</v>
       </c>
       <c r="AA17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC17">
         <v>2.24</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="P18">
-        <v>2.26</v>
+        <v>2.75</v>
       </c>
       <c r="Q18">
         <v>2.9</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="Q19">
-        <v>2.81</v>
+        <v>2.35</v>
       </c>
       <c r="R19">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S19">
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA19">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB19">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC19">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD19">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>2.22</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.59</v>
+        <v>2.82</v>
       </c>
       <c r="Q20">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="R20">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V20">
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z20">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD20">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF20">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,55 +3732,55 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.24</v>
+        <v>3.7</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="Q21">
         <v>4.2</v>
       </c>
       <c r="R21">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S21">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="U21">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="V21">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
         <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.32</v>
       </c>
       <c r="Z21">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="AA21">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC21">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD21">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE21">
         <v>1.05</v>
@@ -3789,7 +3789,7 @@
         <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>2.55</v>
       </c>
       <c r="O22">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="P22">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
         <v>3.2</v>
@@ -4097,7 +4097,7 @@
         <v>4.15</v>
       </c>
       <c r="AA23">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB23">
         <v>2.2</v>
@@ -4242,7 +4242,7 @@
         <v>3</v>
       </c>
       <c r="U24">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V24">
         <v>1.47</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q25">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="R25">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S25">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T25">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U25">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V25">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W25">
         <v>1.21</v>
@@ -4417,16 +4417,16 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z25">
         <v>7.5</v>
       </c>
       <c r="AA25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB25">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC25">
         <v>1.79</v>
@@ -4435,7 +4435,7 @@
         <v>1.88</v>
       </c>
       <c r="AE25">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
         <v>1.33</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O28">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="P28">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="Q28">
         <v>2.8</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q29">
         <v>3.6</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="O31">
         <v>3.6</v>
       </c>
       <c r="P31">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
         <v>1.95</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -5890,10 +5890,10 @@
         <v>2.7</v>
       </c>
       <c r="AA34">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB34">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC34">
         <v>4.15</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="O35">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P35">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O37">
         <v>3.24</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>6.26</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
+        <v>3.07</v>
+      </c>
+      <c r="R41">
         <v>2</v>
       </c>
-      <c r="R41">
-        <v>2.25</v>
-      </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="U41">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z41">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AA41">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AB41">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC41">
-        <v>3.08</v>
+        <v>3.76</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE41">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG41">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK41">
-        <v>2.38</v>
+        <v>1.45</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="O42">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="Q42">
-        <v>3.07</v>
+        <v>2</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z42">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA42">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AB42">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC42">
-        <v>3.76</v>
+        <v>3.08</v>
       </c>
       <c r="AD42">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK42">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
         <v>3</v>
       </c>
       <c r="P43">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="Q43">
         <v>2.57</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -7505,7 +7505,7 @@
         <v>2.65</v>
       </c>
       <c r="V44">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W44">
         <v>1.1</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="O48">
         <v>3.77</v>
@@ -8302,7 +8302,7 @@
         <v>3.83</v>
       </c>
       <c r="P49">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="Q49">
         <v>2.36</v>
@@ -8311,19 +8311,19 @@
         <v>2.38</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T49">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U49">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V49">
         <v>1.7</v>
       </c>
       <c r="W49">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X49">
         <v>1.02</v>
@@ -8335,10 +8335,10 @@
         <v>6.15</v>
       </c>
       <c r="AA49">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB49">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC49">
         <v>1.98</v>
@@ -8507,7 +8507,7 @@
         <v>2.7</v>
       </c>
       <c r="AD50">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE50">
         <v>1.1</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="O53">
-        <v>3.26</v>
+        <v>2.95</v>
       </c>
       <c r="P53">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="Q53">
         <v>2.88</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O54">
         <v>6.25</v>
@@ -9168,7 +9168,7 @@
         <v>2.15</v>
       </c>
       <c r="AG54">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="O55">
         <v>3.35</v>
@@ -9926,31 +9926,31 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="O59">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Q59">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="R59">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="U59">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
         <v>1.08</v>
@@ -9959,25 +9959,25 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB59">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AC59">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD59">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE59">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF59">
         <v>1.57</v>
@@ -10089,31 +10089,31 @@
         </is>
       </c>
       <c r="N60">
-        <v>4.2</v>
+        <v>3.81</v>
       </c>
       <c r="O60">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="P60">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q60">
-        <v>4.1</v>
+        <v>4.61</v>
       </c>
       <c r="R60">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="S60">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T60">
         <v>2.8</v>
       </c>
       <c r="U60">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V60">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W60">
         <v>1.06</v>
@@ -10131,7 +10131,7 @@
         <v>1.95</v>
       </c>
       <c r="AB60">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AC60">
         <v>2.75</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AK60">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,43 +10252,43 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="O61">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="R61">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S61">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="U61">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V61">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W61">
         <v>1.06</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z61">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA61">
         <v>1.95</v>
@@ -10300,13 +10300,13 @@
         <v>3.2</v>
       </c>
       <c r="AD61">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE61">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF61">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AG61">
         <v>2</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AK61">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10436,10 +10436,10 @@
         <v>4</v>
       </c>
       <c r="U62">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W62">
         <v>1.18</v>
@@ -10454,22 +10454,22 @@
         <v>5.4</v>
       </c>
       <c r="AA62">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB62">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC62">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
         <v>1.76</v>
       </c>
       <c r="AE62">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG62">
         <v>2.26</v>
@@ -10581,7 +10581,7 @@
         <v>2.5</v>
       </c>
       <c r="O63">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
         <v>2.7</v>
@@ -10596,7 +10596,7 @@
         <v>1.36</v>
       </c>
       <c r="T63">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U63">
         <v>2.85</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q64">
         <v>2.79</v>
@@ -11402,16 +11402,16 @@
         <v>2.12</v>
       </c>
       <c r="Q68">
-        <v>3.41</v>
+        <v>3.47</v>
       </c>
       <c r="R68">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S68">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T68">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U68">
         <v>2.31</v>
@@ -11423,25 +11423,25 @@
         <v>1.1</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
         <v>1.17</v>
       </c>
       <c r="Z68">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="AA68">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB68">
         <v>2.05</v>
       </c>
       <c r="AC68">
-        <v>2.53</v>
+        <v>2.66</v>
       </c>
       <c r="AD68">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE68">
         <v>1.13</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK68">
         <v>1.36</v>
@@ -11565,19 +11565,19 @@
         <v>11</v>
       </c>
       <c r="Q69">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R69">
         <v>2.73</v>
       </c>
       <c r="S69">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U69">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V69">
         <v>1.71</v>
@@ -11595,13 +11595,13 @@
         <v>5.9</v>
       </c>
       <c r="AA69">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB69">
         <v>2.7</v>
       </c>
       <c r="AC69">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AD69">
         <v>1.72</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK69">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12208,25 +12208,25 @@
         </is>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="P73">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q73">
-        <v>3.13</v>
+        <v>3.66</v>
       </c>
       <c r="R73">
         <v>2.04</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>2.22</v>
+        <v>2.75</v>
       </c>
       <c r="U73">
         <v>2.8</v>
@@ -12253,7 +12253,7 @@
         <v>1.73</v>
       </c>
       <c r="AC73">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="AD73">
         <v>1.2</v>
@@ -12265,7 +12265,7 @@
         <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>2.62</v>
       </c>
       <c r="S74">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T74">
         <v>4.5</v>
@@ -12555,7 +12555,7 @@
         <v>3.48</v>
       </c>
       <c r="U75">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="V75">
         <v>1.61</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -14001,31 +14001,31 @@
         </is>
       </c>
       <c r="N84">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O84">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P84">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Q84">
         <v>7.55</v>
       </c>
       <c r="R84">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="S84">
         <v>1.22</v>
       </c>
       <c r="T84">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="V84">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W84">
         <v>1.12</v>
@@ -14043,7 +14043,7 @@
         <v>1.46</v>
       </c>
       <c r="AB84">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AC84">
         <v>2.2</v>
@@ -14176,7 +14176,7 @@
         <v>2.33</v>
       </c>
       <c r="R85">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S85">
         <v>1.21</v>
@@ -14191,28 +14191,28 @@
         <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z85">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="AA85">
         <v>1.42</v>
       </c>
       <c r="AB85">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC85">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AD85">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
         <v>1.22</v>
@@ -14237,7 +14237,7 @@
         <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14366,7 +14366,7 @@
         <v>2.5</v>
       </c>
       <c r="AA86">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AB86">
         <v>1.73</v>
@@ -15166,7 +15166,7 @@
         <v>2.4</v>
       </c>
       <c r="V91">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W91">
         <v>1.1</v>
@@ -15483,10 +15483,10 @@
         <v>2.25</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U93">
         <v>2.38</v>
@@ -15800,13 +15800,13 @@
         <v>3.4</v>
       </c>
       <c r="P95">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="Q95">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R95">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
         <v>1.25</v>
@@ -15818,7 +15818,7 @@
         <v>2.19</v>
       </c>
       <c r="V95">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W95">
         <v>1.12</v>
@@ -15827,7 +15827,7 @@
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z95">
         <v>4.99</v>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15957,22 +15957,22 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="O96">
-        <v>3.85</v>
+        <v>3.73</v>
       </c>
       <c r="P96">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q96">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="R96">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="S96">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T96">
         <v>4</v>
@@ -15993,16 +15993,16 @@
         <v>1.11</v>
       </c>
       <c r="Z96">
-        <v>4.85</v>
+        <v>5.37</v>
       </c>
       <c r="AA96">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB96">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AC96">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="AD96">
         <v>1.61</v>
@@ -16011,10 +16011,10 @@
         <v>1.22</v>
       </c>
       <c r="AF96">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AG96">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK96">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O101">
         <v>3.7</v>
       </c>
       <c r="P101">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="Q101">
         <v>2.21</v>
@@ -17315,7 +17315,7 @@
         <v>1.05</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
         <v>1.9</v>
@@ -17587,10 +17587,10 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O106">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P106">
         <v>3.5</v>
@@ -17756,7 +17756,7 @@
         <v>3.7</v>
       </c>
       <c r="P107">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -17786,10 +17786,10 @@
         <v>1.11</v>
       </c>
       <c r="Z107">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="AA107">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB107">
         <v>2.58</v>
@@ -17913,19 +17913,19 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O108">
         <v>3</v>
       </c>
       <c r="P108">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q108">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R108">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S108">
         <v>1.41</v>
@@ -17934,10 +17934,10 @@
         <v>2.63</v>
       </c>
       <c r="U108">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V108">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W108">
         <v>1.04</v>
@@ -17952,10 +17952,10 @@
         <v>2.74</v>
       </c>
       <c r="AA108">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB108">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC108">
         <v>3.94</v>
@@ -17970,7 +17970,7 @@
         <v>1.88</v>
       </c>
       <c r="AG108">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK108">
         <v>1.58</v>
@@ -18082,25 +18082,25 @@
         <v>3.2</v>
       </c>
       <c r="P109">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q109">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R109">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S109">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T109">
-        <v>2.76</v>
+        <v>3.03</v>
       </c>
       <c r="U109">
         <v>2.64</v>
       </c>
       <c r="V109">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W109">
         <v>1.04</v>
@@ -18118,7 +18118,7 @@
         <v>1.8</v>
       </c>
       <c r="AB109">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC109">
         <v>2.92</v>
@@ -18133,7 +18133,7 @@
         <v>1.62</v>
       </c>
       <c r="AG109">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>4</v>
       </c>
       <c r="Q110">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R110">
         <v>2.3</v>
@@ -18257,13 +18257,13 @@
         <v>1.3</v>
       </c>
       <c r="T110">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U110">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="V110">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W110">
         <v>1.1</v>
@@ -18281,7 +18281,7 @@
         <v>1.72</v>
       </c>
       <c r="AB110">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC110">
         <v>2.74</v>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18586,7 +18586,7 @@
         <v>3.5</v>
       </c>
       <c r="U112">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="V112">
         <v>1.6</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>5.15</v>
+        <v>6.35</v>
       </c>
       <c r="O113">
         <v>4.9</v>
@@ -19389,7 +19389,7 @@
         <v>3.1</v>
       </c>
       <c r="Q117">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="R117">
         <v>2.03</v>
@@ -19398,10 +19398,10 @@
         <v>1.42</v>
       </c>
       <c r="T117">
-        <v>2.58</v>
+        <v>2.9</v>
       </c>
       <c r="U117">
-        <v>2.76</v>
+        <v>3.11</v>
       </c>
       <c r="V117">
         <v>1.33</v>
@@ -19582,25 +19582,25 @@
         <v>5</v>
       </c>
       <c r="AA118">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB118">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC118">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AD118">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE118">
         <v>1.18</v>
       </c>
       <c r="AF118">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG118">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19718,13 +19718,13 @@
         <v>2.6</v>
       </c>
       <c r="R119">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="S119">
         <v>1.36</v>
       </c>
       <c r="T119">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="U119">
         <v>2.6</v>
@@ -19742,13 +19742,13 @@
         <v>1.22</v>
       </c>
       <c r="Z119">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AA119">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB119">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AC119">
         <v>2.96</v>
@@ -19884,7 +19884,7 @@
         <v>2.24</v>
       </c>
       <c r="S120">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T120">
         <v>3.5</v>
@@ -20038,7 +20038,7 @@
         <v>3.5</v>
       </c>
       <c r="P121">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q121">
         <v>3.31</v>
@@ -20231,7 +20231,7 @@
         <v>1.16</v>
       </c>
       <c r="Z122">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA122">
         <v>1.6</v>
@@ -20240,19 +20240,19 @@
         <v>2.3</v>
       </c>
       <c r="AC122">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AD122">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE122">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF122">
         <v>1.67</v>
       </c>
       <c r="AG122">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK122">
         <v>2.2</v>
@@ -20358,19 +20358,19 @@
         </is>
       </c>
       <c r="N123">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O123">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P123">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q123">
         <v>3.5</v>
       </c>
       <c r="R123">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="S123">
         <v>1.25</v>
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="N128">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="O128">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="P128">
         <v>2.55</v>
@@ -21230,7 +21230,7 @@
         <v>1.77</v>
       </c>
       <c r="AG128">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21351,10 +21351,10 @@
         <v>2.79</v>
       </c>
       <c r="S129">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T129">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="U129">
         <v>1.87</v>
@@ -21375,10 +21375,10 @@
         <v>6.4</v>
       </c>
       <c r="AA129">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB129">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AC129">
         <v>1.81</v>
@@ -21390,10 +21390,10 @@
         <v>1.35</v>
       </c>
       <c r="AF129">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG129">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>1.06</v>
       </c>
       <c r="AK129">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21668,7 +21668,7 @@
         <v>3.7</v>
       </c>
       <c r="P131">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q131">
         <v>2.2</v>
@@ -21677,10 +21677,10 @@
         <v>2.3</v>
       </c>
       <c r="S131">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="T131">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U131">
         <v>2.5</v>
@@ -21701,7 +21701,7 @@
         <v>4.15</v>
       </c>
       <c r="AA131">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB131">
         <v>2.15</v>
@@ -21834,16 +21834,16 @@
         <v>13</v>
       </c>
       <c r="Q132">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R132">
         <v>3.3</v>
       </c>
       <c r="S132">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T132">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="U132">
         <v>2.01</v>
@@ -21861,7 +21861,7 @@
         <v>1.06</v>
       </c>
       <c r="Z132">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA132">
         <v>1.33</v>
@@ -21870,19 +21870,19 @@
         <v>3</v>
       </c>
       <c r="AC132">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD132">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE132">
         <v>1.32</v>
       </c>
       <c r="AF132">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AG132">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>1.01</v>
       </c>
       <c r="AK132">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -22000,19 +22000,19 @@
         <v>2.25</v>
       </c>
       <c r="R133">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S133">
         <v>1.36</v>
       </c>
       <c r="T133">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="U133">
         <v>2.79</v>
       </c>
       <c r="V133">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W133">
         <v>1.08</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AA136">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB136">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC136">
         <v>0</v>
@@ -22649,16 +22649,16 @@
         <v>1.75</v>
       </c>
       <c r="Q137">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R137">
         <v>2.3</v>
       </c>
       <c r="S137">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U137">
         <v>2.4</v>
@@ -22676,7 +22676,7 @@
         <v>1.18</v>
       </c>
       <c r="Z137">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA137">
         <v>1.66</v>
@@ -22691,13 +22691,13 @@
         <v>1.41</v>
       </c>
       <c r="AE137">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF137">
         <v>1.58</v>
       </c>
       <c r="AG137">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AK137">
         <v>1.21</v>
@@ -22812,7 +22812,7 @@
         <v>3.05</v>
       </c>
       <c r="Q138">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="R138">
         <v>2.1</v>
@@ -22966,16 +22966,16 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O139">
         <v>3.8</v>
       </c>
       <c r="P139">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q139">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R139">
         <v>2.38</v>
@@ -23304,7 +23304,7 @@
         <v>3.88</v>
       </c>
       <c r="R141">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S141">
         <v>1.29</v>
@@ -23455,19 +23455,19 @@
         </is>
       </c>
       <c r="N142">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="O142">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="P142">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q142">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="R142">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S142">
         <v>1.25</v>
@@ -23476,13 +23476,13 @@
         <v>3.5</v>
       </c>
       <c r="U142">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="V142">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W142">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X142">
         <v>1.01</v>
@@ -23497,22 +23497,22 @@
         <v>1.57</v>
       </c>
       <c r="AB142">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AC142">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD142">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE142">
         <v>1.18</v>
       </c>
       <c r="AF142">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG142">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
@@ -23525,10 +23525,10 @@
         </is>
       </c>
       <c r="AJ142">
-        <v>1.13</v>
+        <v>2.36</v>
       </c>
       <c r="AK142">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL142">
         <v>0</v>
@@ -23784,7 +23784,7 @@
         <v>2.29</v>
       </c>
       <c r="O144">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="P144">
         <v>2.94</v>
@@ -24119,7 +24119,7 @@
         <v>2.33</v>
       </c>
       <c r="R146">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="S146">
         <v>1.22</v>
@@ -24931,7 +24931,7 @@
         <v>0</v>
       </c>
       <c r="Q151">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R151">
         <v>2.78</v>
@@ -24976,10 +24976,10 @@
         <v>1.35</v>
       </c>
       <c r="AF151">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG151">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
@@ -25248,10 +25248,10 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="O153">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="P153">
         <v>3.15</v>
@@ -25595,7 +25595,7 @@
         <v>3.84</v>
       </c>
       <c r="U155">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="V155">
         <v>1.78</v>
@@ -26081,7 +26081,7 @@
         <v>1.13</v>
       </c>
       <c r="T158">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U158">
         <v>1.85</v>
@@ -26117,7 +26117,7 @@
         <v>1.29</v>
       </c>
       <c r="AF158">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG158">
         <v>1.41</v>
@@ -26398,13 +26398,13 @@
         <v>6.1</v>
       </c>
       <c r="Q160">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R160">
         <v>2.5</v>
       </c>
       <c r="S160">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T160">
         <v>3.6</v>
@@ -26413,7 +26413,7 @@
         <v>2.15</v>
       </c>
       <c r="V160">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W160">
         <v>1.14</v>
@@ -26437,7 +26437,7 @@
         <v>2.33</v>
       </c>
       <c r="AD160">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE160">
         <v>1.19</v>
@@ -26446,7 +26446,7 @@
         <v>1.7</v>
       </c>
       <c r="AG160">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AH160" t="inlineStr">
         <is>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AK160">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -27095,7 +27095,7 @@
         <v>1.1</v>
       </c>
       <c r="AF164">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG164">
         <v>2.2</v>
@@ -28345,31 +28345,31 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="O172">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P172">
         <v>2.1</v>
       </c>
       <c r="Q172">
-        <v>3.07</v>
+        <v>3.11</v>
       </c>
       <c r="R172">
         <v>2.25</v>
       </c>
       <c r="S172">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T172">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="U172">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="V172">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W172">
         <v>1.1</v>
@@ -28390,10 +28390,10 @@
         <v>2.29</v>
       </c>
       <c r="AC172">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD172">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE172">
         <v>1.16</v>
@@ -28415,7 +28415,7 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK172">
         <v>1.37</v>
@@ -28852,7 +28852,7 @@
         <v>1.36</v>
       </c>
       <c r="T175">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U175">
         <v>2.88</v>
@@ -29504,7 +29504,7 @@
         <v>1.22</v>
       </c>
       <c r="T179">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U179">
         <v>2.13</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="O181">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="P181">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q181">
-        <v>8.85</v>
+        <v>4.38</v>
       </c>
       <c r="R181">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="S181">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T181">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="U181">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="V181">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="W181">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X181">
         <v>1.01</v>
       </c>
       <c r="Y181">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z181">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA181">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AB181">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AC181">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="AD181">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AE181">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AF181">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AG181">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>3.66</v>
+        <v>2.13</v>
       </c>
       <c r="AK181">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O182">
-        <v>3.63</v>
+        <v>6</v>
       </c>
       <c r="P182">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q182">
+        <v>8.85</v>
+      </c>
+      <c r="R182">
         <v>2.78</v>
       </c>
-      <c r="R182">
-        <v>2.4</v>
-      </c>
       <c r="S182">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="T182">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U182">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="V182">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W182">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X182">
         <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z182">
-        <v>4.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA182">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB182">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AC182">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="AD182">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AE182">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF182">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG182">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.25</v>
+        <v>3.66</v>
       </c>
       <c r="AK182">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,34 +30138,34 @@
         </is>
       </c>
       <c r="N183">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="O183">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="P183">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="Q183">
-        <v>4.38</v>
+        <v>2.78</v>
       </c>
       <c r="R183">
+        <v>2.4</v>
+      </c>
+      <c r="S183">
+        <v>1.24</v>
+      </c>
+      <c r="T183">
+        <v>3.6</v>
+      </c>
+      <c r="U183">
         <v>2.28</v>
       </c>
-      <c r="S183">
-        <v>1.25</v>
-      </c>
-      <c r="T183">
-        <v>3.4</v>
-      </c>
-      <c r="U183">
-        <v>2.27</v>
-      </c>
       <c r="V183">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W183">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X183">
         <v>1.01</v>
@@ -30174,28 +30174,28 @@
         <v>1.14</v>
       </c>
       <c r="Z183">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA183">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AB183">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC183">
-        <v>2.43</v>
+        <v>2.26</v>
       </c>
       <c r="AD183">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE183">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF183">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG183">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>2.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK183">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30630,10 +30630,10 @@
         <v>3.2</v>
       </c>
       <c r="O186">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P186">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
@@ -30666,7 +30666,7 @@
         <v>6.2</v>
       </c>
       <c r="AA186">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB186">
         <v>3.25</v>
@@ -30790,7 +30790,7 @@
         </is>
       </c>
       <c r="N187">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O187">
         <v>4.5</v>
@@ -30799,7 +30799,7 @@
         <v>1.39</v>
       </c>
       <c r="Q187">
-        <v>5.6</v>
+        <v>5.76</v>
       </c>
       <c r="R187">
         <v>2.44</v>
@@ -30808,13 +30808,13 @@
         <v>1.2</v>
       </c>
       <c r="T187">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="U187">
         <v>2.05</v>
       </c>
       <c r="V187">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W187">
         <v>1.18</v>
@@ -30829,16 +30829,16 @@
         <v>5.95</v>
       </c>
       <c r="AA187">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB187">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AC187">
         <v>2.02</v>
       </c>
       <c r="AD187">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AE187">
         <v>1.26</v>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
+        <v>1.11</v>
+      </c>
+      <c r="AK187">
         <v>1.13</v>
-      </c>
-      <c r="AK187">
-        <v>1.08</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="O188">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="P188">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="Q188">
         <v>2.8</v>
@@ -30998,19 +30998,19 @@
         <v>2</v>
       </c>
       <c r="AC188">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD188">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE188">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF188">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG188">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,7 +31023,7 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK188">
         <v>1.53</v>
@@ -31605,7 +31605,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.54</v>
+        <v>2.35</v>
       </c>
       <c r="O192">
         <v>3.7</v>
@@ -31768,7 +31768,7 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O193">
         <v>3.8</v>
@@ -31777,10 +31777,10 @@
         <v>2.52</v>
       </c>
       <c r="Q193">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="R193">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="S193">
         <v>1.2</v>
@@ -31934,7 +31934,7 @@
         <v>1.2</v>
       </c>
       <c r="O194">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="P194">
         <v>6.5</v>
@@ -32103,55 +32103,55 @@
         <v>0</v>
       </c>
       <c r="Q195">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S195">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T195">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="U195">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V195">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W195">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X195">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y195">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z195">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA195">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB195">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC195">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD195">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE195">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF195">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG195">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK195">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32266,55 +32266,55 @@
         <v>0</v>
       </c>
       <c r="Q196">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S196">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T196">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U196">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V196">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X196">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y196">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z196">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AA196">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB196">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AC196">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD196">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE196">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF196">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AG196">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK196">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -33253,7 +33253,7 @@
         <v>1.55</v>
       </c>
       <c r="T202">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="U202">
         <v>3.25</v>
@@ -33754,7 +33754,7 @@
         <v>1.09</v>
       </c>
       <c r="X205">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y205">
         <v>1.22</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="O212">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P212">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -35028,7 +35028,7 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O213">
         <v>3.15</v>
@@ -35055,7 +35055,7 @@
         <v>1.4</v>
       </c>
       <c r="W213">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X213">
         <v>1.03</v>
@@ -35212,7 +35212,7 @@
         <v>3.2</v>
       </c>
       <c r="U214">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V214">
         <v>1.44</v>
@@ -35360,7 +35360,7 @@
         <v>3.35</v>
       </c>
       <c r="P215">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q215">
         <v>2.9</v>
@@ -35517,7 +35517,7 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="O216">
         <v>3.5</v>
@@ -35562,7 +35562,7 @@
         <v>2.3</v>
       </c>
       <c r="AC216">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AD216">
         <v>1.53</v>
@@ -36181,7 +36181,7 @@
         <v>2.01</v>
       </c>
       <c r="R220">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S220">
         <v>1.28</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O221">
         <v>3.9</v>
       </c>
       <c r="P221">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q221">
         <v>6.1</v>
@@ -36353,7 +36353,7 @@
         <v>3.09</v>
       </c>
       <c r="U221">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="V221">
         <v>1.4</v>
@@ -36368,16 +36368,16 @@
         <v>1.25</v>
       </c>
       <c r="Z221">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA221">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AB221">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AC221">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD221">
         <v>1.3</v>
@@ -36504,19 +36504,19 @@
         <v>1.67</v>
       </c>
       <c r="Q222">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="R222">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S222">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T222">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="U222">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V222">
         <v>1.33</v>
@@ -36528,31 +36528,31 @@
         <v>1.04</v>
       </c>
       <c r="Y222">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z222">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA222">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AB222">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC222">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AD222">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE222">
         <v>1.03</v>
       </c>
       <c r="AF222">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AG222">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
@@ -36565,10 +36565,10 @@
         </is>
       </c>
       <c r="AJ222">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK222">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AL222">
         <v>0</v>
@@ -36984,64 +36984,64 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O225">
         <v>3.25</v>
       </c>
       <c r="P225">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="Q225">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="R225">
         <v>2.2</v>
       </c>
       <c r="S225">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T225">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="U225">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="V225">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W225">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X225">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y225">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z225">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AA225">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AB225">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC225">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD225">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE225">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF225">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AG225">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AH225" t="inlineStr">
         <is>
@@ -37054,10 +37054,10 @@
         </is>
       </c>
       <c r="AJ225">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK225">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL225">
         <v>0</v>
@@ -37156,10 +37156,10 @@
         <v>2.45</v>
       </c>
       <c r="Q226">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="R226">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S226">
         <v>1.4</v>
@@ -37168,10 +37168,10 @@
         <v>2.75</v>
       </c>
       <c r="U226">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="V226">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W226">
         <v>1.06</v>
@@ -37186,7 +37186,7 @@
         <v>2.83</v>
       </c>
       <c r="AA226">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB226">
         <v>1.64</v>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK226">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37527,7 +37527,7 @@
         <v>1.02</v>
       </c>
       <c r="AF228">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG228">
         <v>1.84</v>
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O229">
         <v>3.2</v>
       </c>
       <c r="P229">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q229">
         <v>2.4</v>
@@ -37799,19 +37799,19 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="O230">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="P230">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="Q230">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="R230">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="S230">
         <v>1.2</v>
@@ -37820,7 +37820,7 @@
         <v>4.6</v>
       </c>
       <c r="U230">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="V230">
         <v>1.73</v>
@@ -37832,7 +37832,7 @@
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z230">
         <v>7</v>
@@ -37844,7 +37844,7 @@
         <v>3</v>
       </c>
       <c r="AC230">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AD230">
         <v>1.87</v>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AK230">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37965,7 +37965,7 @@
         <v>1.46</v>
       </c>
       <c r="O231">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P231">
         <v>7.1</v>
@@ -38140,7 +38140,7 @@
         <v>2.19</v>
       </c>
       <c r="S232">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T232">
         <v>3.08</v>
@@ -38173,16 +38173,16 @@
         <v>2.65</v>
       </c>
       <c r="AD232">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE232">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF232">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG232">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AK232">
         <v>1.3</v>
@@ -38798,10 +38798,10 @@
         <v>2.79</v>
       </c>
       <c r="U236">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="V236">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W236">
         <v>1.05</v>
@@ -38850,7 +38850,7 @@
         <v>1.55</v>
       </c>
       <c r="AK236">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38946,13 +38946,13 @@
         <v>4.2</v>
       </c>
       <c r="P237">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q237">
         <v>4.47</v>
       </c>
       <c r="R237">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="S237">
         <v>1.22</v>
@@ -38988,7 +38988,7 @@
         <v>2.33</v>
       </c>
       <c r="AD237">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE237">
         <v>1.19</v>
@@ -39755,31 +39755,31 @@
         </is>
       </c>
       <c r="N242">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O242">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P242">
         <v>4.33</v>
       </c>
       <c r="Q242">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R242">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="S242">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T242">
         <v>3.4</v>
       </c>
       <c r="U242">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="V242">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W242">
         <v>1.1</v>
@@ -39791,13 +39791,13 @@
         <v>1.12</v>
       </c>
       <c r="Z242">
-        <v>4.7</v>
+        <v>4.54</v>
       </c>
       <c r="AA242">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB242">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="AC242">
         <v>2.4</v>
@@ -39806,7 +39806,7 @@
         <v>1.53</v>
       </c>
       <c r="AE242">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF242">
         <v>1.57</v>
@@ -39828,7 +39828,7 @@
         <v>1.22</v>
       </c>
       <c r="AK242">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL242">
         <v>0</v>
@@ -40081,13 +40081,13 @@
         </is>
       </c>
       <c r="N244">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O244">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P244">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q244">
         <v>0</v>
@@ -40120,10 +40120,10 @@
         <v>0</v>
       </c>
       <c r="AA244">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB244">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC244">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O245">
         <v>3.4</v>
       </c>
       <c r="P245">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q245">
         <v>3.15</v>
@@ -40317,7 +40317,7 @@
         <v>1.28</v>
       </c>
       <c r="AK245">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40570,22 +40570,22 @@
         </is>
       </c>
       <c r="N247">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O247">
         <v>3.8</v>
       </c>
       <c r="P247">
-        <v>3.95</v>
+        <v>3.52</v>
       </c>
       <c r="Q247">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="R247">
         <v>2.25</v>
       </c>
       <c r="S247">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T247">
         <v>3.25</v>
@@ -40615,13 +40615,13 @@
         <v>2.12</v>
       </c>
       <c r="AC247">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AD247">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE247">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF247">
         <v>1.65</v>
@@ -40640,7 +40640,7 @@
         </is>
       </c>
       <c r="AJ247">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK247">
         <v>1.93</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="O248">
         <v>3.3</v>
       </c>
       <c r="P248">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q248">
         <v>2.4</v>
@@ -40748,16 +40748,16 @@
         <v>2.15</v>
       </c>
       <c r="S248">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T248">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="U248">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V248">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W248">
         <v>1.08</v>
@@ -40775,7 +40775,7 @@
         <v>1.93</v>
       </c>
       <c r="AB248">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AC248">
         <v>3.28</v>
@@ -41059,13 +41059,13 @@
         </is>
       </c>
       <c r="N250">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="O250">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P250">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="Q250">
         <v>2.7</v>
@@ -41074,10 +41074,10 @@
         <v>2.1</v>
       </c>
       <c r="S250">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T250">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U250">
         <v>2.22</v>
@@ -41222,7 +41222,7 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="O251">
         <v>3.75</v>
@@ -41587,7 +41587,7 @@
         <v>2.65</v>
       </c>
       <c r="AA253">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB253">
         <v>1.59</v>
@@ -41723,7 +41723,7 @@
         <v>3.72</v>
       </c>
       <c r="R254">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S254">
         <v>1.34</v>
@@ -42529,7 +42529,7 @@
         <v>2.85</v>
       </c>
       <c r="O259">
-        <v>3.38</v>
+        <v>3.37</v>
       </c>
       <c r="P259">
         <v>2.33</v>
@@ -42565,7 +42565,7 @@
         <v>3.25</v>
       </c>
       <c r="AA259">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB259">
         <v>1.8</v>
@@ -42701,7 +42701,7 @@
         <v>3.1</v>
       </c>
       <c r="R260">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S260">
         <v>1.3</v>
@@ -42713,10 +42713,10 @@
         <v>2.44</v>
       </c>
       <c r="V260">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W260">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X260">
         <v>1</v>
@@ -42728,7 +42728,7 @@
         <v>3</v>
       </c>
       <c r="AA260">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AB260">
         <v>2.02</v>
@@ -42894,7 +42894,7 @@
         <v>2.22</v>
       </c>
       <c r="AB261">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AC261">
         <v>4.1</v>
@@ -43021,13 +43021,13 @@
         <v>4.3</v>
       </c>
       <c r="P262">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q262">
         <v>1.99</v>
       </c>
       <c r="R262">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S262">
         <v>1.29</v>
@@ -43054,7 +43054,7 @@
         <v>4.47</v>
       </c>
       <c r="AA262">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB262">
         <v>2.22</v>
@@ -43356,19 +43356,19 @@
         <v>2.15</v>
       </c>
       <c r="S264">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T264">
         <v>2.97</v>
       </c>
       <c r="U264">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V264">
         <v>1.39</v>
       </c>
       <c r="W264">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X264">
         <v>1.03</v>
@@ -43386,7 +43386,7 @@
         <v>1.85</v>
       </c>
       <c r="AC264">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD264">
         <v>1.27</v>
@@ -43676,10 +43676,10 @@
         <v>4.87</v>
       </c>
       <c r="Q266">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="R266">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="S266">
         <v>1.44</v>
@@ -43688,7 +43688,7 @@
         <v>2.7</v>
       </c>
       <c r="U266">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="V266">
         <v>1.32</v>
@@ -43697,13 +43697,13 @@
         <v>1.04</v>
       </c>
       <c r="X266">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y266">
         <v>1.38</v>
       </c>
       <c r="Z266">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="AA266">
         <v>2.19</v>
@@ -43712,19 +43712,19 @@
         <v>1.65</v>
       </c>
       <c r="AC266">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD266">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE266">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF266">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AG266">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AH266" t="inlineStr">
         <is>
@@ -43740,7 +43740,7 @@
         <v>1.21</v>
       </c>
       <c r="AK266">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL266">
         <v>0</v>
@@ -44319,10 +44319,10 @@
         </is>
       </c>
       <c r="N270">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="O270">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P270">
         <v>12</v>
@@ -44482,52 +44482,52 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O271">
         <v>2.85</v>
       </c>
       <c r="P271">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q271">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="R271">
         <v>2.1</v>
       </c>
       <c r="S271">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="T271">
-        <v>3.34</v>
+        <v>2.63</v>
       </c>
       <c r="U271">
-        <v>2.43</v>
+        <v>3.14</v>
       </c>
       <c r="V271">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="W271">
         <v>1.02</v>
       </c>
       <c r="X271">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y271">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Z271">
-        <v>3.39</v>
+        <v>2.45</v>
       </c>
       <c r="AA271">
-        <v>1.92</v>
+        <v>2.57</v>
       </c>
       <c r="AB271">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AC271">
-        <v>3.57</v>
+        <v>4.7</v>
       </c>
       <c r="AD271">
         <v>1.23</v>
@@ -44536,10 +44536,10 @@
         <v>0</v>
       </c>
       <c r="AF271">
-        <v>1.73</v>
+        <v>2.01</v>
       </c>
       <c r="AG271">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44645,7 +44645,7 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="O272">
         <v>3.1</v>
@@ -44811,7 +44811,7 @@
         <v>1.44</v>
       </c>
       <c r="O273">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P273">
         <v>6.08</v>
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,64 +44971,64 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="O274">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="P274">
-        <v>7.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q274">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="R274">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="S274">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T274">
-        <v>5.2</v>
+        <v>3.98</v>
       </c>
       <c r="U274">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V274">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="W274">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X274">
         <v>1.01</v>
       </c>
       <c r="Y274">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z274">
-        <v>6.65</v>
+        <v>6.05</v>
       </c>
       <c r="AA274">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB274">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AC274">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD274">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AE274">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF274">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG274">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45041,10 +45041,10 @@
         </is>
       </c>
       <c r="AJ274">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK274">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,64 +45134,64 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="O275">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="P275">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q275">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="R275">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="S275">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T275">
-        <v>3.98</v>
+        <v>5.2</v>
       </c>
       <c r="U275">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="V275">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="W275">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="X275">
         <v>1.01</v>
       </c>
       <c r="Y275">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z275">
-        <v>6.05</v>
+        <v>6.65</v>
       </c>
       <c r="AA275">
+        <v>1.3</v>
+      </c>
+      <c r="AB275">
+        <v>3.4</v>
+      </c>
+      <c r="AC275">
+        <v>1.87</v>
+      </c>
+      <c r="AD275">
+        <v>1.88</v>
+      </c>
+      <c r="AE275">
         <v>1.36</v>
       </c>
-      <c r="AB275">
-        <v>3</v>
-      </c>
-      <c r="AC275">
-        <v>1.88</v>
-      </c>
-      <c r="AD275">
-        <v>1.79</v>
-      </c>
-      <c r="AE275">
-        <v>1.31</v>
-      </c>
       <c r="AF275">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG275">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="AH275" t="inlineStr">
         <is>
@@ -45204,10 +45204,10 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK275">
-        <v>2.3</v>
+        <v>3.24</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45653,7 +45653,7 @@
         <v>1.03</v>
       </c>
       <c r="X278">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Y278">
         <v>1.7</v>
@@ -45677,7 +45677,7 @@
         <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="AG278">
         <v>1.45</v>
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O279">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P279">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q279">
         <v>2.96</v>
@@ -45807,7 +45807,7 @@
         <v>2.5</v>
       </c>
       <c r="U279">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V279">
         <v>1.25</v>
@@ -45822,7 +45822,7 @@
         <v>1.46</v>
       </c>
       <c r="Z279">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="AA279">
         <v>2.5</v>
@@ -45952,7 +45952,7 @@
         <v>1.67</v>
       </c>
       <c r="O280">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P280">
         <v>4.5</v>
@@ -46438,7 +46438,7 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O283">
         <v>3.52</v>
@@ -46456,7 +46456,7 @@
         <v>1.33</v>
       </c>
       <c r="T283">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U283">
         <v>2.5</v>
@@ -46480,7 +46480,7 @@
         <v>1.83</v>
       </c>
       <c r="AB283">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC283">
         <v>2.88</v>
@@ -46495,7 +46495,7 @@
         <v>1.63</v>
       </c>
       <c r="AG283">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH283" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>1.44</v>
       </c>
       <c r="AB284">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC284">
         <v>2.02</v>
@@ -46770,7 +46770,7 @@
         <v>3.5</v>
       </c>
       <c r="P285">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q285">
         <v>2.17</v>
@@ -46945,7 +46945,7 @@
         <v>1.5</v>
       </c>
       <c r="T286">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="U286">
         <v>3.26</v>
@@ -47262,19 +47262,19 @@
         <v>11</v>
       </c>
       <c r="Q288">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="R288">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="S288">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T288">
         <v>4.33</v>
       </c>
       <c r="U288">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="V288">
         <v>1.76</v>
@@ -47289,7 +47289,7 @@
         <v>1.08</v>
       </c>
       <c r="Z288">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA288">
         <v>1.38</v>
@@ -47298,19 +47298,19 @@
         <v>2.76</v>
       </c>
       <c r="AC288">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD288">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE288">
         <v>1.31</v>
       </c>
       <c r="AF288">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG288">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH288" t="inlineStr">
         <is>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK288">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="O289">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P289">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="Q289">
         <v>3.87</v>
@@ -47431,7 +47431,7 @@
         <v>1.89</v>
       </c>
       <c r="S289">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T289">
         <v>2.45</v>
@@ -47449,7 +47449,7 @@
         <v>1.05</v>
       </c>
       <c r="Y289">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Z289">
         <v>2.52</v>
@@ -47470,7 +47470,7 @@
         <v>1.03</v>
       </c>
       <c r="AF289">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG289">
         <v>1.73</v>
@@ -47486,10 +47486,10 @@
         </is>
       </c>
       <c r="AJ289">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AK289">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL289">
         <v>0</v>
@@ -47579,19 +47579,19 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O290">
         <v>3.65</v>
       </c>
       <c r="P290">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q290">
         <v>2.15</v>
       </c>
       <c r="R290">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S290">
         <v>1.35</v>
@@ -47600,10 +47600,10 @@
         <v>3</v>
       </c>
       <c r="U290">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="V290">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W290">
         <v>1.04</v>
@@ -47612,7 +47612,7 @@
         <v>1.01</v>
       </c>
       <c r="Y290">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z290">
         <v>3.28</v>
@@ -47627,7 +47627,7 @@
         <v>3.17</v>
       </c>
       <c r="AD290">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE290">
         <v>1.07</v>
@@ -47745,10 +47745,10 @@
         <v>2.1</v>
       </c>
       <c r="O291">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P291">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="Q291">
         <v>2.6</v>
@@ -47757,13 +47757,13 @@
         <v>1.91</v>
       </c>
       <c r="S291">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T291">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="U291">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="V291">
         <v>1.28</v>
@@ -47947,7 +47947,7 @@
         <v>1.25</v>
       </c>
       <c r="AB292">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC292">
         <v>1.64</v>
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="O295">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P295">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Q295">
         <v>4.94</v>
@@ -48415,10 +48415,10 @@
         <v>2.63</v>
       </c>
       <c r="U295">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="V295">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W295">
         <v>1.05</v>
@@ -48427,31 +48427,31 @@
         <v>1.1</v>
       </c>
       <c r="Y295">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z295">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AA295">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AB295">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC295">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD295">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE295">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF295">
         <v>2.1</v>
       </c>
       <c r="AG295">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AH295" t="inlineStr">
         <is>
@@ -48464,7 +48464,7 @@
         </is>
       </c>
       <c r="AJ295">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK295">
         <v>1.01</v>
@@ -48560,61 +48560,61 @@
         <v>1.45</v>
       </c>
       <c r="O296">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P296">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q296">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R296">
+        <v>2.14</v>
+      </c>
+      <c r="S296">
+        <v>1.36</v>
+      </c>
+      <c r="T296">
+        <v>2.61</v>
+      </c>
+      <c r="U296">
+        <v>2.83</v>
+      </c>
+      <c r="V296">
+        <v>1.33</v>
+      </c>
+      <c r="W296">
+        <v>1.08</v>
+      </c>
+      <c r="X296">
+        <v>1.02</v>
+      </c>
+      <c r="Y296">
+        <v>1.29</v>
+      </c>
+      <c r="Z296">
+        <v>3.04</v>
+      </c>
+      <c r="AA296">
         <v>2.1</v>
       </c>
-      <c r="S296">
-        <v>1.43</v>
-      </c>
-      <c r="T296">
-        <v>2.6</v>
-      </c>
-      <c r="U296">
-        <v>2.9</v>
-      </c>
-      <c r="V296">
-        <v>1.35</v>
-      </c>
-      <c r="W296">
-        <v>1.05</v>
-      </c>
-      <c r="X296">
-        <v>1.04</v>
-      </c>
-      <c r="Y296">
-        <v>1.34</v>
-      </c>
-      <c r="Z296">
-        <v>2.9</v>
-      </c>
-      <c r="AA296">
-        <v>2.06</v>
-      </c>
       <c r="AB296">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC296">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD296">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE296">
         <v>1.06</v>
       </c>
       <c r="AF296">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AG296">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK296">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -49445,7 +49445,7 @@
         <v>1.25</v>
       </c>
       <c r="AK301">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL301">
         <v>0</v>
@@ -49535,13 +49535,13 @@
         </is>
       </c>
       <c r="N302">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O302">
         <v>3.1</v>
       </c>
       <c r="P302">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q302">
         <v>2.46</v>
@@ -49556,7 +49556,7 @@
         <v>2.39</v>
       </c>
       <c r="U302">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V302">
         <v>1.25</v>
@@ -49873,7 +49873,7 @@
         <v>2.8</v>
       </c>
       <c r="R304">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S304">
         <v>1.25</v>
@@ -49888,7 +49888,7 @@
         <v>1.6</v>
       </c>
       <c r="W304">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X304">
         <v>1.02</v>
@@ -49903,7 +49903,7 @@
         <v>1.43</v>
       </c>
       <c r="AB304">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AC304">
         <v>1.99</v>
@@ -49915,7 +49915,7 @@
         <v>1.14</v>
       </c>
       <c r="AF304">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG304">
         <v>2.45</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O305">
         <v>4.05</v>
       </c>
       <c r="P305">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="Q305">
         <v>2.45</v>
@@ -50190,10 +50190,10 @@
         <v>2.6</v>
       </c>
       <c r="O306">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P306">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q306">
         <v>3.25</v>
@@ -50220,13 +50220,13 @@
         <v>1.02</v>
       </c>
       <c r="Y306">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z306">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA306">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB306">
         <v>1.64</v>
@@ -50260,7 +50260,7 @@
         <v>1.33</v>
       </c>
       <c r="AK306">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL306">
         <v>0</v>
@@ -50519,7 +50519,7 @@
         <v>3.7</v>
       </c>
       <c r="P308">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q308">
         <v>3.68</v>
@@ -50567,7 +50567,7 @@
         <v>1.12</v>
       </c>
       <c r="AF308">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG308">
         <v>2.3</v>
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O309">
         <v>2.75</v>
       </c>
       <c r="P309">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q309">
         <v>2.98</v>
@@ -50718,7 +50718,7 @@
         <v>2.7</v>
       </c>
       <c r="AB309">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC309">
         <v>5.55</v>
@@ -50860,7 +50860,7 @@
         <v>2.9</v>
       </c>
       <c r="U310">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="V310">
         <v>1.39</v>
@@ -51174,55 +51174,55 @@
         <v>0</v>
       </c>
       <c r="Q312">
-        <v>7.55</v>
+        <v>7.26</v>
       </c>
       <c r="R312">
+        <v>2.3</v>
+      </c>
+      <c r="S312">
+        <v>1.25</v>
+      </c>
+      <c r="T312">
+        <v>3.6</v>
+      </c>
+      <c r="U312">
         <v>2.38</v>
       </c>
-      <c r="S312">
-        <v>1.24</v>
-      </c>
-      <c r="T312">
-        <v>3.8</v>
-      </c>
-      <c r="U312">
-        <v>2.35</v>
-      </c>
       <c r="V312">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W312">
         <v>1.12</v>
       </c>
       <c r="X312">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y312">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z312">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA312">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB312">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AC312">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AD312">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE312">
         <v>1.14</v>
       </c>
       <c r="AF312">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG312">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AH312" t="inlineStr">
         <is>
@@ -51235,10 +51235,10 @@
         </is>
       </c>
       <c r="AJ312">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK312">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51367,19 +51367,19 @@
         <v>6.5</v>
       </c>
       <c r="AA313">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB313">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AC313">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD313">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AE313">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF313">
         <v>1.36</v>
@@ -51398,10 +51398,10 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK313">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AL313">
         <v>0</v>

--- a/jogos_2026-10-18.xlsx
+++ b/jogos_2026-10-18.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>1.93</v>
+      </c>
+      <c r="O4">
+        <v>3.33</v>
+      </c>
+      <c r="P4">
+        <v>3.23</v>
+      </c>
+      <c r="Q4">
+        <v>2.5</v>
+      </c>
+      <c r="R4">
+        <v>2.2</v>
+      </c>
+      <c r="S4">
+        <v>1.35</v>
+      </c>
+      <c r="T4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>2.67</v>
+      </c>
+      <c r="V4">
         <v>1.4</v>
       </c>
-      <c r="O4">
-        <v>4.6</v>
-      </c>
-      <c r="P4">
-        <v>6.7</v>
-      </c>
-      <c r="Q4">
-        <v>1.75</v>
-      </c>
-      <c r="R4">
-        <v>2.34</v>
-      </c>
-      <c r="S4">
-        <v>1.22</v>
-      </c>
-      <c r="T4">
-        <v>3.8</v>
-      </c>
-      <c r="U4">
-        <v>2.25</v>
-      </c>
-      <c r="V4">
-        <v>1.57</v>
-      </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z4">
-        <v>4.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC4">
-        <v>2.33</v>
+        <v>3.14</v>
       </c>
       <c r="AD4">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>2.81</v>
+        <v>1.81</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,58 +1124,58 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>3.33</v>
+        <v>4.6</v>
       </c>
       <c r="P5">
-        <v>3.23</v>
+        <v>6.7</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U5">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="Z5">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AB5">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AC5">
-        <v>3.08</v>
+        <v>2.33</v>
       </c>
       <c r="AD5">
-        <v>1.28</v>
+        <v>1.56</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>1.87</v>
+        <v>2.81</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>4.6</v>
+        <v>3.83</v>
       </c>
       <c r="P6">
-        <v>7.02</v>
+        <v>4.15</v>
       </c>
       <c r="Q6">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
         <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="AA6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AC6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD6">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.66</v>
+        <v>1.97</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="O7">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>4.15</v>
+        <v>7.02</v>
       </c>
       <c r="Q7">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U7">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
+        <v>1.15</v>
+      </c>
+      <c r="Z7">
+        <v>4.5</v>
+      </c>
+      <c r="AA7">
+        <v>1.64</v>
+      </c>
+      <c r="AB7">
+        <v>2.23</v>
+      </c>
+      <c r="AC7">
+        <v>2.6</v>
+      </c>
+      <c r="AD7">
+        <v>1.46</v>
+      </c>
+      <c r="AE7">
         <v>1.17</v>
       </c>
-      <c r="Z7">
-        <v>3.96</v>
-      </c>
-      <c r="AA7">
-        <v>1.67</v>
-      </c>
-      <c r="AB7">
-        <v>2.14</v>
-      </c>
-      <c r="AC7">
-        <v>2.62</v>
-      </c>
-      <c r="AD7">
-        <v>1.38</v>
-      </c>
-      <c r="AE7">
-        <v>1.12</v>
-      </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK7">
-        <v>1.97</v>
+        <v>2.66</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>2.78</v>
       </c>
       <c r="Q8">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="R8">
         <v>2.04</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
         <v>3.1</v>
@@ -1954,19 +1954,19 @@
         <v>1.85</v>
       </c>
       <c r="S10">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="T10">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="U10">
         <v>3.25</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1.05</v>
@@ -1981,7 +1981,7 @@
         <v>2.29</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC10">
         <v>4.8</v>
@@ -1993,10 +1993,10 @@
         <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG10">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2111,10 +2111,10 @@
         <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.38</v>
@@ -2141,13 +2141,13 @@
         <v>3.47</v>
       </c>
       <c r="AA11">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
         <v>1.8</v>
       </c>
       <c r="AC11">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AD11">
         <v>1.31</v>
@@ -2175,7 +2175,7 @@
         <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2301,19 +2301,19 @@
         <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AA12">
         <v>1.61</v>
       </c>
       <c r="AB12">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AC12">
         <v>2.43</v>
       </c>
       <c r="AD12">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
         <v>1.15</v>
@@ -2772,7 +2772,7 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
         <v>2.4</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="Q19">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="R19">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="S19">
         <v>1.33</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="V19">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z19">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD19">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Albacete II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="Q20">
-        <v>2.81</v>
+        <v>2.35</v>
       </c>
       <c r="R20">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U20">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="V20">
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB20">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE20">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3747,10 +3747,10 @@
         <v>2.02</v>
       </c>
       <c r="S21">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T21">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="U21">
         <v>2.85</v>
@@ -3771,10 +3771,10 @@
         <v>3.16</v>
       </c>
       <c r="AA21">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB21">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC21">
         <v>3.34</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="AK21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4067,7 +4067,7 @@
         <v>2.28</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R23">
         <v>2.3</v>
@@ -4550,7 +4550,7 @@
         <v>2.48</v>
       </c>
       <c r="O26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P26">
         <v>2.38</v>
@@ -4565,10 +4565,10 @@
         <v>1.41</v>
       </c>
       <c r="T26">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="U26">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="V26">
         <v>1.34</v>
@@ -4592,19 +4592,19 @@
         <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>2.2</v>
       </c>
       <c r="O28">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
         <v>3</v>
@@ -5202,7 +5202,7 @@
         <v>3.64</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>1.87</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P31">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q31">
         <v>1.95</v>
@@ -5401,7 +5401,7 @@
         <v>3.03</v>
       </c>
       <c r="AA31">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB31">
         <v>1.71</v>
@@ -5534,7 +5534,7 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R32">
         <v>2.06</v>
@@ -5564,7 +5564,7 @@
         <v>2.88</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB32">
         <v>1.65</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P34">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="R34">
         <v>1.92</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
         <v>1.45</v>
@@ -6026,7 +6026,7 @@
         <v>3.3</v>
       </c>
       <c r="R35">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6346,7 +6346,7 @@
         <v>3.24</v>
       </c>
       <c r="P37">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>1.41</v>
       </c>
       <c r="T40">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
         <v>2.95</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Murcia II</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="Q41">
-        <v>3.07</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z41">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="AA41">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC41">
-        <v>3.76</v>
+        <v>3.08</v>
       </c>
       <c r="AD41">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG41">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>1.45</v>
+        <v>2.38</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Murcia II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>5.75</v>
+        <v>2.75</v>
       </c>
       <c r="Q42">
+        <v>3.04</v>
+      </c>
+      <c r="R42">
         <v>2</v>
       </c>
-      <c r="R42">
-        <v>2.25</v>
-      </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T42">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U42">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA42">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC42">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AD42">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE42">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG42">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7496,13 +7496,13 @@
         <v>2.06</v>
       </c>
       <c r="S44">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
         <v>3</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="V44">
         <v>1.44</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
         <v>1.53</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="O47">
         <v>4</v>
@@ -8136,10 +8136,10 @@
         <v>3.3</v>
       </c>
       <c r="O48">
-        <v>3.77</v>
+        <v>3.85</v>
       </c>
       <c r="P48">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q48">
         <v>3.9</v>
@@ -8320,7 +8320,7 @@
         <v>2.08</v>
       </c>
       <c r="V49">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W49">
         <v>1.2</v>
@@ -8474,49 +8474,49 @@
         <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U50">
         <v>2.63</v>
       </c>
       <c r="V50">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W50">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="AA50">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB50">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
         <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG50">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
         <v>2.3</v>
@@ -8625,13 +8625,13 @@
         <v>2.25</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Q51">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
         <v>2.04</v>
@@ -8791,7 +8791,7 @@
         <v>3.4</v>
       </c>
       <c r="P52">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="Q52">
         <v>3.12</v>
@@ -8951,16 +8951,16 @@
         <v>2.2</v>
       </c>
       <c r="O53">
+        <v>3</v>
+      </c>
+      <c r="P53">
         <v>2.95</v>
-      </c>
-      <c r="P53">
-        <v>3.1</v>
       </c>
       <c r="Q53">
         <v>2.88</v>
       </c>
       <c r="R53">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="S53">
         <v>1.44</v>
@@ -8981,10 +8981,10 @@
         <v>1.05</v>
       </c>
       <c r="Y53">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z53">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA53">
         <v>2.27</v>
@@ -8993,10 +8993,10 @@
         <v>1.6</v>
       </c>
       <c r="AC53">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AD53">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE53">
         <v>1.03</v>
@@ -9005,7 +9005,7 @@
         <v>1.95</v>
       </c>
       <c r="AG53">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>9.5</v>
       </c>
       <c r="Q54">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R54">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="S54">
         <v>1.22</v>
@@ -9132,10 +9132,10 @@
         <v>3.75</v>
       </c>
       <c r="U54">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="V54">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W54">
         <v>1.14</v>
@@ -9144,31 +9144,31 @@
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>4.55</v>
+        <v>4.85</v>
       </c>
       <c r="AA54">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AB54">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC54">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="AD54">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE54">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF54">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AG54">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK54">
         <v>4.5</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -10605,7 +10605,7 @@
         <v>1.39</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X63">
         <v>1.03</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q64">
         <v>2.79</v>
@@ -10814,7 +10814,7 @@
         <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,25 +10913,25 @@
         <v>2.79</v>
       </c>
       <c r="Q65">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U65">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11242,7 +11242,7 @@
         <v>1.82</v>
       </c>
       <c r="R67">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="S67">
         <v>1.32</v>
@@ -11728,7 +11728,7 @@
         <v>2.25</v>
       </c>
       <c r="Q70">
-        <v>3.79</v>
+        <v>3.64</v>
       </c>
       <c r="R70">
         <v>1.99</v>
@@ -12537,10 +12537,10 @@
         <v>2.45</v>
       </c>
       <c r="O75">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P75">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q75">
         <v>3.05</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="O76">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="P76">
-        <v>2.72</v>
+        <v>2.52</v>
       </c>
       <c r="Q76">
         <v>2.5</v>
@@ -12712,13 +12712,13 @@
         <v>2.5</v>
       </c>
       <c r="S76">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
         <v>4</v>
       </c>
       <c r="U76">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="V76">
         <v>1.75</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O78">
         <v>3.6</v>
@@ -14327,31 +14327,31 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="O86">
         <v>3.15</v>
       </c>
       <c r="P86">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="Q86">
         <v>3.02</v>
       </c>
       <c r="R86">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="S86">
         <v>1.39</v>
       </c>
       <c r="T86">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="U86">
         <v>2.8</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W86">
         <v>1.05</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK86">
         <v>1.5</v>
@@ -14991,25 +14991,25 @@
         <v>2.69</v>
       </c>
       <c r="R90">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S90">
         <v>1.26</v>
       </c>
       <c r="T90">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="U90">
         <v>2.32</v>
       </c>
       <c r="V90">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W90">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
         <v>1.15</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O91">
         <v>3.75</v>
       </c>
       <c r="P91">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q91">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="R91">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S91">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="U91">
         <v>2.4</v>
       </c>
       <c r="V91">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W91">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X91">
         <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AA91">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AB91">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC91">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AD91">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE91">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF91">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>1.25</v>
       </c>
       <c r="AK91">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15308,7 +15308,7 @@
         <v>2.21</v>
       </c>
       <c r="O92">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
         <v>2.52</v>
@@ -15468,16 +15468,16 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O93">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q93">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R93">
         <v>2.25</v>
@@ -15501,22 +15501,22 @@
         <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AA93">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB93">
         <v>2.12</v>
       </c>
       <c r="AC93">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AD93">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE93">
         <v>1.13</v>
@@ -15836,7 +15836,7 @@
         <v>1.57</v>
       </c>
       <c r="AB95">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC95">
         <v>2.35</v>
@@ -15960,7 +15960,7 @@
         <v>3.7</v>
       </c>
       <c r="O96">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
         <v>1.85</v>
@@ -15969,7 +15969,7 @@
         <v>3.5</v>
       </c>
       <c r="R96">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S96">
         <v>1.23</v>
@@ -15978,7 +15978,7 @@
         <v>4</v>
       </c>
       <c r="U96">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V96">
         <v>1.6</v>
@@ -16005,7 +16005,7 @@
         <v>2.21</v>
       </c>
       <c r="AD96">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE96">
         <v>1.22</v>
@@ -16612,7 +16612,7 @@
         <v>1.95</v>
       </c>
       <c r="O100">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="P100">
         <v>3.4</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB100">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O104">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P104">
         <v>2.6</v>
@@ -17279,10 +17279,10 @@
         <v>1.36</v>
       </c>
       <c r="T104">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V104">
         <v>1.38</v>
@@ -17294,7 +17294,7 @@
         <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
         <v>2.97</v>
@@ -17306,10 +17306,10 @@
         <v>1.7</v>
       </c>
       <c r="AC104">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD104">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE104">
         <v>1.05</v>
@@ -17433,7 +17433,7 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="R105">
         <v>2.13</v>
@@ -17454,7 +17454,7 @@
         <v>1.07</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y105">
         <v>1.28</v>
@@ -17590,10 +17590,10 @@
         <v>1.75</v>
       </c>
       <c r="O106">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P106">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q106">
         <v>2.2</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O107">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P107">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="Q107">
         <v>3</v>
@@ -17765,13 +17765,13 @@
         <v>2.3</v>
       </c>
       <c r="S107">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T107">
         <v>3.6</v>
       </c>
       <c r="U107">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="V107">
         <v>1.59</v>
@@ -17801,7 +17801,7 @@
         <v>1.66</v>
       </c>
       <c r="AE107">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF107">
         <v>1.44</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="O112">
         <v>3.55</v>
       </c>
       <c r="P112">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="Q112">
         <v>2.5</v>
@@ -18586,7 +18586,7 @@
         <v>3.5</v>
       </c>
       <c r="U112">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="V112">
         <v>1.6</v>
@@ -18610,7 +18610,7 @@
         <v>2.26</v>
       </c>
       <c r="AC112">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AD112">
         <v>1.55</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>6.35</v>
+        <v>5.15</v>
       </c>
       <c r="O113">
         <v>4.9</v>
       </c>
       <c r="P113">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Q113">
         <v>5.5</v>
@@ -19223,7 +19223,7 @@
         <v>3.3</v>
       </c>
       <c r="P116">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q116">
         <v>3.2</v>
@@ -19389,10 +19389,10 @@
         <v>3.1</v>
       </c>
       <c r="Q117">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="R117">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S117">
         <v>1.42</v>
@@ -19555,7 +19555,7 @@
         <v>1.91</v>
       </c>
       <c r="R118">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S118">
         <v>1.25</v>
@@ -19588,16 +19588,16 @@
         <v>2.29</v>
       </c>
       <c r="AC118">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AD118">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE118">
         <v>1.18</v>
       </c>
       <c r="AF118">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG118">
         <v>2.15</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK118">
         <v>2.38</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O119">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="P119">
-        <v>3.56</v>
+        <v>2.53</v>
       </c>
       <c r="Q119">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="R119">
+        <v>2.24</v>
+      </c>
+      <c r="S119">
+        <v>1.25</v>
+      </c>
+      <c r="T119">
+        <v>3.5</v>
+      </c>
+      <c r="U119">
+        <v>2.3</v>
+      </c>
+      <c r="V119">
+        <v>1.55</v>
+      </c>
+      <c r="W119">
+        <v>1.11</v>
+      </c>
+      <c r="X119">
+        <v>1.01</v>
+      </c>
+      <c r="Y119">
+        <v>1.17</v>
+      </c>
+      <c r="Z119">
+        <v>4.4</v>
+      </c>
+      <c r="AA119">
+        <v>1.72</v>
+      </c>
+      <c r="AB119">
         <v>2.32</v>
       </c>
-      <c r="S119">
-        <v>1.36</v>
-      </c>
-      <c r="T119">
-        <v>2.82</v>
-      </c>
-      <c r="U119">
-        <v>2.6</v>
-      </c>
-      <c r="V119">
-        <v>1.44</v>
-      </c>
-      <c r="W119">
-        <v>1.07</v>
-      </c>
-      <c r="X119">
-        <v>1.02</v>
-      </c>
-      <c r="Y119">
-        <v>1.22</v>
-      </c>
-      <c r="Z119">
-        <v>3.6</v>
-      </c>
-      <c r="AA119">
-        <v>1.78</v>
-      </c>
-      <c r="AB119">
-        <v>1.89</v>
-      </c>
       <c r="AC119">
-        <v>2.96</v>
+        <v>2.48</v>
       </c>
       <c r="AD119">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE119">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF119">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AG119">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK119">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O120">
+        <v>3.45</v>
+      </c>
+      <c r="P120">
         <v>3.56</v>
       </c>
-      <c r="P120">
-        <v>2.53</v>
-      </c>
       <c r="Q120">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="R120">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="S120">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="U120">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V120">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W120">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z120">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA120">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AB120">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="AC120">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="AD120">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AG120">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20038,7 +20038,7 @@
         <v>3.5</v>
       </c>
       <c r="P121">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q121">
         <v>3.31</v>
@@ -20234,10 +20234,10 @@
         <v>4.15</v>
       </c>
       <c r="AA122">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB122">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC122">
         <v>2.49</v>
@@ -20400,13 +20400,13 @@
         <v>1.67</v>
       </c>
       <c r="AB123">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AC123">
         <v>2.4</v>
       </c>
       <c r="AD123">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE123">
         <v>1.16</v>
@@ -20415,7 +20415,7 @@
         <v>1.53</v>
       </c>
       <c r="AG123">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>1.21</v>
       </c>
       <c r="AK123">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20856,7 +20856,7 @@
         <v>1.75</v>
       </c>
       <c r="Q126">
-        <v>4.52</v>
+        <v>3.9</v>
       </c>
       <c r="R126">
         <v>2.47</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="O127">
         <v>3.85</v>
@@ -21019,7 +21019,7 @@
         <v>1.52</v>
       </c>
       <c r="Q127">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="R127">
         <v>2.38</v>
@@ -21191,13 +21191,13 @@
         <v>1.43</v>
       </c>
       <c r="T128">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="U128">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="V128">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W128">
         <v>1.03</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="O138">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P138">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="Q138">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="R138">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S138">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T138">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="U138">
-        <v>2.89</v>
+        <v>2.51</v>
       </c>
       <c r="V138">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W138">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z138">
-        <v>3.4</v>
+        <v>4.03</v>
       </c>
       <c r="AA138">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="AB138">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AC138">
-        <v>3.32</v>
+        <v>2.76</v>
       </c>
       <c r="AD138">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF138">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG138">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK138">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,80 +22966,80 @@
         </is>
       </c>
       <c r="N139">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="O139">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P139">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q139">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="R139">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S139">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T139">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="U139">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="V139">
+        <v>1.36</v>
+      </c>
+      <c r="W139">
+        <v>1.08</v>
+      </c>
+      <c r="X139">
+        <v>1.01</v>
+      </c>
+      <c r="Y139">
+        <v>1.29</v>
+      </c>
+      <c r="Z139">
+        <v>3.4</v>
+      </c>
+      <c r="AA139">
+        <v>1.96</v>
+      </c>
+      <c r="AB139">
+        <v>1.79</v>
+      </c>
+      <c r="AC139">
+        <v>3.32</v>
+      </c>
+      <c r="AD139">
+        <v>1.27</v>
+      </c>
+      <c r="AE139">
+        <v>1.07</v>
+      </c>
+      <c r="AF139">
+        <v>1.72</v>
+      </c>
+      <c r="AG139">
+        <v>1.98</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>1.24</v>
+      </c>
+      <c r="AK139">
         <v>1.53</v>
-      </c>
-      <c r="W139">
-        <v>1.11</v>
-      </c>
-      <c r="X139">
-        <v>1</v>
-      </c>
-      <c r="Y139">
-        <v>1.18</v>
-      </c>
-      <c r="Z139">
-        <v>4.03</v>
-      </c>
-      <c r="AA139">
-        <v>1.7</v>
-      </c>
-      <c r="AB139">
-        <v>2.1</v>
-      </c>
-      <c r="AC139">
-        <v>2.76</v>
-      </c>
-      <c r="AD139">
-        <v>1.34</v>
-      </c>
-      <c r="AE139">
-        <v>1.13</v>
-      </c>
-      <c r="AF139">
-        <v>1.74</v>
-      </c>
-      <c r="AG139">
-        <v>1.93</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>1.09</v>
-      </c>
-      <c r="AK139">
-        <v>2.16</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23132,13 +23132,13 @@
         <v>1.33</v>
       </c>
       <c r="O140">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P140">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="Q140">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R140">
         <v>2.32</v>
@@ -23147,10 +23147,10 @@
         <v>1.3</v>
       </c>
       <c r="T140">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="U140">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V140">
         <v>1.51</v>
@@ -23174,10 +23174,10 @@
         <v>2.25</v>
       </c>
       <c r="AC140">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AD140">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE140">
         <v>1.17</v>
@@ -23292,7 +23292,7 @@
         </is>
       </c>
       <c r="N141">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O141">
         <v>3.65</v>
@@ -23304,7 +23304,7 @@
         <v>3.88</v>
       </c>
       <c r="R141">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S141">
         <v>1.29</v>
@@ -23482,7 +23482,7 @@
         <v>1.57</v>
       </c>
       <c r="W142">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X142">
         <v>1.01</v>
@@ -23805,7 +23805,7 @@
         <v>2.54</v>
       </c>
       <c r="V144">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W144">
         <v>1.08</v>
@@ -23817,10 +23817,10 @@
         <v>1.19</v>
       </c>
       <c r="Z144">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="AA144">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB144">
         <v>2.19</v>
@@ -25248,13 +25248,13 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O153">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P153">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q153">
         <v>3.44</v>
@@ -25266,22 +25266,22 @@
         <v>1.66</v>
       </c>
       <c r="T153">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W153">
         <v>0</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y153">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Z153">
         <v>1.91</v>
@@ -25293,19 +25293,19 @@
         <v>1.23</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AE153">
         <v>0</v>
       </c>
       <c r="AF153">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="AG153">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25414,10 +25414,10 @@
         <v>1.81</v>
       </c>
       <c r="O154">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P154">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q154">
         <v>2.3</v>
@@ -25583,13 +25583,13 @@
         <v>4.44</v>
       </c>
       <c r="Q155">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R155">
         <v>2.5</v>
       </c>
       <c r="S155">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T155">
         <v>3.84</v>
@@ -25737,7 +25737,7 @@
         </is>
       </c>
       <c r="N156">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O156">
         <v>3.1</v>
@@ -25761,7 +25761,7 @@
         <v>3.24</v>
       </c>
       <c r="V156">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W156">
         <v>1.05</v>
@@ -27041,10 +27041,10 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="O164">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P164">
         <v>2.57</v>
@@ -27222,7 +27222,7 @@
         <v>1.22</v>
       </c>
       <c r="T165">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U165">
         <v>2.15</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O172">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P172">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q172">
         <v>3.11</v>
@@ -28366,7 +28366,7 @@
         <v>3.6</v>
       </c>
       <c r="U172">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="V172">
         <v>1.53</v>
@@ -28508,7 +28508,7 @@
         </is>
       </c>
       <c r="N173">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O173">
         <v>3.82</v>
@@ -28526,7 +28526,7 @@
         <v>1.3</v>
       </c>
       <c r="T173">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U173">
         <v>2.3</v>
@@ -28840,10 +28840,10 @@
         <v>3.2</v>
       </c>
       <c r="P175">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="Q175">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="R175">
         <v>2</v>
@@ -28997,28 +28997,28 @@
         </is>
       </c>
       <c r="N176">
+        <v>2.17</v>
+      </c>
+      <c r="O176">
+        <v>3.15</v>
+      </c>
+      <c r="P176">
+        <v>3.4</v>
+      </c>
+      <c r="Q176">
+        <v>2.94</v>
+      </c>
+      <c r="R176">
         <v>2.13</v>
-      </c>
-      <c r="O176">
-        <v>3.2</v>
-      </c>
-      <c r="P176">
-        <v>3.6</v>
-      </c>
-      <c r="Q176">
-        <v>2.75</v>
-      </c>
-      <c r="R176">
-        <v>2.02</v>
       </c>
       <c r="S176">
         <v>1.47</v>
       </c>
       <c r="T176">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="U176">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="V176">
         <v>1.32</v>
@@ -29030,10 +29030,10 @@
         <v>1.02</v>
       </c>
       <c r="Y176">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z176">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA176">
         <v>2.3</v>
@@ -29051,7 +29051,7 @@
         <v>1.02</v>
       </c>
       <c r="AF176">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG176">
         <v>1.8</v>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK176">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O178">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P178">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q178">
         <v>3.52</v>
@@ -29513,7 +29513,7 @@
         <v>1.61</v>
       </c>
       <c r="W179">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X179">
         <v>1.02</v>
@@ -29559,7 +29559,7 @@
         <v>1.19</v>
       </c>
       <c r="AK179">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29655,7 +29655,7 @@
         <v>6</v>
       </c>
       <c r="P180">
-        <v>14.1</v>
+        <v>10</v>
       </c>
       <c r="Q180">
         <v>1.57</v>
@@ -29818,7 +29818,7 @@
         <v>3.9</v>
       </c>
       <c r="P181">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q181">
         <v>4.38</v>
@@ -29866,7 +29866,7 @@
         <v>1.14</v>
       </c>
       <c r="AF181">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG181">
         <v>2.16</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="O182">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="P182">
+        <v>2.45</v>
+      </c>
+      <c r="Q182">
+        <v>2.78</v>
+      </c>
+      <c r="R182">
+        <v>2.4</v>
+      </c>
+      <c r="S182">
         <v>1.24</v>
       </c>
-      <c r="Q182">
-        <v>8.85</v>
-      </c>
-      <c r="R182">
-        <v>2.78</v>
-      </c>
-      <c r="S182">
-        <v>1.16</v>
-      </c>
       <c r="T182">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="U182">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="V182">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="W182">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X182">
         <v>1.01</v>
       </c>
       <c r="Y182">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z182">
-        <v>6.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA182">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB182">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AC182">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="AD182">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AE182">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AF182">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="AG182">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>3.66</v>
+        <v>1.25</v>
       </c>
       <c r="AK182">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O183">
-        <v>3.63</v>
+        <v>5.75</v>
       </c>
       <c r="P183">
-        <v>2.45</v>
+        <v>1.24</v>
       </c>
       <c r="Q183">
+        <v>8.85</v>
+      </c>
+      <c r="R183">
         <v>2.78</v>
       </c>
-      <c r="R183">
-        <v>2.4</v>
-      </c>
       <c r="S183">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="T183">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U183">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="V183">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W183">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X183">
         <v>1.01</v>
       </c>
       <c r="Y183">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z183">
-        <v>4.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA183">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB183">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AC183">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AD183">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AE183">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF183">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="AG183">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.25</v>
+        <v>3.66</v>
       </c>
       <c r="AK183">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O186">
         <v>3.95</v>
       </c>
       <c r="P186">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="Q186">
         <v>3.6</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O188">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="P188">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q188">
         <v>2.8</v>
@@ -31023,7 +31023,7 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK188">
         <v>1.53</v>
@@ -31119,10 +31119,10 @@
         <v>1.54</v>
       </c>
       <c r="O189">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P189">
-        <v>5.31</v>
+        <v>5</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31442,16 +31442,16 @@
         </is>
       </c>
       <c r="N191">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="O191">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="P191">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="Q191">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="R191">
         <v>1.97</v>
@@ -31460,7 +31460,7 @@
         <v>1.4</v>
       </c>
       <c r="T191">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U191">
         <v>2.9</v>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK191">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31617,7 +31617,7 @@
         <v>2.83</v>
       </c>
       <c r="R192">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="S192">
         <v>1.26</v>
@@ -31774,10 +31774,10 @@
         <v>3.8</v>
       </c>
       <c r="P193">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="Q193">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="R193">
         <v>2.43</v>
@@ -31943,13 +31943,13 @@
         <v>1.65</v>
       </c>
       <c r="R194">
-        <v>2.79</v>
+        <v>3.08</v>
       </c>
       <c r="S194">
         <v>1.14</v>
       </c>
       <c r="T194">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="U194">
         <v>1.91</v>
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R195">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T195">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U195">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V195">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W195">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X195">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z195">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC195">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD195">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE195">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF195">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG195">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK195">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T196">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U196">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V196">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W196">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y196">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z196">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC196">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD196">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE196">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF196">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG196">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK196">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>CD Don Benito</t>
+          <t>CD Badajoz</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,19 +32420,19 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="O197">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P197">
-        <v>3.67</v>
+        <v>4.75</v>
       </c>
       <c r="Q197">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="R197">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S197">
         <v>1.4</v>
@@ -32447,37 +32447,37 @@
         <v>1.33</v>
       </c>
       <c r="W197">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z197">
         <v>2.88</v>
       </c>
       <c r="AA197">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AB197">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AC197">
-        <v>3.86</v>
+        <v>3.48</v>
       </c>
       <c r="AD197">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE197">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF197">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG197">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK197">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CD Badajoz</t>
+          <t>CD Don Benito</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,19 +32583,19 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="O198">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P198">
-        <v>4.76</v>
+        <v>3.67</v>
       </c>
       <c r="Q198">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="R198">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S198">
         <v>1.4</v>
@@ -32610,53 +32610,53 @@
         <v>1.33</v>
       </c>
       <c r="W198">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X198">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y198">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="Z198">
         <v>2.88</v>
       </c>
       <c r="AA198">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB198">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AC198">
-        <v>3.48</v>
+        <v>3.86</v>
       </c>
       <c r="AD198">
+        <v>1.18</v>
+      </c>
+      <c r="AE198">
+        <v>1.04</v>
+      </c>
+      <c r="AF198">
+        <v>1.88</v>
+      </c>
+      <c r="AG198">
+        <v>1.81</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ198">
         <v>1.22</v>
       </c>
-      <c r="AE198">
-        <v>1.05</v>
-      </c>
-      <c r="AF198">
-        <v>2</v>
-      </c>
-      <c r="AG198">
-        <v>1.75</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ198">
-        <v>1.14</v>
-      </c>
       <c r="AK198">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32746,19 +32746,19 @@
         </is>
       </c>
       <c r="N199">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O199">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P199">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q199">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="R199">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S199">
         <v>1.3</v>
@@ -32770,10 +32770,10 @@
         <v>2.4</v>
       </c>
       <c r="V199">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W199">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X199">
         <v>1.01</v>
@@ -32782,28 +32782,28 @@
         <v>1.16</v>
       </c>
       <c r="Z199">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA199">
         <v>1.7</v>
       </c>
       <c r="AB199">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AC199">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="AD199">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE199">
         <v>1.13</v>
       </c>
       <c r="AF199">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG199">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32819,7 +32819,7 @@
         <v>1.21</v>
       </c>
       <c r="AK199">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32909,13 +32909,13 @@
         </is>
       </c>
       <c r="N200">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O200">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P200">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q200">
         <v>4</v>
@@ -32927,7 +32927,7 @@
         <v>1.4</v>
       </c>
       <c r="T200">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="U200">
         <v>3</v>
@@ -33072,13 +33072,13 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O201">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P201">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="Q201">
         <v>2.53</v>
@@ -33114,7 +33114,7 @@
         <v>1.69</v>
       </c>
       <c r="AB201">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC201">
         <v>2.79</v>
@@ -33129,7 +33129,7 @@
         <v>1.59</v>
       </c>
       <c r="AG201">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33235,10 +33235,10 @@
         </is>
       </c>
       <c r="N202">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O202">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P202">
         <v>2.1</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O203">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P203">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q203">
         <v>2.52</v>
@@ -33437,7 +33437,7 @@
         <v>3.2</v>
       </c>
       <c r="AA203">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB203">
         <v>1.85</v>
@@ -33561,10 +33561,10 @@
         </is>
       </c>
       <c r="N204">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O204">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P204">
         <v>3.67</v>
@@ -33751,7 +33751,7 @@
         <v>1.43</v>
       </c>
       <c r="W205">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X205">
         <v>1</v>
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G206">
@@ -33887,64 +33887,64 @@
         </is>
       </c>
       <c r="N206">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="O206">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P206">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="Q206">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="R206">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="S206">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T206">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U206">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="V206">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="W206">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X206">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y206">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Z206">
-        <v>6.45</v>
+        <v>5.59</v>
       </c>
       <c r="AA206">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AB206">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AC206">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="AD206">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AE206">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AF206">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AG206">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AH206" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>1.21</v>
       </c>
       <c r="AK206">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="AL206">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G207">
@@ -34050,80 +34050,80 @@
         </is>
       </c>
       <c r="N207">
-        <v>1.86</v>
+        <v>6.1</v>
       </c>
       <c r="O207">
-        <v>3.7</v>
+        <v>4.95</v>
       </c>
       <c r="P207">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="Q207">
-        <v>2.31</v>
+        <v>4.81</v>
       </c>
       <c r="R207">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="S207">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T207">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U207">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="V207">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="W207">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X207">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y207">
+        <v>1.01</v>
+      </c>
+      <c r="Z207">
+        <v>8.4</v>
+      </c>
+      <c r="AA207">
+        <v>1.25</v>
+      </c>
+      <c r="AB207">
+        <v>4</v>
+      </c>
+      <c r="AC207">
+        <v>1.65</v>
+      </c>
+      <c r="AD207">
+        <v>2.21</v>
+      </c>
+      <c r="AE207">
+        <v>1.52</v>
+      </c>
+      <c r="AF207">
+        <v>1.4</v>
+      </c>
+      <c r="AG207">
+        <v>2.7</v>
+      </c>
+      <c r="AH207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ207">
         <v>1.09</v>
       </c>
-      <c r="Z207">
-        <v>5.59</v>
-      </c>
-      <c r="AA207">
-        <v>1.39</v>
-      </c>
-      <c r="AB207">
-        <v>2.59</v>
-      </c>
-      <c r="AC207">
-        <v>2.09</v>
-      </c>
-      <c r="AD207">
-        <v>1.68</v>
-      </c>
-      <c r="AE207">
-        <v>1.25</v>
-      </c>
-      <c r="AF207">
-        <v>1.42</v>
-      </c>
-      <c r="AG207">
-        <v>2.62</v>
-      </c>
-      <c r="AH207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI207" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ207">
-        <v>1.21</v>
-      </c>
       <c r="AK207">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
       <c r="AL207">
         <v>0</v>
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,64 +34213,64 @@
         </is>
       </c>
       <c r="N208">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="O208">
-        <v>4.95</v>
+        <v>3.68</v>
       </c>
       <c r="P208">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q208">
-        <v>4.81</v>
+        <v>2.37</v>
       </c>
       <c r="R208">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="S208">
         <v>1.13</v>
       </c>
       <c r="T208">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U208">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="V208">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="W208">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X208">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y208">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Z208">
-        <v>8.4</v>
+        <v>6.34</v>
       </c>
       <c r="AA208">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AB208">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="AC208">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="AD208">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AE208">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AF208">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG208">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK208">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,61 +34376,61 @@
         </is>
       </c>
       <c r="N209">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="O209">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P209">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Q209">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="R209">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="S209">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T209">
         <v>4.4</v>
       </c>
       <c r="U209">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="V209">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="W209">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X209">
         <v>1.01</v>
       </c>
       <c r="Y209">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z209">
-        <v>6.34</v>
+        <v>6.45</v>
       </c>
       <c r="AA209">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AB209">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AC209">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AD209">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE209">
+        <v>1.37</v>
+      </c>
+      <c r="AF209">
         <v>1.33</v>
-      </c>
-      <c r="AF209">
-        <v>1.36</v>
       </c>
       <c r="AG209">
         <v>3.1</v>
@@ -34446,10 +34446,10 @@
         </is>
       </c>
       <c r="AJ209">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK209">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AL209">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O212">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P212">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -35200,13 +35200,13 @@
         <v>2.02</v>
       </c>
       <c r="Q214">
-        <v>4.27</v>
+        <v>3.75</v>
       </c>
       <c r="R214">
         <v>2.15</v>
       </c>
       <c r="S214">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T214">
         <v>3.2</v>
@@ -35261,7 +35261,7 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AK214">
         <v>1.29</v>
@@ -35357,7 +35357,7 @@
         <v>2.3</v>
       </c>
       <c r="O215">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P215">
         <v>3.1</v>
@@ -35366,7 +35366,7 @@
         <v>2.9</v>
       </c>
       <c r="R215">
-        <v>2.31</v>
+        <v>2.11</v>
       </c>
       <c r="S215">
         <v>1.37</v>
@@ -35523,7 +35523,7 @@
         <v>3.5</v>
       </c>
       <c r="P216">
-        <v>3.17</v>
+        <v>2.68</v>
       </c>
       <c r="Q216">
         <v>2.88</v>
@@ -35541,10 +35541,10 @@
         <v>2.45</v>
       </c>
       <c r="V216">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W216">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X216">
         <v>1</v>
@@ -35680,7 +35680,7 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="O217">
         <v>3.24</v>
@@ -35689,7 +35689,7 @@
         <v>2.88</v>
       </c>
       <c r="Q217">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R217">
         <v>2.1</v>
@@ -35716,7 +35716,7 @@
         <v>1.25</v>
       </c>
       <c r="Z217">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="AA217">
         <v>1.87</v>
@@ -35725,10 +35725,10 @@
         <v>1.85</v>
       </c>
       <c r="AC217">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="AD217">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE217">
         <v>1.06</v>
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O218">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P218">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q218">
         <v>3.5</v>
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="O219">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P219">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="Q219">
         <v>3.08</v>
@@ -36172,10 +36172,10 @@
         <v>1.55</v>
       </c>
       <c r="O220">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P220">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q220">
         <v>2.01</v>
@@ -36332,16 +36332,16 @@
         </is>
       </c>
       <c r="N221">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O221">
-        <v>3.9</v>
+        <v>3.97</v>
       </c>
       <c r="P221">
         <v>1.61</v>
       </c>
       <c r="Q221">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="R221">
         <v>2.2</v>
@@ -36350,10 +36350,10 @@
         <v>1.35</v>
       </c>
       <c r="T221">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="U221">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V221">
         <v>1.4</v>
@@ -36371,10 +36371,10 @@
         <v>3.7</v>
       </c>
       <c r="AA221">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AB221">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC221">
         <v>3.08</v>
@@ -36537,7 +36537,7 @@
         <v>2.17</v>
       </c>
       <c r="AB222">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AC222">
         <v>3.94</v>
@@ -37349,10 +37349,10 @@
         <v>2.88</v>
       </c>
       <c r="AA227">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB227">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC227">
         <v>3.5</v>
@@ -37473,16 +37473,16 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O228">
+        <v>3.1</v>
+      </c>
+      <c r="P228">
+        <v>2.75</v>
+      </c>
+      <c r="Q228">
         <v>3</v>
-      </c>
-      <c r="P228">
-        <v>2.87</v>
-      </c>
-      <c r="Q228">
-        <v>3.12</v>
       </c>
       <c r="R228">
         <v>2</v>
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O229">
         <v>3.2</v>
       </c>
       <c r="P229">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q229">
         <v>2.4</v>
@@ -37675,7 +37675,7 @@
         <v>3.05</v>
       </c>
       <c r="AA229">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB229">
         <v>1.68</v>
@@ -37799,16 +37799,16 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="O230">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="P230">
         <v>2.07</v>
       </c>
       <c r="Q230">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R230">
         <v>2.62</v>
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O232">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P232">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="Q232">
         <v>3.6</v>
@@ -38524,7 +38524,7 @@
         <v>1.25</v>
       </c>
       <c r="AK234">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38792,13 +38792,13 @@
         <v>2.15</v>
       </c>
       <c r="S236">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T236">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U236">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V236">
         <v>1.45</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>1.61</v>
+        <v>1.65</v>
       <